--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="406">
   <si>
     <t>trade_time</t>
   </si>
@@ -268,13 +268,10 @@
     <t>2021-02-05</t>
   </si>
   <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
     <t>2021-04-09</t>
   </si>
   <si>
-    <t>2021-07-19</t>
+    <t>2021-07-20</t>
   </si>
   <si>
     <t>2021-06-11</t>
@@ -670,7 +667,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-07-20</t>
+    <t>2021-07-22</t>
   </si>
   <si>
     <t>2021-06-30</t>
@@ -1202,6 +1199,18 @@
   </si>
   <si>
     <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
   </si>
   <si>
     <t>2021-04-21</t>
@@ -1580,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P396"/>
+  <dimension ref="A1:P400"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1641,7 +1650,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1677,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1691,7 +1700,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1727,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1777,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1827,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1841,7 +1850,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1877,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1891,7 +1900,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1927,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1941,7 +1950,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1977,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1991,7 +2000,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2027,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2041,7 +2050,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2077,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2091,7 +2100,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2127,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2141,7 +2150,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2177,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2191,7 +2200,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2227,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2241,7 +2250,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2277,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2291,7 +2300,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2327,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2341,7 +2350,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2377,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2391,7 +2400,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2427,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2441,7 +2450,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2477,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2491,7 +2500,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2527,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2541,7 +2550,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2577,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2591,7 +2600,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2627,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2641,7 +2650,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2677,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2691,7 +2700,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2727,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2741,7 +2750,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2777,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2791,7 +2800,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2827,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2841,7 +2850,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2877,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2891,7 +2900,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2927,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2941,7 +2950,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2977,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2991,7 +3000,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3027,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3041,7 +3050,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3077,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3091,7 +3100,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3127,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3141,7 +3150,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3177,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3191,7 +3200,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3227,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3241,7 +3250,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3277,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3291,7 +3300,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3327,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3341,7 +3350,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3377,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3391,7 +3400,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3427,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,7 +3450,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3477,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3491,7 +3500,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3527,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3541,7 +3550,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3577,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3591,7 +3600,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3627,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3641,7 +3650,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3677,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3691,7 +3700,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3727,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3741,7 +3750,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3777,7 +3786,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3791,7 +3800,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3827,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3841,7 +3850,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3877,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3891,7 +3900,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3927,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3941,7 +3950,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3977,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3991,7 +4000,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4027,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4041,7 +4050,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4077,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4091,7 +4100,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4127,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4141,7 +4150,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4177,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4191,7 +4200,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4227,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4241,7 +4250,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4277,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4291,7 +4300,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4327,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4341,7 +4350,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4377,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4391,7 +4400,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4427,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4441,7 +4450,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4477,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4491,7 +4500,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4527,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4541,7 +4550,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4577,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4591,7 +4600,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4627,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4641,7 +4650,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4677,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4691,7 +4700,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4727,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4741,7 +4750,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4777,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4791,7 +4800,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4827,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4841,7 +4850,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4877,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4891,7 +4900,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4927,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4941,7 +4950,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4977,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4991,7 +5000,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5027,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5041,7 +5050,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5077,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5091,7 +5100,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5127,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5141,7 +5150,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5177,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5191,7 +5200,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5227,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5241,7 +5250,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5277,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5291,7 +5300,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5327,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5341,7 +5350,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5377,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5391,7 +5400,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5427,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5441,7 +5450,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5477,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5491,7 +5500,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5527,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5541,7 +5550,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5577,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5591,7 +5600,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5627,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5641,7 +5650,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5677,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5691,7 +5700,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5727,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5741,7 +5750,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5777,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5791,7 +5800,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5827,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5841,7 +5850,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5877,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5891,7 +5900,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5927,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5941,7 +5950,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5977,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5991,7 +6000,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6027,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6041,7 +6050,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6077,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6091,7 +6100,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6127,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6141,7 +6150,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6177,7 +6186,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6191,7 +6200,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6241,7 +6250,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6277,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6291,7 +6300,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6327,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6341,7 +6350,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6377,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6391,7 +6400,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6427,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6441,7 +6450,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6477,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6491,7 +6500,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6527,7 +6536,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6541,7 +6550,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6577,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6591,7 +6600,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6627,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6641,7 +6650,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6677,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6691,7 +6700,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6727,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6741,7 +6750,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6777,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6791,7 +6800,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6827,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6841,7 +6850,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6877,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6891,7 +6900,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6927,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6941,7 +6950,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6977,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6991,7 +7000,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7027,7 +7036,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7041,7 +7050,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7077,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7091,7 +7100,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7127,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7141,7 +7150,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7177,7 +7186,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7191,7 +7200,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7227,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7241,7 +7250,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7277,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7291,7 +7300,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7327,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7341,7 +7350,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7377,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7391,7 +7400,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7427,7 +7436,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7441,7 +7450,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7477,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7491,7 +7500,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7527,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7541,7 +7550,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7577,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7591,7 +7600,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7627,7 +7636,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7641,7 +7650,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7677,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7691,7 +7700,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7727,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7741,7 +7750,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7777,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7791,7 +7800,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7827,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7841,7 +7850,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7877,7 +7886,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7891,7 +7900,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7927,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7941,7 +7950,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7977,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7991,7 +8000,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8027,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8041,7 +8050,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8077,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8091,7 +8100,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8127,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8141,7 +8150,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8177,7 +8186,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8191,7 +8200,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8227,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8241,7 +8250,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8277,7 +8286,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8291,7 +8300,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8327,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8341,7 +8350,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8377,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8391,7 +8400,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8427,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8441,7 +8450,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8477,7 +8486,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8491,7 +8500,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8527,7 +8536,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8541,7 +8550,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8577,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8591,7 +8600,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8627,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8641,7 +8650,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8677,7 +8686,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8691,7 +8700,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8727,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8741,7 +8750,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8777,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8791,7 +8800,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8827,7 +8836,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8841,7 +8850,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8877,7 +8886,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8891,7 +8900,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8927,7 +8936,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8941,7 +8950,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8977,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8991,7 +9000,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9027,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9041,7 +9050,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9077,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9091,7 +9100,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9127,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9141,7 +9150,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9177,7 +9186,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9191,7 +9200,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9227,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9241,7 +9250,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9277,7 +9286,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9291,7 +9300,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9327,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9341,7 +9350,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9377,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9391,7 +9400,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9427,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9441,7 +9450,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9477,7 +9486,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9491,7 +9500,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9527,7 +9536,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9541,7 +9550,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9577,7 +9586,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9591,7 +9600,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9627,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9641,7 +9650,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9677,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9691,7 +9700,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9727,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9741,7 +9750,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9777,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9791,7 +9800,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9827,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9841,7 +9850,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9877,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9891,7 +9900,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9927,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9941,7 +9950,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9977,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9991,7 +10000,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10027,7 +10036,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10041,7 +10050,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10077,7 +10086,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10091,7 +10100,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10127,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10141,7 +10150,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10191,7 +10200,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10227,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10241,7 +10250,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10277,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10291,7 +10300,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10327,7 +10336,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10341,7 +10350,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10377,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10391,7 +10400,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10427,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10441,7 +10450,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10477,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10491,7 +10500,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10527,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10541,7 +10550,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10577,7 +10586,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10591,7 +10600,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10627,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10641,7 +10650,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10677,7 +10686,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10691,7 +10700,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10727,7 +10736,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10777,7 +10786,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10827,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10877,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10927,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10941,7 +10950,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10977,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10991,7 +11000,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11027,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11041,7 +11050,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11077,7 +11086,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11091,7 +11100,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11127,7 +11136,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11141,7 +11150,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11177,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11191,7 +11200,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11227,7 +11236,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11241,7 +11250,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11277,7 +11286,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11291,7 +11300,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11327,7 +11336,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11341,7 +11350,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11377,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11391,7 +11400,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11427,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11441,7 +11450,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11477,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11491,7 +11500,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11527,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11541,7 +11550,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11577,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11591,7 +11600,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11627,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11641,7 +11650,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11677,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11691,7 +11700,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11727,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11741,7 +11750,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11777,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11791,7 +11800,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11827,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11841,7 +11850,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11877,7 +11886,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11891,7 +11900,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11927,7 +11936,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11941,7 +11950,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11977,7 +11986,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11991,7 +12000,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12027,7 +12036,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12041,7 +12050,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12077,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12091,7 +12100,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12127,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12141,7 +12150,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12177,7 +12186,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12191,7 +12200,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12227,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12241,7 +12250,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12277,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12291,7 +12300,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12327,7 +12336,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12341,7 +12350,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12377,7 +12386,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12391,7 +12400,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12427,7 +12436,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12441,7 +12450,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12477,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12491,7 +12500,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12527,7 +12536,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12541,7 +12550,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12577,7 +12586,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12591,7 +12600,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12627,7 +12636,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12641,7 +12650,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12677,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12691,7 +12700,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12727,7 +12736,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12741,7 +12750,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12777,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12791,7 +12800,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12827,7 +12836,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12841,7 +12850,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12877,7 +12886,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12891,7 +12900,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12927,7 +12936,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12941,7 +12950,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12977,7 +12986,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12991,7 +13000,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13027,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13041,7 +13050,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13077,7 +13086,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13091,7 +13100,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13127,7 +13136,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13141,7 +13150,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13177,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13191,7 +13200,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13227,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13241,7 +13250,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13277,7 +13286,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13291,7 +13300,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13327,7 +13336,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13341,7 +13350,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13377,7 +13386,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13391,7 +13400,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13427,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13441,7 +13450,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13477,7 +13486,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13491,7 +13500,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13527,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13541,7 +13550,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13577,7 +13586,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13591,7 +13600,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13627,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13641,7 +13650,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13677,7 +13686,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13691,7 +13700,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13727,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13741,7 +13750,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13777,7 +13786,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13791,7 +13800,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13827,7 +13836,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13841,7 +13850,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13877,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13891,7 +13900,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13927,7 +13936,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13941,7 +13950,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13977,7 +13986,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13991,7 +14000,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14027,7 +14036,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14041,7 +14050,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14077,7 +14086,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14091,7 +14100,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14127,7 +14136,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14141,7 +14150,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14177,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14191,7 +14200,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14227,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14241,7 +14250,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14277,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14291,7 +14300,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14327,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14341,7 +14350,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14377,7 +14386,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14391,7 +14400,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14427,7 +14436,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14441,7 +14450,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14477,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14491,7 +14500,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14527,7 +14536,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14541,7 +14550,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14577,7 +14586,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14591,7 +14600,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14627,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14641,7 +14650,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14677,7 +14686,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14691,7 +14700,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14727,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14741,7 +14750,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14827,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14841,7 +14850,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14877,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14891,7 +14900,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14927,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14941,7 +14950,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14977,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14991,7 +15000,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15027,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15041,7 +15050,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15077,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15091,7 +15100,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15127,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15141,7 +15150,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15177,7 +15186,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15191,7 +15200,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15227,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15241,7 +15250,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15277,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15291,7 +15300,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15327,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15341,7 +15350,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15377,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15391,7 +15400,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15427,7 +15436,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15441,7 +15450,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15477,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15491,7 +15500,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15527,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15541,7 +15550,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15577,7 +15586,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15591,7 +15600,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15627,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15641,7 +15650,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15677,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15691,7 +15700,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15727,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15741,7 +15750,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15777,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15827,7 +15836,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15877,7 +15886,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15891,7 +15900,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15927,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15941,7 +15950,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15977,7 +15986,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +16000,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16027,7 +16036,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16041,7 +16050,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16077,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16091,7 +16100,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16127,7 +16136,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16177,7 +16186,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16227,7 +16236,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16241,7 +16250,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16277,7 +16286,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16291,7 +16300,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16327,7 +16336,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16341,7 +16350,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16377,7 +16386,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16400,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16427,7 +16436,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16450,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16477,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16491,7 +16500,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16527,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16541,7 +16550,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16577,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16627,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16677,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16691,7 +16700,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16727,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16741,7 +16750,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16777,7 +16786,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16791,7 +16800,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16827,7 +16836,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16841,7 +16850,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16877,7 +16886,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16891,7 +16900,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16927,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16941,7 +16950,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16977,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16991,7 +17000,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17027,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17041,7 +17050,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17077,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17091,7 +17100,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17127,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17141,7 +17150,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17177,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17200,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17227,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17277,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17327,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17350,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17377,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17427,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17477,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17500,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17527,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17577,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17627,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17650,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17677,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17727,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17777,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17791,7 +17800,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17827,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17877,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17927,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17950,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17977,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18027,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18077,7 +18086,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18100,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18127,7 +18136,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18177,7 +18186,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18227,7 +18236,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18241,7 +18250,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18277,7 +18286,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18327,7 +18336,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18377,7 +18386,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18391,7 +18400,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18427,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18541,7 +18550,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18627,7 +18636,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18650,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18677,7 +18686,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18727,7 +18736,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18777,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18800,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18827,7 +18836,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18991,7 +19000,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19077,7 +19086,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19127,7 +19136,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19150,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19177,7 +19186,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19191,7 +19200,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19277,7 +19286,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19291,7 +19300,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19327,7 +19336,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19377,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19391,7 +19400,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19427,7 +19436,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19491,7 +19500,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19541,7 +19550,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19577,7 +19586,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19591,7 +19600,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19627,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19650,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19677,7 +19686,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19700,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19777,7 +19786,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,7 +19800,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19827,7 +19836,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19877,7 +19886,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19927,7 +19936,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,7 +19950,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19977,7 +19986,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,7 +20000,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20027,7 +20036,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20041,7 +20050,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20077,7 +20086,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20091,7 +20100,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20127,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20141,7 +20150,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20177,7 +20186,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20200,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20227,7 +20236,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20241,7 +20250,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20277,7 +20286,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20291,7 +20300,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20327,7 +20336,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20341,7 +20350,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20377,7 +20386,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20427,7 +20436,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20441,7 +20450,7 @@
         <v>1.767440067057837</v>
       </c>
       <c r="D378" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E378">
         <v>1.917324392288349</v>
@@ -20477,7 +20486,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20491,7 +20500,7 @@
         <v>1.755766974015088</v>
       </c>
       <c r="D379" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E379">
         <v>1.917324392288349</v>
@@ -20527,7 +20536,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20541,7 +20550,7 @@
         <v>1.799235962112094</v>
       </c>
       <c r="D380" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E380">
         <v>1.953237741378409</v>
@@ -20577,7 +20586,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20591,7 +20600,7 @@
         <v>1.787791616515778</v>
       </c>
       <c r="D381" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E381">
         <v>1.953237741378409</v>
@@ -20627,7 +20636,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,7 +20650,7 @@
         <v>1.884012465206341</v>
       </c>
       <c r="D382" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E382">
         <v>2.048992496671911</v>
@@ -20677,7 +20686,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20685,13 +20694,13 @@
         <v>1</v>
       </c>
       <c r="B383" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C383">
-        <v>1.902343579813627</v>
+        <v>1.873178022509984</v>
       </c>
       <c r="D383" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E383">
         <v>2.048992496671911</v>
@@ -20700,22 +20709,22 @@
         <v>1</v>
       </c>
       <c r="G383">
-        <v>0.002137656420186373</v>
+        <v>0.002106821977490016</v>
       </c>
       <c r="H383">
         <v>0.002311007503328089</v>
       </c>
       <c r="I383">
-        <v>0.1466489168582843</v>
+        <v>0.175814474161927</v>
       </c>
       <c r="J383">
         <v>0.0834442696357255</v>
       </c>
       <c r="K383">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="L383">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="M383">
         <v>1.57</v>
@@ -20727,7 +20736,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20741,7 +20750,7 @@
         <v>1.862102797346283</v>
       </c>
       <c r="D384" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E384">
         <v>2.02424560563573</v>
@@ -20777,7 +20786,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20785,13 +20794,13 @@
         <v>1</v>
       </c>
       <c r="B385" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C385">
-        <v>1.880118664933999</v>
+        <v>1.851110731140141</v>
       </c>
       <c r="D385" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E385">
         <v>2.02424560563573</v>
@@ -20800,22 +20809,22 @@
         <v>1</v>
       </c>
       <c r="G385">
-        <v>0.002159881335066001</v>
+        <v>0.002128889268859859</v>
       </c>
       <c r="H385">
         <v>0.00233575439436427</v>
       </c>
       <c r="I385">
-        <v>0.1441269407017307</v>
+        <v>0.1731348744955887</v>
       </c>
       <c r="J385">
         <v>0.09920662061418481</v>
       </c>
       <c r="K385">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="L385">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="M385">
         <v>1.57</v>
@@ -20827,7 +20836,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20841,7 +20850,7 @@
         <v>1.758150385501947</v>
       </c>
       <c r="D386" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E386">
         <v>1.906831730387091</v>
@@ -20877,7 +20886,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20891,7 +20900,7 @@
         <v>1.746410460217788</v>
       </c>
       <c r="D387" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E387">
         <v>1.906831730387091</v>
@@ -20927,7 +20936,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20935,13 +20944,13 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C388">
         <v>0.9159503213647138</v>
       </c>
       <c r="D388" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E388">
         <v>0.7959503213647137</v>
@@ -20977,7 +20986,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20985,13 +20994,13 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C389">
         <v>0.8094230769230786</v>
       </c>
       <c r="D389" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E389">
         <v>0.6894230769230785</v>
@@ -21027,7 +21036,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21035,49 +21044,49 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C390">
-        <v>0.4705873043784086</v>
+        <v>0.589142733736006</v>
       </c>
       <c r="D390" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E390">
-        <v>0.493721771458717</v>
+        <v>0.5356396245689339</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003709412695621591</v>
+        <v>0.003590857266263994</v>
       </c>
       <c r="H390">
-        <v>0.003686278228541283</v>
+        <v>0.003624360375431066</v>
       </c>
       <c r="I390">
-        <v>-0.02313446708030842</v>
+        <v>0.05350310916707213</v>
       </c>
       <c r="J390">
-        <v>1.156723354015422</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K390">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L390">
         <v>2.09</v>
       </c>
       <c r="M390">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="N390">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21085,49 +21094,49 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C391">
-        <v>0.4170080814394805</v>
+        <v>0.5536378221197245</v>
       </c>
       <c r="D391" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E391">
-        <v>0.4409079659903452</v>
+        <v>0.4991055850797166</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003762991918560519</v>
+        <v>0.003626362177880275</v>
       </c>
       <c r="H391">
-        <v>0.003739092034009655</v>
+        <v>0.003660894414920284</v>
       </c>
       <c r="I391">
-        <v>-0.02389988455086467</v>
+        <v>0.05453223704000787</v>
       </c>
       <c r="J391">
-        <v>1.194994227543228</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K391">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L391">
         <v>2.09</v>
       </c>
       <c r="M391">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="N391">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21135,49 +21144,49 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C392">
-        <v>0.4196070443561668</v>
+        <v>0.5314031526074197</v>
       </c>
       <c r="D392" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E392">
-        <v>0.4434698008653646</v>
+        <v>0.4762264323931422</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.003760392955643833</v>
+        <v>0.00364859684739258</v>
       </c>
       <c r="H392">
-        <v>0.003736530199134635</v>
+        <v>0.003683773567606858</v>
       </c>
       <c r="I392">
-        <v>-0.02386275650919778</v>
+        <v>0.05517672021427744</v>
       </c>
       <c r="J392">
-        <v>1.193137825459881</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K392">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L392">
         <v>2.09</v>
       </c>
       <c r="M392">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="N392">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21185,49 +21194,49 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C393">
-        <v>0.4246018572404555</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D393" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E393">
-        <v>0.4483932592798776</v>
+        <v>0.4601531833413135</v>
       </c>
       <c r="F393">
         <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.003755398142759544</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H393">
-        <v>0.003731606740720122</v>
+        <v>0.003699846816658687</v>
       </c>
       <c r="I393">
-        <v>-0.02379140203942209</v>
+        <v>0.0556294877932022</v>
       </c>
       <c r="J393">
-        <v>1.189570101971103</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K393">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L393">
         <v>2.09</v>
       </c>
       <c r="M393">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="N393">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21235,49 +21244,49 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C394">
-        <v>0.4205832919170494</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D394" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E394">
-        <v>0.4444321020325201</v>
+        <v>0.4374528372981001</v>
       </c>
       <c r="F394">
         <v>-1</v>
       </c>
       <c r="G394">
-        <v>0.003759416708082951</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H394">
-        <v>0.00373556789796748</v>
+        <v>0.0037225471627019</v>
       </c>
       <c r="I394">
-        <v>-0.0238488101154708</v>
+        <v>0.05626893416061685</v>
       </c>
       <c r="J394">
-        <v>1.192440505773536</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K394">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L394">
         <v>2.09</v>
       </c>
       <c r="M394">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="N394">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21285,49 +21294,49 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C395">
-        <v>2.36240774237655</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D395" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E395">
-        <v>2.264739428294711</v>
+        <v>0.3831081968886161</v>
       </c>
       <c r="F395">
         <v>-1</v>
       </c>
       <c r="G395">
-        <v>0.00205759225762345</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H395">
-        <v>0.001975260571705289</v>
+        <v>0.003776891803111384</v>
       </c>
       <c r="I395">
-        <v>0.09766831408183885</v>
+        <v>0.05779976910172913</v>
       </c>
       <c r="J395">
-        <v>-0.0958539260229872</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K395">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="L395">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="M395">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="N395">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21335,49 +21344,249 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C396">
+        <v>0.4434698008653646</v>
+      </c>
+      <c r="D396" t="s">
+        <v>217</v>
+      </c>
+      <c r="E396">
+        <v>0.3857442878469695</v>
+      </c>
+      <c r="F396">
+        <v>-1</v>
+      </c>
+      <c r="G396">
+        <v>0.003736530199134635</v>
+      </c>
+      <c r="H396">
+        <v>0.003774255712153031</v>
+      </c>
+      <c r="I396">
+        <v>0.05772551301839512</v>
+      </c>
+      <c r="J396">
+        <v>1.193137825459881</v>
+      </c>
+      <c r="K396">
+        <v>1.38</v>
+      </c>
+      <c r="L396">
+        <v>2.09</v>
+      </c>
+      <c r="M396">
+        <v>1.42</v>
+      </c>
+      <c r="N396">
+        <v>2.08</v>
+      </c>
+      <c r="O396">
+        <v>1</v>
+      </c>
+      <c r="P396" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16">
+      <c r="A397" s="1">
+        <v>0</v>
+      </c>
+      <c r="B397" t="s">
+        <v>85</v>
+      </c>
+      <c r="C397">
+        <v>0.4483932592798776</v>
+      </c>
+      <c r="D397" t="s">
+        <v>217</v>
+      </c>
+      <c r="E397">
+        <v>0.3908104552010336</v>
+      </c>
+      <c r="F397">
+        <v>-1</v>
+      </c>
+      <c r="G397">
+        <v>0.003731606740720122</v>
+      </c>
+      <c r="H397">
+        <v>0.003769189544798967</v>
+      </c>
+      <c r="I397">
+        <v>0.05758280407884397</v>
+      </c>
+      <c r="J397">
+        <v>1.189570101971103</v>
+      </c>
+      <c r="K397">
+        <v>1.38</v>
+      </c>
+      <c r="L397">
+        <v>2.09</v>
+      </c>
+      <c r="M397">
+        <v>1.42</v>
+      </c>
+      <c r="N397">
+        <v>2.08</v>
+      </c>
+      <c r="O397">
+        <v>1</v>
+      </c>
+      <c r="P397" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16">
+      <c r="A398" s="1">
+        <v>0</v>
+      </c>
+      <c r="B398" t="s">
+        <v>85</v>
+      </c>
+      <c r="C398">
+        <v>0.4444321020325201</v>
+      </c>
+      <c r="D398" t="s">
+        <v>217</v>
+      </c>
+      <c r="E398">
+        <v>0.386734481801579</v>
+      </c>
+      <c r="F398">
+        <v>-1</v>
+      </c>
+      <c r="G398">
+        <v>0.00373556789796748</v>
+      </c>
+      <c r="H398">
+        <v>0.003773265518198421</v>
+      </c>
+      <c r="I398">
+        <v>0.05769762023094116</v>
+      </c>
+      <c r="J398">
+        <v>1.192440505773536</v>
+      </c>
+      <c r="K398">
+        <v>1.38</v>
+      </c>
+      <c r="L398">
+        <v>2.09</v>
+      </c>
+      <c r="M398">
+        <v>1.42</v>
+      </c>
+      <c r="N398">
+        <v>2.08</v>
+      </c>
+      <c r="O398">
+        <v>1</v>
+      </c>
+      <c r="P398" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16">
+      <c r="A399" s="1">
+        <v>0</v>
+      </c>
+      <c r="B399" t="s">
+        <v>86</v>
+      </c>
+      <c r="C399">
+        <v>2.36240774237655</v>
+      </c>
+      <c r="D399" t="s">
+        <v>218</v>
+      </c>
+      <c r="E399">
+        <v>2.264739428294711</v>
+      </c>
+      <c r="F399">
+        <v>-1</v>
+      </c>
+      <c r="G399">
+        <v>0.00205759225762345</v>
+      </c>
+      <c r="H399">
+        <v>0.001975260571705289</v>
+      </c>
+      <c r="I399">
+        <v>0.09766831408183885</v>
+      </c>
+      <c r="J399">
+        <v>-0.0958539260229872</v>
+      </c>
+      <c r="K399">
+        <v>1.59</v>
+      </c>
+      <c r="L399">
+        <v>2.21</v>
+      </c>
+      <c r="M399">
+        <v>1.51</v>
+      </c>
+      <c r="N399">
+        <v>2.12</v>
+      </c>
+      <c r="O399">
+        <v>1</v>
+      </c>
+      <c r="P399" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16">
+      <c r="A400" s="1">
+        <v>0</v>
+      </c>
+      <c r="B400" t="s">
+        <v>86</v>
+      </c>
+      <c r="C400">
         <v>2.526368817680956</v>
       </c>
-      <c r="D396" t="s">
-        <v>219</v>
-      </c>
-      <c r="E396">
+      <c r="D400" t="s">
+        <v>218</v>
+      </c>
+      <c r="E400">
         <v>2.420450889747324</v>
       </c>
-      <c r="F396">
-        <v>-1</v>
-      </c>
-      <c r="G396">
+      <c r="F400">
+        <v>-1</v>
+      </c>
+      <c r="G400">
         <v>0.001893631182319044</v>
       </c>
-      <c r="H396">
+      <c r="H400">
         <v>0.001819549110252677</v>
       </c>
-      <c r="I396">
+      <c r="I400">
         <v>0.1059179279336329</v>
       </c>
-      <c r="J396">
+      <c r="J400">
         <v>-0.1989740991704129</v>
       </c>
-      <c r="K396">
+      <c r="K400">
         <v>1.59</v>
       </c>
-      <c r="L396">
+      <c r="L400">
         <v>2.21</v>
       </c>
-      <c r="M396">
+      <c r="M400">
         <v>1.51</v>
       </c>
-      <c r="N396">
+      <c r="N400">
         <v>2.12</v>
       </c>
-      <c r="O396">
-        <v>1</v>
-      </c>
-      <c r="P396" t="s">
-        <v>402</v>
+      <c r="O400">
+        <v>1</v>
+      </c>
+      <c r="P400" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -667,7 +667,7 @@
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-07-22</t>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-06-30</t>
@@ -21053,7 +21053,7 @@
         <v>217</v>
       </c>
       <c r="E390">
-        <v>0.5356396245689339</v>
+        <v>0.5673911791524699</v>
       </c>
       <c r="F390">
         <v>-1</v>
@@ -21062,10 +21062,10 @@
         <v>0.003590857266263994</v>
       </c>
       <c r="H390">
-        <v>0.003624360375431066</v>
+        <v>0.00361260882084753</v>
       </c>
       <c r="I390">
-        <v>0.05350310916707213</v>
+        <v>0.02175155458353606</v>
       </c>
       <c r="J390">
         <v>1.087577729176807</v>
@@ -21077,10 +21077,10 @@
         <v>2.09</v>
       </c>
       <c r="M390">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N390">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21103,7 +21103,7 @@
         <v>217</v>
       </c>
       <c r="E391">
-        <v>0.4991055850797166</v>
+        <v>0.5313717035997205</v>
       </c>
       <c r="F391">
         <v>-1</v>
@@ -21112,10 +21112,10 @@
         <v>0.003626362177880275</v>
       </c>
       <c r="H391">
-        <v>0.003660894414920284</v>
+        <v>0.003648628296400279</v>
       </c>
       <c r="I391">
-        <v>0.05453223704000787</v>
+        <v>0.02226611852000393</v>
       </c>
       <c r="J391">
         <v>1.1133059260002</v>
@@ -21127,10 +21127,10 @@
         <v>2.09</v>
       </c>
       <c r="M391">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N391">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O391">
         <v>1</v>
@@ -21153,7 +21153,7 @@
         <v>217</v>
       </c>
       <c r="E392">
-        <v>0.4762264323931422</v>
+        <v>0.5088147925002808</v>
       </c>
       <c r="F392">
         <v>-1</v>
@@ -21162,10 +21162,10 @@
         <v>0.00364859684739258</v>
       </c>
       <c r="H392">
-        <v>0.003683773567606858</v>
+        <v>0.003671185207499719</v>
       </c>
       <c r="I392">
-        <v>0.05517672021427744</v>
+        <v>0.02258836010713883</v>
       </c>
       <c r="J392">
         <v>1.129418005356942</v>
@@ -21177,10 +21177,10 @@
         <v>2.09</v>
       </c>
       <c r="M392">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N392">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21203,7 +21203,7 @@
         <v>217</v>
       </c>
       <c r="E393">
-        <v>0.4601531833413135</v>
+        <v>0.4929679272379144</v>
       </c>
       <c r="F393">
         <v>-1</v>
@@ -21212,10 +21212,10 @@
         <v>0.003664217328865484</v>
       </c>
       <c r="H393">
-        <v>0.003699846816658687</v>
+        <v>0.003687032072762086</v>
       </c>
       <c r="I393">
-        <v>0.0556294877932022</v>
+        <v>0.02281474389660132</v>
       </c>
       <c r="J393">
         <v>1.140737194830061</v>
@@ -21227,10 +21227,10 @@
         <v>2.09</v>
       </c>
       <c r="M393">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N393">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O393">
         <v>1</v>
@@ -21253,7 +21253,7 @@
         <v>217</v>
       </c>
       <c r="E394">
-        <v>0.4374528372981001</v>
+        <v>0.4705873043784086</v>
       </c>
       <c r="F394">
         <v>-1</v>
@@ -21262,10 +21262,10 @@
         <v>0.003686278228541283</v>
       </c>
       <c r="H394">
-        <v>0.0037225471627019</v>
+        <v>0.003709412695621591</v>
       </c>
       <c r="I394">
-        <v>0.05626893416061685</v>
+        <v>0.02313446708030842</v>
       </c>
       <c r="J394">
         <v>1.156723354015422</v>
@@ -21277,10 +21277,10 @@
         <v>2.09</v>
       </c>
       <c r="M394">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N394">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O394">
         <v>1</v>
@@ -21303,7 +21303,7 @@
         <v>217</v>
       </c>
       <c r="E395">
-        <v>0.3831081968886161</v>
+        <v>0.4170080814394805</v>
       </c>
       <c r="F395">
         <v>-1</v>
@@ -21312,10 +21312,10 @@
         <v>0.003739092034009655</v>
       </c>
       <c r="H395">
-        <v>0.003776891803111384</v>
+        <v>0.003762991918560519</v>
       </c>
       <c r="I395">
-        <v>0.05779976910172913</v>
+        <v>0.02389988455086467</v>
       </c>
       <c r="J395">
         <v>1.194994227543228</v>
@@ -21327,10 +21327,10 @@
         <v>2.09</v>
       </c>
       <c r="M395">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N395">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O395">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>217</v>
       </c>
       <c r="E396">
-        <v>0.3857442878469695</v>
+        <v>0.4196070443561668</v>
       </c>
       <c r="F396">
         <v>-1</v>
@@ -21362,10 +21362,10 @@
         <v>0.003736530199134635</v>
       </c>
       <c r="H396">
-        <v>0.003774255712153031</v>
+        <v>0.003760392955643833</v>
       </c>
       <c r="I396">
-        <v>0.05772551301839512</v>
+        <v>0.02386275650919778</v>
       </c>
       <c r="J396">
         <v>1.193137825459881</v>
@@ -21377,10 +21377,10 @@
         <v>2.09</v>
       </c>
       <c r="M396">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N396">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O396">
         <v>1</v>
@@ -21403,7 +21403,7 @@
         <v>217</v>
       </c>
       <c r="E397">
-        <v>0.3908104552010336</v>
+        <v>0.4246018572404555</v>
       </c>
       <c r="F397">
         <v>-1</v>
@@ -21412,10 +21412,10 @@
         <v>0.003731606740720122</v>
       </c>
       <c r="H397">
-        <v>0.003769189544798967</v>
+        <v>0.003755398142759544</v>
       </c>
       <c r="I397">
-        <v>0.05758280407884397</v>
+        <v>0.02379140203942209</v>
       </c>
       <c r="J397">
         <v>1.189570101971103</v>
@@ -21427,10 +21427,10 @@
         <v>2.09</v>
       </c>
       <c r="M397">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N397">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O397">
         <v>1</v>
@@ -21453,7 +21453,7 @@
         <v>217</v>
       </c>
       <c r="E398">
-        <v>0.386734481801579</v>
+        <v>0.4205832919170494</v>
       </c>
       <c r="F398">
         <v>-1</v>
@@ -21462,10 +21462,10 @@
         <v>0.00373556789796748</v>
       </c>
       <c r="H398">
-        <v>0.003773265518198421</v>
+        <v>0.003759416708082951</v>
       </c>
       <c r="I398">
-        <v>0.05769762023094116</v>
+        <v>0.0238488101154708</v>
       </c>
       <c r="J398">
         <v>1.192440505773536</v>
@@ -21477,10 +21477,10 @@
         <v>2.09</v>
       </c>
       <c r="M398">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="N398">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O398">
         <v>1</v>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="400">
   <si>
     <t>trade_time</t>
   </si>
@@ -274,964 +274,946 @@
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2016-04-13</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-09-20</t>
+  </si>
+  <si>
+    <t>2016-04-29</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
+    <t>2016-10-11</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>2016-10-14</t>
+  </si>
+  <si>
+    <t>2016-10-18</t>
+  </si>
+  <si>
+    <t>2016-10-19</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>2017-02-17</t>
+  </si>
+  <si>
+    <t>2017-02-20</t>
+  </si>
+  <si>
+    <t>2017-02-21</t>
+  </si>
+  <si>
+    <t>2017-02-22</t>
+  </si>
+  <si>
+    <t>2017-02-23</t>
+  </si>
+  <si>
+    <t>2017-02-24</t>
+  </si>
+  <si>
+    <t>2017-02-27</t>
+  </si>
+  <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>2017-03-02</t>
+  </si>
+  <si>
+    <t>2017-03-03</t>
+  </si>
+  <si>
+    <t>2017-03-06</t>
+  </si>
+  <si>
+    <t>2017-03-07</t>
+  </si>
+  <si>
+    <t>2017-03-08</t>
+  </si>
+  <si>
+    <t>2017-03-09</t>
+  </si>
+  <si>
+    <t>2017-03-10</t>
+  </si>
+  <si>
+    <t>2017-03-13</t>
+  </si>
+  <si>
+    <t>2017-03-14</t>
+  </si>
+  <si>
+    <t>2017-03-16</t>
+  </si>
+  <si>
+    <t>2017-03-17</t>
+  </si>
+  <si>
+    <t>2017-03-28</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-07</t>
+  </si>
+  <si>
+    <t>2017-03-15</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-07-18</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>2017-09-26</t>
+  </si>
+  <si>
+    <t>2017-09-27</t>
+  </si>
+  <si>
+    <t>2017-09-19</t>
+  </si>
+  <si>
+    <t>2017-10-16</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>2018-02-23</t>
+  </si>
+  <si>
+    <t>2018-04-04</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2017-12-28</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-09-18</t>
+  </si>
+  <si>
+    <t>2018-10-12</t>
+  </si>
+  <si>
+    <t>2018-12-13</t>
+  </si>
+  <si>
+    <t>2018-12-17</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-01-04</t>
+  </si>
+  <si>
+    <t>2018-09-07</t>
+  </si>
+  <si>
+    <t>2019-01-07</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-12-07</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-10-31</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-21</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-17</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-10-30</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2016-02-15</t>
+  </si>
+  <si>
+    <t>2016-02-24</t>
+  </si>
+  <si>
+    <t>2016-03-03</t>
+  </si>
+  <si>
+    <t>2016-03-04</t>
+  </si>
+  <si>
+    <t>2016-03-07</t>
+  </si>
+  <si>
+    <t>2016-03-08</t>
+  </si>
+  <si>
+    <t>2016-03-09</t>
+  </si>
+  <si>
+    <t>2016-03-10</t>
+  </si>
+  <si>
+    <t>2016-03-11</t>
+  </si>
+  <si>
+    <t>2016-03-15</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-07-04</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-12</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-14</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-22</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-07-28</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-08-01</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-08-04</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>2016-08-08</t>
+  </si>
+  <si>
+    <t>2016-08-10</t>
+  </si>
+  <si>
+    <t>2016-08-11</t>
+  </si>
+  <si>
+    <t>2016-08-22</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>2016-08-26</t>
+  </si>
+  <si>
+    <t>2016-11-18</t>
+  </si>
+  <si>
+    <t>2016-11-30</t>
+  </si>
+  <si>
+    <t>2016-12-01</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>2016-12-05</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-09</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2016-12-13</t>
+  </si>
+  <si>
+    <t>2017-03-30</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-20</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-04-24</t>
+  </si>
+  <si>
+    <t>2017-05-09</t>
+  </si>
+  <si>
+    <t>2017-05-10</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-09-04</t>
+  </si>
+  <si>
+    <t>2017-09-05</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>2017-09-12</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-15</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2018-03-23</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-03-27</t>
+  </si>
+  <si>
+    <t>2018-03-28</t>
+  </si>
+  <si>
+    <t>2018-03-29</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-23</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-06</t>
+  </si>
+  <si>
+    <t>2018-06-07</t>
+  </si>
+  <si>
+    <t>2018-06-08</t>
+  </si>
+  <si>
+    <t>2018-06-11</t>
+  </si>
+  <si>
+    <t>2018-06-12</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-06-15</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-22</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-07-04</t>
+  </si>
+  <si>
+    <t>2018-07-05</t>
+  </si>
+  <si>
+    <t>2018-07-06</t>
+  </si>
+  <si>
+    <t>2018-07-09</t>
+  </si>
+  <si>
+    <t>2018-07-10</t>
+  </si>
+  <si>
+    <t>2018-07-11</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-08-28</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-10-25</t>
+  </si>
+  <si>
+    <t>2019-12-03</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-09</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-16</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2019-12-30</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-09</t>
+  </si>
+  <si>
+    <t>2020-01-10</t>
+  </si>
+  <si>
+    <t>2020-01-13</t>
+  </si>
+  <si>
+    <t>2020-01-14</t>
+  </si>
+  <si>
+    <t>2020-01-15</t>
+  </si>
+  <si>
+    <t>2020-01-16</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>2020-05-25</t>
+  </si>
+  <si>
+    <t>2020-05-28</t>
+  </si>
+  <si>
+    <t>2020-06-01</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>2020-06-19</t>
+  </si>
+  <si>
+    <t>2020-06-22</t>
+  </si>
+  <si>
+    <t>2020-06-23</t>
+  </si>
+  <si>
+    <t>2020-06-24</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-10-27</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-07</t>
+  </si>
+  <si>
     <t>2021-06-11</t>
   </si>
   <si>
-    <t>2016-04-13</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-09-20</t>
-  </si>
-  <si>
-    <t>2016-04-29</t>
-  </si>
-  <si>
-    <t>2016-09-28</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-09-30</t>
-  </si>
-  <si>
-    <t>2016-10-11</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-10-13</t>
-  </si>
-  <si>
-    <t>2016-10-14</t>
-  </si>
-  <si>
-    <t>2016-10-18</t>
-  </si>
-  <si>
-    <t>2016-10-19</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-02-16</t>
-  </si>
-  <si>
-    <t>2017-02-17</t>
-  </si>
-  <si>
-    <t>2017-02-20</t>
-  </si>
-  <si>
-    <t>2017-02-21</t>
-  </si>
-  <si>
-    <t>2017-02-22</t>
-  </si>
-  <si>
-    <t>2017-02-23</t>
-  </si>
-  <si>
-    <t>2017-02-24</t>
-  </si>
-  <si>
-    <t>2017-02-27</t>
-  </si>
-  <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
-    <t>2017-03-01</t>
-  </si>
-  <si>
-    <t>2017-03-02</t>
-  </si>
-  <si>
-    <t>2017-03-03</t>
-  </si>
-  <si>
-    <t>2017-03-06</t>
-  </si>
-  <si>
-    <t>2017-03-07</t>
-  </si>
-  <si>
-    <t>2017-03-08</t>
-  </si>
-  <si>
-    <t>2017-03-09</t>
-  </si>
-  <si>
-    <t>2017-03-10</t>
-  </si>
-  <si>
-    <t>2017-03-13</t>
-  </si>
-  <si>
-    <t>2017-03-14</t>
-  </si>
-  <si>
-    <t>2017-03-16</t>
-  </si>
-  <si>
-    <t>2017-03-17</t>
-  </si>
-  <si>
-    <t>2017-03-28</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-07</t>
-  </si>
-  <si>
-    <t>2017-03-15</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-07-18</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>2017-09-26</t>
-  </si>
-  <si>
-    <t>2017-09-27</t>
-  </si>
-  <si>
-    <t>2017-09-19</t>
-  </si>
-  <si>
-    <t>2017-10-16</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-02-23</t>
-  </si>
-  <si>
-    <t>2018-04-04</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2017-12-28</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-09-18</t>
-  </si>
-  <si>
-    <t>2018-10-12</t>
-  </si>
-  <si>
-    <t>2018-12-13</t>
-  </si>
-  <si>
-    <t>2018-12-17</t>
-  </si>
-  <si>
-    <t>2018-12-18</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-01-04</t>
-  </si>
-  <si>
-    <t>2018-09-07</t>
-  </si>
-  <si>
-    <t>2019-01-07</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-12-07</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-10-31</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-21</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-17</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-10-30</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2016-02-15</t>
-  </si>
-  <si>
-    <t>2016-02-24</t>
-  </si>
-  <si>
-    <t>2016-03-03</t>
-  </si>
-  <si>
-    <t>2016-03-04</t>
-  </si>
-  <si>
-    <t>2016-03-07</t>
-  </si>
-  <si>
-    <t>2016-03-08</t>
-  </si>
-  <si>
-    <t>2016-03-09</t>
-  </si>
-  <si>
-    <t>2016-03-10</t>
-  </si>
-  <si>
-    <t>2016-03-11</t>
-  </si>
-  <si>
-    <t>2016-03-15</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-06-27</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-07-04</t>
-  </si>
-  <si>
-    <t>2016-07-05</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-12</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-14</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-22</t>
-  </si>
-  <si>
-    <t>2016-07-25</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-07-28</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-08-01</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-08-04</t>
-  </si>
-  <si>
-    <t>2016-08-05</t>
-  </si>
-  <si>
-    <t>2016-08-08</t>
-  </si>
-  <si>
-    <t>2016-08-10</t>
-  </si>
-  <si>
-    <t>2016-08-11</t>
-  </si>
-  <si>
-    <t>2016-08-22</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>2016-08-26</t>
-  </si>
-  <si>
-    <t>2016-11-18</t>
-  </si>
-  <si>
-    <t>2016-11-30</t>
-  </si>
-  <si>
-    <t>2016-12-01</t>
-  </si>
-  <si>
-    <t>2016-12-02</t>
-  </si>
-  <si>
-    <t>2016-12-05</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-09</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2016-12-13</t>
-  </si>
-  <si>
-    <t>2017-03-30</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-04-10</t>
-  </si>
-  <si>
-    <t>2017-04-11</t>
-  </si>
-  <si>
-    <t>2017-04-12</t>
-  </si>
-  <si>
-    <t>2017-04-13</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-20</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-04-24</t>
-  </si>
-  <si>
-    <t>2017-05-09</t>
-  </si>
-  <si>
-    <t>2017-05-10</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-09-04</t>
-  </si>
-  <si>
-    <t>2017-09-05</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2017-09-11</t>
-  </si>
-  <si>
-    <t>2017-09-12</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-15</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2018-03-23</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-03-27</t>
-  </si>
-  <si>
-    <t>2018-03-28</t>
-  </si>
-  <si>
-    <t>2018-03-29</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-23</t>
-  </si>
-  <si>
-    <t>2018-06-04</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-06</t>
-  </si>
-  <si>
-    <t>2018-06-07</t>
-  </si>
-  <si>
-    <t>2018-06-08</t>
-  </si>
-  <si>
-    <t>2018-06-11</t>
-  </si>
-  <si>
-    <t>2018-06-12</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-14</t>
-  </si>
-  <si>
-    <t>2018-06-15</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-22</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-07-04</t>
-  </si>
-  <si>
-    <t>2018-07-05</t>
-  </si>
-  <si>
-    <t>2018-07-06</t>
-  </si>
-  <si>
-    <t>2018-07-09</t>
-  </si>
-  <si>
-    <t>2018-07-10</t>
-  </si>
-  <si>
-    <t>2018-07-11</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-08-28</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-10-25</t>
-  </si>
-  <si>
-    <t>2019-12-03</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-09</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-16</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2019-12-30</t>
-  </si>
-  <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-09</t>
-  </si>
-  <si>
-    <t>2020-01-10</t>
-  </si>
-  <si>
-    <t>2020-01-13</t>
-  </si>
-  <si>
-    <t>2020-01-14</t>
-  </si>
-  <si>
-    <t>2020-01-15</t>
-  </si>
-  <si>
-    <t>2020-01-16</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
-  </si>
-  <si>
-    <t>2020-05-18</t>
-  </si>
-  <si>
-    <t>2020-05-19</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>2020-05-25</t>
-  </si>
-  <si>
-    <t>2020-05-28</t>
-  </si>
-  <si>
-    <t>2020-06-01</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>2020-06-19</t>
-  </si>
-  <si>
-    <t>2020-06-22</t>
-  </si>
-  <si>
-    <t>2020-06-23</t>
-  </si>
-  <si>
-    <t>2020-06-24</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-10-27</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
+    <t>2021-06-15</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P400"/>
+  <dimension ref="A1:P395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1686,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1736,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1786,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1836,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1886,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1936,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1986,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2036,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2086,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2136,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2186,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2236,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2286,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2336,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2386,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2436,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2486,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2536,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2586,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2636,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2686,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2736,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2786,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2836,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2886,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2936,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2986,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3036,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3086,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3136,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3186,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3236,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3286,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3336,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3386,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3436,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3486,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3536,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3586,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3636,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3686,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3736,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3786,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3836,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3886,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3936,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3986,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4036,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4086,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4136,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4186,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4236,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4286,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4336,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4386,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4436,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4486,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4536,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4586,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4636,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4686,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4736,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4786,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4836,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4886,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4936,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4986,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5036,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5086,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5136,7 +5118,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5186,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5236,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5286,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5336,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5386,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5436,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5486,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5536,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5586,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5636,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5686,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5736,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5786,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5836,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5886,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5936,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5986,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6036,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6086,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6136,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6186,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6286,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6336,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6386,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6436,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6486,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6536,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6586,7 +6568,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6636,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6686,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6736,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6786,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6836,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6886,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6936,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6986,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7036,7 +7018,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7086,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7136,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7186,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7236,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7286,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7336,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7386,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7436,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7486,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7536,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7586,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7636,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7686,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7736,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7786,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7836,7 +7818,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7886,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7936,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7986,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8036,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8086,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8136,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8186,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8686,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8836,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8936,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8986,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9036,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9086,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9136,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9186,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9236,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9286,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9336,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9386,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9436,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9486,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9536,7 +9518,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9586,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9636,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9686,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9736,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9786,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9836,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9886,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9936,7 +9918,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9986,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10036,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10086,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10136,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10236,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10286,7 +10268,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10386,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10436,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10486,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10536,7 +10518,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10586,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10636,7 +10618,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10686,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10736,7 +10718,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10786,7 +10768,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10836,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10886,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10986,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11036,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11086,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11136,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11186,7 +11168,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11236,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11286,7 +11268,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11336,7 +11318,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11386,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11436,7 +11418,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11486,7 +11468,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11536,7 +11518,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11586,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11636,7 +11618,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11686,7 +11668,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11736,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11786,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11836,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11886,7 +11868,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11936,7 +11918,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11986,7 +11968,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12036,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12086,7 +12068,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12136,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12186,7 +12168,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12236,7 +12218,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12286,7 +12268,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12336,7 +12318,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12386,7 +12368,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12436,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12486,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12536,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12586,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12636,7 +12618,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12686,7 +12668,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12736,7 +12718,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12786,7 +12768,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12836,7 +12818,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12886,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12936,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12986,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13036,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13086,7 +13068,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13136,7 +13118,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13186,7 +13168,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13236,7 +13218,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13286,7 +13268,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13336,7 +13318,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13386,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13436,7 +13418,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13486,7 +13468,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13536,7 +13518,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13586,7 +13568,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13636,7 +13618,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13686,7 +13668,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13736,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13786,7 +13768,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13836,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13886,7 +13868,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13936,7 +13918,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13986,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14036,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14086,7 +14068,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14136,7 +14118,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14186,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14236,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14286,7 +14268,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14336,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14386,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14436,7 +14418,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14486,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14536,7 +14518,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14586,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14636,7 +14618,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14686,7 +14668,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14736,7 +14718,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14836,7 +14818,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14886,7 +14868,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14936,7 +14918,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14986,7 +14968,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15036,7 +15018,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15086,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15136,7 +15118,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15186,7 +15168,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15236,7 +15218,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15286,7 +15268,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15336,7 +15318,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15386,7 +15368,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15436,7 +15418,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15486,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15536,7 +15518,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15586,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15636,7 +15618,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15686,7 +15668,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15736,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15786,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15836,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15886,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15936,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15986,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16036,7 +16018,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16086,7 +16068,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16136,7 +16118,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16186,7 +16168,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16236,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16286,7 +16268,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16336,7 +16318,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16386,7 +16368,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16436,7 +16418,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16486,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16536,7 +16518,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16586,7 +16568,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16636,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16686,7 +16668,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16736,7 +16718,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16786,7 +16768,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16836,7 +16818,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16886,7 +16868,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16936,7 +16918,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16986,7 +16968,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17036,7 +17018,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17086,7 +17068,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17136,7 +17118,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17186,7 +17168,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17236,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17286,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17336,7 +17318,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17386,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17436,7 +17418,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17486,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17536,7 +17518,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17586,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17636,7 +17618,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17686,7 +17668,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17736,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17786,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17836,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17886,7 +17868,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17936,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17986,7 +17968,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18036,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18086,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18136,7 +18118,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18186,7 +18168,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18236,7 +18218,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18286,7 +18268,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18336,7 +18318,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18386,7 +18368,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18436,7 +18418,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18636,7 +18618,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18686,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18736,7 +18718,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18786,7 +18768,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18836,7 +18818,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19086,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19136,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19186,7 +19168,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19286,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19336,7 +19318,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19386,7 +19368,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19436,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19586,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19636,7 +19618,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19686,7 +19668,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19786,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19836,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19886,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19936,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19986,7 +19968,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20036,7 +20018,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20086,7 +20068,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20136,7 +20118,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20186,7 +20168,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20236,7 +20218,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20286,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20336,7 +20318,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20436,7 +20418,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20486,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20536,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20586,7 +20568,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20636,7 +20618,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20686,7 +20668,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20736,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20786,7 +20768,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20836,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20986,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20994,49 +20976,49 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C389">
-        <v>0.8094230769230786</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D389" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E389">
-        <v>0.6894230769230785</v>
+        <v>0.4299907056193337</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.003730576923076922</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H389">
-        <v>0.003610576923076922</v>
+        <v>0.003530009294380666</v>
       </c>
       <c r="I389">
-        <v>0.1200000000000001</v>
+        <v>0.06373106583938326</v>
       </c>
       <c r="J389">
-        <v>0.9423076923076913</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K389">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="L389">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="M389">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="N389">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21047,28 +21029,28 @@
         <v>85</v>
       </c>
       <c r="C390">
-        <v>0.589142733736006</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D390" t="s">
         <v>217</v>
       </c>
       <c r="E390">
-        <v>0.5673911791524699</v>
+        <v>0.3787077350920742</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003590857266263994</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H390">
-        <v>0.00361260882084753</v>
+        <v>0.003581292264907926</v>
       </c>
       <c r="I390">
-        <v>0.02175155458353606</v>
+        <v>0.06220023089827098</v>
       </c>
       <c r="J390">
-        <v>1.087577729176807</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K390">
         <v>1.38</v>
@@ -21077,16 +21059,16 @@
         <v>2.09</v>
       </c>
       <c r="M390">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N390">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21097,28 +21079,28 @@
         <v>85</v>
       </c>
       <c r="C391">
-        <v>0.5536378221197245</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D391" t="s">
         <v>217</v>
       </c>
       <c r="E391">
-        <v>0.5313717035997205</v>
+        <v>0.3811953138837596</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003626362177880275</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H391">
-        <v>0.003648628296400279</v>
+        <v>0.00357880468611624</v>
       </c>
       <c r="I391">
-        <v>0.02226611852000393</v>
+        <v>0.06227448698160498</v>
       </c>
       <c r="J391">
-        <v>1.1133059260002</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K391">
         <v>1.38</v>
@@ -21127,16 +21109,16 @@
         <v>2.09</v>
       </c>
       <c r="M391">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N391">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21144,49 +21126,49 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C392">
-        <v>0.5314031526074197</v>
+        <v>2.138444260870803</v>
       </c>
       <c r="D392" t="s">
         <v>217</v>
       </c>
       <c r="E392">
-        <v>0.5088147925002808</v>
+        <v>2.108444260870803</v>
       </c>
       <c r="F392">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G392">
-        <v>0.00364859684739258</v>
+        <v>0.001881555739129197</v>
       </c>
       <c r="H392">
-        <v>0.003671185207499719</v>
+        <v>0.001851555739129197</v>
       </c>
       <c r="I392">
-        <v>0.02258836010713883</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J392">
-        <v>1.129418005356942</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K392">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L392">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M392">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N392">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21194,49 +21176,49 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C393">
-        <v>0.5157826711345157</v>
+        <v>2.276625292888353</v>
       </c>
       <c r="D393" t="s">
         <v>217</v>
       </c>
       <c r="E393">
-        <v>0.4929679272379144</v>
+        <v>2.246625292888353</v>
       </c>
       <c r="F393">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G393">
-        <v>0.003664217328865484</v>
+        <v>0.001743374707111646</v>
       </c>
       <c r="H393">
-        <v>0.003687032072762086</v>
+        <v>0.001713374707111647</v>
       </c>
       <c r="I393">
-        <v>0.02281474389660132</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J393">
-        <v>1.140737194830061</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K393">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L393">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M393">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N393">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21244,49 +21226,49 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C394">
-        <v>0.493721771458717</v>
+        <v>2.340948171745636</v>
       </c>
       <c r="D394" t="s">
         <v>217</v>
       </c>
       <c r="E394">
-        <v>0.4705873043784086</v>
+        <v>2.310948171745637</v>
       </c>
       <c r="F394">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G394">
-        <v>0.003686278228541283</v>
+        <v>0.001679051828254363</v>
       </c>
       <c r="H394">
-        <v>0.003709412695621591</v>
+        <v>0.001649051828254363</v>
       </c>
       <c r="I394">
-        <v>0.02313446708030842</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J394">
-        <v>1.156723354015422</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K394">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L394">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M394">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N394">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21294,299 +21276,49 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C395">
-        <v>0.4409079659903452</v>
+        <v>2.376110233960097</v>
       </c>
       <c r="D395" t="s">
         <v>217</v>
       </c>
       <c r="E395">
-        <v>0.4170080814394805</v>
+        <v>2.346110233960097</v>
       </c>
       <c r="F395">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G395">
-        <v>0.003739092034009655</v>
+        <v>0.001643889766039903</v>
       </c>
       <c r="H395">
-        <v>0.003762991918560519</v>
+        <v>0.001613889766039903</v>
       </c>
       <c r="I395">
-        <v>0.02389988455086467</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J395">
-        <v>1.194994227543228</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K395">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L395">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M395">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N395">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="396" spans="1:16">
-      <c r="A396" s="1">
-        <v>0</v>
-      </c>
-      <c r="B396" t="s">
-        <v>85</v>
-      </c>
-      <c r="C396">
-        <v>0.4434698008653646</v>
-      </c>
-      <c r="D396" t="s">
-        <v>217</v>
-      </c>
-      <c r="E396">
-        <v>0.4196070443561668</v>
-      </c>
-      <c r="F396">
-        <v>-1</v>
-      </c>
-      <c r="G396">
-        <v>0.003736530199134635</v>
-      </c>
-      <c r="H396">
-        <v>0.003760392955643833</v>
-      </c>
-      <c r="I396">
-        <v>0.02386275650919778</v>
-      </c>
-      <c r="J396">
-        <v>1.193137825459881</v>
-      </c>
-      <c r="K396">
-        <v>1.38</v>
-      </c>
-      <c r="L396">
-        <v>2.09</v>
-      </c>
-      <c r="M396">
-        <v>1.4</v>
-      </c>
-      <c r="N396">
-        <v>2.09</v>
-      </c>
-      <c r="O396">
-        <v>1</v>
-      </c>
-      <c r="P396" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="397" spans="1:16">
-      <c r="A397" s="1">
-        <v>0</v>
-      </c>
-      <c r="B397" t="s">
-        <v>85</v>
-      </c>
-      <c r="C397">
-        <v>0.4483932592798776</v>
-      </c>
-      <c r="D397" t="s">
-        <v>217</v>
-      </c>
-      <c r="E397">
-        <v>0.4246018572404555</v>
-      </c>
-      <c r="F397">
-        <v>-1</v>
-      </c>
-      <c r="G397">
-        <v>0.003731606740720122</v>
-      </c>
-      <c r="H397">
-        <v>0.003755398142759544</v>
-      </c>
-      <c r="I397">
-        <v>0.02379140203942209</v>
-      </c>
-      <c r="J397">
-        <v>1.189570101971103</v>
-      </c>
-      <c r="K397">
-        <v>1.38</v>
-      </c>
-      <c r="L397">
-        <v>2.09</v>
-      </c>
-      <c r="M397">
-        <v>1.4</v>
-      </c>
-      <c r="N397">
-        <v>2.09</v>
-      </c>
-      <c r="O397">
-        <v>1</v>
-      </c>
-      <c r="P397" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="398" spans="1:16">
-      <c r="A398" s="1">
-        <v>0</v>
-      </c>
-      <c r="B398" t="s">
-        <v>85</v>
-      </c>
-      <c r="C398">
-        <v>0.4444321020325201</v>
-      </c>
-      <c r="D398" t="s">
-        <v>217</v>
-      </c>
-      <c r="E398">
-        <v>0.4205832919170494</v>
-      </c>
-      <c r="F398">
-        <v>-1</v>
-      </c>
-      <c r="G398">
-        <v>0.00373556789796748</v>
-      </c>
-      <c r="H398">
-        <v>0.003759416708082951</v>
-      </c>
-      <c r="I398">
-        <v>0.0238488101154708</v>
-      </c>
-      <c r="J398">
-        <v>1.192440505773536</v>
-      </c>
-      <c r="K398">
-        <v>1.38</v>
-      </c>
-      <c r="L398">
-        <v>2.09</v>
-      </c>
-      <c r="M398">
-        <v>1.4</v>
-      </c>
-      <c r="N398">
-        <v>2.09</v>
-      </c>
-      <c r="O398">
-        <v>1</v>
-      </c>
-      <c r="P398" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="399" spans="1:16">
-      <c r="A399" s="1">
-        <v>0</v>
-      </c>
-      <c r="B399" t="s">
-        <v>86</v>
-      </c>
-      <c r="C399">
-        <v>2.36240774237655</v>
-      </c>
-      <c r="D399" t="s">
-        <v>218</v>
-      </c>
-      <c r="E399">
-        <v>2.264739428294711</v>
-      </c>
-      <c r="F399">
-        <v>-1</v>
-      </c>
-      <c r="G399">
-        <v>0.00205759225762345</v>
-      </c>
-      <c r="H399">
-        <v>0.001975260571705289</v>
-      </c>
-      <c r="I399">
-        <v>0.09766831408183885</v>
-      </c>
-      <c r="J399">
-        <v>-0.0958539260229872</v>
-      </c>
-      <c r="K399">
-        <v>1.59</v>
-      </c>
-      <c r="L399">
-        <v>2.21</v>
-      </c>
-      <c r="M399">
-        <v>1.51</v>
-      </c>
-      <c r="N399">
-        <v>2.12</v>
-      </c>
-      <c r="O399">
-        <v>1</v>
-      </c>
-      <c r="P399" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="400" spans="1:16">
-      <c r="A400" s="1">
-        <v>0</v>
-      </c>
-      <c r="B400" t="s">
-        <v>86</v>
-      </c>
-      <c r="C400">
-        <v>2.526368817680956</v>
-      </c>
-      <c r="D400" t="s">
-        <v>218</v>
-      </c>
-      <c r="E400">
-        <v>2.420450889747324</v>
-      </c>
-      <c r="F400">
-        <v>-1</v>
-      </c>
-      <c r="G400">
-        <v>0.001893631182319044</v>
-      </c>
-      <c r="H400">
-        <v>0.001819549110252677</v>
-      </c>
-      <c r="I400">
-        <v>0.1059179279336329</v>
-      </c>
-      <c r="J400">
-        <v>-0.1989740991704129</v>
-      </c>
-      <c r="K400">
-        <v>1.59</v>
-      </c>
-      <c r="L400">
-        <v>2.21</v>
-      </c>
-      <c r="M400">
-        <v>1.51</v>
-      </c>
-      <c r="N400">
-        <v>2.12</v>
-      </c>
-      <c r="O400">
-        <v>1</v>
-      </c>
-      <c r="P400" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="401">
   <si>
     <t>trade_time</t>
   </si>
@@ -262,21 +262,18 @@
     <t>2020-10-28</t>
   </si>
   <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
     <t>2021-02-05</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-04-09</t>
   </si>
   <si>
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
     <t>2016-04-13</t>
   </si>
   <si>
@@ -664,12 +661,12 @@
     <t>2021-02-22</t>
   </si>
   <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
     <t>2021-04-26</t>
   </si>
   <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
     <t>2016-02-15</t>
   </si>
   <si>
@@ -1193,6 +1190,12 @@
   </si>
   <si>
     <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
   </si>
   <si>
     <t>2021-04-21</t>
@@ -1571,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P395"/>
+  <dimension ref="A1:P397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1632,7 +1635,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1668,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1682,7 +1685,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1718,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1768,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1818,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1832,7 +1835,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1868,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1882,7 +1885,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1918,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1932,7 +1935,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1968,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1982,7 +1985,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2018,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2032,7 +2035,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2068,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2082,7 +2085,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2118,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2132,7 +2135,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2168,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2182,7 +2185,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2218,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2232,7 +2235,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2268,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2282,7 +2285,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2318,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2332,7 +2335,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2368,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2382,7 +2385,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2418,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2432,7 +2435,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2468,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2482,7 +2485,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2518,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2532,7 +2535,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2568,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2582,7 +2585,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2618,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2632,7 +2635,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2668,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2682,7 +2685,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2718,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2732,7 +2735,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2768,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2782,7 +2785,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2818,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2832,7 +2835,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2868,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2882,7 +2885,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2918,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2932,7 +2935,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2968,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2982,7 +2985,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3018,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3032,7 +3035,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3068,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3082,7 +3085,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3118,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3132,7 +3135,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3168,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3182,7 +3185,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3218,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3232,7 +3235,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3268,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3282,7 +3285,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3318,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3332,7 +3335,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3368,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3382,7 +3385,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3418,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3432,7 +3435,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3468,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3482,7 +3485,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3518,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3532,7 +3535,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3568,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3582,7 +3585,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3618,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3632,7 +3635,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3668,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3682,7 +3685,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3718,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3732,7 +3735,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3768,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3782,7 +3785,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3818,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3832,7 +3835,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3868,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3882,7 +3885,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3918,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3932,7 +3935,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3968,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3982,7 +3985,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4018,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4032,7 +4035,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4068,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4082,7 +4085,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4118,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4132,7 +4135,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4168,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4182,7 +4185,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4218,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4232,7 +4235,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4268,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4282,7 +4285,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4318,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4332,7 +4335,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4368,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4382,7 +4385,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4418,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4432,7 +4435,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4468,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4482,7 +4485,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4518,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4532,7 +4535,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4568,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4582,7 +4585,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4618,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4632,7 +4635,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4668,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4682,7 +4685,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4718,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4732,7 +4735,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4768,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4782,7 +4785,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4818,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4832,7 +4835,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4868,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4882,7 +4885,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4918,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4932,7 +4935,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4968,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4982,7 +4985,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5018,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5032,7 +5035,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5068,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5082,7 +5085,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5118,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5132,7 +5135,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5168,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5182,7 +5185,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5218,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5232,7 +5235,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5268,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5282,7 +5285,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5318,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5332,7 +5335,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5368,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5382,7 +5385,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5418,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5432,7 +5435,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5468,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5482,7 +5485,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5518,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5532,7 +5535,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5568,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5582,7 +5585,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5618,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5632,7 +5635,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5668,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5682,7 +5685,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5718,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5732,7 +5735,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5768,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5782,7 +5785,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5818,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5832,7 +5835,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5868,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5882,7 +5885,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5918,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5932,7 +5935,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5968,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5982,7 +5985,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6018,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6032,7 +6035,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6068,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6082,7 +6085,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6118,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6132,7 +6135,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6168,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6182,7 +6185,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6232,7 +6235,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6268,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6282,7 +6285,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6318,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6332,7 +6335,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6368,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6382,7 +6385,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6418,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6432,7 +6435,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6468,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6482,7 +6485,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6518,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6532,7 +6535,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6568,7 +6571,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6582,7 +6585,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6618,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6632,7 +6635,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6668,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6682,7 +6685,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6718,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6732,7 +6735,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6768,7 +6771,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6782,7 +6785,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6818,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6832,7 +6835,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6868,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6882,7 +6885,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6918,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6932,7 +6935,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6968,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6982,7 +6985,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7018,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7032,7 +7035,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7068,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7082,7 +7085,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7118,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7132,7 +7135,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7168,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7182,7 +7185,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7218,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7232,7 +7235,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7268,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7282,7 +7285,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7318,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7332,7 +7335,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7368,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7382,7 +7385,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7418,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7432,7 +7435,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7468,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7482,7 +7485,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7518,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7532,7 +7535,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7568,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7582,7 +7585,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7618,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7632,7 +7635,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7668,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7682,7 +7685,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7718,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7732,7 +7735,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7768,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7782,7 +7785,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7818,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7832,7 +7835,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7868,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7882,7 +7885,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7918,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7932,7 +7935,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7968,7 +7971,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7982,7 +7985,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8018,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8032,7 +8035,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8068,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8082,7 +8085,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8118,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8132,7 +8135,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8168,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8182,7 +8185,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8218,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8232,7 +8235,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8268,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8282,7 +8285,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8318,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8332,7 +8335,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8368,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8382,7 +8385,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8418,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8432,7 +8435,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8468,7 +8471,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8482,7 +8485,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8518,7 +8521,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8532,7 +8535,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8568,7 +8571,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8582,7 +8585,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8618,7 +8621,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8632,7 +8635,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8668,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8682,7 +8685,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8718,7 +8721,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8732,7 +8735,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8768,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8782,7 +8785,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8818,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8832,7 +8835,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8868,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8882,7 +8885,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8918,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8932,7 +8935,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8968,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8982,7 +8985,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9018,7 +9021,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9032,7 +9035,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9068,7 +9071,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9082,7 +9085,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9118,7 +9121,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9132,7 +9135,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9168,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9182,7 +9185,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9218,7 +9221,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9232,7 +9235,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9268,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9282,7 +9285,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9318,7 +9321,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9332,7 +9335,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9368,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9382,7 +9385,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9418,7 +9421,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9432,7 +9435,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9468,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9482,7 +9485,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9518,7 +9521,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9532,7 +9535,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9568,7 +9571,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9582,7 +9585,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9618,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9632,7 +9635,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9668,7 +9671,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9682,7 +9685,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9718,7 +9721,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9732,7 +9735,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9768,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9782,7 +9785,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9818,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9832,7 +9835,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9868,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9882,7 +9885,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9918,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9932,7 +9935,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9968,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9982,7 +9985,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10018,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10032,7 +10035,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10068,7 +10071,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10082,7 +10085,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10118,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10132,7 +10135,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10182,7 +10185,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10218,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10232,7 +10235,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10268,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10282,7 +10285,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10318,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10332,7 +10335,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10368,7 +10371,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10382,7 +10385,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10418,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10432,7 +10435,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10468,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10482,7 +10485,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10518,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10532,7 +10535,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10568,7 +10571,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10582,7 +10585,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10618,7 +10621,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10632,7 +10635,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10668,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10682,7 +10685,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10718,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10768,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10818,7 +10821,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10868,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10918,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10932,7 +10935,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10968,7 +10971,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10982,7 +10985,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11018,7 +11021,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11032,7 +11035,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11068,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11082,7 +11085,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11118,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11132,7 +11135,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11168,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11182,7 +11185,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11218,7 +11221,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11232,7 +11235,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11268,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11282,7 +11285,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11318,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11332,7 +11335,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11368,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11382,7 +11385,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11418,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11432,7 +11435,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11468,7 +11471,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11482,7 +11485,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11518,7 +11521,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11532,7 +11535,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11568,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11582,7 +11585,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11618,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11632,7 +11635,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11668,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11682,7 +11685,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11718,7 +11721,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11732,7 +11735,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11768,7 +11771,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11782,7 +11785,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11818,7 +11821,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11832,7 +11835,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11868,7 +11871,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11882,7 +11885,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11918,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11932,7 +11935,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11968,7 +11971,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11982,7 +11985,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12018,7 +12021,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12032,7 +12035,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12068,7 +12071,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12082,7 +12085,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12118,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12132,7 +12135,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12168,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12182,7 +12185,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12218,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12232,7 +12235,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12268,7 +12271,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12282,7 +12285,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12318,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12332,7 +12335,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12368,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12382,7 +12385,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12418,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12432,7 +12435,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12468,7 +12471,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12482,7 +12485,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12518,7 +12521,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12532,7 +12535,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12568,7 +12571,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12582,7 +12585,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12618,7 +12621,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12632,7 +12635,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12668,7 +12671,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12682,7 +12685,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12718,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12732,7 +12735,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12768,7 +12771,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12782,7 +12785,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12818,7 +12821,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12832,7 +12835,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12868,7 +12871,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12882,7 +12885,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12918,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12932,7 +12935,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12968,7 +12971,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12982,7 +12985,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13018,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13032,7 +13035,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13068,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13082,7 +13085,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13118,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13132,7 +13135,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13168,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13182,7 +13185,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13218,7 +13221,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13232,7 +13235,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13268,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13282,7 +13285,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13318,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13332,7 +13335,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13368,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13382,7 +13385,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13418,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13432,7 +13435,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13468,7 +13471,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13482,7 +13485,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13518,7 +13521,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13532,7 +13535,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13568,7 +13571,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13582,7 +13585,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13618,7 +13621,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13632,7 +13635,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13668,7 +13671,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13682,7 +13685,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13718,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13732,7 +13735,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13768,7 +13771,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13782,7 +13785,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13818,7 +13821,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13832,7 +13835,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13868,7 +13871,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13882,7 +13885,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13918,7 +13921,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13932,7 +13935,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13968,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13982,7 +13985,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14018,7 +14021,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14032,7 +14035,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14068,7 +14071,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14082,7 +14085,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14118,7 +14121,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14132,7 +14135,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14168,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14182,7 +14185,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14218,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14232,7 +14235,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14268,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14282,7 +14285,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14318,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14332,7 +14335,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14368,7 +14371,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14382,7 +14385,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14418,7 +14421,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14432,7 +14435,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14468,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14482,7 +14485,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14518,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14532,7 +14535,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14568,7 +14571,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14582,7 +14585,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14618,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14632,7 +14635,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14668,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14682,7 +14685,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14718,7 +14721,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14732,7 +14735,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14818,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14832,7 +14835,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14868,7 +14871,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14882,7 +14885,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14918,7 +14921,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14932,7 +14935,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14968,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14982,7 +14985,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15018,7 +15021,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15032,7 +15035,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15068,7 +15071,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15082,7 +15085,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15118,7 +15121,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15132,7 +15135,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15168,7 +15171,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15182,7 +15185,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15218,7 +15221,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15232,7 +15235,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15268,7 +15271,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15282,7 +15285,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15318,7 +15321,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15332,7 +15335,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15368,7 +15371,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15382,7 +15385,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15418,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15432,7 +15435,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15468,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15482,7 +15485,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15518,7 +15521,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15532,7 +15535,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15568,7 +15571,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15582,7 +15585,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15618,7 +15621,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15632,7 +15635,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15668,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15682,7 +15685,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15718,7 +15721,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15732,7 +15735,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15768,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15818,7 +15821,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15868,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15882,7 +15885,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15918,7 +15921,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15932,7 +15935,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15968,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15982,7 +15985,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16018,7 +16021,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16032,7 +16035,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16068,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16082,7 +16085,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16118,7 +16121,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16168,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16218,7 +16221,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16232,7 +16235,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16268,7 +16271,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16282,7 +16285,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16318,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16332,7 +16335,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16368,7 +16371,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16382,7 +16385,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16418,7 +16421,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16432,7 +16435,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16468,7 +16471,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16482,7 +16485,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16518,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16532,7 +16535,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16568,7 +16571,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16618,7 +16621,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16668,7 +16671,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16682,7 +16685,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16718,7 +16721,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16732,7 +16735,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16768,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16782,7 +16785,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16818,7 +16821,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16832,7 +16835,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16868,7 +16871,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16882,7 +16885,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16918,7 +16921,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16932,7 +16935,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16968,7 +16971,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16982,7 +16985,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17018,7 +17021,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17032,7 +17035,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17068,7 +17071,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17082,7 +17085,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17118,7 +17121,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17132,7 +17135,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17168,7 +17171,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17182,7 +17185,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17218,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17268,7 +17271,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17318,7 +17321,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17332,7 +17335,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17368,7 +17371,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17418,7 +17421,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17468,7 +17471,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17482,7 +17485,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17518,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17618,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17632,7 +17635,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17668,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17768,7 +17771,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17782,7 +17785,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17818,7 +17821,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17871,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17918,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17932,7 +17935,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17968,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18068,7 +18071,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18082,7 +18085,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18118,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18168,7 +18171,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18218,7 +18221,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18232,7 +18235,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18268,7 +18271,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18318,7 +18321,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18368,7 +18371,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18382,7 +18385,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18418,7 +18421,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18532,7 +18535,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18618,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18632,7 +18635,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18668,7 +18671,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18718,7 +18721,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18768,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18782,7 +18785,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18818,7 +18821,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18982,7 +18985,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19068,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19118,7 +19121,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19132,7 +19135,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19168,7 +19171,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19182,7 +19185,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19268,7 +19271,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19282,7 +19285,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19318,7 +19321,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19368,7 +19371,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19382,7 +19385,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19418,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19482,7 +19485,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19532,7 +19535,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19568,7 +19571,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19582,7 +19585,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19618,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19632,7 +19635,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19668,7 +19671,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19682,7 +19685,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19768,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19782,7 +19785,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19818,7 +19821,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19868,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19918,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19932,7 +19935,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19968,7 +19971,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19982,7 +19985,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20018,7 +20021,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20032,7 +20035,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20068,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20082,7 +20085,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20118,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20132,7 +20135,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20168,7 +20171,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20182,7 +20185,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20218,7 +20221,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20232,7 +20235,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20268,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20282,7 +20285,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20318,7 +20321,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20332,7 +20335,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20368,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20418,7 +20421,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20429,10 +20432,10 @@
         <v>82</v>
       </c>
       <c r="C378">
-        <v>1.767440067057837</v>
+        <v>1.755766974015088</v>
       </c>
       <c r="D378" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E378">
         <v>1.917324392288349</v>
@@ -20441,22 +20444,22 @@
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.002232559932942163</v>
+        <v>0.002224233025984912</v>
       </c>
       <c r="H378">
         <v>0.002442675607711651</v>
       </c>
       <c r="I378">
-        <v>0.1498843252305115</v>
+        <v>0.1615574182732609</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
       </c>
       <c r="K378">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L378">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M378">
         <v>1.57</v>
@@ -20468,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20479,46 +20482,46 @@
         <v>83</v>
       </c>
       <c r="C379">
-        <v>1.755766974015088</v>
+        <v>1.755805532271584</v>
       </c>
       <c r="D379" t="s">
         <v>215</v>
       </c>
       <c r="E379">
-        <v>1.917324392288349</v>
+        <v>1.715805532271584</v>
       </c>
       <c r="F379">
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.002224233025984912</v>
+        <v>0.002204194467728416</v>
       </c>
       <c r="H379">
-        <v>0.002442675607711651</v>
+        <v>0.002164194467728416</v>
       </c>
       <c r="I379">
-        <v>0.1615574182732609</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J379">
         <v>0.1673093042749371</v>
       </c>
       <c r="K379">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L379">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="M379">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N379">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20529,10 +20532,10 @@
         <v>82</v>
       </c>
       <c r="C380">
-        <v>1.799235962112094</v>
+        <v>1.787791616515778</v>
       </c>
       <c r="D380" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E380">
         <v>1.953237741378409</v>
@@ -20541,22 +20544,22 @@
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.002200764037887906</v>
+        <v>0.002192208383484222</v>
       </c>
       <c r="H380">
         <v>0.002406762258621592</v>
       </c>
       <c r="I380">
-        <v>0.1540017792663146</v>
+        <v>0.1654461248626304</v>
       </c>
       <c r="J380">
         <v>0.1444345596315869</v>
       </c>
       <c r="K380">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L380">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M380">
         <v>1.57</v>
@@ -20568,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20579,46 +20582,46 @@
         <v>83</v>
       </c>
       <c r="C381">
-        <v>1.787791616515778</v>
+        <v>1.786457690093674</v>
       </c>
       <c r="D381" t="s">
         <v>215</v>
       </c>
       <c r="E381">
-        <v>1.953237741378409</v>
+        <v>1.746457690093673</v>
       </c>
       <c r="F381">
         <v>1</v>
       </c>
       <c r="G381">
-        <v>0.002192208383484222</v>
+        <v>0.002173542309906327</v>
       </c>
       <c r="H381">
-        <v>0.002406762258621592</v>
+        <v>0.002133542309906327</v>
       </c>
       <c r="I381">
-        <v>0.1654461248626304</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J381">
         <v>0.1444345596315869</v>
       </c>
       <c r="K381">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L381">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="M381">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N381">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20629,10 +20632,10 @@
         <v>82</v>
       </c>
       <c r="C382">
-        <v>1.884012465206341</v>
+        <v>1.873178022509984</v>
       </c>
       <c r="D382" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E382">
         <v>2.048992496671911</v>
@@ -20641,22 +20644,22 @@
         <v>1</v>
       </c>
       <c r="G382">
-        <v>0.002115987534793658</v>
+        <v>0.002106821977490016</v>
       </c>
       <c r="H382">
         <v>0.002311007503328089</v>
       </c>
       <c r="I382">
-        <v>0.1649800314655698</v>
+        <v>0.175814474161927</v>
       </c>
       <c r="J382">
         <v>0.0834442696357255</v>
       </c>
       <c r="K382">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L382">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M382">
         <v>1.57</v>
@@ -20668,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20679,46 +20682,46 @@
         <v>83</v>
       </c>
       <c r="C383">
-        <v>1.873178022509984</v>
+        <v>1.868184678688128</v>
       </c>
       <c r="D383" t="s">
         <v>215</v>
       </c>
       <c r="E383">
-        <v>2.048992496671911</v>
+        <v>1.828184678688128</v>
       </c>
       <c r="F383">
         <v>1</v>
       </c>
       <c r="G383">
-        <v>0.002106821977490016</v>
+        <v>0.002091815321311872</v>
       </c>
       <c r="H383">
-        <v>0.002311007503328089</v>
+        <v>0.002051815321311872</v>
       </c>
       <c r="I383">
-        <v>0.175814474161927</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J383">
         <v>0.0834442696357255</v>
       </c>
       <c r="K383">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L383">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="M383">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N383">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O383">
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20729,10 +20732,10 @@
         <v>82</v>
       </c>
       <c r="C384">
-        <v>1.862102797346283</v>
+        <v>1.851110731140141</v>
       </c>
       <c r="D384" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E384">
         <v>2.02424560563573</v>
@@ -20741,22 +20744,22 @@
         <v>1</v>
       </c>
       <c r="G384">
-        <v>0.002137897202653717</v>
+        <v>0.002128889268859859</v>
       </c>
       <c r="H384">
         <v>0.00233575439436427</v>
       </c>
       <c r="I384">
-        <v>0.1621428082894469</v>
+        <v>0.1731348744955887</v>
       </c>
       <c r="J384">
         <v>0.09920662061418481</v>
       </c>
       <c r="K384">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L384">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M384">
         <v>1.57</v>
@@ -20768,7 +20771,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20779,46 +20782,46 @@
         <v>83</v>
       </c>
       <c r="C385">
-        <v>1.851110731140141</v>
+        <v>1.847063128376992</v>
       </c>
       <c r="D385" t="s">
         <v>215</v>
       </c>
       <c r="E385">
-        <v>2.02424560563573</v>
+        <v>1.807063128376992</v>
       </c>
       <c r="F385">
         <v>1</v>
       </c>
       <c r="G385">
-        <v>0.002128889268859859</v>
+        <v>0.002112936871623007</v>
       </c>
       <c r="H385">
-        <v>0.00233575439436427</v>
+        <v>0.002072936871623007</v>
       </c>
       <c r="I385">
-        <v>0.1731348744955887</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J385">
         <v>0.09920662061418481</v>
       </c>
       <c r="K385">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L385">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="M385">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N385">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20829,10 +20832,10 @@
         <v>82</v>
       </c>
       <c r="C386">
-        <v>1.758150385501947</v>
+        <v>1.746410460217788</v>
       </c>
       <c r="D386" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E386">
         <v>1.906831730387091</v>
@@ -20841,22 +20844,22 @@
         <v>1</v>
       </c>
       <c r="G386">
-        <v>0.002241849614498053</v>
+        <v>0.002233589539782212</v>
       </c>
       <c r="H386">
         <v>0.002453168269612909</v>
       </c>
       <c r="I386">
-        <v>0.1486813448851443</v>
+        <v>0.1604212701693031</v>
       </c>
       <c r="J386">
         <v>0.1739925284158654</v>
       </c>
       <c r="K386">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="L386">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="M386">
         <v>1.57</v>
@@ -20868,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20879,46 +20882,46 @@
         <v>83</v>
       </c>
       <c r="C387">
-        <v>1.746410460217788</v>
+        <v>1.74685001192274</v>
       </c>
       <c r="D387" t="s">
         <v>215</v>
       </c>
       <c r="E387">
-        <v>1.906831730387091</v>
+        <v>1.70685001192274</v>
       </c>
       <c r="F387">
         <v>1</v>
       </c>
       <c r="G387">
-        <v>0.002233589539782212</v>
+        <v>0.00221314998807726</v>
       </c>
       <c r="H387">
-        <v>0.002453168269612909</v>
+        <v>0.002173149988077259</v>
       </c>
       <c r="I387">
-        <v>0.1604212701693031</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J387">
         <v>0.1739925284158654</v>
       </c>
       <c r="K387">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L387">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="M387">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N387">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O387">
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20968,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20976,49 +20979,49 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C389">
-        <v>0.493721771458717</v>
+        <v>0.8094230769230786</v>
       </c>
       <c r="D389" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E389">
-        <v>0.4299907056193337</v>
+        <v>0.6894230769230785</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.003686278228541283</v>
+        <v>0.003730576923076922</v>
       </c>
       <c r="H389">
-        <v>0.003530009294380666</v>
+        <v>0.003610576923076922</v>
       </c>
       <c r="I389">
-        <v>0.06373106583938326</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="J389">
-        <v>1.156723354015422</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K389">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="L389">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="M389">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="N389">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21029,28 +21032,28 @@
         <v>85</v>
       </c>
       <c r="C390">
-        <v>0.4409079659903452</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D390" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E390">
-        <v>0.3787077350920742</v>
+        <v>0.411412158927718</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003739092034009655</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H390">
-        <v>0.003581292264907926</v>
+        <v>0.003468587841072282</v>
       </c>
       <c r="I390">
-        <v>0.06220023089827098</v>
+        <v>0.1043705122067977</v>
       </c>
       <c r="J390">
-        <v>1.194994227543228</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K390">
         <v>1.38</v>
@@ -21062,13 +21065,13 @@
         <v>1.34</v>
       </c>
       <c r="N390">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21079,28 +21082,28 @@
         <v>85</v>
       </c>
       <c r="C391">
-        <v>0.4434698008653646</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D391" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E391">
-        <v>0.3811953138837596</v>
+        <v>0.3899907056193337</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003736530199134635</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H391">
-        <v>0.00357880468611624</v>
+        <v>0.003490009294380666</v>
       </c>
       <c r="I391">
-        <v>0.06227448698160498</v>
+        <v>0.1037310658393833</v>
       </c>
       <c r="J391">
-        <v>1.193137825459881</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K391">
         <v>1.38</v>
@@ -21112,13 +21115,13 @@
         <v>1.34</v>
       </c>
       <c r="N391">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21126,49 +21129,49 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C392">
-        <v>2.138444260870803</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D392" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E392">
-        <v>2.108444260870803</v>
+        <v>0.3387077350920742</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.001881555739129197</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H392">
-        <v>0.001851555739129197</v>
+        <v>0.003541292264907926</v>
       </c>
       <c r="I392">
-        <v>-0.0299999999999998</v>
+        <v>0.102200230898271</v>
       </c>
       <c r="J392">
-        <v>-0.0958539260229872</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K392">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L392">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M392">
         <v>1.34</v>
       </c>
       <c r="N392">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21176,49 +21179,49 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C393">
-        <v>2.276625292888353</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D393" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E393">
-        <v>2.246625292888353</v>
+        <v>0.3411953138837596</v>
       </c>
       <c r="F393">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.001743374707111646</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H393">
-        <v>0.001713374707111647</v>
+        <v>0.00353880468611624</v>
       </c>
       <c r="I393">
-        <v>-0.0299999999999998</v>
+        <v>0.102274486981605</v>
       </c>
       <c r="J393">
-        <v>-0.1989740991704129</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K393">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L393">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M393">
         <v>1.34</v>
       </c>
       <c r="N393">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21226,49 +21229,49 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C394">
-        <v>2.340948171745636</v>
+        <v>2.108444260870803</v>
       </c>
       <c r="D394" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E394">
-        <v>2.310948171745637</v>
+        <v>2.068444260870803</v>
       </c>
       <c r="F394">
         <v>1</v>
       </c>
       <c r="G394">
-        <v>0.001679051828254363</v>
+        <v>0.001851555739129197</v>
       </c>
       <c r="H394">
-        <v>0.001649051828254363</v>
+        <v>0.001811555739129197</v>
       </c>
       <c r="I394">
-        <v>-0.0299999999999998</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J394">
-        <v>-0.2469762475713705</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K394">
         <v>1.34</v>
       </c>
       <c r="L394">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="M394">
         <v>1.34</v>
       </c>
       <c r="N394">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21276,49 +21279,149 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C395">
-        <v>2.376110233960097</v>
+        <v>2.246625292888353</v>
       </c>
       <c r="D395" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E395">
-        <v>2.346110233960097</v>
+        <v>2.206625292888353</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001643889766039903</v>
+        <v>0.001713374707111647</v>
       </c>
       <c r="H395">
-        <v>0.001613889766039903</v>
+        <v>0.001673374707111647</v>
       </c>
       <c r="I395">
-        <v>-0.0299999999999998</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="J395">
-        <v>-0.2732165925075352</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K395">
         <v>1.34</v>
       </c>
       <c r="L395">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="M395">
         <v>1.34</v>
       </c>
       <c r="N395">
+        <v>1.94</v>
+      </c>
+      <c r="O395">
+        <v>1</v>
+      </c>
+      <c r="P395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16">
+      <c r="A396" s="1">
+        <v>0</v>
+      </c>
+      <c r="B396" t="s">
+        <v>83</v>
+      </c>
+      <c r="C396">
+        <v>2.310948171745637</v>
+      </c>
+      <c r="D396" t="s">
+        <v>215</v>
+      </c>
+      <c r="E396">
+        <v>2.270948171745637</v>
+      </c>
+      <c r="F396">
+        <v>1</v>
+      </c>
+      <c r="G396">
+        <v>0.001649051828254363</v>
+      </c>
+      <c r="H396">
+        <v>0.001609051828254363</v>
+      </c>
+      <c r="I396">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J396">
+        <v>-0.2469762475713705</v>
+      </c>
+      <c r="K396">
+        <v>1.34</v>
+      </c>
+      <c r="L396">
         <v>1.98</v>
       </c>
-      <c r="O395">
-        <v>1</v>
-      </c>
-      <c r="P395" t="s">
+      <c r="M396">
+        <v>1.34</v>
+      </c>
+      <c r="N396">
+        <v>1.94</v>
+      </c>
+      <c r="O396">
+        <v>1</v>
+      </c>
+      <c r="P396" t="s">
         <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16">
+      <c r="A397" s="1">
+        <v>0</v>
+      </c>
+      <c r="B397" t="s">
+        <v>83</v>
+      </c>
+      <c r="C397">
+        <v>2.346110233960097</v>
+      </c>
+      <c r="D397" t="s">
+        <v>215</v>
+      </c>
+      <c r="E397">
+        <v>2.306110233960097</v>
+      </c>
+      <c r="F397">
+        <v>1</v>
+      </c>
+      <c r="G397">
+        <v>0.001613889766039903</v>
+      </c>
+      <c r="H397">
+        <v>0.001573889766039903</v>
+      </c>
+      <c r="I397">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="J397">
+        <v>-0.2732165925075352</v>
+      </c>
+      <c r="K397">
+        <v>1.34</v>
+      </c>
+      <c r="L397">
+        <v>1.98</v>
+      </c>
+      <c r="M397">
+        <v>1.34</v>
+      </c>
+      <c r="N397">
+        <v>1.94</v>
+      </c>
+      <c r="O397">
+        <v>1</v>
+      </c>
+      <c r="P397" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="403">
   <si>
     <t>trade_time</t>
   </si>
@@ -262,10 +262,7 @@
     <t>2020-10-28</t>
   </si>
   <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-04-09</t>
@@ -274,6 +271,9 @@
     <t>2021-07-20</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2016-04-13</t>
   </si>
   <si>
@@ -658,10 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-02-22</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1195,6 +1192,12 @@
     <t>2021-04-08</t>
   </si>
   <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
     <t>2021-04-20</t>
   </si>
   <si>
@@ -1205,6 +1208,9 @@
   </si>
   <si>
     <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1574,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P397"/>
+  <dimension ref="A1:P396"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1671,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1721,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1771,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1821,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1871,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1921,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1971,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2021,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2071,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2121,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2171,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2221,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2271,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2321,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2371,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2421,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2471,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2521,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2571,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2621,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2671,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2721,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2771,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2821,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2871,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2921,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2971,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3021,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3071,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3121,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3171,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3221,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3271,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3321,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3371,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3421,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3471,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3521,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3571,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3621,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3671,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3721,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3771,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3821,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3871,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3921,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3971,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4021,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4071,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4121,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4171,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4221,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4271,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4321,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4371,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4421,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4471,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4521,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4571,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4621,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4671,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4721,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4771,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4821,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4871,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4921,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4971,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5021,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5071,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5121,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5171,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5221,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5271,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5321,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5371,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5421,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5471,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5521,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5571,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5621,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5671,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5721,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5771,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5821,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5871,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5921,7 +5927,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5971,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6021,7 +6027,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6071,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6121,7 +6127,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6171,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6271,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6321,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6371,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6421,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6471,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6521,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6571,7 +6577,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6621,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6671,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6721,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6771,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6821,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6871,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6921,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6971,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7021,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7071,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7121,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7171,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7221,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7271,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7321,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7371,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7421,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7471,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7521,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7571,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7621,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7671,7 +7677,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7721,7 +7727,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7771,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7821,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7871,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7921,7 +7927,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7971,7 +7977,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8021,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8071,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8121,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8171,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8671,7 +8677,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8821,7 +8827,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8921,7 +8927,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8971,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9021,7 +9027,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9071,7 +9077,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9121,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9171,7 +9177,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9221,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9271,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9321,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9371,7 +9377,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9421,7 +9427,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9471,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9521,7 +9527,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9571,7 +9577,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9621,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9671,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9721,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9771,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9821,7 +9827,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9871,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9921,7 +9927,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9971,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10021,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10071,7 +10077,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10121,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10221,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10271,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10371,7 +10377,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10421,7 +10427,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10471,7 +10477,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10521,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10571,7 +10577,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10621,7 +10627,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10671,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10721,7 +10727,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10771,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10821,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10871,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10971,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11021,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11071,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11121,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11171,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11221,7 +11227,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11271,7 +11277,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11321,7 +11327,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11371,7 +11377,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11421,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11471,7 +11477,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11521,7 +11527,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11571,7 +11577,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11621,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11671,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11721,7 +11727,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11771,7 +11777,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11821,7 +11827,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11871,7 +11877,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11921,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11971,7 +11977,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12021,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12071,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12121,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12171,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12221,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12271,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12321,7 +12327,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12371,7 +12377,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12421,7 +12427,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12471,7 +12477,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12521,7 +12527,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12571,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12621,7 +12627,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12671,7 +12677,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12721,7 +12727,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12771,7 +12777,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12821,7 +12827,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12871,7 +12877,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12921,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12971,7 +12977,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13021,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13071,7 +13077,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13121,7 +13127,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13171,7 +13177,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13221,7 +13227,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13271,7 +13277,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13321,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13371,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13421,7 +13427,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13471,7 +13477,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13521,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13571,7 +13577,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13621,7 +13627,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13671,7 +13677,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13721,7 +13727,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13771,7 +13777,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13821,7 +13827,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13871,7 +13877,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13921,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13971,7 +13977,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14021,7 +14027,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14071,7 +14077,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14121,7 +14127,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14171,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14221,7 +14227,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14271,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14321,7 +14327,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14371,7 +14377,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14421,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14471,7 +14477,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14521,7 +14527,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14571,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14621,7 +14627,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14671,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14721,7 +14727,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14821,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14871,7 +14877,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14921,7 +14927,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14971,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15021,7 +15027,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15071,7 +15077,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15121,7 +15127,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15171,7 +15177,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15221,7 +15227,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15271,7 +15277,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15321,7 +15327,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15371,7 +15377,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15421,7 +15427,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15471,7 +15477,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15521,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15571,7 +15577,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15621,7 +15627,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15671,7 +15677,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15721,7 +15727,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15771,7 +15777,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15821,7 +15827,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15871,7 +15877,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15921,7 +15927,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15971,7 +15977,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16021,7 +16027,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16071,7 +16077,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16121,7 +16127,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16171,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16221,7 +16227,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16271,7 +16277,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16321,7 +16327,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16371,7 +16377,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16421,7 +16427,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16471,7 +16477,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16521,7 +16527,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16571,7 +16577,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16621,7 +16627,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16671,7 +16677,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16721,7 +16727,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16771,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16821,7 +16827,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16871,7 +16877,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16921,7 +16927,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16971,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17021,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17071,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17121,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17171,7 +17177,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17221,7 +17227,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17271,7 +17277,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17321,7 +17327,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17371,7 +17377,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17421,7 +17427,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17471,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17521,7 +17527,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17571,7 +17577,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17621,7 +17627,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17671,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17721,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17771,7 +17777,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17821,7 +17827,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17871,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17921,7 +17927,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17971,7 +17977,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18021,7 +18027,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18071,7 +18077,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18121,7 +18127,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18171,7 +18177,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18221,7 +18227,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18271,7 +18277,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18321,7 +18327,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18371,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18421,7 +18427,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18621,7 +18627,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18671,7 +18677,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18721,7 +18727,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18771,7 +18777,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18821,7 +18827,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19071,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19121,7 +19127,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19171,7 +19177,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19271,7 +19277,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19321,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19371,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19421,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19571,7 +19577,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19621,7 +19627,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19671,7 +19677,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19771,7 +19777,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19821,7 +19827,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19871,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19921,7 +19927,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19971,7 +19977,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20021,7 +20027,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20071,7 +20077,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20121,7 +20127,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20171,7 +20177,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20221,7 +20227,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20271,7 +20277,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20321,7 +20327,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20421,7 +20427,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20432,90 +20438,90 @@
         <v>82</v>
       </c>
       <c r="C378">
-        <v>1.755766974015088</v>
+        <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
         <v>214</v>
       </c>
       <c r="E378">
-        <v>1.917324392288349</v>
+        <v>1.685805532271584</v>
       </c>
       <c r="F378">
         <v>1</v>
       </c>
       <c r="G378">
-        <v>0.002224233025984912</v>
+        <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002442675607711651</v>
+        <v>0.002134194467728415</v>
       </c>
       <c r="I378">
-        <v>0.1615574182732609</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
       </c>
       <c r="K378">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L378">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N378">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="379" spans="1:16">
       <c r="A379" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B379" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C379">
-        <v>1.755805532271584</v>
+        <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E379">
-        <v>1.715805532271584</v>
+        <v>1.716457690093673</v>
       </c>
       <c r="F379">
         <v>1</v>
       </c>
       <c r="G379">
-        <v>0.002204194467728416</v>
+        <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002164194467728416</v>
+        <v>0.002103542309906327</v>
       </c>
       <c r="I379">
-        <v>-0.04000000000000004</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="J379">
-        <v>0.1673093042749371</v>
+        <v>0.1444345596315869</v>
       </c>
       <c r="K379">
         <v>1.34</v>
       </c>
       <c r="L379">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="M379">
         <v>1.34</v>
       </c>
       <c r="N379">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20532,40 +20538,40 @@
         <v>82</v>
       </c>
       <c r="C380">
-        <v>1.787791616515778</v>
+        <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
         <v>214</v>
       </c>
       <c r="E380">
-        <v>1.953237741378409</v>
+        <v>1.798184678688128</v>
       </c>
       <c r="F380">
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.002192208383484222</v>
+        <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002406762258621592</v>
+        <v>0.002021815321311872</v>
       </c>
       <c r="I380">
-        <v>0.1654461248626304</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="J380">
-        <v>0.1444345596315869</v>
+        <v>0.0834442696357255</v>
       </c>
       <c r="K380">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L380">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N380">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20576,52 +20582,52 @@
     </row>
     <row r="381" spans="1:16">
       <c r="A381" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B381" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C381">
-        <v>1.786457690093674</v>
+        <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E381">
-        <v>1.746457690093673</v>
+        <v>1.777063128376992</v>
       </c>
       <c r="F381">
         <v>1</v>
       </c>
       <c r="G381">
-        <v>0.002173542309906327</v>
+        <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002133542309906327</v>
+        <v>0.002042936871623008</v>
       </c>
       <c r="I381">
-        <v>-0.04000000000000004</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="J381">
-        <v>0.1444345596315869</v>
+        <v>0.09920662061418481</v>
       </c>
       <c r="K381">
         <v>1.34</v>
       </c>
       <c r="L381">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="M381">
         <v>1.34</v>
       </c>
       <c r="N381">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20632,96 +20638,96 @@
         <v>82</v>
       </c>
       <c r="C382">
-        <v>1.873178022509984</v>
+        <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
         <v>214</v>
       </c>
       <c r="E382">
-        <v>2.048992496671911</v>
+        <v>1.67685001192274</v>
       </c>
       <c r="F382">
         <v>1</v>
       </c>
       <c r="G382">
-        <v>0.002106821977490016</v>
+        <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002311007503328089</v>
+        <v>0.00214314998807726</v>
       </c>
       <c r="I382">
-        <v>0.175814474161927</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="J382">
-        <v>0.0834442696357255</v>
+        <v>0.1739925284158654</v>
       </c>
       <c r="K382">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="L382">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N382">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>389</v>
+        <v>212</v>
       </c>
     </row>
     <row r="383" spans="1:16">
       <c r="A383" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B383" t="s">
         <v>83</v>
       </c>
       <c r="C383">
-        <v>1.868184678688128</v>
+        <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
         <v>215</v>
       </c>
       <c r="E383">
-        <v>1.828184678688128</v>
+        <v>0.7959503213647137</v>
       </c>
       <c r="F383">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G383">
-        <v>0.002091815321311872</v>
+        <v>0.003624049678635286</v>
       </c>
       <c r="H383">
-        <v>0.002051815321311872</v>
+        <v>0.003504049678635286</v>
       </c>
       <c r="I383">
-        <v>-0.04000000000000004</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="J383">
-        <v>0.0834442696357255</v>
+        <v>0.8735804378292169</v>
       </c>
       <c r="K383">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="L383">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="M383">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="N383">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="O383">
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20729,99 +20735,99 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C384">
-        <v>1.851110731140141</v>
+        <v>0.8094230769230786</v>
       </c>
       <c r="D384" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E384">
-        <v>2.02424560563573</v>
+        <v>0.6894230769230785</v>
       </c>
       <c r="F384">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.002128889268859859</v>
+        <v>0.003730576923076922</v>
       </c>
       <c r="H384">
-        <v>0.00233575439436427</v>
+        <v>0.003610576923076922</v>
       </c>
       <c r="I384">
-        <v>0.1731348744955887</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="J384">
-        <v>0.09920662061418481</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K384">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="L384">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="M384">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="N384">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O384">
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="385" spans="1:16">
       <c r="A385" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C385">
-        <v>1.847063128376992</v>
+        <v>0.5536378221197245</v>
       </c>
       <c r="D385" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E385">
-        <v>1.807063128376992</v>
+        <v>0.4181700591597324</v>
       </c>
       <c r="F385">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.002112936871623007</v>
+        <v>0.003626362177880275</v>
       </c>
       <c r="H385">
-        <v>0.002072936871623007</v>
+        <v>0.003401829940840267</v>
       </c>
       <c r="I385">
-        <v>-0.04000000000000004</v>
+        <v>0.1354677629599921</v>
       </c>
       <c r="J385">
-        <v>0.09920662061418481</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K385">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L385">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="M385">
         <v>1.34</v>
       </c>
       <c r="N385">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20829,99 +20835,99 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C386">
-        <v>1.746410460217788</v>
+        <v>0.5314031526074197</v>
       </c>
       <c r="D386" t="s">
         <v>214</v>
       </c>
       <c r="E386">
-        <v>1.906831730387091</v>
+        <v>0.3965798728216972</v>
       </c>
       <c r="F386">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G386">
-        <v>0.002233589539782212</v>
+        <v>0.00364859684739258</v>
       </c>
       <c r="H386">
-        <v>0.002453168269612909</v>
+        <v>0.003423420127178303</v>
       </c>
       <c r="I386">
-        <v>0.1604212701693031</v>
+        <v>0.1348232797857225</v>
       </c>
       <c r="J386">
-        <v>0.1739925284158654</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K386">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="L386">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="M386">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="N386">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="O386">
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>212</v>
+        <v>393</v>
       </c>
     </row>
     <row r="387" spans="1:16">
       <c r="A387" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C387">
-        <v>1.74685001192274</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D387" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E387">
-        <v>1.70685001192274</v>
+        <v>0.381412158927718</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.00221314998807726</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H387">
-        <v>0.002173149988077259</v>
+        <v>0.003438587841072282</v>
       </c>
       <c r="I387">
-        <v>-0.04000000000000004</v>
+        <v>0.1343705122067977</v>
       </c>
       <c r="J387">
-        <v>0.1739925284158654</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K387">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L387">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="M387">
         <v>1.34</v>
       </c>
       <c r="N387">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O387">
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>212</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20932,46 +20938,46 @@
         <v>84</v>
       </c>
       <c r="C388">
-        <v>0.9159503213647138</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D388" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E388">
-        <v>0.7959503213647137</v>
+        <v>0.3599907056193337</v>
       </c>
       <c r="F388">
         <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.003624049678635286</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H388">
-        <v>0.003504049678635286</v>
+        <v>0.003460009294380666</v>
       </c>
       <c r="I388">
-        <v>0.1200000000000001</v>
+        <v>0.1337310658393833</v>
       </c>
       <c r="J388">
-        <v>0.8735804378292169</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K388">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="L388">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="M388">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="N388">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O388">
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20982,46 +20988,46 @@
         <v>84</v>
       </c>
       <c r="C389">
-        <v>0.8094230769230786</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D389" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E389">
-        <v>0.6894230769230785</v>
+        <v>0.3087077350920742</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.003730576923076922</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H389">
-        <v>0.003610576923076922</v>
+        <v>0.003511292264907926</v>
       </c>
       <c r="I389">
-        <v>0.1200000000000001</v>
+        <v>0.132200230898271</v>
       </c>
       <c r="J389">
-        <v>0.9423076923076913</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K389">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="L389">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="M389">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="N389">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21029,31 +21035,31 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C390">
-        <v>0.5157826711345157</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D390" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E390">
-        <v>0.411412158927718</v>
+        <v>0.3111953138837595</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003664217328865484</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H390">
-        <v>0.003468587841072282</v>
+        <v>0.003508804686116241</v>
       </c>
       <c r="I390">
-        <v>0.1043705122067977</v>
+        <v>0.132274486981605</v>
       </c>
       <c r="J390">
-        <v>1.140737194830061</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K390">
         <v>1.38</v>
@@ -21065,13 +21071,13 @@
         <v>1.34</v>
       </c>
       <c r="N390">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21079,31 +21085,31 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C391">
-        <v>0.493721771458717</v>
+        <v>0.4483932592798776</v>
       </c>
       <c r="D391" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E391">
-        <v>0.3899907056193337</v>
+        <v>0.3159760633587216</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003686278228541283</v>
+        <v>0.003731606740720122</v>
       </c>
       <c r="H391">
-        <v>0.003490009294380666</v>
+        <v>0.003504023936641279</v>
       </c>
       <c r="I391">
-        <v>0.1037310658393833</v>
+        <v>0.132417195921156</v>
       </c>
       <c r="J391">
-        <v>1.156723354015422</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K391">
         <v>1.38</v>
@@ -21115,13 +21121,13 @@
         <v>1.34</v>
       </c>
       <c r="N391">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21129,49 +21135,49 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C392">
-        <v>0.4409079659903452</v>
+        <v>2.068444260870803</v>
       </c>
       <c r="D392" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E392">
-        <v>0.3387077350920742</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="F392">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G392">
-        <v>0.003739092034009655</v>
+        <v>0.001811555739129197</v>
       </c>
       <c r="H392">
-        <v>0.003541292264907926</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="I392">
-        <v>0.102200230898271</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J392">
-        <v>1.194994227543228</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K392">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L392">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M392">
         <v>1.34</v>
       </c>
       <c r="N392">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21179,99 +21185,99 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C393">
-        <v>0.4434698008653646</v>
+        <v>2.206625292888353</v>
       </c>
       <c r="D393" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E393">
-        <v>0.3411953138837596</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="F393">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G393">
-        <v>0.003736530199134635</v>
+        <v>0.001673374707111647</v>
       </c>
       <c r="H393">
-        <v>0.00353880468611624</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="I393">
-        <v>0.102274486981605</v>
+        <v>-0.03000000000000025</v>
       </c>
       <c r="J393">
-        <v>1.193137825459881</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K393">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L393">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M393">
         <v>1.34</v>
       </c>
       <c r="N393">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="394" spans="1:16">
       <c r="A394" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B394" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C394">
-        <v>2.108444260870803</v>
+        <v>2.216625292888353</v>
       </c>
       <c r="D394" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E394">
-        <v>2.068444260870803</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="F394">
         <v>1</v>
       </c>
       <c r="G394">
-        <v>0.001851555739129197</v>
+        <v>0.001683374707111647</v>
       </c>
       <c r="H394">
-        <v>0.001811555739129197</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="I394">
         <v>-0.04000000000000004</v>
       </c>
       <c r="J394">
-        <v>-0.0958539260229872</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K394">
         <v>1.34</v>
       </c>
       <c r="L394">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M394">
         <v>1.34</v>
       </c>
       <c r="N394">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21279,49 +21285,49 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C395">
-        <v>2.246625292888353</v>
+        <v>2.270948171745637</v>
       </c>
       <c r="D395" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E395">
-        <v>2.206625292888353</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001713374707111647</v>
+        <v>0.001609051828254363</v>
       </c>
       <c r="H395">
-        <v>0.001673374707111647</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="I395">
-        <v>-0.04000000000000004</v>
+        <v>-0.03000000000000025</v>
       </c>
       <c r="J395">
-        <v>-0.1989740991704129</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K395">
         <v>1.34</v>
       </c>
       <c r="L395">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="M395">
         <v>1.34</v>
       </c>
       <c r="N395">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21329,99 +21335,49 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C396">
-        <v>2.310948171745637</v>
+        <v>2.306110233960097</v>
       </c>
       <c r="D396" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E396">
-        <v>2.270948171745637</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="F396">
         <v>1</v>
       </c>
       <c r="G396">
-        <v>0.001649051828254363</v>
+        <v>0.001573889766039903</v>
       </c>
       <c r="H396">
-        <v>0.001609051828254363</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="I396">
-        <v>-0.04000000000000004</v>
+        <v>-0.0299999999999998</v>
       </c>
       <c r="J396">
-        <v>-0.2469762475713705</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K396">
         <v>1.34</v>
       </c>
       <c r="L396">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="M396">
         <v>1.34</v>
       </c>
       <c r="N396">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O396">
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="397" spans="1:16">
-      <c r="A397" s="1">
-        <v>0</v>
-      </c>
-      <c r="B397" t="s">
-        <v>83</v>
-      </c>
-      <c r="C397">
-        <v>2.346110233960097</v>
-      </c>
-      <c r="D397" t="s">
-        <v>215</v>
-      </c>
-      <c r="E397">
-        <v>2.306110233960097</v>
-      </c>
-      <c r="F397">
-        <v>1</v>
-      </c>
-      <c r="G397">
-        <v>0.001613889766039903</v>
-      </c>
-      <c r="H397">
-        <v>0.001573889766039903</v>
-      </c>
-      <c r="I397">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="J397">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K397">
-        <v>1.34</v>
-      </c>
-      <c r="L397">
-        <v>1.98</v>
-      </c>
-      <c r="M397">
-        <v>1.34</v>
-      </c>
-      <c r="N397">
-        <v>1.94</v>
-      </c>
-      <c r="O397">
-        <v>1</v>
-      </c>
-      <c r="P397" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -271,7 +271,7 @@
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-08-03</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2016-04-13</t>
@@ -658,7 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -20444,7 +20444,7 @@
         <v>214</v>
       </c>
       <c r="E378">
-        <v>1.685805532271584</v>
+        <v>1.705805532271584</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20453,10 +20453,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002134194467728415</v>
+        <v>0.002154194467728415</v>
       </c>
       <c r="I378">
-        <v>-0.0299999999999998</v>
+        <v>-0.009999999999999787</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20471,7 +20471,7 @@
         <v>1.34</v>
       </c>
       <c r="N378">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O378">
         <v>1</v>
@@ -20494,7 +20494,7 @@
         <v>214</v>
       </c>
       <c r="E379">
-        <v>1.716457690093673</v>
+        <v>1.736457690093673</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20503,10 +20503,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002103542309906327</v>
+        <v>0.002123542309906326</v>
       </c>
       <c r="I379">
-        <v>-0.03000000000000003</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20521,7 +20521,7 @@
         <v>1.34</v>
       </c>
       <c r="N379">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20544,7 +20544,7 @@
         <v>214</v>
       </c>
       <c r="E380">
-        <v>1.798184678688128</v>
+        <v>1.818184678688128</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20553,10 +20553,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002021815321311872</v>
+        <v>0.002041815321311872</v>
       </c>
       <c r="I380">
-        <v>-0.03000000000000003</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20571,7 +20571,7 @@
         <v>1.34</v>
       </c>
       <c r="N380">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20594,7 +20594,7 @@
         <v>214</v>
       </c>
       <c r="E381">
-        <v>1.777063128376992</v>
+        <v>1.797063128376992</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20603,10 +20603,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002042936871623008</v>
+        <v>0.002062936871623008</v>
       </c>
       <c r="I381">
-        <v>-0.03000000000000003</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20621,7 +20621,7 @@
         <v>1.34</v>
       </c>
       <c r="N381">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20644,7 +20644,7 @@
         <v>214</v>
       </c>
       <c r="E382">
-        <v>1.67685001192274</v>
+        <v>1.69685001192274</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20653,10 +20653,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.00214314998807726</v>
+        <v>0.00216314998807726</v>
       </c>
       <c r="I382">
-        <v>-0.03000000000000003</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20671,7 +20671,7 @@
         <v>1.34</v>
       </c>
       <c r="N382">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20791,7 +20791,7 @@
         <v>0.5536378221197245</v>
       </c>
       <c r="D385" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="E385">
         <v>0.4181700591597324</v>
@@ -20841,7 +20841,7 @@
         <v>0.5314031526074197</v>
       </c>
       <c r="D386" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="E386">
         <v>0.3965798728216972</v>
@@ -20891,7 +20891,7 @@
         <v>0.5157826711345157</v>
       </c>
       <c r="D387" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="E387">
         <v>0.381412158927718</v>
@@ -20941,7 +20941,7 @@
         <v>0.493721771458717</v>
       </c>
       <c r="D388" t="s">
-        <v>214</v>
+        <v>85</v>
       </c>
       <c r="E388">
         <v>0.3599907056193337</v>
@@ -20994,7 +20994,7 @@
         <v>214</v>
       </c>
       <c r="E389">
-        <v>0.3087077350920742</v>
+        <v>0.3287077350920742</v>
       </c>
       <c r="F389">
         <v>-1</v>
@@ -21003,10 +21003,10 @@
         <v>0.003739092034009655</v>
       </c>
       <c r="H389">
-        <v>0.003511292264907926</v>
+        <v>0.003531292264907926</v>
       </c>
       <c r="I389">
-        <v>0.132200230898271</v>
+        <v>0.112200230898271</v>
       </c>
       <c r="J389">
         <v>1.194994227543228</v>
@@ -21021,7 +21021,7 @@
         <v>1.34</v>
       </c>
       <c r="N389">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O389">
         <v>1</v>
@@ -21044,7 +21044,7 @@
         <v>214</v>
       </c>
       <c r="E390">
-        <v>0.3111953138837595</v>
+        <v>0.3311953138837596</v>
       </c>
       <c r="F390">
         <v>-1</v>
@@ -21053,10 +21053,10 @@
         <v>0.003736530199134635</v>
       </c>
       <c r="H390">
-        <v>0.003508804686116241</v>
+        <v>0.00352880468611624</v>
       </c>
       <c r="I390">
-        <v>0.132274486981605</v>
+        <v>0.112274486981605</v>
       </c>
       <c r="J390">
         <v>1.193137825459881</v>
@@ -21071,7 +21071,7 @@
         <v>1.34</v>
       </c>
       <c r="N390">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21094,7 +21094,7 @@
         <v>214</v>
       </c>
       <c r="E391">
-        <v>0.3159760633587216</v>
+        <v>0.3359760633587217</v>
       </c>
       <c r="F391">
         <v>-1</v>
@@ -21103,10 +21103,10 @@
         <v>0.003731606740720122</v>
       </c>
       <c r="H391">
-        <v>0.003504023936641279</v>
+        <v>0.003524023936641278</v>
       </c>
       <c r="I391">
-        <v>0.132417195921156</v>
+        <v>0.112417195921156</v>
       </c>
       <c r="J391">
         <v>1.189570101971103</v>
@@ -21121,7 +21121,7 @@
         <v>1.34</v>
       </c>
       <c r="N391">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O391">
         <v>1</v>
@@ -21144,7 +21144,7 @@
         <v>214</v>
       </c>
       <c r="E392">
-        <v>2.038444260870803</v>
+        <v>2.058444260870803</v>
       </c>
       <c r="F392">
         <v>1</v>
@@ -21153,10 +21153,10 @@
         <v>0.001811555739129197</v>
       </c>
       <c r="H392">
-        <v>0.001781555739129197</v>
+        <v>0.001801555739129197</v>
       </c>
       <c r="I392">
-        <v>-0.0299999999999998</v>
+        <v>-0.009999999999999787</v>
       </c>
       <c r="J392">
         <v>-0.0958539260229872</v>
@@ -21171,7 +21171,7 @@
         <v>1.34</v>
       </c>
       <c r="N392">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21182,81 +21182,81 @@
     </row>
     <row r="393" spans="1:16">
       <c r="A393" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B393" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C393">
-        <v>2.206625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D393" t="s">
         <v>214</v>
       </c>
       <c r="E393">
-        <v>2.176625292888353</v>
+        <v>2.058444260870803</v>
       </c>
       <c r="F393">
         <v>1</v>
       </c>
       <c r="G393">
-        <v>0.001673374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H393">
-        <v>0.001643374707111647</v>
+        <v>0.001801555739129197</v>
       </c>
       <c r="I393">
-        <v>-0.03000000000000025</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="J393">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K393">
         <v>1.34</v>
       </c>
       <c r="L393">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="M393">
         <v>1.34</v>
       </c>
       <c r="N393">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="394" spans="1:16">
       <c r="A394" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B394" t="s">
         <v>85</v>
       </c>
       <c r="C394">
-        <v>2.216625292888353</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D394" t="s">
         <v>214</v>
       </c>
       <c r="E394">
-        <v>2.176625292888353</v>
+        <v>2.196625292888353</v>
       </c>
       <c r="F394">
         <v>1</v>
       </c>
       <c r="G394">
-        <v>0.001683374707111647</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H394">
-        <v>0.001643374707111647</v>
+        <v>0.001663374707111647</v>
       </c>
       <c r="I394">
-        <v>-0.04000000000000004</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="J394">
         <v>-0.1989740991704129</v>
@@ -21265,13 +21265,13 @@
         <v>1.34</v>
       </c>
       <c r="L394">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="M394">
         <v>1.34</v>
       </c>
       <c r="N394">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O394">
         <v>1</v>
@@ -21285,28 +21285,28 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C395">
-        <v>2.270948171745637</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D395" t="s">
         <v>214</v>
       </c>
       <c r="E395">
-        <v>2.240948171745636</v>
+        <v>2.260948171745636</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001609051828254363</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H395">
-        <v>0.001579051828254363</v>
+        <v>0.001599051828254364</v>
       </c>
       <c r="I395">
-        <v>-0.03000000000000025</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="J395">
         <v>-0.2469762475713705</v>
@@ -21315,13 +21315,13 @@
         <v>1.34</v>
       </c>
       <c r="L395">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="M395">
         <v>1.34</v>
       </c>
       <c r="N395">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O395">
         <v>1</v>
@@ -21335,28 +21335,28 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C396">
-        <v>2.306110233960097</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D396" t="s">
         <v>214</v>
       </c>
       <c r="E396">
-        <v>2.276110233960097</v>
+        <v>2.296110233960097</v>
       </c>
       <c r="F396">
         <v>1</v>
       </c>
       <c r="G396">
-        <v>0.001573889766039903</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H396">
-        <v>0.001543889766039903</v>
+        <v>0.001563889766039903</v>
       </c>
       <c r="I396">
-        <v>-0.0299999999999998</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="J396">
         <v>-0.2732165925075352</v>
@@ -21365,13 +21365,13 @@
         <v>1.34</v>
       </c>
       <c r="L396">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="M396">
         <v>1.34</v>
       </c>
       <c r="N396">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O396">
         <v>1</v>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="405">
   <si>
     <t>trade_time</t>
   </si>
@@ -268,6 +268,9 @@
     <t>2021-04-09</t>
   </si>
   <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
     <t>2021-07-20</t>
   </si>
   <si>
@@ -658,12 +661,15 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-05</t>
+    <t>2021-08-09</t>
   </si>
   <si>
     <t>2021-04-26</t>
   </si>
   <si>
+    <t>2021-06-11</t>
+  </si>
+  <si>
     <t>2016-02-15</t>
   </si>
   <si>
@@ -1192,6 +1198,9 @@
     <t>2021-04-08</t>
   </si>
   <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
     <t>2021-04-16</t>
   </si>
   <si>
@@ -1217,9 +1226,6 @@
   </si>
   <si>
     <t>2021-06-07</t>
-  </si>
-  <si>
-    <t>2021-06-11</t>
   </si>
   <si>
     <t>2021-06-15</t>
@@ -1580,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P396"/>
+  <dimension ref="A1:P397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1641,7 +1647,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1677,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1691,7 +1697,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1727,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1777,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1827,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1841,7 +1847,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1877,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1891,7 +1897,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1927,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1941,7 +1947,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1977,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1991,7 +1997,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2027,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2041,7 +2047,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2077,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2091,7 +2097,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2127,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2141,7 +2147,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2177,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2191,7 +2197,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2227,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2241,7 +2247,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2277,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2291,7 +2297,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2327,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2341,7 +2347,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2377,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2391,7 +2397,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2427,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2441,7 +2447,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2477,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2491,7 +2497,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2527,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2541,7 +2547,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2577,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2591,7 +2597,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2627,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2641,7 +2647,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2677,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2691,7 +2697,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2727,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2741,7 +2747,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2777,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2791,7 +2797,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2827,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2841,7 +2847,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2877,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2891,7 +2897,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2927,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2941,7 +2947,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2977,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2991,7 +2997,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3027,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3041,7 +3047,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3077,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3091,7 +3097,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3127,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3141,7 +3147,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3177,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3191,7 +3197,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3227,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3241,7 +3247,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3277,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3291,7 +3297,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3327,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3341,7 +3347,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3377,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3391,7 +3397,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3427,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,7 +3447,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3477,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3491,7 +3497,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3527,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3541,7 +3547,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3577,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3591,7 +3597,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3627,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3641,7 +3647,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3677,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3691,7 +3697,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3727,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3741,7 +3747,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3777,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3791,7 +3797,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3827,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3841,7 +3847,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3877,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3891,7 +3897,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3927,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3941,7 +3947,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3977,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3991,7 +3997,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4027,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4041,7 +4047,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4077,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4091,7 +4097,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4127,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4141,7 +4147,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4177,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4191,7 +4197,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4227,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4241,7 +4247,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4277,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4291,7 +4297,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4327,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4341,7 +4347,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4377,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4391,7 +4397,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4427,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4441,7 +4447,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4477,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4491,7 +4497,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4527,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4541,7 +4547,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4577,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4591,7 +4597,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4627,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4641,7 +4647,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4677,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4691,7 +4697,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4727,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4741,7 +4747,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4777,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4791,7 +4797,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4827,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4841,7 +4847,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4877,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4891,7 +4897,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4927,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4941,7 +4947,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4977,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4991,7 +4997,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5027,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5041,7 +5047,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5077,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5091,7 +5097,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5127,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5141,7 +5147,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5177,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5191,7 +5197,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5227,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5241,7 +5247,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5277,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5291,7 +5297,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5327,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5341,7 +5347,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5377,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5391,7 +5397,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5427,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5441,7 +5447,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5477,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5491,7 +5497,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5527,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5541,7 +5547,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5577,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5591,7 +5597,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5627,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5641,7 +5647,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5677,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5691,7 +5697,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5727,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5741,7 +5747,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5777,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5791,7 +5797,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5827,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5841,7 +5847,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5877,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5891,7 +5897,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5927,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5941,7 +5947,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5977,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5991,7 +5997,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6027,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6041,7 +6047,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6077,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6091,7 +6097,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6127,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6141,7 +6147,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6177,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6191,7 +6197,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6241,7 +6247,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6277,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6291,7 +6297,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6327,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6341,7 +6347,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6377,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6391,7 +6397,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6427,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6441,7 +6447,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6477,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6491,7 +6497,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6527,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6541,7 +6547,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6577,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6591,7 +6597,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6627,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6641,7 +6647,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6677,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6691,7 +6697,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6727,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6741,7 +6747,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6777,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6791,7 +6797,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6827,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6841,7 +6847,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6877,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6891,7 +6897,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6927,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6941,7 +6947,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6977,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6991,7 +6997,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7027,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7041,7 +7047,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7077,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7091,7 +7097,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7127,7 +7133,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7141,7 +7147,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7177,7 +7183,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7191,7 +7197,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7227,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7241,7 +7247,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7277,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7291,7 +7297,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7327,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7341,7 +7347,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7377,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7391,7 +7397,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7427,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7441,7 +7447,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7477,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7491,7 +7497,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7527,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7541,7 +7547,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7577,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7591,7 +7597,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7627,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7641,7 +7647,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7677,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7691,7 +7697,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7727,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7741,7 +7747,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7777,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7791,7 +7797,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7827,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7841,7 +7847,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7877,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7891,7 +7897,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7927,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7941,7 +7947,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7977,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7991,7 +7997,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8027,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8041,7 +8047,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8077,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8091,7 +8097,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8127,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8141,7 +8147,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8177,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8191,7 +8197,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8227,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8241,7 +8247,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8277,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8291,7 +8297,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8327,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8341,7 +8347,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8377,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8391,7 +8397,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8427,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8441,7 +8447,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8477,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8491,7 +8497,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8527,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8541,7 +8547,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8577,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8591,7 +8597,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8627,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8641,7 +8647,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8677,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8691,7 +8697,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8727,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8741,7 +8747,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8777,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8791,7 +8797,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8827,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8841,7 +8847,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8877,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8891,7 +8897,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8927,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8941,7 +8947,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8977,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8991,7 +8997,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9027,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9041,7 +9047,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9077,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9091,7 +9097,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9127,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9141,7 +9147,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9177,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9191,7 +9197,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9227,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9241,7 +9247,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9277,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9291,7 +9297,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9327,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9341,7 +9347,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9377,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9391,7 +9397,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9427,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9441,7 +9447,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9477,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9491,7 +9497,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9527,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9541,7 +9547,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9577,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9591,7 +9597,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9627,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9641,7 +9647,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9677,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9691,7 +9697,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9727,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9741,7 +9747,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9777,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9791,7 +9797,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9827,7 +9833,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9841,7 +9847,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9877,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9891,7 +9897,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9927,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9941,7 +9947,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9977,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9991,7 +9997,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10027,7 +10033,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10041,7 +10047,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10077,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10091,7 +10097,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10127,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10141,7 +10147,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10191,7 +10197,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10227,7 +10233,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10241,7 +10247,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10277,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10291,7 +10297,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10327,7 +10333,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10341,7 +10347,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10377,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10391,7 +10397,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10427,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10441,7 +10447,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10477,7 +10483,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10491,7 +10497,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10527,7 +10533,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10541,7 +10547,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10577,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10591,7 +10597,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10627,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10641,7 +10647,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10677,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10691,7 +10697,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10727,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10777,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10827,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10877,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10927,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10941,7 +10947,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10977,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10991,7 +10997,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11027,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11041,7 +11047,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11077,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11091,7 +11097,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11127,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11141,7 +11147,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11177,7 +11183,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11191,7 +11197,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11227,7 +11233,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11241,7 +11247,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11277,7 +11283,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11291,7 +11297,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11327,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11341,7 +11347,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11377,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11391,7 +11397,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11427,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11441,7 +11447,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11477,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11491,7 +11497,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11527,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11541,7 +11547,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11577,7 +11583,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11591,7 +11597,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11627,7 +11633,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11641,7 +11647,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11677,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11691,7 +11697,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11727,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11741,7 +11747,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11777,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11791,7 +11797,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11827,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11841,7 +11847,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11877,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11891,7 +11897,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11927,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11941,7 +11947,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11977,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11991,7 +11997,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12027,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12041,7 +12047,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12077,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12091,7 +12097,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12127,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12141,7 +12147,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12177,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12191,7 +12197,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12227,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12241,7 +12247,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12277,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12291,7 +12297,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12327,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12341,7 +12347,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12377,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12391,7 +12397,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12427,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12441,7 +12447,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12477,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12491,7 +12497,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12527,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12541,7 +12547,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12577,7 +12583,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12591,7 +12597,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12627,7 +12633,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12641,7 +12647,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12677,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12691,7 +12697,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12727,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12741,7 +12747,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12777,7 +12783,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12791,7 +12797,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12827,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12841,7 +12847,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12877,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12891,7 +12897,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12927,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12941,7 +12947,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12977,7 +12983,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12991,7 +12997,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13027,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13041,7 +13047,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13077,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13091,7 +13097,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13127,7 +13133,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13141,7 +13147,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13177,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13191,7 +13197,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13227,7 +13233,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13241,7 +13247,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13277,7 +13283,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13291,7 +13297,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13327,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13341,7 +13347,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13377,7 +13383,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13391,7 +13397,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13427,7 +13433,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13441,7 +13447,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13477,7 +13483,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13491,7 +13497,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13527,7 +13533,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13541,7 +13547,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13577,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13591,7 +13597,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13627,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13641,7 +13647,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13677,7 +13683,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13691,7 +13697,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13727,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13741,7 +13747,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13777,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13791,7 +13797,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13827,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13841,7 +13847,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13877,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13891,7 +13897,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13927,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13941,7 +13947,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13977,7 +13983,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13991,7 +13997,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14027,7 +14033,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14041,7 +14047,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14077,7 +14083,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14091,7 +14097,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14127,7 +14133,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14141,7 +14147,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14177,7 +14183,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14191,7 +14197,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14227,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14241,7 +14247,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14277,7 +14283,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14291,7 +14297,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14327,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14341,7 +14347,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14377,7 +14383,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14391,7 +14397,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14427,7 +14433,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14441,7 +14447,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14477,7 +14483,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14491,7 +14497,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14527,7 +14533,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14541,7 +14547,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14577,7 +14583,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14591,7 +14597,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14627,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14641,7 +14647,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14677,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14691,7 +14697,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14727,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14741,7 +14747,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14827,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14841,7 +14847,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14877,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14891,7 +14897,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14927,7 +14933,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14941,7 +14947,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14977,7 +14983,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14991,7 +14997,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15027,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15041,7 +15047,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15077,7 +15083,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15091,7 +15097,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15127,7 +15133,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15141,7 +15147,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15177,7 +15183,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15191,7 +15197,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15227,7 +15233,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15241,7 +15247,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15277,7 +15283,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15291,7 +15297,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15327,7 +15333,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15341,7 +15347,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15377,7 +15383,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15391,7 +15397,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15427,7 +15433,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15441,7 +15447,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15477,7 +15483,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15491,7 +15497,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15527,7 +15533,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15541,7 +15547,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15577,7 +15583,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15591,7 +15597,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15627,7 +15633,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15641,7 +15647,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15677,7 +15683,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15691,7 +15697,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15727,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15741,7 +15747,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15777,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15827,7 +15833,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15877,7 +15883,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15891,7 +15897,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15927,7 +15933,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15941,7 +15947,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15977,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +15997,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16027,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16041,7 +16047,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16077,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16091,7 +16097,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16127,7 +16133,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16177,7 +16183,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16227,7 +16233,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16241,7 +16247,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16277,7 +16283,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16291,7 +16297,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16327,7 +16333,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16341,7 +16347,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16377,7 +16383,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16397,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16427,7 +16433,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16447,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16477,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16491,7 +16497,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16527,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16541,7 +16547,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16577,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16627,7 +16633,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16677,7 +16683,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16691,7 +16697,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16727,7 +16733,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16741,7 +16747,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16777,7 +16783,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16791,7 +16797,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16827,7 +16833,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16841,7 +16847,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16877,7 +16883,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16891,7 +16897,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16927,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16941,7 +16947,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16977,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16991,7 +16997,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17027,7 +17033,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17041,7 +17047,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17077,7 +17083,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17091,7 +17097,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17127,7 +17133,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17141,7 +17147,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17177,7 +17183,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17197,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17227,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17277,7 +17283,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17327,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17347,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17377,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17427,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17477,7 +17483,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17497,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17527,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17577,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17627,7 +17633,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17647,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17677,7 +17683,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17727,7 +17733,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17777,7 +17783,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17791,7 +17797,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17827,7 +17833,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17877,7 +17883,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17927,7 +17933,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17947,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17977,7 +17983,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18027,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18077,7 +18083,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18097,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18127,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18177,7 +18183,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18227,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18241,7 +18247,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18277,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18327,7 +18333,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18377,7 +18383,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18391,7 +18397,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18427,7 +18433,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18541,7 +18547,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18627,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18647,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18677,7 +18683,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18727,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18777,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18797,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18827,7 +18833,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18991,7 +18997,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19077,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19127,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19147,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19177,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19191,7 +19197,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19277,7 +19283,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19291,7 +19297,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19327,7 +19333,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19377,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19391,7 +19397,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19427,7 +19433,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19491,7 +19497,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19541,7 +19547,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19577,7 +19583,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19591,7 +19597,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19627,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19647,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19677,7 +19683,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19697,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19777,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,7 +19797,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19827,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19877,7 +19883,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19927,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,7 +19947,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19977,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,7 +19997,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20027,7 +20033,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20041,7 +20047,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20077,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20091,7 +20097,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20127,7 +20133,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20141,7 +20147,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20177,7 +20183,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20197,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20227,7 +20233,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20241,7 +20247,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20277,7 +20283,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20291,7 +20297,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20327,7 +20333,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20341,7 +20347,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20377,7 +20383,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20427,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20441,10 +20447,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E378">
-        <v>1.705805532271584</v>
+        <v>1.759113160100587</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20453,10 +20459,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002154194467728415</v>
+        <v>0.002220886839899414</v>
       </c>
       <c r="I378">
-        <v>-0.009999999999999787</v>
+        <v>0.04330762782900277</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20468,16 +20474,16 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N378">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20491,10 +20497,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E379">
-        <v>1.736457690093673</v>
+        <v>1.79068030770841</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20503,10 +20509,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002123542309906326</v>
+        <v>0.00218931969229159</v>
       </c>
       <c r="I379">
-        <v>-0.01000000000000001</v>
+        <v>0.04422261761473667</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20518,16 +20524,16 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N379">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20541,10 +20547,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E380">
-        <v>1.818184678688128</v>
+        <v>1.874846907902699</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20553,10 +20559,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002041815321311872</v>
+        <v>0.002105153092097301</v>
       </c>
       <c r="I380">
-        <v>-0.01000000000000001</v>
+        <v>0.04666222921457108</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20568,16 +20574,16 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N380">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20591,10 +20597,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E381">
-        <v>1.797063128376992</v>
+        <v>1.853094863552425</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20603,10 +20609,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002062936871623008</v>
+        <v>0.002126905136447575</v>
       </c>
       <c r="I381">
-        <v>-0.01000000000000001</v>
+        <v>0.04603173517543269</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20618,16 +20624,16 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N381">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,10 +20647,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E382">
-        <v>1.69685001192274</v>
+        <v>1.749890310786106</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20653,10 +20659,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.00216314998807726</v>
+        <v>0.002230109689213894</v>
       </c>
       <c r="I382">
-        <v>-0.01000000000000001</v>
+        <v>0.04304029886336536</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20668,16 +20674,16 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N382">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20691,7 +20697,7 @@
         <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E383">
         <v>0.7959503213647137</v>
@@ -20727,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20741,7 +20747,7 @@
         <v>0.8094230769230786</v>
       </c>
       <c r="D384" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E384">
         <v>0.6894230769230785</v>
@@ -20777,7 +20783,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20788,46 +20794,46 @@
         <v>84</v>
       </c>
       <c r="C385">
-        <v>0.5536378221197245</v>
+        <v>0.3546209695665004</v>
       </c>
       <c r="D385" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="E385">
-        <v>0.4181700591597324</v>
+        <v>0.4807514106088764</v>
       </c>
       <c r="F385">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G385">
-        <v>0.003626362177880275</v>
+        <v>0.0039653790304335</v>
       </c>
       <c r="H385">
-        <v>0.003401829940840267</v>
+        <v>0.003939248589391124</v>
       </c>
       <c r="I385">
-        <v>0.1354677629599921</v>
+        <v>0.126130441042376</v>
       </c>
       <c r="J385">
-        <v>1.1133059260002</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K385">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L385">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M385">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N385">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20838,78 +20844,78 @@
         <v>84</v>
       </c>
       <c r="C386">
-        <v>0.5314031526074197</v>
+        <v>0.3119121628396688</v>
       </c>
       <c r="D386" t="s">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="E386">
-        <v>0.3965798728216972</v>
+        <v>0.4398435776596825</v>
       </c>
       <c r="F386">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G386">
-        <v>0.00364859684739258</v>
+        <v>0.004008087837160332</v>
       </c>
       <c r="H386">
-        <v>0.003423420127178303</v>
+        <v>0.003980156422340318</v>
       </c>
       <c r="I386">
-        <v>0.1348232797857225</v>
+        <v>0.1279314148200137</v>
       </c>
       <c r="J386">
-        <v>1.129418005356942</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K386">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L386">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M386">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N386">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O386">
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="387" spans="1:16">
       <c r="A387" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B387" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C387">
-        <v>0.5157826711345157</v>
+        <v>0.5536378221197245</v>
       </c>
       <c r="D387" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E387">
-        <v>0.381412158927718</v>
+        <v>0.4181700591597324</v>
       </c>
       <c r="F387">
         <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.003664217328865484</v>
+        <v>0.003626362177880275</v>
       </c>
       <c r="H387">
-        <v>0.003438587841072282</v>
+        <v>0.003401829940840267</v>
       </c>
       <c r="I387">
-        <v>0.1343705122067977</v>
+        <v>0.1354677629599921</v>
       </c>
       <c r="J387">
-        <v>1.140737194830061</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K387">
         <v>1.38</v>
@@ -20927,7 +20933,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20935,31 +20941,31 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C388">
-        <v>0.493721771458717</v>
+        <v>0.5314031526074197</v>
       </c>
       <c r="D388" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E388">
-        <v>0.3599907056193337</v>
+        <v>0.3965798728216972</v>
       </c>
       <c r="F388">
         <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.003686278228541283</v>
+        <v>0.00364859684739258</v>
       </c>
       <c r="H388">
-        <v>0.003460009294380666</v>
+        <v>0.003423420127178303</v>
       </c>
       <c r="I388">
-        <v>0.1337310658393833</v>
+        <v>0.1348232797857225</v>
       </c>
       <c r="J388">
-        <v>1.156723354015422</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K388">
         <v>1.38</v>
@@ -20977,7 +20983,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20985,31 +20991,31 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C389">
-        <v>0.4409079659903452</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D389" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="E389">
-        <v>0.3287077350920742</v>
+        <v>0.381412158927718</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.003739092034009655</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H389">
-        <v>0.003531292264907926</v>
+        <v>0.003438587841072282</v>
       </c>
       <c r="I389">
-        <v>0.112200230898271</v>
+        <v>0.1343705122067977</v>
       </c>
       <c r="J389">
-        <v>1.194994227543228</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K389">
         <v>1.38</v>
@@ -21021,13 +21027,13 @@
         <v>1.34</v>
       </c>
       <c r="N389">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21035,31 +21041,31 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C390">
-        <v>0.4434698008653646</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D390" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="E390">
-        <v>0.3311953138837596</v>
+        <v>0.3599907056193337</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003736530199134635</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H390">
-        <v>0.00352880468611624</v>
+        <v>0.003460009294380666</v>
       </c>
       <c r="I390">
-        <v>0.112274486981605</v>
+        <v>0.1337310658393833</v>
       </c>
       <c r="J390">
-        <v>1.193137825459881</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K390">
         <v>1.38</v>
@@ -21071,13 +21077,13 @@
         <v>1.34</v>
       </c>
       <c r="N390">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21085,31 +21091,31 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C391">
-        <v>0.4483932592798776</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D391" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E391">
-        <v>0.3359760633587217</v>
+        <v>0.3409079659903453</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003731606740720122</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H391">
-        <v>0.003524023936641278</v>
+        <v>0.003639092034009654</v>
       </c>
       <c r="I391">
-        <v>0.112417195921156</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="J391">
-        <v>1.189570101971103</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K391">
         <v>1.38</v>
@@ -21118,16 +21124,16 @@
         <v>2.09</v>
       </c>
       <c r="M391">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N391">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21135,99 +21141,99 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C392">
-        <v>2.068444260870803</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D392" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E392">
-        <v>2.058444260870803</v>
+        <v>0.3434698008653647</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.001811555739129197</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H392">
-        <v>0.001801555739129197</v>
+        <v>0.003636530199134636</v>
       </c>
       <c r="I392">
-        <v>-0.009999999999999787</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="J392">
-        <v>-0.0958539260229872</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K392">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L392">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M392">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N392">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="393" spans="1:16">
       <c r="A393" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B393" t="s">
         <v>85</v>
       </c>
       <c r="C393">
-        <v>2.038444260870803</v>
+        <v>0.4483932592798776</v>
       </c>
       <c r="D393" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E393">
-        <v>2.058444260870803</v>
+        <v>0.3483932592798777</v>
       </c>
       <c r="F393">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.001781555739129197</v>
+        <v>0.003731606740720122</v>
       </c>
       <c r="H393">
-        <v>0.001801555739129197</v>
+        <v>0.003631606740720122</v>
       </c>
       <c r="I393">
-        <v>0.02000000000000002</v>
+        <v>0.09999999999999987</v>
       </c>
       <c r="J393">
-        <v>-0.0958539260229872</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K393">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L393">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="M393">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N393">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21235,31 +21241,31 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C394">
-        <v>2.176625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D394" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E394">
-        <v>2.196625292888353</v>
+        <v>2.122278417911722</v>
       </c>
       <c r="F394">
         <v>1</v>
       </c>
       <c r="G394">
-        <v>0.001643374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H394">
-        <v>0.001663374707111647</v>
+        <v>0.001857721582088278</v>
       </c>
       <c r="I394">
-        <v>0.02000000000000002</v>
+        <v>0.08383415704091934</v>
       </c>
       <c r="J394">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K394">
         <v>1.34</v>
@@ -21268,16 +21274,16 @@
         <v>1.91</v>
       </c>
       <c r="M394">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N394">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21285,31 +21291,31 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C395">
-        <v>2.240948171745636</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D395" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E395">
-        <v>2.260948171745636</v>
+        <v>2.26458425685517</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001579051828254363</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H395">
-        <v>0.001599051828254364</v>
+        <v>0.00171541574314483</v>
       </c>
       <c r="I395">
-        <v>0.02000000000000002</v>
+        <v>0.08795896396681657</v>
       </c>
       <c r="J395">
-        <v>-0.2469762475713705</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K395">
         <v>1.34</v>
@@ -21318,16 +21324,16 @@
         <v>1.91</v>
       </c>
       <c r="M395">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="N395">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21335,31 +21341,31 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C396">
-        <v>2.276110233960097</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D396" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E396">
-        <v>2.296110233960097</v>
+        <v>2.330827221648491</v>
       </c>
       <c r="F396">
         <v>1</v>
       </c>
       <c r="G396">
-        <v>0.001543889766039903</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H396">
-        <v>0.001563889766039903</v>
+        <v>0.001649172778351509</v>
       </c>
       <c r="I396">
-        <v>0.02000000000000002</v>
+        <v>0.089879049902855</v>
       </c>
       <c r="J396">
-        <v>-0.2732165925075352</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K396">
         <v>1.34</v>
@@ -21368,16 +21374,66 @@
         <v>1.91</v>
       </c>
       <c r="M396">
+        <v>1.38</v>
+      </c>
+      <c r="N396">
+        <v>1.99</v>
+      </c>
+      <c r="O396">
+        <v>1</v>
+      </c>
+      <c r="P396" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16">
+      <c r="A397" s="1">
+        <v>0</v>
+      </c>
+      <c r="B397" t="s">
+        <v>86</v>
+      </c>
+      <c r="C397">
+        <v>2.276110233960097</v>
+      </c>
+      <c r="D397" t="s">
+        <v>215</v>
+      </c>
+      <c r="E397">
+        <v>2.367038897660398</v>
+      </c>
+      <c r="F397">
+        <v>1</v>
+      </c>
+      <c r="G397">
+        <v>0.001543889766039903</v>
+      </c>
+      <c r="H397">
+        <v>0.001612961102339602</v>
+      </c>
+      <c r="I397">
+        <v>0.09092866370030128</v>
+      </c>
+      <c r="J397">
+        <v>-0.2732165925075352</v>
+      </c>
+      <c r="K397">
         <v>1.34</v>
       </c>
-      <c r="N396">
-        <v>1.93</v>
-      </c>
-      <c r="O396">
-        <v>1</v>
-      </c>
-      <c r="P396" t="s">
-        <v>402</v>
+      <c r="L397">
+        <v>1.91</v>
+      </c>
+      <c r="M397">
+        <v>1.38</v>
+      </c>
+      <c r="N397">
+        <v>1.99</v>
+      </c>
+      <c r="O397">
+        <v>1</v>
+      </c>
+      <c r="P397" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="406">
   <si>
     <t>trade_time</t>
   </si>
@@ -661,7 +661,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1220,6 +1220,9 @@
   </si>
   <si>
     <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1586,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P397"/>
+  <dimension ref="A1:P402"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -20450,7 +20453,7 @@
         <v>215</v>
       </c>
       <c r="E378">
-        <v>1.759113160100587</v>
+        <v>1.767440067057837</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20459,10 +20462,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002220886839899414</v>
+        <v>0.002232559932942163</v>
       </c>
       <c r="I378">
-        <v>0.04330762782900277</v>
+        <v>0.05163453478625324</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20474,10 +20477,10 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N378">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O378">
         <v>1</v>
@@ -20500,7 +20503,7 @@
         <v>215</v>
       </c>
       <c r="E379">
-        <v>1.79068030770841</v>
+        <v>1.799235962112094</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20509,10 +20512,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.00218931969229159</v>
+        <v>0.002200764037887906</v>
       </c>
       <c r="I379">
-        <v>0.04422261761473667</v>
+        <v>0.05277827201842067</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20524,10 +20527,10 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N379">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20550,7 +20553,7 @@
         <v>215</v>
       </c>
       <c r="E380">
-        <v>1.874846907902699</v>
+        <v>1.884012465206341</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20559,10 +20562,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002105153092097301</v>
+        <v>0.002115987534793658</v>
       </c>
       <c r="I380">
-        <v>0.04666222921457108</v>
+        <v>0.05582778651821374</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20574,10 +20577,10 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N380">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20600,7 +20603,7 @@
         <v>215</v>
       </c>
       <c r="E381">
-        <v>1.853094863552425</v>
+        <v>1.862102797346283</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20609,10 +20612,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002126905136447575</v>
+        <v>0.002137897202653717</v>
       </c>
       <c r="I381">
-        <v>0.04603173517543269</v>
+        <v>0.05503966896929091</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20624,10 +20627,10 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N381">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20650,7 +20653,7 @@
         <v>215</v>
       </c>
       <c r="E382">
-        <v>1.749890310786106</v>
+        <v>1.758150385501947</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20659,10 +20662,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002230109689213894</v>
+        <v>0.002241849614498053</v>
       </c>
       <c r="I382">
-        <v>0.04304029886336536</v>
+        <v>0.0513003735792068</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20674,10 +20677,10 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N382">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20794,28 +20797,28 @@
         <v>84</v>
       </c>
       <c r="C385">
-        <v>0.3546209695665004</v>
+        <v>0.5115789925525314</v>
       </c>
       <c r="D385" t="s">
         <v>217</v>
       </c>
       <c r="E385">
-        <v>0.4807514106088764</v>
+        <v>0.6310907217822437</v>
       </c>
       <c r="F385">
         <v>1</v>
       </c>
       <c r="G385">
-        <v>0.0039653790304335</v>
+        <v>0.003808421007447469</v>
       </c>
       <c r="H385">
-        <v>0.003939248589391124</v>
+        <v>0.003788909278217756</v>
       </c>
       <c r="I385">
-        <v>0.126130441042376</v>
+        <v>0.1195117292297123</v>
       </c>
       <c r="J385">
-        <v>1.087577729176807</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K385">
         <v>1.66</v>
@@ -20833,7 +20836,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20844,28 +20847,28 @@
         <v>84</v>
       </c>
       <c r="C386">
-        <v>0.3119121628396688</v>
+        <v>0.3546209695665004</v>
       </c>
       <c r="D386" t="s">
         <v>217</v>
       </c>
       <c r="E386">
-        <v>0.4398435776596825</v>
+        <v>0.4807514106088764</v>
       </c>
       <c r="F386">
         <v>1</v>
       </c>
       <c r="G386">
-        <v>0.004008087837160332</v>
+        <v>0.0039653790304335</v>
       </c>
       <c r="H386">
-        <v>0.003980156422340318</v>
+        <v>0.003939248589391124</v>
       </c>
       <c r="I386">
-        <v>0.1279314148200137</v>
+        <v>0.126130441042376</v>
       </c>
       <c r="J386">
-        <v>1.1133059260002</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K386">
         <v>1.66</v>
@@ -20883,7 +20886,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20894,28 +20897,28 @@
         <v>85</v>
       </c>
       <c r="C387">
-        <v>0.5536378221197245</v>
+        <v>0.589142733736006</v>
       </c>
       <c r="D387" t="s">
         <v>86</v>
       </c>
       <c r="E387">
-        <v>0.4181700591597324</v>
+        <v>0.4526458429030782</v>
       </c>
       <c r="F387">
         <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.003626362177880275</v>
+        <v>0.003590857266263994</v>
       </c>
       <c r="H387">
-        <v>0.003401829940840267</v>
+        <v>0.003367354157096922</v>
       </c>
       <c r="I387">
-        <v>0.1354677629599921</v>
+        <v>0.1364968908329278</v>
       </c>
       <c r="J387">
-        <v>1.1133059260002</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K387">
         <v>1.38</v>
@@ -20933,7 +20936,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20941,81 +20944,81 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C388">
-        <v>0.5314031526074197</v>
+        <v>0.3119121628396688</v>
       </c>
       <c r="D388" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="E388">
-        <v>0.3965798728216972</v>
+        <v>0.4398435776596825</v>
       </c>
       <c r="F388">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G388">
-        <v>0.00364859684739258</v>
+        <v>0.004008087837160332</v>
       </c>
       <c r="H388">
-        <v>0.003423420127178303</v>
+        <v>0.003980156422340318</v>
       </c>
       <c r="I388">
-        <v>0.1348232797857225</v>
+        <v>0.1279314148200137</v>
       </c>
       <c r="J388">
-        <v>1.129418005356942</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K388">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L388">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M388">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N388">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O388">
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="389" spans="1:16">
       <c r="A389" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B389" t="s">
         <v>85</v>
       </c>
       <c r="C389">
-        <v>0.5157826711345157</v>
+        <v>0.5536378221197245</v>
       </c>
       <c r="D389" t="s">
         <v>86</v>
       </c>
       <c r="E389">
-        <v>0.381412158927718</v>
+        <v>0.4181700591597324</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.003664217328865484</v>
+        <v>0.003626362177880275</v>
       </c>
       <c r="H389">
-        <v>0.003438587841072282</v>
+        <v>0.003401829940840267</v>
       </c>
       <c r="I389">
-        <v>0.1343705122067977</v>
+        <v>0.1354677629599921</v>
       </c>
       <c r="J389">
-        <v>1.140737194830061</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K389">
         <v>1.38</v>
@@ -21033,7 +21036,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21041,81 +21044,81 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C390">
-        <v>0.493721771458717</v>
+        <v>0.2851661111074761</v>
       </c>
       <c r="D390" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="E390">
-        <v>0.3599907056193337</v>
+        <v>0.4142253714824617</v>
       </c>
       <c r="F390">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G390">
-        <v>0.003686278228541283</v>
+        <v>0.004034833888892524</v>
       </c>
       <c r="H390">
-        <v>0.003460009294380666</v>
+        <v>0.004005774628517539</v>
       </c>
       <c r="I390">
-        <v>0.1337310658393833</v>
+        <v>0.1290592603749856</v>
       </c>
       <c r="J390">
-        <v>1.156723354015422</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K390">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L390">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M390">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N390">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="391" spans="1:16">
       <c r="A391" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B391" t="s">
         <v>85</v>
       </c>
       <c r="C391">
-        <v>0.4409079659903452</v>
+        <v>0.5314031526074197</v>
       </c>
       <c r="D391" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="E391">
-        <v>0.3409079659903453</v>
+        <v>0.3965798728216972</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003739092034009655</v>
+        <v>0.00364859684739258</v>
       </c>
       <c r="H391">
-        <v>0.003639092034009654</v>
+        <v>0.003423420127178303</v>
       </c>
       <c r="I391">
-        <v>0.09999999999999987</v>
+        <v>0.1348232797857225</v>
       </c>
       <c r="J391">
-        <v>1.194994227543228</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K391">
         <v>1.38</v>
@@ -21124,16 +21127,16 @@
         <v>2.09</v>
       </c>
       <c r="M391">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="N391">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21141,81 +21144,81 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C392">
-        <v>0.4434698008653646</v>
+        <v>0.2663762565820988</v>
       </c>
       <c r="D392" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E392">
-        <v>0.3434698008653647</v>
+        <v>0.3962278602202027</v>
       </c>
       <c r="F392">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G392">
-        <v>0.003736530199134635</v>
+        <v>0.004053623743417901</v>
       </c>
       <c r="H392">
-        <v>0.003636530199134636</v>
+        <v>0.004023772139779798</v>
       </c>
       <c r="I392">
-        <v>0.09999999999999987</v>
+        <v>0.1298516036381039</v>
       </c>
       <c r="J392">
-        <v>1.193137825459881</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K392">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L392">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M392">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="N392">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="393" spans="1:16">
       <c r="A393" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B393" t="s">
         <v>85</v>
       </c>
       <c r="C393">
-        <v>0.4483932592798776</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D393" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="E393">
-        <v>0.3483932592798777</v>
+        <v>0.381412158927718</v>
       </c>
       <c r="F393">
         <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.003731606740720122</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H393">
-        <v>0.003631606740720122</v>
+        <v>0.003438587841072282</v>
       </c>
       <c r="I393">
-        <v>0.09999999999999987</v>
+        <v>0.1343705122067977</v>
       </c>
       <c r="J393">
-        <v>1.189570101971103</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K393">
         <v>1.38</v>
@@ -21224,16 +21227,16 @@
         <v>2.09</v>
       </c>
       <c r="M393">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="N393">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21241,49 +21244,49 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
+        <v>85</v>
+      </c>
+      <c r="C394">
+        <v>0.493721771458717</v>
+      </c>
+      <c r="D394" t="s">
         <v>86</v>
       </c>
-      <c r="C394">
-        <v>2.038444260870803</v>
-      </c>
-      <c r="D394" t="s">
-        <v>215</v>
-      </c>
       <c r="E394">
-        <v>2.122278417911722</v>
+        <v>0.3599907056193337</v>
       </c>
       <c r="F394">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G394">
-        <v>0.001781555739129197</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H394">
-        <v>0.001857721582088278</v>
+        <v>0.003460009294380666</v>
       </c>
       <c r="I394">
-        <v>0.08383415704091934</v>
+        <v>0.1337310658393833</v>
       </c>
       <c r="J394">
-        <v>-0.0958539260229872</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K394">
+        <v>1.38</v>
+      </c>
+      <c r="L394">
+        <v>2.09</v>
+      </c>
+      <c r="M394">
         <v>1.34</v>
       </c>
-      <c r="L394">
+      <c r="N394">
         <v>1.91</v>
       </c>
-      <c r="M394">
-        <v>1.38</v>
-      </c>
-      <c r="N394">
-        <v>1.99</v>
-      </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21291,49 +21294,49 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C395">
-        <v>2.176625292888353</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D395" t="s">
         <v>215</v>
       </c>
       <c r="E395">
-        <v>2.26458425685517</v>
+        <v>0.338958023714913</v>
       </c>
       <c r="F395">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G395">
-        <v>0.001643374707111647</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H395">
-        <v>0.00171541574314483</v>
+        <v>0.003661041976285087</v>
       </c>
       <c r="I395">
-        <v>0.08795896396681657</v>
+        <v>0.1019499422754322</v>
       </c>
       <c r="J395">
-        <v>-0.1989740991704129</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K395">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L395">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="M395">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N395">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21341,49 +21344,49 @@
         <v>0</v>
       </c>
       <c r="B396" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C396">
-        <v>2.240948171745636</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D396" t="s">
         <v>215</v>
       </c>
       <c r="E396">
-        <v>2.330827221648491</v>
+        <v>0.3415384226107658</v>
       </c>
       <c r="F396">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G396">
-        <v>0.001579051828254363</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H396">
-        <v>0.001649172778351509</v>
+        <v>0.003658461577389234</v>
       </c>
       <c r="I396">
-        <v>0.089879049902855</v>
+        <v>0.1019313782545987</v>
       </c>
       <c r="J396">
-        <v>-0.2469762475713705</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K396">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L396">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="M396">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N396">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O396">
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>217</v>
+        <v>400</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21391,49 +21394,299 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C397">
-        <v>2.276110233960097</v>
+        <v>0.4483932592798776</v>
       </c>
       <c r="D397" t="s">
         <v>215</v>
       </c>
       <c r="E397">
-        <v>2.367038897660398</v>
+        <v>0.3464975582601668</v>
       </c>
       <c r="F397">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G397">
+        <v>0.003731606740720122</v>
+      </c>
+      <c r="H397">
+        <v>0.003653502441739833</v>
+      </c>
+      <c r="I397">
+        <v>0.1018957010197108</v>
+      </c>
+      <c r="J397">
+        <v>1.189570101971103</v>
+      </c>
+      <c r="K397">
+        <v>1.38</v>
+      </c>
+      <c r="L397">
+        <v>2.09</v>
+      </c>
+      <c r="M397">
+        <v>1.39</v>
+      </c>
+      <c r="N397">
+        <v>2</v>
+      </c>
+      <c r="O397">
+        <v>1</v>
+      </c>
+      <c r="P397" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16">
+      <c r="A398" s="1">
+        <v>0</v>
+      </c>
+      <c r="B398" t="s">
+        <v>85</v>
+      </c>
+      <c r="C398">
+        <v>0.4444321020325201</v>
+      </c>
+      <c r="D398" t="s">
+        <v>215</v>
+      </c>
+      <c r="E398">
+        <v>0.3425076969747849</v>
+      </c>
+      <c r="F398">
+        <v>-1</v>
+      </c>
+      <c r="G398">
+        <v>0.00373556789796748</v>
+      </c>
+      <c r="H398">
+        <v>0.003657492303025215</v>
+      </c>
+      <c r="I398">
+        <v>0.1019244050577353</v>
+      </c>
+      <c r="J398">
+        <v>1.192440505773536</v>
+      </c>
+      <c r="K398">
+        <v>1.38</v>
+      </c>
+      <c r="L398">
+        <v>2.09</v>
+      </c>
+      <c r="M398">
+        <v>1.39</v>
+      </c>
+      <c r="N398">
+        <v>2</v>
+      </c>
+      <c r="O398">
+        <v>1</v>
+      </c>
+      <c r="P398" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16">
+      <c r="A399" s="1">
+        <v>0</v>
+      </c>
+      <c r="B399" t="s">
+        <v>86</v>
+      </c>
+      <c r="C399">
+        <v>2.038444260870803</v>
+      </c>
+      <c r="D399" t="s">
+        <v>215</v>
+      </c>
+      <c r="E399">
+        <v>2.133236957171952</v>
+      </c>
+      <c r="F399">
+        <v>1</v>
+      </c>
+      <c r="G399">
+        <v>0.001781555739129197</v>
+      </c>
+      <c r="H399">
+        <v>0.001866763042828048</v>
+      </c>
+      <c r="I399">
+        <v>0.09479269630114917</v>
+      </c>
+      <c r="J399">
+        <v>-0.0958539260229872</v>
+      </c>
+      <c r="K399">
+        <v>1.34</v>
+      </c>
+      <c r="L399">
+        <v>1.91</v>
+      </c>
+      <c r="M399">
+        <v>1.39</v>
+      </c>
+      <c r="N399">
+        <v>2</v>
+      </c>
+      <c r="O399">
+        <v>1</v>
+      </c>
+      <c r="P399" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16">
+      <c r="A400" s="1">
+        <v>0</v>
+      </c>
+      <c r="B400" t="s">
+        <v>86</v>
+      </c>
+      <c r="C400">
+        <v>2.176625292888353</v>
+      </c>
+      <c r="D400" t="s">
+        <v>215</v>
+      </c>
+      <c r="E400">
+        <v>2.276573997846874</v>
+      </c>
+      <c r="F400">
+        <v>1</v>
+      </c>
+      <c r="G400">
+        <v>0.001643374707111647</v>
+      </c>
+      <c r="H400">
+        <v>0.001723426002153126</v>
+      </c>
+      <c r="I400">
+        <v>0.09994870495852082</v>
+      </c>
+      <c r="J400">
+        <v>-0.1989740991704129</v>
+      </c>
+      <c r="K400">
+        <v>1.34</v>
+      </c>
+      <c r="L400">
+        <v>1.91</v>
+      </c>
+      <c r="M400">
+        <v>1.39</v>
+      </c>
+      <c r="N400">
+        <v>2</v>
+      </c>
+      <c r="O400">
+        <v>1</v>
+      </c>
+      <c r="P400" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16">
+      <c r="A401" s="1">
+        <v>0</v>
+      </c>
+      <c r="B401" t="s">
+        <v>86</v>
+      </c>
+      <c r="C401">
+        <v>2.240948171745636</v>
+      </c>
+      <c r="D401" t="s">
+        <v>215</v>
+      </c>
+      <c r="E401">
+        <v>2.343296984124205</v>
+      </c>
+      <c r="F401">
+        <v>1</v>
+      </c>
+      <c r="G401">
+        <v>0.001579051828254363</v>
+      </c>
+      <c r="H401">
+        <v>0.001656703015875795</v>
+      </c>
+      <c r="I401">
+        <v>0.1023488123785685</v>
+      </c>
+      <c r="J401">
+        <v>-0.2469762475713705</v>
+      </c>
+      <c r="K401">
+        <v>1.34</v>
+      </c>
+      <c r="L401">
+        <v>1.91</v>
+      </c>
+      <c r="M401">
+        <v>1.39</v>
+      </c>
+      <c r="N401">
+        <v>2</v>
+      </c>
+      <c r="O401">
+        <v>1</v>
+      </c>
+      <c r="P401" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16">
+      <c r="A402" s="1">
+        <v>0</v>
+      </c>
+      <c r="B402" t="s">
+        <v>86</v>
+      </c>
+      <c r="C402">
+        <v>2.276110233960097</v>
+      </c>
+      <c r="D402" t="s">
+        <v>215</v>
+      </c>
+      <c r="E402">
+        <v>2.379771063585474</v>
+      </c>
+      <c r="F402">
+        <v>1</v>
+      </c>
+      <c r="G402">
         <v>0.001543889766039903</v>
       </c>
-      <c r="H397">
-        <v>0.001612961102339602</v>
-      </c>
-      <c r="I397">
-        <v>0.09092866370030128</v>
-      </c>
-      <c r="J397">
+      <c r="H402">
+        <v>0.001620228936414526</v>
+      </c>
+      <c r="I402">
+        <v>0.1036608296253765</v>
+      </c>
+      <c r="J402">
         <v>-0.2732165925075352</v>
       </c>
-      <c r="K397">
+      <c r="K402">
         <v>1.34</v>
       </c>
-      <c r="L397">
+      <c r="L402">
         <v>1.91</v>
       </c>
-      <c r="M397">
-        <v>1.38</v>
-      </c>
-      <c r="N397">
-        <v>1.99</v>
-      </c>
-      <c r="O397">
-        <v>1</v>
-      </c>
-      <c r="P397" t="s">
-        <v>404</v>
+      <c r="M402">
+        <v>1.39</v>
+      </c>
+      <c r="N402">
+        <v>2</v>
+      </c>
+      <c r="O402">
+        <v>1</v>
+      </c>
+      <c r="P402" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="406">
   <si>
     <t>trade_time</t>
   </si>
@@ -268,6 +268,9 @@
     <t>2021-04-09</t>
   </si>
   <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
     <t>2021-05-21</t>
   </si>
   <si>
@@ -661,7 +664,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-11</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1220,9 +1223,6 @@
   </si>
   <si>
     <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1589,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P402"/>
+  <dimension ref="A1:P403"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1650,7 +1650,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1700,7 +1700,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1786,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1836,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1850,7 +1850,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1900,7 +1900,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1936,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1950,7 +1950,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2000,7 +2000,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2036,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2050,7 +2050,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2100,7 +2100,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2136,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2150,7 +2150,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2186,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2200,7 +2200,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2250,7 +2250,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2300,7 +2300,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2336,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2350,7 +2350,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2400,7 +2400,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2436,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2450,7 +2450,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2486,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2500,7 +2500,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2550,7 +2550,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2586,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2600,7 +2600,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2650,7 +2650,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2700,7 +2700,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2736,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2750,7 +2750,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2800,7 +2800,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2836,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2850,7 +2850,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2886,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2900,7 +2900,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2950,7 +2950,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3000,7 +3000,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3036,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3050,7 +3050,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3086,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3100,7 +3100,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3136,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3150,7 +3150,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3186,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3200,7 +3200,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3236,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3250,7 +3250,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3286,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3300,7 +3300,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3350,7 +3350,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3386,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3400,7 +3400,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3436,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3450,7 +3450,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3486,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3500,7 +3500,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3536,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3550,7 +3550,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3586,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3600,7 +3600,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3636,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3650,7 +3650,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3686,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3700,7 +3700,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3736,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3750,7 +3750,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3786,7 +3786,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3800,7 +3800,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3836,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3850,7 +3850,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3886,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3900,7 +3900,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3950,7 +3950,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3986,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4000,7 +4000,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4036,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4050,7 +4050,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4086,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4100,7 +4100,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4136,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4150,7 +4150,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4186,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4200,7 +4200,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4236,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4250,7 +4250,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4286,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4300,7 +4300,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4350,7 +4350,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4386,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4400,7 +4400,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4436,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4450,7 +4450,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4486,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4500,7 +4500,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4536,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4550,7 +4550,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4586,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4600,7 +4600,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4636,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4650,7 +4650,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4686,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4700,7 +4700,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4736,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4750,7 +4750,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4786,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4800,7 +4800,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4836,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4850,7 +4850,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4886,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4900,7 +4900,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4936,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4950,7 +4950,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4986,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5000,7 +5000,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5050,7 +5050,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5086,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5100,7 +5100,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5136,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5150,7 +5150,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5186,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5200,7 +5200,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5236,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5250,7 +5250,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5286,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5300,7 +5300,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5336,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5350,7 +5350,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5386,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5400,7 +5400,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5436,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5450,7 +5450,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5486,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5500,7 +5500,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5536,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5550,7 +5550,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5586,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5600,7 +5600,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5636,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5650,7 +5650,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5686,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5700,7 +5700,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5736,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5750,7 +5750,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5786,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5800,7 +5800,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5836,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5850,7 +5850,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5886,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5900,7 +5900,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5936,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5950,7 +5950,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5986,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6000,7 +6000,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6036,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6050,7 +6050,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6086,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6100,7 +6100,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6136,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6150,7 +6150,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6186,7 +6186,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6200,7 +6200,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6250,7 +6250,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6286,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6300,7 +6300,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6336,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6350,7 +6350,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6386,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6400,7 +6400,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6436,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6450,7 +6450,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6486,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6500,7 +6500,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6536,7 +6536,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6550,7 +6550,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6586,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6600,7 +6600,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6636,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6650,7 +6650,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6686,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6700,7 +6700,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6750,7 +6750,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6786,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6800,7 +6800,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6836,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6850,7 +6850,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6886,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6900,7 +6900,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6936,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6950,7 +6950,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6986,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7000,7 +7000,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7036,7 +7036,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7050,7 +7050,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7086,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7100,7 +7100,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7136,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7150,7 +7150,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7186,7 +7186,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7200,7 +7200,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7250,7 +7250,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7286,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7300,7 +7300,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7336,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7350,7 +7350,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7386,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7400,7 +7400,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7436,7 +7436,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7450,7 +7450,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7486,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7500,7 +7500,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7536,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7550,7 +7550,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7586,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7600,7 +7600,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7636,7 +7636,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7650,7 +7650,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7686,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7700,7 +7700,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7736,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7750,7 +7750,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7786,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7800,7 +7800,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7836,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7850,7 +7850,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7886,7 +7886,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7900,7 +7900,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7936,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7950,7 +7950,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7986,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8000,7 +8000,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8036,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8050,7 +8050,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8086,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8100,7 +8100,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8136,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8150,7 +8150,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8186,7 +8186,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8200,7 +8200,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8236,7 +8236,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8250,7 +8250,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8286,7 +8286,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8300,7 +8300,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8336,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8350,7 +8350,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8386,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8400,7 +8400,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8450,7 +8450,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8486,7 +8486,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8500,7 +8500,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8536,7 +8536,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8550,7 +8550,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8586,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8600,7 +8600,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8636,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8650,7 +8650,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8686,7 +8686,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8700,7 +8700,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8736,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8750,7 +8750,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8800,7 +8800,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8836,7 +8836,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8850,7 +8850,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8886,7 +8886,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8900,7 +8900,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8936,7 +8936,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8950,7 +8950,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8986,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9000,7 +9000,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9036,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9050,7 +9050,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9086,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9100,7 +9100,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9136,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9150,7 +9150,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9186,7 +9186,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9200,7 +9200,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9236,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9250,7 +9250,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9286,7 +9286,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9300,7 +9300,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9336,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9350,7 +9350,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9400,7 +9400,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9436,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9450,7 +9450,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9486,7 +9486,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9500,7 +9500,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9536,7 +9536,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9550,7 +9550,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9586,7 +9586,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9600,7 +9600,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9636,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9650,7 +9650,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9686,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9700,7 +9700,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9736,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9750,7 +9750,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9786,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9800,7 +9800,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9836,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9850,7 +9850,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9886,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9900,7 +9900,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9936,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9950,7 +9950,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9986,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10000,7 +10000,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10036,7 +10036,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10050,7 +10050,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10086,7 +10086,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10100,7 +10100,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10136,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10150,7 +10150,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10200,7 +10200,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10236,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10250,7 +10250,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10286,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10300,7 +10300,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10336,7 +10336,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10350,7 +10350,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10386,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10400,7 +10400,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10436,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10450,7 +10450,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10486,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10500,7 +10500,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10550,7 +10550,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10586,7 +10586,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10600,7 +10600,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10636,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10650,7 +10650,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10686,7 +10686,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10700,7 +10700,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10736,7 +10736,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10786,7 +10786,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10836,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10886,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10936,7 +10936,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10950,7 +10950,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10986,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11000,7 +11000,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11036,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11050,7 +11050,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11086,7 +11086,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11100,7 +11100,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11136,7 +11136,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11150,7 +11150,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11186,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11200,7 +11200,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11236,7 +11236,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11250,7 +11250,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11286,7 +11286,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11300,7 +11300,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11336,7 +11336,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11350,7 +11350,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11386,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11400,7 +11400,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11436,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11450,7 +11450,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11486,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11500,7 +11500,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11536,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11550,7 +11550,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11586,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11600,7 +11600,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11636,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11650,7 +11650,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11686,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11700,7 +11700,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11736,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11750,7 +11750,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11786,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11800,7 +11800,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11836,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11850,7 +11850,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11886,7 +11886,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11900,7 +11900,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11936,7 +11936,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11950,7 +11950,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11986,7 +11986,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12000,7 +12000,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12036,7 +12036,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12050,7 +12050,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12086,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12100,7 +12100,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12136,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12150,7 +12150,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12186,7 +12186,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12200,7 +12200,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12236,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12250,7 +12250,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12286,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12300,7 +12300,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12336,7 +12336,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12350,7 +12350,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12386,7 +12386,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12400,7 +12400,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12436,7 +12436,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12450,7 +12450,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12486,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12500,7 +12500,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12536,7 +12536,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12550,7 +12550,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12586,7 +12586,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12600,7 +12600,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12636,7 +12636,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12650,7 +12650,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12686,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12700,7 +12700,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12736,7 +12736,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12750,7 +12750,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12786,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12800,7 +12800,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12836,7 +12836,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12850,7 +12850,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12886,7 +12886,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12900,7 +12900,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12936,7 +12936,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12950,7 +12950,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12986,7 +12986,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13000,7 +13000,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13036,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13050,7 +13050,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13086,7 +13086,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13100,7 +13100,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13136,7 +13136,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13150,7 +13150,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13186,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13200,7 +13200,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13236,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13250,7 +13250,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13286,7 +13286,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13300,7 +13300,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13336,7 +13336,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13350,7 +13350,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13386,7 +13386,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13400,7 +13400,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13436,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13450,7 +13450,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13486,7 +13486,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13500,7 +13500,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13536,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13550,7 +13550,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13586,7 +13586,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13600,7 +13600,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13636,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13650,7 +13650,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13686,7 +13686,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13700,7 +13700,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13736,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13750,7 +13750,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13786,7 +13786,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13800,7 +13800,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13836,7 +13836,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13850,7 +13850,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13886,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13900,7 +13900,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13936,7 +13936,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13950,7 +13950,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13986,7 +13986,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14000,7 +14000,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14036,7 +14036,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14050,7 +14050,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14086,7 +14086,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14100,7 +14100,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14136,7 +14136,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14150,7 +14150,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14186,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14200,7 +14200,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14236,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14250,7 +14250,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14286,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14300,7 +14300,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14336,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14350,7 +14350,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14386,7 +14386,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14400,7 +14400,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14436,7 +14436,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14450,7 +14450,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14486,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14500,7 +14500,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14536,7 +14536,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14550,7 +14550,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14586,7 +14586,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14600,7 +14600,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14636,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14650,7 +14650,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14686,7 +14686,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14700,7 +14700,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14736,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14750,7 +14750,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14836,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14850,7 +14850,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14886,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14900,7 +14900,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14936,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14950,7 +14950,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14986,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15000,7 +15000,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15036,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15050,7 +15050,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15086,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15100,7 +15100,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15136,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15150,7 +15150,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15186,7 +15186,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15200,7 +15200,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15236,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15250,7 +15250,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15286,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15300,7 +15300,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15336,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15350,7 +15350,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15386,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15400,7 +15400,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15436,7 +15436,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15450,7 +15450,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15486,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15500,7 +15500,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15536,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15550,7 +15550,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15586,7 +15586,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15600,7 +15600,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15636,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15650,7 +15650,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15686,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15700,7 +15700,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15736,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15750,7 +15750,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15786,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15836,7 +15836,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15886,7 +15886,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15900,7 +15900,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15936,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15950,7 +15950,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15986,7 +15986,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16000,7 +16000,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16036,7 +16036,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16050,7 +16050,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16086,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16100,7 +16100,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16136,7 +16136,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16186,7 +16186,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16236,7 +16236,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16250,7 +16250,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16286,7 +16286,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16300,7 +16300,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16336,7 +16336,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16350,7 +16350,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16386,7 +16386,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16400,7 +16400,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16436,7 +16436,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16450,7 +16450,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16486,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16500,7 +16500,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16536,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16550,7 +16550,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16586,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16636,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16686,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16700,7 +16700,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16736,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16750,7 +16750,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16786,7 +16786,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16800,7 +16800,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16836,7 +16836,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16850,7 +16850,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16886,7 +16886,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16900,7 +16900,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16936,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16950,7 +16950,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16986,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17000,7 +17000,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17036,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17050,7 +17050,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17086,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17100,7 +17100,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17136,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17150,7 +17150,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17186,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17200,7 +17200,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17236,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17286,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17336,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17350,7 +17350,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17386,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17436,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17486,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17500,7 +17500,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17536,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17586,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17636,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17650,7 +17650,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17686,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17736,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17786,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17800,7 +17800,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17836,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17886,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17936,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17950,7 +17950,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17986,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18036,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18086,7 +18086,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18100,7 +18100,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18136,7 +18136,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18186,7 +18186,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18236,7 +18236,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18250,7 +18250,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18286,7 +18286,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18336,7 +18336,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18386,7 +18386,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18400,7 +18400,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18436,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18550,7 +18550,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18636,7 +18636,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18650,7 +18650,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18686,7 +18686,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18736,7 +18736,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18786,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18800,7 +18800,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18836,7 +18836,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19000,7 +19000,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19086,7 +19086,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19136,7 +19136,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19150,7 +19150,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19186,7 +19186,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19200,7 +19200,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19286,7 +19286,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19300,7 +19300,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19336,7 +19336,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19386,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19400,7 +19400,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19436,7 +19436,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19500,7 +19500,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19550,7 +19550,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19586,7 +19586,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19600,7 +19600,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19636,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19650,7 +19650,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19686,7 +19686,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19700,7 +19700,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19786,7 +19786,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19800,7 +19800,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19836,7 +19836,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19886,7 +19886,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19936,7 +19936,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19950,7 +19950,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19986,7 +19986,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20000,7 +20000,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20036,7 +20036,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20050,7 +20050,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20086,7 +20086,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20100,7 +20100,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20136,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20150,7 +20150,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20186,7 +20186,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20200,7 +20200,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20236,7 +20236,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20250,7 +20250,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20286,7 +20286,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20300,7 +20300,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20336,7 +20336,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20350,7 +20350,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20386,7 +20386,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20436,7 +20436,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20450,10 +20450,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E378">
-        <v>1.767440067057837</v>
+        <v>1.777440067057837</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20462,10 +20462,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002232559932942163</v>
+        <v>0.002242559932942162</v>
       </c>
       <c r="I378">
-        <v>0.05163453478625324</v>
+        <v>0.06163453478625303</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20480,13 +20480,13 @@
         <v>1.39</v>
       </c>
       <c r="N378">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20500,10 +20500,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E379">
-        <v>1.799235962112094</v>
+        <v>1.809235962112094</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20512,10 +20512,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002200764037887906</v>
+        <v>0.002210764037887906</v>
       </c>
       <c r="I379">
-        <v>0.05277827201842067</v>
+        <v>0.06277827201842046</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20530,13 +20530,13 @@
         <v>1.39</v>
       </c>
       <c r="N379">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20550,10 +20550,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E380">
-        <v>1.884012465206341</v>
+        <v>1.894012465206341</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20562,10 +20562,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002115987534793658</v>
+        <v>0.002125987534793658</v>
       </c>
       <c r="I380">
-        <v>0.05582778651821374</v>
+        <v>0.06582778651821353</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20580,13 +20580,13 @@
         <v>1.39</v>
       </c>
       <c r="N380">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20600,10 +20600,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E381">
-        <v>1.862102797346283</v>
+        <v>1.872102797346283</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20612,10 +20612,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002137897202653717</v>
+        <v>0.002147897202653717</v>
       </c>
       <c r="I381">
-        <v>0.05503966896929091</v>
+        <v>0.0650396689692907</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20630,13 +20630,13 @@
         <v>1.39</v>
       </c>
       <c r="N381">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20650,10 +20650,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E382">
-        <v>1.758150385501947</v>
+        <v>1.768150385501947</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20662,10 +20662,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002241849614498053</v>
+        <v>0.002251849614498053</v>
       </c>
       <c r="I382">
-        <v>0.0513003735792068</v>
+        <v>0.06130037357920659</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20680,13 +20680,13 @@
         <v>1.39</v>
       </c>
       <c r="N382">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20700,7 +20700,7 @@
         <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E383">
         <v>0.7959503213647137</v>
@@ -20736,42 +20736,42 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="384" spans="1:16">
       <c r="A384" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B384" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C384">
-        <v>0.8094230769230786</v>
+        <v>0.9072145169864216</v>
       </c>
       <c r="D384" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E384">
-        <v>0.6894230769230785</v>
+        <v>0.7959503213647137</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.003730576923076922</v>
+        <v>0.003632785483013579</v>
       </c>
       <c r="H384">
-        <v>0.003610576923076922</v>
+        <v>0.003504049678635286</v>
       </c>
       <c r="I384">
-        <v>0.1200000000000001</v>
+        <v>0.111264195621708</v>
       </c>
       <c r="J384">
-        <v>0.9423076923076913</v>
+        <v>0.8735804378292169</v>
       </c>
       <c r="K384">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="L384">
         <v>2.27</v>
@@ -20794,49 +20794,49 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C385">
-        <v>0.5115789925525314</v>
+        <v>0.8094230769230786</v>
       </c>
       <c r="D385" t="s">
         <v>217</v>
       </c>
       <c r="E385">
-        <v>0.6310907217822437</v>
+        <v>0.6894230769230785</v>
       </c>
       <c r="F385">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.003808421007447469</v>
+        <v>0.003730576923076922</v>
       </c>
       <c r="H385">
-        <v>0.003788909278217756</v>
+        <v>0.003610576923076922</v>
       </c>
       <c r="I385">
-        <v>0.1195117292297123</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="J385">
-        <v>0.9930247032816077</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K385">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="L385">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="M385">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="N385">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>83</v>
+        <v>394</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20844,31 +20844,31 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C386">
-        <v>0.3546209695665004</v>
+        <v>0.5115789925525314</v>
       </c>
       <c r="D386" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E386">
-        <v>0.4807514106088764</v>
+        <v>0.6310907217822437</v>
       </c>
       <c r="F386">
         <v>1</v>
       </c>
       <c r="G386">
-        <v>0.0039653790304335</v>
+        <v>0.003808421007447469</v>
       </c>
       <c r="H386">
-        <v>0.003939248589391124</v>
+        <v>0.003788909278217756</v>
       </c>
       <c r="I386">
-        <v>0.126130441042376</v>
+        <v>0.1195117292297123</v>
       </c>
       <c r="J386">
-        <v>1.087577729176807</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K386">
         <v>1.66</v>
@@ -20886,101 +20886,101 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="387" spans="1:16">
       <c r="A387" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B387" t="s">
         <v>85</v>
       </c>
       <c r="C387">
-        <v>0.589142733736006</v>
+        <v>0.3546209695665004</v>
       </c>
       <c r="D387" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="E387">
-        <v>0.4526458429030782</v>
+        <v>0.4807514106088764</v>
       </c>
       <c r="F387">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G387">
-        <v>0.003590857266263994</v>
+        <v>0.0039653790304335</v>
       </c>
       <c r="H387">
-        <v>0.003367354157096922</v>
+        <v>0.003939248589391124</v>
       </c>
       <c r="I387">
-        <v>0.1364968908329278</v>
+        <v>0.126130441042376</v>
       </c>
       <c r="J387">
         <v>1.087577729176807</v>
       </c>
       <c r="K387">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L387">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M387">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N387">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O387">
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="388" spans="1:16">
       <c r="A388" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B388" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C388">
-        <v>0.3119121628396688</v>
+        <v>0.589142733736006</v>
       </c>
       <c r="D388" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="E388">
-        <v>0.4398435776596825</v>
+        <v>0.4526458429030782</v>
       </c>
       <c r="F388">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.004008087837160332</v>
+        <v>0.003590857266263994</v>
       </c>
       <c r="H388">
-        <v>0.003980156422340318</v>
+        <v>0.003367354157096922</v>
       </c>
       <c r="I388">
-        <v>0.1279314148200137</v>
+        <v>0.1364968908329278</v>
       </c>
       <c r="J388">
-        <v>1.1133059260002</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K388">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="L388">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="M388">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="N388">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20991,96 +20991,96 @@
     </row>
     <row r="389" spans="1:16">
       <c r="A389" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B389" t="s">
         <v>85</v>
       </c>
       <c r="C389">
-        <v>0.5536378221197245</v>
+        <v>0.3119121628396688</v>
       </c>
       <c r="D389" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="E389">
-        <v>0.4181700591597324</v>
+        <v>0.4398435776596825</v>
       </c>
       <c r="F389">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G389">
-        <v>0.003626362177880275</v>
+        <v>0.004008087837160332</v>
       </c>
       <c r="H389">
-        <v>0.003401829940840267</v>
+        <v>0.003980156422340318</v>
       </c>
       <c r="I389">
-        <v>0.1354677629599921</v>
+        <v>0.1279314148200137</v>
       </c>
       <c r="J389">
         <v>1.1133059260002</v>
       </c>
       <c r="K389">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L389">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M389">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N389">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="390" spans="1:16">
       <c r="A390" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B390" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C390">
-        <v>0.2851661111074761</v>
+        <v>0.5536378221197245</v>
       </c>
       <c r="D390" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="E390">
-        <v>0.4142253714824617</v>
+        <v>0.4181700591597324</v>
       </c>
       <c r="F390">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.004034833888892524</v>
+        <v>0.003626362177880275</v>
       </c>
       <c r="H390">
-        <v>0.004005774628517539</v>
+        <v>0.003401829940840267</v>
       </c>
       <c r="I390">
-        <v>0.1290592603749856</v>
+        <v>0.1354677629599921</v>
       </c>
       <c r="J390">
-        <v>1.129418005356942</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K390">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="L390">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="M390">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="N390">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21091,96 +21091,96 @@
     </row>
     <row r="391" spans="1:16">
       <c r="A391" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B391" t="s">
         <v>85</v>
       </c>
       <c r="C391">
-        <v>0.5314031526074197</v>
+        <v>0.2851661111074761</v>
       </c>
       <c r="D391" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="E391">
-        <v>0.3965798728216972</v>
+        <v>0.4142253714824617</v>
       </c>
       <c r="F391">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G391">
-        <v>0.00364859684739258</v>
+        <v>0.004034833888892524</v>
       </c>
       <c r="H391">
-        <v>0.003423420127178303</v>
+        <v>0.004005774628517539</v>
       </c>
       <c r="I391">
-        <v>0.1348232797857225</v>
+        <v>0.1290592603749856</v>
       </c>
       <c r="J391">
         <v>1.129418005356942</v>
       </c>
       <c r="K391">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L391">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M391">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N391">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="392" spans="1:16">
       <c r="A392" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B392" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C392">
-        <v>0.2663762565820988</v>
+        <v>0.5314031526074197</v>
       </c>
       <c r="D392" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="E392">
-        <v>0.3962278602202027</v>
+        <v>0.3965798728216972</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.004053623743417901</v>
+        <v>0.00364859684739258</v>
       </c>
       <c r="H392">
-        <v>0.004023772139779798</v>
+        <v>0.003423420127178303</v>
       </c>
       <c r="I392">
-        <v>0.1298516036381039</v>
+        <v>0.1348232797857225</v>
       </c>
       <c r="J392">
-        <v>1.140737194830061</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K392">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="L392">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="M392">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="N392">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21191,84 +21191,84 @@
     </row>
     <row r="393" spans="1:16">
       <c r="A393" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B393" t="s">
         <v>85</v>
       </c>
       <c r="C393">
-        <v>0.5157826711345157</v>
+        <v>0.2663762565820988</v>
       </c>
       <c r="D393" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="E393">
-        <v>0.381412158927718</v>
+        <v>0.3962278602202027</v>
       </c>
       <c r="F393">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G393">
-        <v>0.003664217328865484</v>
+        <v>0.004053623743417901</v>
       </c>
       <c r="H393">
-        <v>0.003438587841072282</v>
+        <v>0.004023772139779798</v>
       </c>
       <c r="I393">
-        <v>0.1343705122067977</v>
+        <v>0.1298516036381039</v>
       </c>
       <c r="J393">
         <v>1.140737194830061</v>
       </c>
       <c r="K393">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L393">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M393">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N393">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="394" spans="1:16">
       <c r="A394" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B394" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C394">
-        <v>0.493721771458717</v>
+        <v>0.5157826711345157</v>
       </c>
       <c r="D394" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E394">
-        <v>0.3599907056193337</v>
+        <v>0.381412158927718</v>
       </c>
       <c r="F394">
         <v>-1</v>
       </c>
       <c r="G394">
-        <v>0.003686278228541283</v>
+        <v>0.003664217328865484</v>
       </c>
       <c r="H394">
-        <v>0.003460009294380666</v>
+        <v>0.003438587841072282</v>
       </c>
       <c r="I394">
-        <v>0.1337310658393833</v>
+        <v>0.1343705122067977</v>
       </c>
       <c r="J394">
-        <v>1.156723354015422</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K394">
         <v>1.38</v>
@@ -21297,40 +21297,40 @@
         <v>85</v>
       </c>
       <c r="C395">
-        <v>0.4409079659903452</v>
+        <v>0.239839232334399</v>
       </c>
       <c r="D395" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E395">
-        <v>0.338958023714913</v>
+        <v>0.370809867115478</v>
       </c>
       <c r="F395">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G395">
-        <v>0.003739092034009655</v>
+        <v>0.004080160767665601</v>
       </c>
       <c r="H395">
-        <v>0.003661041976285087</v>
+        <v>0.004049190132884522</v>
       </c>
       <c r="I395">
-        <v>0.1019499422754322</v>
+        <v>0.1309706347810791</v>
       </c>
       <c r="J395">
-        <v>1.194994227543228</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K395">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L395">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M395">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="N395">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="O395">
         <v>1</v>
@@ -21341,34 +21341,34 @@
     </row>
     <row r="396" spans="1:16">
       <c r="A396" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B396" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C396">
-        <v>0.4434698008653646</v>
+        <v>0.493721771458717</v>
       </c>
       <c r="D396" t="s">
-        <v>215</v>
+        <v>87</v>
       </c>
       <c r="E396">
-        <v>0.3415384226107658</v>
+        <v>0.3599907056193337</v>
       </c>
       <c r="F396">
         <v>-1</v>
       </c>
       <c r="G396">
-        <v>0.003736530199134635</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H396">
-        <v>0.003658461577389234</v>
+        <v>0.003460009294380666</v>
       </c>
       <c r="I396">
-        <v>0.1019313782545987</v>
+        <v>0.1337310658393833</v>
       </c>
       <c r="J396">
-        <v>1.193137825459881</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K396">
         <v>1.38</v>
@@ -21377,16 +21377,16 @@
         <v>2.09</v>
       </c>
       <c r="M396">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="N396">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O396">
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21394,31 +21394,31 @@
         <v>0</v>
       </c>
       <c r="B397" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C397">
-        <v>0.4483932592798776</v>
+        <v>0.4409079659903452</v>
       </c>
       <c r="D397" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E397">
-        <v>0.3464975582601668</v>
+        <v>0.3489580237149128</v>
       </c>
       <c r="F397">
         <v>-1</v>
       </c>
       <c r="G397">
-        <v>0.003731606740720122</v>
+        <v>0.003739092034009655</v>
       </c>
       <c r="H397">
-        <v>0.003653502441739833</v>
+        <v>0.003671041976285087</v>
       </c>
       <c r="I397">
-        <v>0.1018957010197108</v>
+        <v>0.09194994227543241</v>
       </c>
       <c r="J397">
-        <v>1.189570101971103</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K397">
         <v>1.38</v>
@@ -21430,13 +21430,13 @@
         <v>1.39</v>
       </c>
       <c r="N397">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O397">
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21444,31 +21444,31 @@
         <v>0</v>
       </c>
       <c r="B398" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C398">
-        <v>0.4444321020325201</v>
+        <v>0.4434698008653646</v>
       </c>
       <c r="D398" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E398">
-        <v>0.3425076969747849</v>
+        <v>0.3515384226107656</v>
       </c>
       <c r="F398">
         <v>-1</v>
       </c>
       <c r="G398">
-        <v>0.00373556789796748</v>
+        <v>0.003736530199134635</v>
       </c>
       <c r="H398">
-        <v>0.003657492303025215</v>
+        <v>0.003668461577389234</v>
       </c>
       <c r="I398">
-        <v>0.1019244050577353</v>
+        <v>0.09193137825459896</v>
       </c>
       <c r="J398">
-        <v>1.192440505773536</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K398">
         <v>1.38</v>
@@ -21480,13 +21480,13 @@
         <v>1.39</v>
       </c>
       <c r="N398">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O398">
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21497,46 +21497,46 @@
         <v>86</v>
       </c>
       <c r="C399">
-        <v>2.038444260870803</v>
+        <v>0.4483932592798776</v>
       </c>
       <c r="D399" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E399">
-        <v>2.133236957171952</v>
+        <v>0.3564975582601666</v>
       </c>
       <c r="F399">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G399">
-        <v>0.001781555739129197</v>
+        <v>0.003731606740720122</v>
       </c>
       <c r="H399">
-        <v>0.001866763042828048</v>
+        <v>0.003663502441739833</v>
       </c>
       <c r="I399">
-        <v>0.09479269630114917</v>
+        <v>0.09189570101971101</v>
       </c>
       <c r="J399">
-        <v>-0.0958539260229872</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K399">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="L399">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="M399">
         <v>1.39</v>
       </c>
       <c r="N399">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O399">
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21544,31 +21544,31 @@
         <v>0</v>
       </c>
       <c r="B400" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C400">
-        <v>2.176625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D400" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E400">
-        <v>2.276573997846874</v>
+        <v>2.143236957171952</v>
       </c>
       <c r="F400">
         <v>1</v>
       </c>
       <c r="G400">
-        <v>0.001643374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H400">
-        <v>0.001723426002153126</v>
+        <v>0.001876763042828048</v>
       </c>
       <c r="I400">
-        <v>0.09994870495852082</v>
+        <v>0.104792696301149</v>
       </c>
       <c r="J400">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K400">
         <v>1.34</v>
@@ -21580,13 +21580,13 @@
         <v>1.39</v>
       </c>
       <c r="N400">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O400">
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21594,31 +21594,31 @@
         <v>0</v>
       </c>
       <c r="B401" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C401">
-        <v>2.240948171745636</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D401" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E401">
-        <v>2.343296984124205</v>
+        <v>2.286573997846874</v>
       </c>
       <c r="F401">
         <v>1</v>
       </c>
       <c r="G401">
-        <v>0.001579051828254363</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H401">
-        <v>0.001656703015875795</v>
+        <v>0.001733426002153126</v>
       </c>
       <c r="I401">
-        <v>0.1023488123785685</v>
+        <v>0.1099487049585206</v>
       </c>
       <c r="J401">
-        <v>-0.2469762475713705</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K401">
         <v>1.34</v>
@@ -21630,13 +21630,13 @@
         <v>1.39</v>
       </c>
       <c r="N401">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O401">
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>217</v>
+        <v>404</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21644,31 +21644,31 @@
         <v>0</v>
       </c>
       <c r="B402" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C402">
-        <v>2.276110233960097</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D402" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E402">
-        <v>2.379771063585474</v>
+        <v>2.353296984124205</v>
       </c>
       <c r="F402">
         <v>1</v>
       </c>
       <c r="G402">
-        <v>0.001543889766039903</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H402">
-        <v>0.001620228936414526</v>
+        <v>0.001666703015875795</v>
       </c>
       <c r="I402">
-        <v>0.1036608296253765</v>
+        <v>0.1123488123785683</v>
       </c>
       <c r="J402">
-        <v>-0.2732165925075352</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K402">
         <v>1.34</v>
@@ -21680,12 +21680,62 @@
         <v>1.39</v>
       </c>
       <c r="N402">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O402">
         <v>1</v>
       </c>
       <c r="P402" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16">
+      <c r="A403" s="1">
+        <v>0</v>
+      </c>
+      <c r="B403" t="s">
+        <v>87</v>
+      </c>
+      <c r="C403">
+        <v>2.276110233960097</v>
+      </c>
+      <c r="D403" t="s">
+        <v>216</v>
+      </c>
+      <c r="E403">
+        <v>2.389771063585473</v>
+      </c>
+      <c r="F403">
+        <v>1</v>
+      </c>
+      <c r="G403">
+        <v>0.001543889766039903</v>
+      </c>
+      <c r="H403">
+        <v>0.001630228936414526</v>
+      </c>
+      <c r="I403">
+        <v>0.1136608296253763</v>
+      </c>
+      <c r="J403">
+        <v>-0.2732165925075352</v>
+      </c>
+      <c r="K403">
+        <v>1.34</v>
+      </c>
+      <c r="L403">
+        <v>1.91</v>
+      </c>
+      <c r="M403">
+        <v>1.39</v>
+      </c>
+      <c r="N403">
+        <v>2.01</v>
+      </c>
+      <c r="O403">
+        <v>1</v>
+      </c>
+      <c r="P403" t="s">
         <v>405</v>
       </c>
     </row>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="402">
   <si>
     <t>trade_time</t>
   </si>
@@ -268,9 +268,6 @@
     <t>2021-04-09</t>
   </si>
   <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
     <t>2021-05-21</t>
   </si>
   <si>
@@ -664,7 +661,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-12</t>
+    <t>2021-08-16</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1214,15 +1211,6 @@
   </si>
   <si>
     <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1589,7 +1577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P403"/>
+  <dimension ref="A1:P395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1650,7 +1638,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1686,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1700,7 +1688,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1736,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1786,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1836,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1850,7 +1838,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1886,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1900,7 +1888,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1936,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1950,7 +1938,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1986,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2000,7 +1988,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2036,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2050,7 +2038,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2086,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2100,7 +2088,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2136,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2150,7 +2138,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2186,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2200,7 +2188,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2236,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2250,7 +2238,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2286,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2300,7 +2288,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2336,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2350,7 +2338,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2386,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2400,7 +2388,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2436,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2450,7 +2438,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2486,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2500,7 +2488,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2536,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2550,7 +2538,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2586,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2600,7 +2588,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2636,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2650,7 +2638,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2686,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2700,7 +2688,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2736,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2750,7 +2738,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2786,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2800,7 +2788,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2836,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2850,7 +2838,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2886,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2900,7 +2888,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2936,7 +2924,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2950,7 +2938,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2986,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3000,7 +2988,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3036,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3050,7 +3038,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3086,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3100,7 +3088,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3136,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3150,7 +3138,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3186,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3200,7 +3188,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3236,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3250,7 +3238,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3286,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3300,7 +3288,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3336,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3350,7 +3338,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3386,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3400,7 +3388,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3436,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3450,7 +3438,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3486,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3500,7 +3488,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3536,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3550,7 +3538,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3586,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3600,7 +3588,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3636,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3650,7 +3638,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3686,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3700,7 +3688,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3736,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3750,7 +3738,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3786,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3800,7 +3788,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3836,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3850,7 +3838,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3886,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3900,7 +3888,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3936,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3950,7 +3938,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3986,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4000,7 +3988,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4036,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4050,7 +4038,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4086,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4100,7 +4088,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4136,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4150,7 +4138,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4186,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4200,7 +4188,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4236,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4250,7 +4238,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4286,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4300,7 +4288,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4336,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4350,7 +4338,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4386,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4400,7 +4388,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4436,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4450,7 +4438,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4486,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4500,7 +4488,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4536,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4550,7 +4538,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4586,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4600,7 +4588,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4636,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4650,7 +4638,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4686,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4700,7 +4688,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4736,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4750,7 +4738,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4786,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4800,7 +4788,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4836,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4850,7 +4838,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4886,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4900,7 +4888,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4936,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4950,7 +4938,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4986,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5000,7 +4988,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5036,7 +5024,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5050,7 +5038,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5086,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5100,7 +5088,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5136,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5150,7 +5138,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5186,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5200,7 +5188,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5236,7 +5224,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5250,7 +5238,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5286,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5300,7 +5288,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5336,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5350,7 +5338,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5386,7 +5374,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5400,7 +5388,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5436,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5450,7 +5438,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5486,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5500,7 +5488,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5536,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5550,7 +5538,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5586,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5600,7 +5588,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5636,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5650,7 +5638,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5686,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5700,7 +5688,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5736,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5750,7 +5738,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5786,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5800,7 +5788,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5836,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5850,7 +5838,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5886,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5900,7 +5888,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5936,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5950,7 +5938,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5986,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6000,7 +5988,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6036,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6050,7 +6038,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6086,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6100,7 +6088,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6136,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6150,7 +6138,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6186,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6200,7 +6188,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6250,7 +6238,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6286,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6300,7 +6288,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6336,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6350,7 +6338,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6386,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6400,7 +6388,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6436,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6450,7 +6438,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6486,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6500,7 +6488,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6536,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6550,7 +6538,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6586,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6600,7 +6588,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6636,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6650,7 +6638,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6686,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6700,7 +6688,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6736,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6750,7 +6738,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6786,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6800,7 +6788,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6836,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6850,7 +6838,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6886,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6900,7 +6888,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6936,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6950,7 +6938,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6986,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7000,7 +6988,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7036,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7050,7 +7038,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7086,7 +7074,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7100,7 +7088,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7136,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7150,7 +7138,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7186,7 +7174,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7200,7 +7188,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7236,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7250,7 +7238,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7286,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7300,7 +7288,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7336,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7350,7 +7338,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7386,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7400,7 +7388,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7436,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7450,7 +7438,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7486,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7500,7 +7488,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7536,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7550,7 +7538,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7586,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7600,7 +7588,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7636,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7650,7 +7638,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7686,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7700,7 +7688,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7736,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7750,7 +7738,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7786,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7800,7 +7788,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7836,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7850,7 +7838,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7886,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7900,7 +7888,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7936,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7950,7 +7938,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7986,7 +7974,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8000,7 +7988,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8036,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8050,7 +8038,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8086,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8100,7 +8088,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8136,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8150,7 +8138,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8186,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8200,7 +8188,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8236,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8250,7 +8238,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8286,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8300,7 +8288,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8336,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8350,7 +8338,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8386,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8400,7 +8388,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8436,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8450,7 +8438,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8486,7 +8474,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8500,7 +8488,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8536,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8550,7 +8538,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8586,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8600,7 +8588,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8636,7 +8624,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8650,7 +8638,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8686,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8700,7 +8688,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8736,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8750,7 +8738,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8786,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8800,7 +8788,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8836,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8850,7 +8838,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8886,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8900,7 +8888,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8936,7 +8924,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8950,7 +8938,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8986,7 +8974,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9000,7 +8988,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9036,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9050,7 +9038,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9086,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9100,7 +9088,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9136,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9150,7 +9138,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9186,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9200,7 +9188,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9236,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9250,7 +9238,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9286,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9300,7 +9288,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9336,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9350,7 +9338,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9386,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9400,7 +9388,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9436,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9450,7 +9438,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9486,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9500,7 +9488,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9536,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9550,7 +9538,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9586,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9600,7 +9588,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9636,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9650,7 +9638,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9686,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9700,7 +9688,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9736,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9750,7 +9738,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9786,7 +9774,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9800,7 +9788,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9836,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9850,7 +9838,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9886,7 +9874,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9900,7 +9888,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9936,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9950,7 +9938,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9986,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10000,7 +9988,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10036,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10050,7 +10038,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10086,7 +10074,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10100,7 +10088,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10136,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10150,7 +10138,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10200,7 +10188,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10236,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10250,7 +10238,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10286,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10300,7 +10288,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10336,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10350,7 +10338,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10386,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10400,7 +10388,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10436,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10450,7 +10438,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10486,7 +10474,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10500,7 +10488,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10536,7 +10524,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10550,7 +10538,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10586,7 +10574,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10600,7 +10588,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10636,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10650,7 +10638,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10686,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10700,7 +10688,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10736,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10786,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10836,7 +10824,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10886,7 +10874,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10936,7 +10924,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10950,7 +10938,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10986,7 +10974,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11000,7 +10988,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11036,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11050,7 +11038,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11086,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11100,7 +11088,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11136,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11150,7 +11138,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11186,7 +11174,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11200,7 +11188,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11236,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11250,7 +11238,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11286,7 +11274,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11300,7 +11288,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11336,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11350,7 +11338,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11386,7 +11374,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11400,7 +11388,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11436,7 +11424,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11450,7 +11438,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11486,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11500,7 +11488,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11536,7 +11524,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11550,7 +11538,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11586,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11600,7 +11588,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11636,7 +11624,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11650,7 +11638,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11686,7 +11674,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11700,7 +11688,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11736,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11750,7 +11738,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11786,7 +11774,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11800,7 +11788,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11836,7 +11824,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11850,7 +11838,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11886,7 +11874,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11900,7 +11888,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11936,7 +11924,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11950,7 +11938,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11986,7 +11974,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12000,7 +11988,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12036,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12050,7 +12038,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12086,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12100,7 +12088,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12136,7 +12124,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12150,7 +12138,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12186,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12200,7 +12188,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12236,7 +12224,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12250,7 +12238,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12286,7 +12274,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12300,7 +12288,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12336,7 +12324,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12350,7 +12338,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12386,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12400,7 +12388,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12436,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12450,7 +12438,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12486,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12500,7 +12488,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12536,7 +12524,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12550,7 +12538,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12586,7 +12574,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12600,7 +12588,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12636,7 +12624,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12650,7 +12638,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12686,7 +12674,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12700,7 +12688,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12736,7 +12724,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12750,7 +12738,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12786,7 +12774,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12800,7 +12788,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12836,7 +12824,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12850,7 +12838,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12886,7 +12874,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12900,7 +12888,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12936,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12950,7 +12938,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12986,7 +12974,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13000,7 +12988,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13036,7 +13024,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13050,7 +13038,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13086,7 +13074,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13100,7 +13088,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13136,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13150,7 +13138,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13186,7 +13174,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13200,7 +13188,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13236,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13250,7 +13238,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13286,7 +13274,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13300,7 +13288,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13336,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13350,7 +13338,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13386,7 +13374,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13400,7 +13388,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13436,7 +13424,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13450,7 +13438,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13486,7 +13474,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13500,7 +13488,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13536,7 +13524,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13550,7 +13538,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13586,7 +13574,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13600,7 +13588,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13636,7 +13624,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13650,7 +13638,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13686,7 +13674,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13700,7 +13688,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13736,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13750,7 +13738,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13786,7 +13774,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13800,7 +13788,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13836,7 +13824,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13850,7 +13838,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13886,7 +13874,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13900,7 +13888,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13936,7 +13924,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13950,7 +13938,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13986,7 +13974,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14000,7 +13988,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14036,7 +14024,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14050,7 +14038,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14086,7 +14074,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14100,7 +14088,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14136,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14150,7 +14138,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14186,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14200,7 +14188,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14236,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14250,7 +14238,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14286,7 +14274,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14300,7 +14288,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14336,7 +14324,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14350,7 +14338,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14386,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14400,7 +14388,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14436,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14450,7 +14438,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14486,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14500,7 +14488,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14536,7 +14524,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14550,7 +14538,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14586,7 +14574,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14600,7 +14588,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14636,7 +14624,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14650,7 +14638,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14686,7 +14674,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14700,7 +14688,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14736,7 +14724,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14750,7 +14738,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14836,7 +14824,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14850,7 +14838,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14886,7 +14874,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14900,7 +14888,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14936,7 +14924,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14950,7 +14938,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14986,7 +14974,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15000,7 +14988,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15036,7 +15024,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15050,7 +15038,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15086,7 +15074,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15100,7 +15088,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15136,7 +15124,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15150,7 +15138,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15186,7 +15174,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15200,7 +15188,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15236,7 +15224,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15250,7 +15238,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15286,7 +15274,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15300,7 +15288,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15336,7 +15324,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15350,7 +15338,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15386,7 +15374,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15400,7 +15388,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15436,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15450,7 +15438,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15486,7 +15474,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15500,7 +15488,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15536,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15550,7 +15538,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15586,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15600,7 +15588,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15636,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15650,7 +15638,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15686,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15700,7 +15688,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15736,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15750,7 +15738,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15786,7 +15774,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15836,7 +15824,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15886,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15900,7 +15888,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15936,7 +15924,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15950,7 +15938,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15986,7 +15974,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16000,7 +15988,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16036,7 +16024,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16050,7 +16038,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16086,7 +16074,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16100,7 +16088,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16136,7 +16124,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16186,7 +16174,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16236,7 +16224,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16250,7 +16238,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16286,7 +16274,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16300,7 +16288,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16336,7 +16324,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16350,7 +16338,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16386,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16400,7 +16388,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16436,7 +16424,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16450,7 +16438,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16486,7 +16474,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16500,7 +16488,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16536,7 +16524,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16550,7 +16538,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16586,7 +16574,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16636,7 +16624,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16686,7 +16674,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16700,7 +16688,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16736,7 +16724,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16750,7 +16738,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16786,7 +16774,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16800,7 +16788,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16836,7 +16824,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16850,7 +16838,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16886,7 +16874,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16900,7 +16888,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16936,7 +16924,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16950,7 +16938,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16986,7 +16974,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17000,7 +16988,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17036,7 +17024,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17050,7 +17038,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17086,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17100,7 +17088,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17136,7 +17124,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17150,7 +17138,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17186,7 +17174,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17200,7 +17188,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17236,7 +17224,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17286,7 +17274,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17336,7 +17324,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17350,7 +17338,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17386,7 +17374,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17436,7 +17424,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17486,7 +17474,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17500,7 +17488,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17536,7 +17524,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17586,7 +17574,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17636,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17650,7 +17638,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17686,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17736,7 +17724,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17786,7 +17774,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17800,7 +17788,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17836,7 +17824,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17886,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17936,7 +17924,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17950,7 +17938,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17986,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18036,7 +18024,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18086,7 +18074,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18100,7 +18088,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18136,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18186,7 +18174,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18236,7 +18224,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18250,7 +18238,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18286,7 +18274,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18336,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18386,7 +18374,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18400,7 +18388,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18436,7 +18424,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18550,7 +18538,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18636,7 +18624,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18650,7 +18638,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18686,7 +18674,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18736,7 +18724,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18786,7 +18774,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18800,7 +18788,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18836,7 +18824,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19000,7 +18988,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19086,7 +19074,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19136,7 +19124,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19150,7 +19138,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19186,7 +19174,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19200,7 +19188,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19286,7 +19274,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19300,7 +19288,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19336,7 +19324,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19386,7 +19374,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19400,7 +19388,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19436,7 +19424,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19500,7 +19488,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19550,7 +19538,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19586,7 +19574,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19600,7 +19588,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19636,7 +19624,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19650,7 +19638,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19686,7 +19674,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19700,7 +19688,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19786,7 +19774,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19800,7 +19788,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19836,7 +19824,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19886,7 +19874,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19936,7 +19924,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19950,7 +19938,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19986,7 +19974,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20000,7 +19988,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20036,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20050,7 +20038,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20086,7 +20074,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20100,7 +20088,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20136,7 +20124,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20150,7 +20138,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20186,7 +20174,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20200,7 +20188,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20236,7 +20224,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20250,7 +20238,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20286,7 +20274,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20300,7 +20288,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20336,7 +20324,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20350,7 +20338,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20386,7 +20374,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20436,7 +20424,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20450,10 +20438,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E378">
-        <v>1.777440067057837</v>
+        <v>1.814132439228835</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20462,10 +20450,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002242559932942162</v>
+        <v>0.002265867560771165</v>
       </c>
       <c r="I378">
-        <v>0.06163453478625303</v>
+        <v>0.09832690695725077</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20477,16 +20465,16 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="N378">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20500,10 +20488,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E379">
-        <v>1.809235962112094</v>
+        <v>1.845013344497358</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20512,10 +20500,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002210764037887906</v>
+        <v>0.002234986655502643</v>
       </c>
       <c r="I379">
-        <v>0.06277827201842046</v>
+        <v>0.0985556544036843</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20527,16 +20515,16 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="N379">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20550,10 +20538,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E380">
-        <v>1.894012465206341</v>
+        <v>1.927350235991771</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20562,10 +20550,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002125987534793658</v>
+        <v>0.002152649764008229</v>
       </c>
       <c r="I380">
-        <v>0.06582778651821353</v>
+        <v>0.09916555730364296</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20577,16 +20565,16 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="N380">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20600,10 +20588,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E381">
-        <v>1.872102797346283</v>
+        <v>1.906071062170851</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20612,10 +20600,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002147897202653717</v>
+        <v>0.00217392893782915</v>
       </c>
       <c r="I381">
-        <v>0.0650396689692907</v>
+        <v>0.0990079337938583</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20627,16 +20615,16 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="N381">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20650,10 +20638,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E382">
-        <v>1.768150385501947</v>
+        <v>1.805110086638582</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20662,10 +20650,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002251849614498053</v>
+        <v>0.002274889913361419</v>
       </c>
       <c r="I382">
-        <v>0.06130037357920659</v>
+        <v>0.09826007471584131</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20677,16 +20665,16 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="N382">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20700,7 +20688,7 @@
         <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E383">
         <v>0.7959503213647137</v>
@@ -20736,42 +20724,42 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="384" spans="1:16">
       <c r="A384" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C384">
-        <v>0.9072145169864216</v>
+        <v>0.8094230769230786</v>
       </c>
       <c r="D384" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E384">
-        <v>0.7959503213647137</v>
+        <v>0.6894230769230785</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.003632785483013579</v>
+        <v>0.003730576923076922</v>
       </c>
       <c r="H384">
-        <v>0.003504049678635286</v>
+        <v>0.003610576923076922</v>
       </c>
       <c r="I384">
-        <v>0.111264195621708</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="J384">
-        <v>0.8735804378292169</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K384">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="L384">
         <v>2.27</v>
@@ -20791,52 +20779,52 @@
     </row>
     <row r="385" spans="1:16">
       <c r="A385" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B385" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C385">
-        <v>0.8094230769230786</v>
+        <v>0.5957692307692326</v>
       </c>
       <c r="D385" t="s">
         <v>217</v>
       </c>
       <c r="E385">
-        <v>0.6894230769230785</v>
+        <v>0.7117307692307708</v>
       </c>
       <c r="F385">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G385">
-        <v>0.003730576923076922</v>
+        <v>0.003724230769230767</v>
       </c>
       <c r="H385">
-        <v>0.003610576923076922</v>
+        <v>0.003708269230769229</v>
       </c>
       <c r="I385">
-        <v>0.1200000000000001</v>
+        <v>0.1159615384615382</v>
       </c>
       <c r="J385">
         <v>0.9423076923076913</v>
       </c>
       <c r="K385">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="L385">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="M385">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="N385">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20844,13 +20832,13 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C386">
         <v>0.5115789925525314</v>
       </c>
       <c r="D386" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E386">
         <v>0.6310907217822437</v>
@@ -20894,13 +20882,13 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C387">
         <v>0.3546209695665004</v>
       </c>
       <c r="D387" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E387">
         <v>0.4807514106088764</v>
@@ -20936,51 +20924,51 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:16">
       <c r="A388" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C388">
-        <v>0.589142733736006</v>
+        <v>0.3119121628396688</v>
       </c>
       <c r="D388" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="E388">
-        <v>0.4526458429030782</v>
+        <v>0.4398435776596825</v>
       </c>
       <c r="F388">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G388">
-        <v>0.003590857266263994</v>
+        <v>0.004008087837160332</v>
       </c>
       <c r="H388">
-        <v>0.003367354157096922</v>
+        <v>0.003980156422340318</v>
       </c>
       <c r="I388">
-        <v>0.1364968908329278</v>
+        <v>0.1279314148200137</v>
       </c>
       <c r="J388">
-        <v>1.087577729176807</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K388">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L388">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M388">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N388">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20994,31 +20982,31 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C389">
-        <v>0.3119121628396688</v>
+        <v>0.2851661111074761</v>
       </c>
       <c r="D389" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E389">
-        <v>0.4398435776596825</v>
+        <v>0.4142253714824617</v>
       </c>
       <c r="F389">
         <v>1</v>
       </c>
       <c r="G389">
-        <v>0.004008087837160332</v>
+        <v>0.004034833888892524</v>
       </c>
       <c r="H389">
-        <v>0.003980156422340318</v>
+        <v>0.004005774628517539</v>
       </c>
       <c r="I389">
-        <v>0.1279314148200137</v>
+        <v>0.1290592603749856</v>
       </c>
       <c r="J389">
-        <v>1.1133059260002</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K389">
         <v>1.66</v>
@@ -21041,52 +21029,52 @@
     </row>
     <row r="390" spans="1:16">
       <c r="A390" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C390">
-        <v>0.5536378221197245</v>
+        <v>0.2663762565820988</v>
       </c>
       <c r="D390" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="E390">
-        <v>0.4181700591597324</v>
+        <v>0.3962278602202027</v>
       </c>
       <c r="F390">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G390">
-        <v>0.003626362177880275</v>
+        <v>0.004053623743417901</v>
       </c>
       <c r="H390">
-        <v>0.003401829940840267</v>
+        <v>0.004023772139779798</v>
       </c>
       <c r="I390">
-        <v>0.1354677629599921</v>
+        <v>0.1298516036381039</v>
       </c>
       <c r="J390">
-        <v>1.1133059260002</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K390">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="L390">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="M390">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="N390">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21094,31 +21082,31 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C391">
-        <v>0.2851661111074761</v>
+        <v>0.239839232334399</v>
       </c>
       <c r="D391" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E391">
-        <v>0.4142253714824617</v>
+        <v>0.370809867115478</v>
       </c>
       <c r="F391">
         <v>1</v>
       </c>
       <c r="G391">
-        <v>0.004034833888892524</v>
+        <v>0.004080160767665601</v>
       </c>
       <c r="H391">
-        <v>0.004005774628517539</v>
+        <v>0.004049190132884522</v>
       </c>
       <c r="I391">
-        <v>0.1290592603749856</v>
+        <v>0.1309706347810791</v>
       </c>
       <c r="J391">
-        <v>1.129418005356942</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K391">
         <v>1.66</v>
@@ -21136,7 +21124,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21144,31 +21132,31 @@
         <v>1</v>
       </c>
       <c r="B392" t="s">
+        <v>85</v>
+      </c>
+      <c r="C392">
+        <v>0.493721771458717</v>
+      </c>
+      <c r="D392" t="s">
         <v>86</v>
       </c>
-      <c r="C392">
-        <v>0.5314031526074197</v>
-      </c>
-      <c r="D392" t="s">
-        <v>87</v>
-      </c>
       <c r="E392">
-        <v>0.3965798728216972</v>
+        <v>0.3599907056193337</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.00364859684739258</v>
+        <v>0.003686278228541283</v>
       </c>
       <c r="H392">
-        <v>0.003423420127178303</v>
+        <v>0.003460009294380666</v>
       </c>
       <c r="I392">
-        <v>0.1348232797857225</v>
+        <v>0.1337310658393833</v>
       </c>
       <c r="J392">
-        <v>1.129418005356942</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K392">
         <v>1.38</v>
@@ -21186,7 +21174,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21194,99 +21182,99 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C393">
-        <v>0.2663762565820988</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D393" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E393">
-        <v>0.3962278602202027</v>
+        <v>2.169402800131033</v>
       </c>
       <c r="F393">
         <v>1</v>
       </c>
       <c r="G393">
-        <v>0.004053623743417901</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H393">
-        <v>0.004023772139779798</v>
+        <v>0.001910597199868967</v>
       </c>
       <c r="I393">
-        <v>0.1298516036381039</v>
+        <v>0.1309585392602299</v>
       </c>
       <c r="J393">
-        <v>1.140737194830061</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K393">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="L393">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="M393">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="N393">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="394" spans="1:16">
       <c r="A394" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B394" t="s">
         <v>86</v>
       </c>
       <c r="C394">
-        <v>0.5157826711345157</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D394" t="s">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="E394">
-        <v>0.381412158927718</v>
+        <v>2.308615033880058</v>
       </c>
       <c r="F394">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G394">
-        <v>0.003664217328865484</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H394">
-        <v>0.003438587841072282</v>
+        <v>0.001771384966119942</v>
       </c>
       <c r="I394">
-        <v>0.1343705122067977</v>
+        <v>0.1319897409917044</v>
       </c>
       <c r="J394">
-        <v>1.140737194830061</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K394">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L394">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="M394">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="N394">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21294,449 +21282,49 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C395">
-        <v>0.239839232334399</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D395" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E395">
-        <v>0.370809867115478</v>
+        <v>2.408842399885172</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.004080160767665601</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H395">
-        <v>0.004049190132884522</v>
+        <v>0.001671157600114828</v>
       </c>
       <c r="I395">
-        <v>0.1309706347810791</v>
+        <v>0.1327321659250753</v>
       </c>
       <c r="J395">
-        <v>1.156723354015422</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K395">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="L395">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="M395">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="N395">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="396" spans="1:16">
-      <c r="A396" s="1">
-        <v>1</v>
-      </c>
-      <c r="B396" t="s">
-        <v>86</v>
-      </c>
-      <c r="C396">
-        <v>0.493721771458717</v>
-      </c>
-      <c r="D396" t="s">
-        <v>87</v>
-      </c>
-      <c r="E396">
-        <v>0.3599907056193337</v>
-      </c>
-      <c r="F396">
-        <v>-1</v>
-      </c>
-      <c r="G396">
-        <v>0.003686278228541283</v>
-      </c>
-      <c r="H396">
-        <v>0.003460009294380666</v>
-      </c>
-      <c r="I396">
-        <v>0.1337310658393833</v>
-      </c>
-      <c r="J396">
-        <v>1.156723354015422</v>
-      </c>
-      <c r="K396">
-        <v>1.38</v>
-      </c>
-      <c r="L396">
-        <v>2.09</v>
-      </c>
-      <c r="M396">
-        <v>1.34</v>
-      </c>
-      <c r="N396">
-        <v>1.91</v>
-      </c>
-      <c r="O396">
-        <v>1</v>
-      </c>
-      <c r="P396" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="397" spans="1:16">
-      <c r="A397" s="1">
-        <v>0</v>
-      </c>
-      <c r="B397" t="s">
-        <v>86</v>
-      </c>
-      <c r="C397">
-        <v>0.4409079659903452</v>
-      </c>
-      <c r="D397" t="s">
-        <v>216</v>
-      </c>
-      <c r="E397">
-        <v>0.3489580237149128</v>
-      </c>
-      <c r="F397">
-        <v>-1</v>
-      </c>
-      <c r="G397">
-        <v>0.003739092034009655</v>
-      </c>
-      <c r="H397">
-        <v>0.003671041976285087</v>
-      </c>
-      <c r="I397">
-        <v>0.09194994227543241</v>
-      </c>
-      <c r="J397">
-        <v>1.194994227543228</v>
-      </c>
-      <c r="K397">
-        <v>1.38</v>
-      </c>
-      <c r="L397">
-        <v>2.09</v>
-      </c>
-      <c r="M397">
-        <v>1.39</v>
-      </c>
-      <c r="N397">
-        <v>2.01</v>
-      </c>
-      <c r="O397">
-        <v>1</v>
-      </c>
-      <c r="P397" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="398" spans="1:16">
-      <c r="A398" s="1">
-        <v>0</v>
-      </c>
-      <c r="B398" t="s">
-        <v>86</v>
-      </c>
-      <c r="C398">
-        <v>0.4434698008653646</v>
-      </c>
-      <c r="D398" t="s">
-        <v>216</v>
-      </c>
-      <c r="E398">
-        <v>0.3515384226107656</v>
-      </c>
-      <c r="F398">
-        <v>-1</v>
-      </c>
-      <c r="G398">
-        <v>0.003736530199134635</v>
-      </c>
-      <c r="H398">
-        <v>0.003668461577389234</v>
-      </c>
-      <c r="I398">
-        <v>0.09193137825459896</v>
-      </c>
-      <c r="J398">
-        <v>1.193137825459881</v>
-      </c>
-      <c r="K398">
-        <v>1.38</v>
-      </c>
-      <c r="L398">
-        <v>2.09</v>
-      </c>
-      <c r="M398">
-        <v>1.39</v>
-      </c>
-      <c r="N398">
-        <v>2.01</v>
-      </c>
-      <c r="O398">
-        <v>1</v>
-      </c>
-      <c r="P398" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="399" spans="1:16">
-      <c r="A399" s="1">
-        <v>0</v>
-      </c>
-      <c r="B399" t="s">
-        <v>86</v>
-      </c>
-      <c r="C399">
-        <v>0.4483932592798776</v>
-      </c>
-      <c r="D399" t="s">
-        <v>216</v>
-      </c>
-      <c r="E399">
-        <v>0.3564975582601666</v>
-      </c>
-      <c r="F399">
-        <v>-1</v>
-      </c>
-      <c r="G399">
-        <v>0.003731606740720122</v>
-      </c>
-      <c r="H399">
-        <v>0.003663502441739833</v>
-      </c>
-      <c r="I399">
-        <v>0.09189570101971101</v>
-      </c>
-      <c r="J399">
-        <v>1.189570101971103</v>
-      </c>
-      <c r="K399">
-        <v>1.38</v>
-      </c>
-      <c r="L399">
-        <v>2.09</v>
-      </c>
-      <c r="M399">
-        <v>1.39</v>
-      </c>
-      <c r="N399">
-        <v>2.01</v>
-      </c>
-      <c r="O399">
-        <v>1</v>
-      </c>
-      <c r="P399" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="400" spans="1:16">
-      <c r="A400" s="1">
-        <v>0</v>
-      </c>
-      <c r="B400" t="s">
-        <v>87</v>
-      </c>
-      <c r="C400">
-        <v>2.038444260870803</v>
-      </c>
-      <c r="D400" t="s">
-        <v>216</v>
-      </c>
-      <c r="E400">
-        <v>2.143236957171952</v>
-      </c>
-      <c r="F400">
-        <v>1</v>
-      </c>
-      <c r="G400">
-        <v>0.001781555739129197</v>
-      </c>
-      <c r="H400">
-        <v>0.001876763042828048</v>
-      </c>
-      <c r="I400">
-        <v>0.104792696301149</v>
-      </c>
-      <c r="J400">
-        <v>-0.0958539260229872</v>
-      </c>
-      <c r="K400">
-        <v>1.34</v>
-      </c>
-      <c r="L400">
-        <v>1.91</v>
-      </c>
-      <c r="M400">
-        <v>1.39</v>
-      </c>
-      <c r="N400">
-        <v>2.01</v>
-      </c>
-      <c r="O400">
-        <v>1</v>
-      </c>
-      <c r="P400" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="401" spans="1:16">
-      <c r="A401" s="1">
-        <v>0</v>
-      </c>
-      <c r="B401" t="s">
-        <v>87</v>
-      </c>
-      <c r="C401">
-        <v>2.176625292888353</v>
-      </c>
-      <c r="D401" t="s">
-        <v>216</v>
-      </c>
-      <c r="E401">
-        <v>2.286573997846874</v>
-      </c>
-      <c r="F401">
-        <v>1</v>
-      </c>
-      <c r="G401">
-        <v>0.001643374707111647</v>
-      </c>
-      <c r="H401">
-        <v>0.001733426002153126</v>
-      </c>
-      <c r="I401">
-        <v>0.1099487049585206</v>
-      </c>
-      <c r="J401">
-        <v>-0.1989740991704129</v>
-      </c>
-      <c r="K401">
-        <v>1.34</v>
-      </c>
-      <c r="L401">
-        <v>1.91</v>
-      </c>
-      <c r="M401">
-        <v>1.39</v>
-      </c>
-      <c r="N401">
-        <v>2.01</v>
-      </c>
-      <c r="O401">
-        <v>1</v>
-      </c>
-      <c r="P401" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="402" spans="1:16">
-      <c r="A402" s="1">
-        <v>0</v>
-      </c>
-      <c r="B402" t="s">
-        <v>87</v>
-      </c>
-      <c r="C402">
-        <v>2.240948171745636</v>
-      </c>
-      <c r="D402" t="s">
-        <v>216</v>
-      </c>
-      <c r="E402">
-        <v>2.353296984124205</v>
-      </c>
-      <c r="F402">
-        <v>1</v>
-      </c>
-      <c r="G402">
-        <v>0.001579051828254363</v>
-      </c>
-      <c r="H402">
-        <v>0.001666703015875795</v>
-      </c>
-      <c r="I402">
-        <v>0.1123488123785683</v>
-      </c>
-      <c r="J402">
-        <v>-0.2469762475713705</v>
-      </c>
-      <c r="K402">
-        <v>1.34</v>
-      </c>
-      <c r="L402">
-        <v>1.91</v>
-      </c>
-      <c r="M402">
-        <v>1.39</v>
-      </c>
-      <c r="N402">
-        <v>2.01</v>
-      </c>
-      <c r="O402">
-        <v>1</v>
-      </c>
-      <c r="P402" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="403" spans="1:16">
-      <c r="A403" s="1">
-        <v>0</v>
-      </c>
-      <c r="B403" t="s">
-        <v>87</v>
-      </c>
-      <c r="C403">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D403" t="s">
-        <v>216</v>
-      </c>
-      <c r="E403">
-        <v>2.389771063585473</v>
-      </c>
-      <c r="F403">
-        <v>1</v>
-      </c>
-      <c r="G403">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H403">
-        <v>0.001630228936414526</v>
-      </c>
-      <c r="I403">
-        <v>0.1136608296253763</v>
-      </c>
-      <c r="J403">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K403">
-        <v>1.34</v>
-      </c>
-      <c r="L403">
-        <v>1.91</v>
-      </c>
-      <c r="M403">
-        <v>1.39</v>
-      </c>
-      <c r="N403">
-        <v>2.01</v>
-      </c>
-      <c r="O403">
-        <v>1</v>
-      </c>
-      <c r="P403" t="s">
-        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="400">
   <si>
     <t>trade_time</t>
   </si>
@@ -271,9 +271,6 @@
     <t>2021-05-21</t>
   </si>
   <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -661,7 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1217,9 +1214,6 @@
   </si>
   <si>
     <t>2021-06-07</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
   </si>
 </sst>
 </file>
@@ -1577,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P395"/>
+  <dimension ref="A1:P393"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1638,7 +1632,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1674,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1688,7 +1682,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1724,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1774,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1824,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1838,7 +1832,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1874,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1888,7 +1882,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1924,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1938,7 +1932,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1974,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1988,7 +1982,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2024,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2038,7 +2032,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2074,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2088,7 +2082,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2124,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2138,7 +2132,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2174,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2188,7 +2182,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2224,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2238,7 +2232,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2274,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2288,7 +2282,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2324,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2338,7 +2332,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2374,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2388,7 +2382,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2424,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2438,7 +2432,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2474,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2488,7 +2482,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2524,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2538,7 +2532,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2574,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2588,7 +2582,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2624,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2638,7 +2632,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2674,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2688,7 +2682,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2724,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2738,7 +2732,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2774,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2788,7 +2782,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2824,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2838,7 +2832,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2874,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2888,7 +2882,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2924,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2938,7 +2932,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2974,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2988,7 +2982,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3024,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3038,7 +3032,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3074,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3088,7 +3082,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3124,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3138,7 +3132,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3174,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3188,7 +3182,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3224,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3238,7 +3232,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3274,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3288,7 +3282,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3324,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3338,7 +3332,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3374,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3388,7 +3382,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3424,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3438,7 +3432,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3474,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3488,7 +3482,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3524,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3538,7 +3532,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3574,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3588,7 +3582,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3624,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3638,7 +3632,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3674,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3688,7 +3682,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3724,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3738,7 +3732,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3774,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3788,7 +3782,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3824,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3838,7 +3832,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3874,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3888,7 +3882,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3924,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3938,7 +3932,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3974,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3988,7 +3982,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4024,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4038,7 +4032,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4074,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4088,7 +4082,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4124,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4138,7 +4132,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4174,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4188,7 +4182,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4224,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4238,7 +4232,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4274,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4288,7 +4282,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4324,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4338,7 +4332,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4374,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4388,7 +4382,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4424,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4438,7 +4432,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4474,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4488,7 +4482,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4524,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4538,7 +4532,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4574,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4588,7 +4582,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4624,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4638,7 +4632,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4674,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4688,7 +4682,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4724,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4738,7 +4732,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4774,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4788,7 +4782,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4824,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4838,7 +4832,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4874,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4888,7 +4882,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4924,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4938,7 +4932,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4974,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4988,7 +4982,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5024,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5038,7 +5032,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5074,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5088,7 +5082,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5124,7 +5118,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5138,7 +5132,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5174,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5188,7 +5182,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5224,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5238,7 +5232,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5274,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5288,7 +5282,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5324,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5338,7 +5332,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5374,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5388,7 +5382,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5424,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5438,7 +5432,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5474,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5488,7 +5482,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5524,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5538,7 +5532,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5574,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5588,7 +5582,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5624,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5638,7 +5632,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5674,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5688,7 +5682,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5724,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5738,7 +5732,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5774,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5788,7 +5782,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5824,7 +5818,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5838,7 +5832,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5874,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5888,7 +5882,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5924,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5938,7 +5932,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5974,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5988,7 +5982,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6024,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6038,7 +6032,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6074,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6088,7 +6082,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6124,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6138,7 +6132,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6174,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6188,7 +6182,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6238,7 +6232,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6274,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6288,7 +6282,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6324,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6338,7 +6332,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6374,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6388,7 +6382,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6424,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6438,7 +6432,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6474,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6488,7 +6482,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6524,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6538,7 +6532,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6574,7 +6568,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6588,7 +6582,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6624,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6638,7 +6632,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6674,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6688,7 +6682,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6724,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6738,7 +6732,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6774,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6788,7 +6782,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6824,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6838,7 +6832,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6874,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6888,7 +6882,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6924,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6938,7 +6932,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6974,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6988,7 +6982,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7024,7 +7018,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7038,7 +7032,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7074,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7088,7 +7082,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7124,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7138,7 +7132,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7174,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7188,7 +7182,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7224,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7238,7 +7232,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7274,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7288,7 +7282,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7324,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7338,7 +7332,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7374,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7388,7 +7382,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7424,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7438,7 +7432,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7474,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7488,7 +7482,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7524,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7538,7 +7532,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7574,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7588,7 +7582,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7624,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7638,7 +7632,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7674,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7688,7 +7682,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7724,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7738,7 +7732,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7774,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7788,7 +7782,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7824,7 +7818,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7838,7 +7832,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7874,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7888,7 +7882,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7924,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7938,7 +7932,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7974,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7988,7 +7982,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8024,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8038,7 +8032,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8074,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8088,7 +8082,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8124,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8138,7 +8132,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8174,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8188,7 +8182,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8224,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8238,7 +8232,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8274,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8288,7 +8282,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8324,7 +8318,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8338,7 +8332,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8374,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8388,7 +8382,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8424,7 +8418,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8438,7 +8432,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8474,7 +8468,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8488,7 +8482,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8524,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8538,7 +8532,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8574,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8588,7 +8582,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8624,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8638,7 +8632,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8674,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8688,7 +8682,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8724,7 +8718,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8738,7 +8732,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8774,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8788,7 +8782,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8824,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8838,7 +8832,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8874,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8888,7 +8882,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8924,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8938,7 +8932,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8974,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8988,7 +8982,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9024,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9038,7 +9032,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9074,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9088,7 +9082,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9124,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9138,7 +9132,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9174,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9188,7 +9182,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9224,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9238,7 +9232,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9274,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9288,7 +9282,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9324,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9338,7 +9332,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9374,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9388,7 +9382,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9424,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9438,7 +9432,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9474,7 +9468,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9488,7 +9482,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9524,7 +9518,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9538,7 +9532,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9574,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9588,7 +9582,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9624,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9638,7 +9632,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9674,7 +9668,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9688,7 +9682,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9724,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9738,7 +9732,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9774,7 +9768,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9788,7 +9782,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9824,7 +9818,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9838,7 +9832,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9874,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9888,7 +9882,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9924,7 +9918,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9938,7 +9932,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9974,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9988,7 +9982,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10024,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10038,7 +10032,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10074,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10088,7 +10082,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10124,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10138,7 +10132,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10188,7 +10182,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10224,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10238,7 +10232,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10274,7 +10268,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10288,7 +10282,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10324,7 +10318,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10338,7 +10332,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10374,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10388,7 +10382,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10424,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10438,7 +10432,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10474,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10488,7 +10482,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10524,7 +10518,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10538,7 +10532,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10574,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10588,7 +10582,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10624,7 +10618,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10638,7 +10632,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10674,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10688,7 +10682,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10724,7 +10718,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10774,7 +10768,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10824,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10874,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10924,7 +10918,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10938,7 +10932,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10974,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10988,7 +10982,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11024,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11038,7 +11032,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11074,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11088,7 +11082,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11124,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11138,7 +11132,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11174,7 +11168,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11188,7 +11182,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11224,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11238,7 +11232,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11274,7 +11268,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11288,7 +11282,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11324,7 +11318,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11338,7 +11332,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11374,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11388,7 +11382,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11424,7 +11418,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11438,7 +11432,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11474,7 +11468,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11488,7 +11482,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11524,7 +11518,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11538,7 +11532,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11574,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11588,7 +11582,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11624,7 +11618,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11638,7 +11632,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11674,7 +11668,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11688,7 +11682,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11724,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11738,7 +11732,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11774,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11788,7 +11782,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11824,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11838,7 +11832,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11874,7 +11868,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11888,7 +11882,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11924,7 +11918,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11938,7 +11932,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11974,7 +11968,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11988,7 +11982,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12024,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12038,7 +12032,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12074,7 +12068,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12088,7 +12082,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12124,7 +12118,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12138,7 +12132,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12174,7 +12168,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12188,7 +12182,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12224,7 +12218,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12238,7 +12232,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12274,7 +12268,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12288,7 +12282,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12324,7 +12318,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12338,7 +12332,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12374,7 +12368,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12388,7 +12382,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12424,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12438,7 +12432,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12474,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12488,7 +12482,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12524,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12538,7 +12532,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12574,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12588,7 +12582,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12624,7 +12618,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12638,7 +12632,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12674,7 +12668,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12688,7 +12682,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12724,7 +12718,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12738,7 +12732,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12774,7 +12768,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12788,7 +12782,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12824,7 +12818,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12838,7 +12832,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12874,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12888,7 +12882,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12924,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12938,7 +12932,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12974,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12988,7 +12982,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13024,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13038,7 +13032,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13074,7 +13068,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13088,7 +13082,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13124,7 +13118,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13138,7 +13132,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13174,7 +13168,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13188,7 +13182,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13224,7 +13218,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13238,7 +13232,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13274,7 +13268,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13288,7 +13282,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13324,7 +13318,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13338,7 +13332,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13374,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13388,7 +13382,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13424,7 +13418,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13438,7 +13432,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13474,7 +13468,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13488,7 +13482,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13524,7 +13518,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13538,7 +13532,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13574,7 +13568,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13588,7 +13582,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13624,7 +13618,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13638,7 +13632,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13674,7 +13668,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13688,7 +13682,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13724,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13738,7 +13732,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13774,7 +13768,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13788,7 +13782,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13824,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13838,7 +13832,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13874,7 +13868,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13888,7 +13882,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13924,7 +13918,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13938,7 +13932,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13974,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13988,7 +13982,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14024,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14038,7 +14032,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14074,7 +14068,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14088,7 +14082,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14124,7 +14118,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14138,7 +14132,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14174,7 +14168,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14188,7 +14182,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14224,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14238,7 +14232,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14274,7 +14268,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14288,7 +14282,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14324,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14338,7 +14332,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14374,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14388,7 +14382,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14424,7 +14418,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14438,7 +14432,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14474,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14488,7 +14482,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14524,7 +14518,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14538,7 +14532,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14574,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14588,7 +14582,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14624,7 +14618,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14638,7 +14632,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14674,7 +14668,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14688,7 +14682,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14724,7 +14718,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14738,7 +14732,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14824,7 +14818,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14838,7 +14832,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14874,7 +14868,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14888,7 +14882,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14924,7 +14918,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14938,7 +14932,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14974,7 +14968,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14988,7 +14982,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15024,7 +15018,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15038,7 +15032,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15074,7 +15068,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15088,7 +15082,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15124,7 +15118,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15138,7 +15132,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15174,7 +15168,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15188,7 +15182,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15224,7 +15218,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15238,7 +15232,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15274,7 +15268,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15288,7 +15282,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15324,7 +15318,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15338,7 +15332,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15374,7 +15368,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15388,7 +15382,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15424,7 +15418,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15438,7 +15432,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15474,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15488,7 +15482,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15524,7 +15518,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15538,7 +15532,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15574,7 +15568,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15588,7 +15582,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15624,7 +15618,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15638,7 +15632,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15674,7 +15668,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15688,7 +15682,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15724,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15738,7 +15732,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15774,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15824,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15874,7 +15868,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15888,7 +15882,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15924,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15938,7 +15932,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15974,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15988,7 +15982,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16024,7 +16018,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16038,7 +16032,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16074,7 +16068,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16088,7 +16082,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16124,7 +16118,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16174,7 +16168,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16224,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16238,7 +16232,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16274,7 +16268,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16288,7 +16282,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16324,7 +16318,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16338,7 +16332,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16374,7 +16368,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16388,7 +16382,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16424,7 +16418,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16438,7 +16432,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16474,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16488,7 +16482,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16524,7 +16518,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16538,7 +16532,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16574,7 +16568,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16624,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16674,7 +16668,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16688,7 +16682,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16724,7 +16718,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16738,7 +16732,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16774,7 +16768,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16788,7 +16782,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16824,7 +16818,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16838,7 +16832,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16874,7 +16868,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16888,7 +16882,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16924,7 +16918,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16938,7 +16932,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16974,7 +16968,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16988,7 +16982,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17024,7 +17018,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17038,7 +17032,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17074,7 +17068,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17088,7 +17082,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17124,7 +17118,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17138,7 +17132,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17174,7 +17168,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17188,7 +17182,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17224,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17274,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17324,7 +17318,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17338,7 +17332,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17374,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17424,7 +17418,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17474,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17488,7 +17482,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17524,7 +17518,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17574,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17624,7 +17618,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17638,7 +17632,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17674,7 +17668,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17724,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17774,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17788,7 +17782,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17824,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17874,7 +17868,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17924,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17938,7 +17932,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17974,7 +17968,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18024,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18074,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18088,7 +18082,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18124,7 +18118,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18174,7 +18168,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18224,7 +18218,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18238,7 +18232,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18274,7 +18268,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18324,7 +18318,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18374,7 +18368,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18388,7 +18382,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18424,7 +18418,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18538,7 +18532,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18624,7 +18618,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18638,7 +18632,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18674,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18724,7 +18718,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18774,7 +18768,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18788,7 +18782,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18824,7 +18818,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18988,7 +18982,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19074,7 +19068,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19124,7 +19118,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19138,7 +19132,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19174,7 +19168,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19188,7 +19182,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19274,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19288,7 +19282,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19324,7 +19318,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19374,7 +19368,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19388,7 +19382,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19424,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19488,7 +19482,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19538,7 +19532,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19574,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19588,7 +19582,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19624,7 +19618,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19638,7 +19632,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19674,7 +19668,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19688,7 +19682,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19774,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19788,7 +19782,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19824,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19874,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19924,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19938,7 +19932,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19974,7 +19968,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19988,7 +19982,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20024,7 +20018,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20038,7 +20032,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20074,7 +20068,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20088,7 +20082,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20124,7 +20118,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20138,7 +20132,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20174,7 +20168,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20188,7 +20182,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20224,7 +20218,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20238,7 +20232,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20274,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20288,7 +20282,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20324,7 +20318,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20338,7 +20332,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20374,7 +20368,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20424,7 +20418,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20438,10 +20432,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E378">
-        <v>1.814132439228835</v>
+        <v>1.809151718357083</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20450,10 +20444,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002265867560771165</v>
+        <v>0.002250848281642917</v>
       </c>
       <c r="I378">
-        <v>0.09832690695725077</v>
+        <v>0.09334618608549872</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20465,16 +20459,16 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N378">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20488,10 +20482,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E379">
-        <v>1.845013344497358</v>
+        <v>1.839346381286305</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20500,10 +20494,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002234986655502643</v>
+        <v>0.002220653618713694</v>
       </c>
       <c r="I379">
-        <v>0.0985556544036843</v>
+        <v>0.09288869119263166</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20515,16 +20509,16 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N379">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20538,10 +20532,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E380">
-        <v>1.927350235991771</v>
+        <v>1.919853564080842</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20550,10 +20544,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002152649764008229</v>
+        <v>0.002140146435919157</v>
       </c>
       <c r="I380">
-        <v>0.09916555730364296</v>
+        <v>0.09166888539271434</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20565,16 +20559,16 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N380">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20588,10 +20582,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E381">
-        <v>1.906071062170851</v>
+        <v>1.899047260789276</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20600,10 +20594,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.00217392893782915</v>
+        <v>0.002160952739210724</v>
       </c>
       <c r="I381">
-        <v>0.0990079337938583</v>
+        <v>0.09198413241228365</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20615,16 +20609,16 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N381">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20638,10 +20632,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E382">
-        <v>1.805110086638582</v>
+        <v>1.800329862491058</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20650,10 +20644,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002274889913361419</v>
+        <v>0.002259670137508942</v>
       </c>
       <c r="I382">
-        <v>0.09826007471584131</v>
+        <v>0.0934798505683172</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20665,16 +20659,16 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N382">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20688,7 +20682,7 @@
         <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E383">
         <v>0.7959503213647137</v>
@@ -20724,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20738,7 +20732,7 @@
         <v>0.8094230769230786</v>
       </c>
       <c r="D384" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E384">
         <v>0.6894230769230785</v>
@@ -20774,7 +20768,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20788,7 +20782,7 @@
         <v>0.5957692307692326</v>
       </c>
       <c r="D385" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E385">
         <v>0.7117307692307708</v>
@@ -20824,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20838,7 +20832,7 @@
         <v>0.5115789925525314</v>
       </c>
       <c r="D386" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E386">
         <v>0.6310907217822437</v>
@@ -20888,7 +20882,7 @@
         <v>0.3546209695665004</v>
       </c>
       <c r="D387" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E387">
         <v>0.4807514106088764</v>
@@ -20924,7 +20918,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20938,7 +20932,7 @@
         <v>0.3119121628396688</v>
       </c>
       <c r="D388" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E388">
         <v>0.4398435776596825</v>
@@ -20974,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20988,7 +20982,7 @@
         <v>0.2851661111074761</v>
       </c>
       <c r="D389" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E389">
         <v>0.4142253714824617</v>
@@ -21024,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21038,7 +21032,7 @@
         <v>0.2663762565820988</v>
       </c>
       <c r="D390" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E390">
         <v>0.3962278602202027</v>
@@ -21074,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21088,7 +21082,7 @@
         <v>0.239839232334399</v>
       </c>
       <c r="D391" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E391">
         <v>0.370809867115478</v>
@@ -21124,51 +21118,51 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="392" spans="1:16">
       <c r="A392" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B392" t="s">
         <v>85</v>
       </c>
       <c r="C392">
-        <v>0.493721771458717</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D392" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="E392">
-        <v>0.3599907056193337</v>
+        <v>2.156527182350343</v>
       </c>
       <c r="F392">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G392">
-        <v>0.003686278228541283</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H392">
-        <v>0.003460009294380666</v>
+        <v>0.001903472817649657</v>
       </c>
       <c r="I392">
-        <v>0.1337310658393833</v>
+        <v>0.11808292147954</v>
       </c>
       <c r="J392">
-        <v>1.156723354015422</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K392">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="L392">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="M392">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="N392">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21182,31 +21176,31 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C393">
-        <v>2.038444260870803</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D393" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E393">
-        <v>2.169402800131033</v>
+        <v>2.292645810904945</v>
       </c>
       <c r="F393">
         <v>1</v>
       </c>
       <c r="G393">
-        <v>0.001781555739129197</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H393">
-        <v>0.001910597199868967</v>
+        <v>0.001767354189095055</v>
       </c>
       <c r="I393">
-        <v>0.1309585392602299</v>
+        <v>0.1160205180165916</v>
       </c>
       <c r="J393">
-        <v>-0.0958539260229872</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K393">
         <v>1.34</v>
@@ -21215,116 +21209,16 @@
         <v>1.91</v>
       </c>
       <c r="M393">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="N393">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="394" spans="1:16">
-      <c r="A394" s="1">
-        <v>0</v>
-      </c>
-      <c r="B394" t="s">
-        <v>86</v>
-      </c>
-      <c r="C394">
-        <v>2.176625292888353</v>
-      </c>
-      <c r="D394" t="s">
-        <v>215</v>
-      </c>
-      <c r="E394">
-        <v>2.308615033880058</v>
-      </c>
-      <c r="F394">
-        <v>1</v>
-      </c>
-      <c r="G394">
-        <v>0.001643374707111647</v>
-      </c>
-      <c r="H394">
-        <v>0.001771384966119942</v>
-      </c>
-      <c r="I394">
-        <v>0.1319897409917044</v>
-      </c>
-      <c r="J394">
-        <v>-0.1989740991704129</v>
-      </c>
-      <c r="K394">
-        <v>1.34</v>
-      </c>
-      <c r="L394">
-        <v>1.91</v>
-      </c>
-      <c r="M394">
-        <v>1.35</v>
-      </c>
-      <c r="N394">
-        <v>2.04</v>
-      </c>
-      <c r="O394">
-        <v>1</v>
-      </c>
-      <c r="P394" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="395" spans="1:16">
-      <c r="A395" s="1">
-        <v>0</v>
-      </c>
-      <c r="B395" t="s">
-        <v>86</v>
-      </c>
-      <c r="C395">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D395" t="s">
-        <v>215</v>
-      </c>
-      <c r="E395">
-        <v>2.408842399885172</v>
-      </c>
-      <c r="F395">
-        <v>1</v>
-      </c>
-      <c r="G395">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H395">
-        <v>0.001671157600114828</v>
-      </c>
-      <c r="I395">
-        <v>0.1327321659250753</v>
-      </c>
-      <c r="J395">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K395">
-        <v>1.34</v>
-      </c>
-      <c r="L395">
-        <v>1.91</v>
-      </c>
-      <c r="M395">
-        <v>1.35</v>
-      </c>
-      <c r="N395">
-        <v>2.04</v>
-      </c>
-      <c r="O395">
-        <v>1</v>
-      </c>
-      <c r="P395" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="402">
   <si>
     <t>trade_time</t>
   </si>
@@ -271,6 +271,9 @@
     <t>2021-05-21</t>
   </si>
   <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -658,7 +661,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-17</t>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1208,6 +1211,9 @@
   </si>
   <si>
     <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1571,7 +1577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P393"/>
+  <dimension ref="A1:P394"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1632,7 +1638,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1668,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1682,7 +1688,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1718,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1768,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1818,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1832,7 +1838,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1868,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1882,7 +1888,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1918,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1932,7 +1938,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1968,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1982,7 +1988,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2018,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2032,7 +2038,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2068,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2082,7 +2088,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2118,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2132,7 +2138,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2168,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2182,7 +2188,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2218,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2232,7 +2238,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2268,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2282,7 +2288,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2318,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2332,7 +2338,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2368,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2382,7 +2388,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2418,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2432,7 +2438,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2468,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2482,7 +2488,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2518,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2532,7 +2538,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2568,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2582,7 +2588,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2618,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2632,7 +2638,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2668,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2682,7 +2688,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2718,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2732,7 +2738,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2768,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2782,7 +2788,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2818,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2832,7 +2838,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2868,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2882,7 +2888,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2918,7 +2924,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2932,7 +2938,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2968,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2982,7 +2988,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3018,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3032,7 +3038,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3068,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3082,7 +3088,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3118,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3132,7 +3138,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3168,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3182,7 +3188,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3218,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3232,7 +3238,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3268,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3282,7 +3288,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3318,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3332,7 +3338,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3368,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3382,7 +3388,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3418,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3432,7 +3438,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3468,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3482,7 +3488,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3518,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3532,7 +3538,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3568,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3582,7 +3588,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3618,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3632,7 +3638,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3668,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3682,7 +3688,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3718,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3732,7 +3738,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3768,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3782,7 +3788,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3818,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3832,7 +3838,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3868,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3882,7 +3888,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3918,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3932,7 +3938,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3968,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3982,7 +3988,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4018,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4032,7 +4038,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4068,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4082,7 +4088,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4118,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4132,7 +4138,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4168,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4182,7 +4188,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4218,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4232,7 +4238,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4268,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4282,7 +4288,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4318,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4332,7 +4338,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4368,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4382,7 +4388,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4418,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4432,7 +4438,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4468,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4482,7 +4488,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4518,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4532,7 +4538,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4568,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4582,7 +4588,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4618,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4632,7 +4638,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4668,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4682,7 +4688,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4718,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4732,7 +4738,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4768,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4782,7 +4788,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4818,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4832,7 +4838,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4868,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4882,7 +4888,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4918,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4932,7 +4938,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4968,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4982,7 +4988,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5018,7 +5024,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5032,7 +5038,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5068,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5082,7 +5088,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5118,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5132,7 +5138,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5168,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5182,7 +5188,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5218,7 +5224,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5232,7 +5238,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5268,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5282,7 +5288,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5318,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5332,7 +5338,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5368,7 +5374,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5382,7 +5388,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5418,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5432,7 +5438,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5468,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5482,7 +5488,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5518,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5532,7 +5538,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5568,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5582,7 +5588,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5618,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5632,7 +5638,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5668,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5682,7 +5688,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5718,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5732,7 +5738,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5768,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5782,7 +5788,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5818,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5832,7 +5838,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5868,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5882,7 +5888,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5918,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5932,7 +5938,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5968,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5982,7 +5988,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6018,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6032,7 +6038,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6068,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6082,7 +6088,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6118,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6132,7 +6138,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6168,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6182,7 +6188,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6232,7 +6238,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6268,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6282,7 +6288,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6318,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6332,7 +6338,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6368,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6382,7 +6388,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6418,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6432,7 +6438,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6468,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6482,7 +6488,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6518,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6532,7 +6538,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6568,7 +6574,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6582,7 +6588,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6618,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6632,7 +6638,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6668,7 +6674,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6682,7 +6688,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6718,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6732,7 +6738,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6768,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6782,7 +6788,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6818,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6832,7 +6838,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6868,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6882,7 +6888,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6918,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6932,7 +6938,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6968,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6982,7 +6988,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7018,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7032,7 +7038,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7068,7 +7074,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7082,7 +7088,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7118,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7132,7 +7138,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7168,7 +7174,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7182,7 +7188,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7218,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7232,7 +7238,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7268,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7282,7 +7288,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7318,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7332,7 +7338,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7368,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7382,7 +7388,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7418,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7432,7 +7438,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7468,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7482,7 +7488,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7518,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7532,7 +7538,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7568,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7582,7 +7588,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7618,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7632,7 +7638,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7668,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7682,7 +7688,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7718,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7732,7 +7738,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7768,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7782,7 +7788,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7818,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7832,7 +7838,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7868,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7882,7 +7888,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7918,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7932,7 +7938,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7968,7 +7974,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7982,7 +7988,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8018,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8032,7 +8038,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8068,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8082,7 +8088,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8118,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8132,7 +8138,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8168,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8182,7 +8188,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8218,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8232,7 +8238,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8268,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8282,7 +8288,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8318,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8332,7 +8338,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8368,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8382,7 +8388,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8418,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8432,7 +8438,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8468,7 +8474,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8482,7 +8488,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8518,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8532,7 +8538,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8568,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8582,7 +8588,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8618,7 +8624,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8632,7 +8638,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8668,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8682,7 +8688,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8718,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8732,7 +8738,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8768,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8782,7 +8788,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8818,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8832,7 +8838,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8868,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8882,7 +8888,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8918,7 +8924,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8932,7 +8938,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8968,7 +8974,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8982,7 +8988,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9018,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9032,7 +9038,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9068,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9082,7 +9088,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9118,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9132,7 +9138,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9168,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9182,7 +9188,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9218,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9232,7 +9238,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9268,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9282,7 +9288,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9318,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9332,7 +9338,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9368,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9382,7 +9388,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9418,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9432,7 +9438,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9468,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9482,7 +9488,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9518,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9532,7 +9538,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9568,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9582,7 +9588,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9618,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9632,7 +9638,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9668,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9682,7 +9688,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9718,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9732,7 +9738,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9768,7 +9774,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9782,7 +9788,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9818,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9832,7 +9838,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9868,7 +9874,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9882,7 +9888,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9918,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9932,7 +9938,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9968,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9982,7 +9988,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10018,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10032,7 +10038,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10068,7 +10074,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10082,7 +10088,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10118,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10132,7 +10138,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10182,7 +10188,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10218,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10232,7 +10238,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10268,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10282,7 +10288,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10318,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10332,7 +10338,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10368,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10382,7 +10388,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10418,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10432,7 +10438,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10468,7 +10474,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10482,7 +10488,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10518,7 +10524,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10532,7 +10538,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10568,7 +10574,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10582,7 +10588,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10618,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10632,7 +10638,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10668,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10682,7 +10688,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10718,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10768,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10818,7 +10824,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10868,7 +10874,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10918,7 +10924,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10932,7 +10938,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10968,7 +10974,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10982,7 +10988,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11018,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11032,7 +11038,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11068,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11082,7 +11088,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11118,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11132,7 +11138,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11168,7 +11174,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11182,7 +11188,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11218,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11232,7 +11238,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11268,7 +11274,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11282,7 +11288,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11318,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11332,7 +11338,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11368,7 +11374,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11382,7 +11388,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11418,7 +11424,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11432,7 +11438,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11468,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11482,7 +11488,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11518,7 +11524,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11532,7 +11538,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11568,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11582,7 +11588,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11618,7 +11624,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11632,7 +11638,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11668,7 +11674,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11682,7 +11688,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11718,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11732,7 +11738,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11768,7 +11774,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11782,7 +11788,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11818,7 +11824,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11832,7 +11838,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11868,7 +11874,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11882,7 +11888,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11918,7 +11924,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11932,7 +11938,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11968,7 +11974,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11982,7 +11988,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12018,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12032,7 +12038,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12068,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12082,7 +12088,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12118,7 +12124,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12132,7 +12138,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12168,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12182,7 +12188,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12218,7 +12224,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12232,7 +12238,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12268,7 +12274,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12282,7 +12288,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12318,7 +12324,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12332,7 +12338,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12368,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12382,7 +12388,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12418,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12432,7 +12438,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12468,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12482,7 +12488,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12518,7 +12524,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12532,7 +12538,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12568,7 +12574,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12582,7 +12588,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12618,7 +12624,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12632,7 +12638,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12668,7 +12674,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12682,7 +12688,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12718,7 +12724,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12732,7 +12738,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12768,7 +12774,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12782,7 +12788,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12818,7 +12824,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12832,7 +12838,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12868,7 +12874,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12882,7 +12888,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12918,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12932,7 +12938,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12968,7 +12974,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12982,7 +12988,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13018,7 +13024,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13032,7 +13038,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13068,7 +13074,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13082,7 +13088,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13118,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13132,7 +13138,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13168,7 +13174,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13182,7 +13188,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13218,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13232,7 +13238,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13268,7 +13274,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13282,7 +13288,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13318,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13332,7 +13338,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13368,7 +13374,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13382,7 +13388,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13418,7 +13424,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13432,7 +13438,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13468,7 +13474,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13482,7 +13488,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13518,7 +13524,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13532,7 +13538,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13568,7 +13574,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13582,7 +13588,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13618,7 +13624,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13632,7 +13638,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13668,7 +13674,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13682,7 +13688,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13718,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13732,7 +13738,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13768,7 +13774,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13782,7 +13788,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13818,7 +13824,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13832,7 +13838,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13868,7 +13874,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13882,7 +13888,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13918,7 +13924,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13932,7 +13938,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13968,7 +13974,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13982,7 +13988,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14018,7 +14024,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14032,7 +14038,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14068,7 +14074,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14082,7 +14088,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14118,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14132,7 +14138,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14168,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14182,7 +14188,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14218,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14232,7 +14238,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14268,7 +14274,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14282,7 +14288,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14318,7 +14324,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14332,7 +14338,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14368,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14382,7 +14388,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14418,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14432,7 +14438,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14468,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14482,7 +14488,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14518,7 +14524,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14532,7 +14538,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14568,7 +14574,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14582,7 +14588,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14618,7 +14624,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14632,7 +14638,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14668,7 +14674,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14682,7 +14688,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14718,7 +14724,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14732,7 +14738,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14818,7 +14824,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14832,7 +14838,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14868,7 +14874,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14882,7 +14888,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14918,7 +14924,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14932,7 +14938,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14968,7 +14974,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14982,7 +14988,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15018,7 +15024,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15032,7 +15038,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15068,7 +15074,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15082,7 +15088,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15118,7 +15124,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15132,7 +15138,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15168,7 +15174,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15182,7 +15188,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15218,7 +15224,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15232,7 +15238,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15268,7 +15274,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15282,7 +15288,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15318,7 +15324,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15332,7 +15338,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15368,7 +15374,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15382,7 +15388,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15418,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15432,7 +15438,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15468,7 +15474,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15482,7 +15488,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15518,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15532,7 +15538,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15568,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15582,7 +15588,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15618,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15632,7 +15638,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15668,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15682,7 +15688,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15718,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15732,7 +15738,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15768,7 +15774,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15818,7 +15824,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15868,7 +15874,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15882,7 +15888,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15918,7 +15924,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15932,7 +15938,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15968,7 +15974,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15982,7 +15988,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16018,7 +16024,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16032,7 +16038,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16068,7 +16074,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16082,7 +16088,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16118,7 +16124,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16168,7 +16174,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16218,7 +16224,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16232,7 +16238,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16268,7 +16274,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16282,7 +16288,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16318,7 +16324,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16332,7 +16338,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16368,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16382,7 +16388,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16418,7 +16424,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16432,7 +16438,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16468,7 +16474,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16482,7 +16488,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16518,7 +16524,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16532,7 +16538,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16568,7 +16574,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16618,7 +16624,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16668,7 +16674,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16682,7 +16688,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16718,7 +16724,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16732,7 +16738,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16768,7 +16774,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16782,7 +16788,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16818,7 +16824,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16832,7 +16838,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16868,7 +16874,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16882,7 +16888,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16918,7 +16924,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16932,7 +16938,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16968,7 +16974,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16982,7 +16988,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17018,7 +17024,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17032,7 +17038,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17068,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17082,7 +17088,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17118,7 +17124,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17132,7 +17138,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17168,7 +17174,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17182,7 +17188,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17218,7 +17224,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17268,7 +17274,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17318,7 +17324,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17332,7 +17338,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17368,7 +17374,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17418,7 +17424,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17468,7 +17474,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17482,7 +17488,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17518,7 +17524,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17574,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17618,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17632,7 +17638,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17668,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17724,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17768,7 +17774,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17782,7 +17788,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17818,7 +17824,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17918,7 +17924,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17932,7 +17938,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17968,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +18024,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18068,7 +18074,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18082,7 +18088,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18118,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18168,7 +18174,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18218,7 +18224,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18232,7 +18238,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18268,7 +18274,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18318,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18368,7 +18374,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18382,7 +18388,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18418,7 +18424,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18532,7 +18538,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18618,7 +18624,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18632,7 +18638,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18668,7 +18674,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18718,7 +18724,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18768,7 +18774,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18782,7 +18788,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18818,7 +18824,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18982,7 +18988,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19068,7 +19074,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19118,7 +19124,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19132,7 +19138,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19168,7 +19174,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19182,7 +19188,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19268,7 +19274,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19282,7 +19288,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19318,7 +19324,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19368,7 +19374,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19382,7 +19388,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19418,7 +19424,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19482,7 +19488,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19532,7 +19538,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19568,7 +19574,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19582,7 +19588,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19618,7 +19624,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19632,7 +19638,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19668,7 +19674,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19682,7 +19688,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19768,7 +19774,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19782,7 +19788,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19818,7 +19824,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19868,7 +19874,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19918,7 +19924,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19932,7 +19938,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19968,7 +19974,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19982,7 +19988,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20018,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20032,7 +20038,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20068,7 +20074,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20082,7 +20088,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20118,7 +20124,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20132,7 +20138,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20168,7 +20174,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20182,7 +20188,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20218,7 +20224,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20232,7 +20238,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20268,7 +20274,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20282,7 +20288,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20318,7 +20324,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20332,7 +20338,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20368,7 +20374,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20418,7 +20424,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20432,10 +20438,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E378">
-        <v>1.809151718357083</v>
+        <v>1.810824811399832</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20444,10 +20450,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002250848281642917</v>
+        <v>0.002249175188600167</v>
       </c>
       <c r="I378">
-        <v>0.09334618608549872</v>
+        <v>0.09501927912824804</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20459,7 +20465,7 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N378">
         <v>2.03</v>
@@ -20468,7 +20474,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20482,10 +20488,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E379">
-        <v>1.839346381286305</v>
+        <v>1.840790726882621</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20494,10 +20500,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002220653618713694</v>
+        <v>0.002219209273117379</v>
       </c>
       <c r="I379">
-        <v>0.09288869119263166</v>
+        <v>0.09433303678894744</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20509,7 +20515,7 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N379">
         <v>2.03</v>
@@ -20518,7 +20524,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20532,10 +20538,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E380">
-        <v>1.919853564080842</v>
+        <v>1.920688006777199</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20544,10 +20550,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002140146435919157</v>
+        <v>0.0021393119932228</v>
       </c>
       <c r="I380">
-        <v>0.09166888539271434</v>
+        <v>0.09250332808907169</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20559,7 +20565,7 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N380">
         <v>2.03</v>
@@ -20568,7 +20574,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20582,10 +20588,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E381">
-        <v>1.899047260789276</v>
+        <v>1.900039326995418</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20594,10 +20600,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002160952739210724</v>
+        <v>0.002159960673004582</v>
       </c>
       <c r="I381">
-        <v>0.09198413241228365</v>
+        <v>0.09297619861842543</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20609,7 +20615,7 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N381">
         <v>2.03</v>
@@ -20618,7 +20624,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20632,10 +20638,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E382">
-        <v>1.800329862491058</v>
+        <v>1.802069787775216</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20644,10 +20650,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002259670137508942</v>
+        <v>0.002257930212224784</v>
       </c>
       <c r="I382">
-        <v>0.0934798505683172</v>
+        <v>0.09521977585247576</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20659,7 +20665,7 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N382">
         <v>2.03</v>
@@ -20668,7 +20674,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20682,7 +20688,7 @@
         <v>0.9159503213647138</v>
       </c>
       <c r="D383" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E383">
         <v>0.7959503213647137</v>
@@ -20718,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20732,7 +20738,7 @@
         <v>0.8094230769230786</v>
       </c>
       <c r="D384" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E384">
         <v>0.6894230769230785</v>
@@ -20768,7 +20774,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20782,7 +20788,7 @@
         <v>0.5957692307692326</v>
       </c>
       <c r="D385" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E385">
         <v>0.7117307692307708</v>
@@ -20818,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20832,7 +20838,7 @@
         <v>0.5115789925525314</v>
       </c>
       <c r="D386" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E386">
         <v>0.6310907217822437</v>
@@ -20882,7 +20888,7 @@
         <v>0.3546209695665004</v>
       </c>
       <c r="D387" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E387">
         <v>0.4807514106088764</v>
@@ -20918,7 +20924,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20932,7 +20938,7 @@
         <v>0.3119121628396688</v>
       </c>
       <c r="D388" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E388">
         <v>0.4398435776596825</v>
@@ -20968,7 +20974,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20982,7 +20988,7 @@
         <v>0.2851661111074761</v>
       </c>
       <c r="D389" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E389">
         <v>0.4142253714824617</v>
@@ -21018,7 +21024,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21032,7 +21038,7 @@
         <v>0.2663762565820988</v>
       </c>
       <c r="D390" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E390">
         <v>0.3962278602202027</v>
@@ -21068,7 +21074,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21076,49 +21082,49 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C391">
-        <v>0.239839232334399</v>
+        <v>0.503125172699642</v>
       </c>
       <c r="D391" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E391">
-        <v>0.370809867115478</v>
+        <v>0.5146924062397964</v>
       </c>
       <c r="F391">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.004080160767665601</v>
+        <v>0.003556874827300358</v>
       </c>
       <c r="H391">
-        <v>0.004049190132884522</v>
+        <v>0.003545307593760203</v>
       </c>
       <c r="I391">
-        <v>0.1309706347810791</v>
+        <v>-0.01156723354015443</v>
       </c>
       <c r="J391">
         <v>1.156723354015422</v>
       </c>
       <c r="K391">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="L391">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M391">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="N391">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21129,37 +21135,37 @@
         <v>85</v>
       </c>
       <c r="C392">
-        <v>2.038444260870803</v>
+        <v>0.4526076196429385</v>
       </c>
       <c r="D392" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E392">
-        <v>2.156527182350343</v>
+        <v>0.4645575619183708</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.001781555739129197</v>
+        <v>0.003607392380357061</v>
       </c>
       <c r="H392">
-        <v>0.001903472817649657</v>
+        <v>0.003595442438081629</v>
       </c>
       <c r="I392">
-        <v>0.11808292147954</v>
+        <v>-0.01194994227543233</v>
       </c>
       <c r="J392">
-        <v>-0.0958539260229872</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K392">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="L392">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="M392">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N392">
         <v>2.03</v>
@@ -21168,7 +21174,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21176,31 +21182,31 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C393">
-        <v>2.176625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D393" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E393">
-        <v>2.292645810904945</v>
+        <v>2.155568643090113</v>
       </c>
       <c r="F393">
         <v>1</v>
       </c>
       <c r="G393">
-        <v>0.001643374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H393">
-        <v>0.001767354189095055</v>
+        <v>0.001904431356909886</v>
       </c>
       <c r="I393">
-        <v>0.1160205180165916</v>
+        <v>0.11712438221931</v>
       </c>
       <c r="J393">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K393">
         <v>1.34</v>
@@ -21209,7 +21215,7 @@
         <v>1.91</v>
       </c>
       <c r="M393">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="N393">
         <v>2.03</v>
@@ -21218,7 +21224,57 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>399</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16">
+      <c r="A394" s="1">
+        <v>0</v>
+      </c>
+      <c r="B394" t="s">
+        <v>86</v>
+      </c>
+      <c r="C394">
+        <v>2.176625292888353</v>
+      </c>
+      <c r="D394" t="s">
+        <v>215</v>
+      </c>
+      <c r="E394">
+        <v>2.290656069913241</v>
+      </c>
+      <c r="F394">
+        <v>1</v>
+      </c>
+      <c r="G394">
+        <v>0.001643374707111647</v>
+      </c>
+      <c r="H394">
+        <v>0.001769343930086759</v>
+      </c>
+      <c r="I394">
+        <v>0.1140307770248876</v>
+      </c>
+      <c r="J394">
+        <v>-0.1989740991704129</v>
+      </c>
+      <c r="K394">
+        <v>1.34</v>
+      </c>
+      <c r="L394">
+        <v>1.91</v>
+      </c>
+      <c r="M394">
+        <v>1.31</v>
+      </c>
+      <c r="N394">
+        <v>2.03</v>
+      </c>
+      <c r="O394">
+        <v>1</v>
+      </c>
+      <c r="P394" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="403">
   <si>
     <t>trade_time</t>
   </si>
@@ -271,7 +271,7 @@
     <t>2021-05-21</t>
   </si>
   <si>
-    <t>2021-08-17</t>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-08-04</t>
@@ -661,7 +661,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-18</t>
+    <t>2021-08-19</t>
   </si>
   <si>
     <t>2021-04-26</t>
@@ -1195,9 +1195,6 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
     <t>2021-04-14</t>
   </si>
   <si>
@@ -1214,6 +1211,12 @@
   </si>
   <si>
     <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1577,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P394"/>
+  <dimension ref="A1:P395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -20441,7 +20444,7 @@
         <v>215</v>
       </c>
       <c r="E378">
-        <v>1.810824811399832</v>
+        <v>1.832497904442582</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20450,10 +20453,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002249175188600167</v>
+        <v>0.002267502095557418</v>
       </c>
       <c r="I378">
-        <v>0.09501927912824804</v>
+        <v>0.1166923721709974</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20465,10 +20468,10 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N378">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O378">
         <v>1</v>
@@ -20491,7 +20494,7 @@
         <v>215</v>
       </c>
       <c r="E379">
-        <v>1.840790726882621</v>
+        <v>1.862235072478937</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20500,10 +20503,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002219209273117379</v>
+        <v>0.002237764927521063</v>
       </c>
       <c r="I379">
-        <v>0.09433303678894744</v>
+        <v>0.1157773823852632</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20515,10 +20518,10 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N379">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20541,7 +20544,7 @@
         <v>215</v>
       </c>
       <c r="E380">
-        <v>1.920688006777199</v>
+        <v>1.941522449473557</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20550,10 +20553,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.0021393119932228</v>
+        <v>0.002158477550526443</v>
       </c>
       <c r="I380">
-        <v>0.09250332808907169</v>
+        <v>0.1133377707854288</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20565,10 +20568,10 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N380">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20591,7 +20594,7 @@
         <v>215</v>
       </c>
       <c r="E381">
-        <v>1.900039326995418</v>
+        <v>1.921031393201559</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20600,10 +20603,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002159960673004582</v>
+        <v>0.00217896860679844</v>
       </c>
       <c r="I381">
-        <v>0.09297619861842543</v>
+        <v>0.1139682648245672</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20615,10 +20618,10 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N381">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20641,7 +20644,7 @@
         <v>215</v>
       </c>
       <c r="E382">
-        <v>1.802069787775216</v>
+        <v>1.823809713059375</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20650,10 +20653,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002257930212224784</v>
+        <v>0.002276190286940625</v>
       </c>
       <c r="I382">
-        <v>0.09521977585247576</v>
+        <v>0.1169597011366346</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20665,10 +20668,10 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N382">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20732,81 +20735,81 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
+        <v>84</v>
+      </c>
+      <c r="C384">
+        <v>0.5115789925525314</v>
+      </c>
+      <c r="D384" t="s">
+        <v>217</v>
+      </c>
+      <c r="E384">
+        <v>0.6310907217822437</v>
+      </c>
+      <c r="F384">
+        <v>1</v>
+      </c>
+      <c r="G384">
+        <v>0.003808421007447469</v>
+      </c>
+      <c r="H384">
+        <v>0.003788909278217756</v>
+      </c>
+      <c r="I384">
+        <v>0.1195117292297123</v>
+      </c>
+      <c r="J384">
+        <v>0.9930247032816077</v>
+      </c>
+      <c r="K384">
+        <v>1.66</v>
+      </c>
+      <c r="L384">
+        <v>2.16</v>
+      </c>
+      <c r="M384">
+        <v>1.59</v>
+      </c>
+      <c r="N384">
+        <v>2.21</v>
+      </c>
+      <c r="O384">
+        <v>1</v>
+      </c>
+      <c r="P384" t="s">
         <v>83</v>
-      </c>
-      <c r="C384">
-        <v>0.8094230769230786</v>
-      </c>
-      <c r="D384" t="s">
-        <v>216</v>
-      </c>
-      <c r="E384">
-        <v>0.6894230769230785</v>
-      </c>
-      <c r="F384">
-        <v>-1</v>
-      </c>
-      <c r="G384">
-        <v>0.003730576923076922</v>
-      </c>
-      <c r="H384">
-        <v>0.003610576923076922</v>
-      </c>
-      <c r="I384">
-        <v>0.1200000000000001</v>
-      </c>
-      <c r="J384">
-        <v>0.9423076923076913</v>
-      </c>
-      <c r="K384">
-        <v>1.55</v>
-      </c>
-      <c r="L384">
-        <v>2.27</v>
-      </c>
-      <c r="M384">
-        <v>1.55</v>
-      </c>
-      <c r="N384">
-        <v>2.15</v>
-      </c>
-      <c r="O384">
-        <v>1</v>
-      </c>
-      <c r="P384" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="385" spans="1:16">
       <c r="A385" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B385" t="s">
         <v>84</v>
       </c>
       <c r="C385">
-        <v>0.5957692307692326</v>
+        <v>0.3546209695665004</v>
       </c>
       <c r="D385" t="s">
         <v>217</v>
       </c>
       <c r="E385">
-        <v>0.7117307692307708</v>
+        <v>0.4807514106088764</v>
       </c>
       <c r="F385">
         <v>1</v>
       </c>
       <c r="G385">
-        <v>0.003724230769230767</v>
+        <v>0.0039653790304335</v>
       </c>
       <c r="H385">
-        <v>0.003708269230769229</v>
+        <v>0.003939248589391124</v>
       </c>
       <c r="I385">
-        <v>0.1159615384615382</v>
+        <v>0.126130441042376</v>
       </c>
       <c r="J385">
-        <v>0.9423076923076913</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K385">
         <v>1.66</v>
@@ -20829,52 +20832,52 @@
     </row>
     <row r="386" spans="1:16">
       <c r="A386" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B386" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C386">
-        <v>0.5115789925525314</v>
+        <v>0.6052731747783824</v>
       </c>
       <c r="D386" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E386">
-        <v>0.6310907217822437</v>
+        <v>0.6361489520701504</v>
       </c>
       <c r="F386">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G386">
-        <v>0.003808421007447469</v>
+        <v>0.003454726825221617</v>
       </c>
       <c r="H386">
-        <v>0.003788909278217756</v>
+        <v>0.003463851047929849</v>
       </c>
       <c r="I386">
-        <v>0.1195117292297123</v>
+        <v>-0.03087577729176805</v>
       </c>
       <c r="J386">
-        <v>0.9930247032816077</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K386">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L386">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M386">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="N386">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O386">
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>83</v>
+        <v>393</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20882,43 +20885,43 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C387">
-        <v>0.3546209695665004</v>
+        <v>0.5715692369397383</v>
       </c>
       <c r="D387" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E387">
-        <v>0.4807514106088764</v>
+        <v>0.6027022961997404</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.0039653790304335</v>
+        <v>0.003488430763060262</v>
       </c>
       <c r="H387">
-        <v>0.003939248589391124</v>
+        <v>0.00349729770380026</v>
       </c>
       <c r="I387">
-        <v>0.126130441042376</v>
+        <v>-0.03113305926000209</v>
       </c>
       <c r="J387">
-        <v>1.087577729176807</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K387">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L387">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M387">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="N387">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O387">
         <v>1</v>
@@ -20932,43 +20935,43 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C388">
-        <v>0.3119121628396688</v>
+        <v>0.5504624129824054</v>
       </c>
       <c r="D388" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E388">
-        <v>0.4398435776596825</v>
+        <v>0.5817565930359749</v>
       </c>
       <c r="F388">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.004008087837160332</v>
+        <v>0.003509537587017594</v>
       </c>
       <c r="H388">
-        <v>0.003980156422340318</v>
+        <v>0.003518243406964025</v>
       </c>
       <c r="I388">
-        <v>0.1279314148200137</v>
+        <v>-0.03129418005356954</v>
       </c>
       <c r="J388">
-        <v>1.1133059260002</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K388">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L388">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M388">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="N388">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20982,43 +20985,43 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C389">
-        <v>0.2851661111074761</v>
+        <v>0.5356342747726197</v>
       </c>
       <c r="D389" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E389">
-        <v>0.4142253714824617</v>
+        <v>0.5670416467209203</v>
       </c>
       <c r="F389">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.004034833888892524</v>
+        <v>0.00352436572522738</v>
       </c>
       <c r="H389">
-        <v>0.004005774628517539</v>
+        <v>0.00353295835327908</v>
       </c>
       <c r="I389">
-        <v>0.1290592603749856</v>
+        <v>-0.03140737194830057</v>
       </c>
       <c r="J389">
-        <v>1.129418005356942</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K389">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L389">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M389">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="N389">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O389">
         <v>1</v>
@@ -21032,43 +21035,43 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C390">
-        <v>0.2663762565820988</v>
+        <v>0.5146924062397964</v>
       </c>
       <c r="D390" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E390">
-        <v>0.3962278602202027</v>
+        <v>0.5462596397799506</v>
       </c>
       <c r="F390">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.004053623743417901</v>
+        <v>0.003545307593760203</v>
       </c>
       <c r="H390">
-        <v>0.004023772139779798</v>
+        <v>0.003553740360220049</v>
       </c>
       <c r="I390">
-        <v>0.1298516036381039</v>
+        <v>-0.03156723354015423</v>
       </c>
       <c r="J390">
-        <v>1.140737194830061</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K390">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="L390">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="M390">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="N390">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21085,40 +21088,40 @@
         <v>85</v>
       </c>
       <c r="C391">
-        <v>0.503125172699642</v>
+        <v>0.4645575619183708</v>
       </c>
       <c r="D391" t="s">
         <v>215</v>
       </c>
       <c r="E391">
-        <v>0.5146924062397964</v>
+        <v>0.4965075041938032</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003556874827300358</v>
+        <v>0.003595442438081629</v>
       </c>
       <c r="H391">
-        <v>0.003545307593760203</v>
+        <v>0.003603492495806196</v>
       </c>
       <c r="I391">
-        <v>-0.01156723354015443</v>
+        <v>-0.03194994227543235</v>
       </c>
       <c r="J391">
-        <v>1.156723354015422</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K391">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="L391">
         <v>2.03</v>
       </c>
       <c r="M391">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N391">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O391">
         <v>1</v>
@@ -21135,40 +21138,40 @@
         <v>85</v>
       </c>
       <c r="C392">
-        <v>0.4526076196429385</v>
+        <v>0.4669894486475559</v>
       </c>
       <c r="D392" t="s">
         <v>215</v>
       </c>
       <c r="E392">
-        <v>0.4645575619183708</v>
+        <v>0.4989208269021548</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.003607392380357061</v>
+        <v>0.003593010551352444</v>
       </c>
       <c r="H392">
-        <v>0.003595442438081629</v>
+        <v>0.003601079173097845</v>
       </c>
       <c r="I392">
-        <v>-0.01194994227543233</v>
+        <v>-0.03193137825459891</v>
       </c>
       <c r="J392">
-        <v>1.194994227543228</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K392">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="L392">
         <v>2.03</v>
       </c>
       <c r="M392">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N392">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21182,43 +21185,43 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C393">
-        <v>2.038444260870803</v>
+        <v>0.4716631664178546</v>
       </c>
       <c r="D393" t="s">
         <v>215</v>
       </c>
       <c r="E393">
-        <v>2.155568643090113</v>
+        <v>0.5035588674375657</v>
       </c>
       <c r="F393">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.001781555739129197</v>
+        <v>0.003588336833582145</v>
       </c>
       <c r="H393">
-        <v>0.001904431356909886</v>
+        <v>0.003596441132562434</v>
       </c>
       <c r="I393">
-        <v>0.11712438221931</v>
+        <v>-0.03189570101971118</v>
       </c>
       <c r="J393">
-        <v>-0.0958539260229872</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K393">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="L393">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="M393">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N393">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O393">
         <v>1</v>
@@ -21235,28 +21238,28 @@
         <v>86</v>
       </c>
       <c r="C394">
-        <v>2.176625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D394" t="s">
         <v>215</v>
       </c>
       <c r="E394">
-        <v>2.290656069913241</v>
+        <v>2.174610103829883</v>
       </c>
       <c r="F394">
         <v>1</v>
       </c>
       <c r="G394">
-        <v>0.001643374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H394">
-        <v>0.001769343930086759</v>
+        <v>0.001925389896170116</v>
       </c>
       <c r="I394">
-        <v>0.1140307770248876</v>
+        <v>0.1361658429590804</v>
       </c>
       <c r="J394">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K394">
         <v>1.34</v>
@@ -21265,16 +21268,66 @@
         <v>1.91</v>
       </c>
       <c r="M394">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="N394">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16">
+      <c r="A395" s="1">
+        <v>0</v>
+      </c>
+      <c r="B395" t="s">
+        <v>86</v>
+      </c>
+      <c r="C395">
+        <v>2.176625292888353</v>
+      </c>
+      <c r="D395" t="s">
+        <v>215</v>
+      </c>
+      <c r="E395">
+        <v>2.308666328921537</v>
+      </c>
+      <c r="F395">
+        <v>1</v>
+      </c>
+      <c r="G395">
+        <v>0.001643374707111647</v>
+      </c>
+      <c r="H395">
+        <v>0.001791333671078463</v>
+      </c>
+      <c r="I395">
+        <v>0.1320410360331836</v>
+      </c>
+      <c r="J395">
+        <v>-0.1989740991704129</v>
+      </c>
+      <c r="K395">
+        <v>1.34</v>
+      </c>
+      <c r="L395">
+        <v>1.91</v>
+      </c>
+      <c r="M395">
+        <v>1.3</v>
+      </c>
+      <c r="N395">
+        <v>2.05</v>
+      </c>
+      <c r="O395">
+        <v>1</v>
+      </c>
+      <c r="P395" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="405">
   <si>
     <t>trade_time</t>
   </si>
@@ -265,964 +265,970 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2016-04-13</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2016-09-20</t>
+  </si>
+  <si>
+    <t>2016-04-29</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
+    <t>2016-10-11</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>2016-10-14</t>
+  </si>
+  <si>
+    <t>2016-10-18</t>
+  </si>
+  <si>
+    <t>2016-10-19</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>2017-02-17</t>
+  </si>
+  <si>
+    <t>2017-02-20</t>
+  </si>
+  <si>
+    <t>2017-02-21</t>
+  </si>
+  <si>
+    <t>2017-02-22</t>
+  </si>
+  <si>
+    <t>2017-02-23</t>
+  </si>
+  <si>
+    <t>2017-02-24</t>
+  </si>
+  <si>
+    <t>2017-02-27</t>
+  </si>
+  <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>2017-03-02</t>
+  </si>
+  <si>
+    <t>2017-03-03</t>
+  </si>
+  <si>
+    <t>2017-03-06</t>
+  </si>
+  <si>
+    <t>2017-03-07</t>
+  </si>
+  <si>
+    <t>2017-03-08</t>
+  </si>
+  <si>
+    <t>2017-03-09</t>
+  </si>
+  <si>
+    <t>2017-03-10</t>
+  </si>
+  <si>
+    <t>2017-03-13</t>
+  </si>
+  <si>
+    <t>2017-03-14</t>
+  </si>
+  <si>
+    <t>2017-03-16</t>
+  </si>
+  <si>
+    <t>2017-03-17</t>
+  </si>
+  <si>
+    <t>2017-03-28</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-07</t>
+  </si>
+  <si>
+    <t>2017-03-15</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-07-18</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>2017-09-26</t>
+  </si>
+  <si>
+    <t>2017-09-27</t>
+  </si>
+  <si>
+    <t>2017-09-19</t>
+  </si>
+  <si>
+    <t>2017-10-16</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2018-01-31</t>
+  </si>
+  <si>
+    <t>2018-02-22</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>2018-02-23</t>
+  </si>
+  <si>
+    <t>2018-04-04</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2017-12-28</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-09-18</t>
+  </si>
+  <si>
+    <t>2018-10-12</t>
+  </si>
+  <si>
+    <t>2018-12-13</t>
+  </si>
+  <si>
+    <t>2018-12-17</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>2019-01-04</t>
+  </si>
+  <si>
+    <t>2018-09-07</t>
+  </si>
+  <si>
+    <t>2019-01-07</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2018-12-07</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-10-31</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-21</t>
+  </si>
+  <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-03-05</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-03-04</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-17</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-10-30</t>
+  </si>
+  <si>
+    <t>2020-11-02</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-15</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2016-02-15</t>
+  </si>
+  <si>
+    <t>2016-02-24</t>
+  </si>
+  <si>
+    <t>2016-03-03</t>
+  </si>
+  <si>
+    <t>2016-03-04</t>
+  </si>
+  <si>
+    <t>2016-03-07</t>
+  </si>
+  <si>
+    <t>2016-03-08</t>
+  </si>
+  <si>
+    <t>2016-03-09</t>
+  </si>
+  <si>
+    <t>2016-03-10</t>
+  </si>
+  <si>
+    <t>2016-03-11</t>
+  </si>
+  <si>
+    <t>2016-03-15</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-07-04</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-12</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-14</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-22</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-07-28</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-08-01</t>
+  </si>
+  <si>
+    <t>2016-08-03</t>
+  </si>
+  <si>
+    <t>2016-08-04</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>2016-08-08</t>
+  </si>
+  <si>
+    <t>2016-08-10</t>
+  </si>
+  <si>
+    <t>2016-08-11</t>
+  </si>
+  <si>
+    <t>2016-08-22</t>
+  </si>
+  <si>
+    <t>2016-08-25</t>
+  </si>
+  <si>
+    <t>2016-08-26</t>
+  </si>
+  <si>
+    <t>2016-11-18</t>
+  </si>
+  <si>
+    <t>2016-11-30</t>
+  </si>
+  <si>
+    <t>2016-12-01</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>2016-12-05</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-09</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2016-12-13</t>
+  </si>
+  <si>
+    <t>2017-03-30</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-20</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-04-24</t>
+  </si>
+  <si>
+    <t>2017-05-09</t>
+  </si>
+  <si>
+    <t>2017-05-10</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-09-04</t>
+  </si>
+  <si>
+    <t>2017-09-05</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>2017-09-12</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-15</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2018-03-23</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-03-27</t>
+  </si>
+  <si>
+    <t>2018-03-28</t>
+  </si>
+  <si>
+    <t>2018-03-29</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-23</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-06</t>
+  </si>
+  <si>
+    <t>2018-06-07</t>
+  </si>
+  <si>
+    <t>2018-06-08</t>
+  </si>
+  <si>
+    <t>2018-06-11</t>
+  </si>
+  <si>
+    <t>2018-06-12</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-06-15</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-22</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>2018-07-04</t>
+  </si>
+  <si>
+    <t>2018-07-05</t>
+  </si>
+  <si>
+    <t>2018-07-06</t>
+  </si>
+  <si>
+    <t>2018-07-09</t>
+  </si>
+  <si>
+    <t>2018-07-10</t>
+  </si>
+  <si>
+    <t>2018-07-11</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-08-28</t>
+  </si>
+  <si>
+    <t>2019-08-29</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-10-25</t>
+  </si>
+  <si>
+    <t>2019-12-03</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-09</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-16</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2019-12-30</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-09</t>
+  </si>
+  <si>
+    <t>2020-01-10</t>
+  </si>
+  <si>
+    <t>2020-01-13</t>
+  </si>
+  <si>
+    <t>2020-01-14</t>
+  </si>
+  <si>
+    <t>2020-01-15</t>
+  </si>
+  <si>
+    <t>2020-01-16</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>2020-05-25</t>
+  </si>
+  <si>
+    <t>2020-05-28</t>
+  </si>
+  <si>
+    <t>2020-06-01</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>2020-06-19</t>
+  </si>
+  <si>
+    <t>2020-06-22</t>
+  </si>
+  <si>
+    <t>2020-06-23</t>
+  </si>
+  <si>
+    <t>2020-06-24</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-10-27</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
     <t>2021-04-09</t>
   </si>
   <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>2016-04-13</t>
-  </si>
-  <si>
-    <t>2016-04-19</t>
-  </si>
-  <si>
-    <t>2016-09-20</t>
-  </si>
-  <si>
-    <t>2016-04-29</t>
-  </si>
-  <si>
-    <t>2016-09-28</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-09-30</t>
-  </si>
-  <si>
-    <t>2016-10-11</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-10-13</t>
-  </si>
-  <si>
-    <t>2016-10-14</t>
-  </si>
-  <si>
-    <t>2016-10-18</t>
-  </si>
-  <si>
-    <t>2016-10-19</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-02-16</t>
-  </si>
-  <si>
-    <t>2017-02-17</t>
-  </si>
-  <si>
-    <t>2017-02-20</t>
-  </si>
-  <si>
-    <t>2017-02-21</t>
-  </si>
-  <si>
-    <t>2017-02-22</t>
-  </si>
-  <si>
-    <t>2017-02-23</t>
-  </si>
-  <si>
-    <t>2017-02-24</t>
-  </si>
-  <si>
-    <t>2017-02-27</t>
-  </si>
-  <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
-    <t>2017-03-01</t>
-  </si>
-  <si>
-    <t>2017-03-02</t>
-  </si>
-  <si>
-    <t>2017-03-03</t>
-  </si>
-  <si>
-    <t>2017-03-06</t>
-  </si>
-  <si>
-    <t>2017-03-07</t>
-  </si>
-  <si>
-    <t>2017-03-08</t>
-  </si>
-  <si>
-    <t>2017-03-09</t>
-  </si>
-  <si>
-    <t>2017-03-10</t>
-  </si>
-  <si>
-    <t>2017-03-13</t>
-  </si>
-  <si>
-    <t>2017-03-14</t>
-  </si>
-  <si>
-    <t>2017-03-16</t>
-  </si>
-  <si>
-    <t>2017-03-17</t>
-  </si>
-  <si>
-    <t>2017-03-28</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-07</t>
-  </si>
-  <si>
-    <t>2017-03-15</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-07-18</t>
-  </si>
-  <si>
-    <t>2017-09-25</t>
-  </si>
-  <si>
-    <t>2017-09-26</t>
-  </si>
-  <si>
-    <t>2017-09-27</t>
-  </si>
-  <si>
-    <t>2017-09-19</t>
-  </si>
-  <si>
-    <t>2017-10-16</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2018-01-31</t>
-  </si>
-  <si>
-    <t>2018-02-22</t>
-  </si>
-  <si>
-    <t>2018-02-01</t>
-  </si>
-  <si>
-    <t>2018-02-23</t>
-  </si>
-  <si>
-    <t>2018-04-04</t>
-  </si>
-  <si>
-    <t>2018-04-03</t>
-  </si>
-  <si>
-    <t>2017-12-28</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-09-18</t>
-  </si>
-  <si>
-    <t>2018-10-12</t>
-  </si>
-  <si>
-    <t>2018-12-13</t>
-  </si>
-  <si>
-    <t>2018-12-17</t>
-  </si>
-  <si>
-    <t>2018-12-18</t>
-  </si>
-  <si>
-    <t>2019-01-03</t>
-  </si>
-  <si>
-    <t>2019-01-04</t>
-  </si>
-  <si>
-    <t>2018-09-07</t>
-  </si>
-  <si>
-    <t>2019-01-07</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2018-12-07</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-10-31</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-21</t>
-  </si>
-  <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-03-05</t>
-  </si>
-  <si>
-    <t>2020-02-21</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-03-04</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-08-04</t>
-  </si>
-  <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-17</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-10-30</t>
-  </si>
-  <si>
-    <t>2020-11-02</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-15</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-07</t>
   </si>
   <si>
     <t>2021-06-11</t>
   </si>
   <si>
-    <t>2016-02-15</t>
-  </si>
-  <si>
-    <t>2016-02-24</t>
-  </si>
-  <si>
-    <t>2016-03-03</t>
-  </si>
-  <si>
-    <t>2016-03-04</t>
-  </si>
-  <si>
-    <t>2016-03-07</t>
-  </si>
-  <si>
-    <t>2016-03-08</t>
-  </si>
-  <si>
-    <t>2016-03-09</t>
-  </si>
-  <si>
-    <t>2016-03-10</t>
-  </si>
-  <si>
-    <t>2016-03-11</t>
-  </si>
-  <si>
-    <t>2016-03-15</t>
-  </si>
-  <si>
-    <t>2016-03-16</t>
-  </si>
-  <si>
-    <t>2016-06-27</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-07-04</t>
-  </si>
-  <si>
-    <t>2016-07-05</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-12</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-14</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-22</t>
-  </si>
-  <si>
-    <t>2016-07-25</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-07-28</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-08-01</t>
-  </si>
-  <si>
-    <t>2016-08-03</t>
-  </si>
-  <si>
-    <t>2016-08-04</t>
-  </si>
-  <si>
-    <t>2016-08-05</t>
-  </si>
-  <si>
-    <t>2016-08-08</t>
-  </si>
-  <si>
-    <t>2016-08-10</t>
-  </si>
-  <si>
-    <t>2016-08-11</t>
-  </si>
-  <si>
-    <t>2016-08-22</t>
-  </si>
-  <si>
-    <t>2016-08-25</t>
-  </si>
-  <si>
-    <t>2016-08-26</t>
-  </si>
-  <si>
-    <t>2016-11-18</t>
-  </si>
-  <si>
-    <t>2016-11-30</t>
-  </si>
-  <si>
-    <t>2016-12-01</t>
-  </si>
-  <si>
-    <t>2016-12-02</t>
-  </si>
-  <si>
-    <t>2016-12-05</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-09</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2016-12-13</t>
-  </si>
-  <si>
-    <t>2017-03-30</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-04-10</t>
-  </si>
-  <si>
-    <t>2017-04-11</t>
-  </si>
-  <si>
-    <t>2017-04-12</t>
-  </si>
-  <si>
-    <t>2017-04-13</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-20</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-04-24</t>
-  </si>
-  <si>
-    <t>2017-05-09</t>
-  </si>
-  <si>
-    <t>2017-05-10</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-09-04</t>
-  </si>
-  <si>
-    <t>2017-09-05</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-09-08</t>
-  </si>
-  <si>
-    <t>2017-09-11</t>
-  </si>
-  <si>
-    <t>2017-09-12</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-15</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2018-03-23</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-03-27</t>
-  </si>
-  <si>
-    <t>2018-03-28</t>
-  </si>
-  <si>
-    <t>2018-03-29</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-23</t>
-  </si>
-  <si>
-    <t>2018-06-04</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-06</t>
-  </si>
-  <si>
-    <t>2018-06-07</t>
-  </si>
-  <si>
-    <t>2018-06-08</t>
-  </si>
-  <si>
-    <t>2018-06-11</t>
-  </si>
-  <si>
-    <t>2018-06-12</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-14</t>
-  </si>
-  <si>
-    <t>2018-06-15</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-22</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-06-28</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-03</t>
-  </si>
-  <si>
-    <t>2018-07-04</t>
-  </si>
-  <si>
-    <t>2018-07-05</t>
-  </si>
-  <si>
-    <t>2018-07-06</t>
-  </si>
-  <si>
-    <t>2018-07-09</t>
-  </si>
-  <si>
-    <t>2018-07-10</t>
-  </si>
-  <si>
-    <t>2018-07-11</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-08-28</t>
-  </si>
-  <si>
-    <t>2019-08-29</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-10-25</t>
-  </si>
-  <si>
-    <t>2019-12-03</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-09</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-16</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2019-12-30</t>
-  </si>
-  <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-09</t>
-  </si>
-  <si>
-    <t>2020-01-10</t>
-  </si>
-  <si>
-    <t>2020-01-13</t>
-  </si>
-  <si>
-    <t>2020-01-14</t>
-  </si>
-  <si>
-    <t>2020-01-15</t>
-  </si>
-  <si>
-    <t>2020-01-16</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
-  </si>
-  <si>
-    <t>2020-05-18</t>
-  </si>
-  <si>
-    <t>2020-05-19</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>2020-05-25</t>
-  </si>
-  <si>
-    <t>2020-05-28</t>
-  </si>
-  <si>
-    <t>2020-06-01</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>2020-06-19</t>
-  </si>
-  <si>
-    <t>2020-06-22</t>
-  </si>
-  <si>
-    <t>2020-06-23</t>
-  </si>
-  <si>
-    <t>2020-06-24</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-10-27</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-07</t>
+    <t>2021-06-15</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P395"/>
+  <dimension ref="A1:P398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1641,7 +1647,7 @@
         <v>-2.893306578447853</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>-3.641148109984271</v>
@@ -1677,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1691,7 +1697,7 @@
         <v>-2.596395683063071</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>-3.641148109984271</v>
@@ -1727,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1777,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1827,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1841,7 +1847,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>-3.697130498869741</v>
@@ -1877,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1891,7 +1897,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>-3.697130498869741</v>
@@ -1927,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1941,7 +1947,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>-4.489266389421874</v>
@@ -1977,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1991,7 +1997,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>-4.489266389421874</v>
@@ -2027,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2041,7 +2047,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>-4.489266389421874</v>
@@ -2077,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2091,7 +2097,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>-4.489266389421874</v>
@@ -2127,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2141,7 +2147,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12">
         <v>-4.701411851904431</v>
@@ -2177,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2191,7 +2197,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>-4.701411851904431</v>
@@ -2227,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2241,7 +2247,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>-4.720848429424226</v>
@@ -2277,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2291,7 +2297,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>-4.720848429424226</v>
@@ -2327,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2341,7 +2347,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>-4.720848429424226</v>
@@ -2377,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2391,7 +2397,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E17">
         <v>-4.896104022270815</v>
@@ -2427,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2441,7 +2447,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18">
         <v>-4.896104022270815</v>
@@ -2477,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2491,7 +2497,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>-5.17427456360058</v>
@@ -2527,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2541,7 +2547,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20">
         <v>-5.17427456360058</v>
@@ -2577,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2591,7 +2597,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
         <v>-5.009626875608229</v>
@@ -2627,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2641,7 +2647,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>-5.009626875608229</v>
@@ -2677,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2691,7 +2697,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23">
         <v>-5.093871903520842</v>
@@ -2727,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2741,7 +2747,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24">
         <v>-5.093871903520842</v>
@@ -2777,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2791,7 +2797,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>-5.117029968483751</v>
@@ -2827,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2841,7 +2847,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26">
         <v>-5.42733388782802</v>
@@ -2877,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2891,7 +2897,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27">
         <v>-5.42733388782802</v>
@@ -2927,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2941,7 +2947,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28">
         <v>-5.200191269318666</v>
@@ -2977,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2991,7 +2997,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>-5.56384792965875</v>
@@ -3027,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3041,7 +3047,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30">
         <v>-5.56384792965875</v>
@@ -3077,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3091,7 +3097,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31">
         <v>-5.140154081961497</v>
@@ -3127,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3141,7 +3147,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>-5.140154081961497</v>
@@ -3177,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3191,7 +3197,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>-5.278966456000339</v>
@@ -3227,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3241,7 +3247,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>-5.066899264800722</v>
@@ -3277,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3291,7 +3297,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35">
         <v>-5.066899264800722</v>
@@ -3327,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3341,7 +3347,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36">
         <v>-5.339173680947644</v>
@@ -3377,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3391,7 +3397,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>-4.976752821893942</v>
@@ -3427,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,7 +3447,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>-4.976752821893942</v>
@@ -3477,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3491,7 +3497,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39">
         <v>-5.332242465048126</v>
@@ -3527,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3541,7 +3547,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>-4.857873642384104</v>
@@ -3577,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3591,7 +3597,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>-4.857873642384104</v>
@@ -3627,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3641,7 +3647,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>-5.212897748344369</v>
@@ -3677,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3691,7 +3697,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43">
         <v>3.637557788757765</v>
@@ -3727,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3741,7 +3747,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>3.637557788757765</v>
@@ -3777,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3791,7 +3797,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45">
         <v>3.696125600943092</v>
@@ -3827,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3841,7 +3847,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46">
         <v>3.696125600943092</v>
@@ -3877,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3891,7 +3897,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47">
         <v>3.562106983197164</v>
@@ -3927,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3941,7 +3947,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48">
         <v>3.562106983197164</v>
@@ -3977,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3991,7 +3997,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E49">
         <v>3.447106959801425</v>
@@ -4027,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4041,7 +4047,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E50">
         <v>3.447106959801425</v>
@@ -4077,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4091,7 +4097,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51">
         <v>2.97063976553844</v>
@@ -4127,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4141,7 +4147,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52">
         <v>2.97063976553844</v>
@@ -4177,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4191,7 +4197,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53">
         <v>2.574206073921443</v>
@@ -4227,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4241,7 +4247,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E54">
         <v>2.574206073921443</v>
@@ -4277,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4291,7 +4297,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55">
         <v>2.392623178946991</v>
@@ -4327,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4341,7 +4347,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>2.392623178946991</v>
@@ -4377,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4391,7 +4397,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>2.257085968244024</v>
@@ -4427,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4441,7 +4447,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>2.257085968244024</v>
@@ -4477,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4491,7 +4497,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59">
         <v>2.268115776754144</v>
@@ -4527,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4541,7 +4547,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>2.268115776754144</v>
@@ -4577,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4591,7 +4597,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61">
         <v>2.130900537967008</v>
@@ -4627,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4641,7 +4647,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>2.130900537967008</v>
@@ -4677,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4691,7 +4697,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>2.23740447163792</v>
@@ -4727,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4741,7 +4747,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>2.23740447163792</v>
@@ -4777,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4791,7 +4797,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>2.216035043209388</v>
@@ -4827,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4841,7 +4847,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66">
         <v>2.216035043209388</v>
@@ -4877,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4891,7 +4897,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E67">
         <v>2.308272197921324</v>
@@ -4927,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4941,7 +4947,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>2.308272197921324</v>
@@ -4977,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4991,7 +4997,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E69">
         <v>2.383994213343331</v>
@@ -5027,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5041,7 +5047,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E70">
         <v>2.383994213343331</v>
@@ -5077,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5091,7 +5097,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.341003053956531</v>
@@ -5127,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5141,7 +5147,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E72">
         <v>2.348235898796299</v>
@@ -5177,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5191,7 +5197,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73">
         <v>2.327107470902277</v>
@@ -5227,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5241,7 +5247,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E74">
         <v>2.280646125088861</v>
@@ -5277,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5291,7 +5297,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>2.302015094188537</v>
@@ -5327,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5341,7 +5347,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E76">
         <v>2.347919152567092</v>
@@ -5377,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5391,7 +5397,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77">
         <v>2.148773116010439</v>
@@ -5427,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5441,7 +5447,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E78">
         <v>2.012974927806115</v>
@@ -5477,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5491,7 +5497,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79">
         <v>2.060469575425552</v>
@@ -5527,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5541,7 +5547,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80">
         <v>1.907509472337494</v>
@@ -5577,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5591,7 +5597,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E81">
         <v>1.98668904020824</v>
@@ -5627,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5641,7 +5647,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82">
         <v>2.261468539033603</v>
@@ -5677,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5691,7 +5697,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E83">
         <v>2.508912235031609</v>
@@ -5727,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5741,7 +5747,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84">
         <v>2.586570834612932</v>
@@ -5777,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5791,7 +5797,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85">
         <v>2.299653216265908</v>
@@ -5827,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5841,7 +5847,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86">
         <v>2.61595715496026</v>
@@ -5877,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5891,7 +5897,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>2.61595715496026</v>
@@ -5927,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5941,7 +5947,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E88">
         <v>2.543317383832596</v>
@@ -5977,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5991,7 +5997,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>2.543317383832596</v>
@@ -6027,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6041,7 +6047,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E90">
         <v>2.265161259044684</v>
@@ -6077,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6091,7 +6097,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E91">
         <v>2.290570133597897</v>
@@ -6127,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6141,7 +6147,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E92">
         <v>2.195461007763983</v>
@@ -6177,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6191,7 +6197,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E93">
         <v>2.350628131035313</v>
@@ -6241,7 +6247,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E94">
         <v>1.879284692646113</v>
@@ -6277,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6291,7 +6297,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E95">
         <v>1.878152907522461</v>
@@ -6327,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6341,7 +6347,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E96">
         <v>1.878152907522461</v>
@@ -6377,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6391,7 +6397,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>1.878152907522461</v>
@@ -6427,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6441,7 +6447,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E98">
         <v>2.076228086890248</v>
@@ -6477,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6491,7 +6497,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E99">
         <v>2.078321265243905</v>
@@ -6527,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6541,7 +6547,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>2.078321265243905</v>
@@ -6577,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6591,7 +6597,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E101">
         <v>2.078321265243905</v>
@@ -6627,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6641,7 +6647,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D102" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E102">
         <v>2.102213303799785</v>
@@ -6677,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6691,7 +6697,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E103">
         <v>2.092366071428574</v>
@@ -6727,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6741,7 +6747,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E104">
         <v>2.092366071428574</v>
@@ -6777,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6791,7 +6797,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105">
         <v>2.092366071428574</v>
@@ -6827,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6841,7 +6847,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E106">
         <v>2.352465933358952</v>
@@ -6877,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6891,7 +6897,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E107">
         <v>2.352465933358952</v>
@@ -6927,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6941,7 +6947,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E108">
         <v>2.316305612395345</v>
@@ -6977,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6991,7 +6997,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D109" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E109">
         <v>2.316305612395345</v>
@@ -7027,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7041,7 +7047,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E110">
         <v>2.316305612395345</v>
@@ -7077,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7091,7 +7097,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E111">
         <v>1.660853987552378</v>
@@ -7127,7 +7133,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7141,7 +7147,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E112">
         <v>1.706062187746931</v>
@@ -7177,7 +7183,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7191,7 +7197,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E113">
         <v>1.706062187746931</v>
@@ -7227,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7241,7 +7247,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E114">
         <v>1.706062187746931</v>
@@ -7277,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7291,7 +7297,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E115">
         <v>0.8890067354016997</v>
@@ -7327,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7341,7 +7347,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E116">
         <v>0.9778684643520892</v>
@@ -7377,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7391,7 +7397,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D117" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E117">
         <v>0.9778684643520892</v>
@@ -7427,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7441,7 +7447,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E118">
         <v>0.9778684643520892</v>
@@ -7477,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7491,7 +7497,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D119" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E119">
         <v>0.9778684643520892</v>
@@ -7527,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7541,7 +7547,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E120">
         <v>0.3875605450183359</v>
@@ -7577,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7591,7 +7597,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E121">
         <v>0.5227816757955743</v>
@@ -7627,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7641,7 +7647,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E122">
         <v>0.5227816757955743</v>
@@ -7677,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7691,7 +7697,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D123" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E123">
         <v>0.5227816757955743</v>
@@ -7727,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7741,7 +7747,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D124" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E124">
         <v>0.0491242407754946</v>
@@ -7777,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7791,7 +7797,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D125" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E125">
         <v>0.159781143472614</v>
@@ -7827,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7841,7 +7847,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E126">
         <v>0.159781143472614</v>
@@ -7877,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7891,7 +7897,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E127">
         <v>-0.4676849642004726</v>
@@ -7927,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7941,7 +7947,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E128">
         <v>-0.3747925900670488</v>
@@ -7977,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7991,7 +7997,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129">
         <v>-0.8235135484933682</v>
@@ -8027,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8041,7 +8047,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>-0.2477467025920381</v>
@@ -8077,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8091,7 +8097,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>-0.8406732630037332</v>
@@ -8127,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8141,7 +8147,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>-0.2128000927823077</v>
@@ -8177,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8191,7 +8197,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D133" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E133">
         <v>0.387889534694934</v>
@@ -8227,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8241,7 +8247,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D134" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E134">
         <v>0.3268838700002261</v>
@@ -8277,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8291,7 +8297,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E135">
         <v>0.3619408673861413</v>
@@ -8327,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8341,7 +8347,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E136">
         <v>0.2887690811642036</v>
@@ -8377,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8391,7 +8397,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D137" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E137">
         <v>0.2054001299670292</v>
@@ -8427,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8441,7 +8447,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D138" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E138">
         <v>0.09424712584458561</v>
@@ -8477,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8491,7 +8497,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E139">
         <v>0.04964505068482161</v>
@@ -8527,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8541,7 +8547,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D140" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E140">
         <v>-0.06178174348131638</v>
@@ -8577,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8591,7 +8597,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E141">
         <v>-0.07084042392839685</v>
@@ -8627,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8641,7 +8647,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E142">
         <v>3.461981920657827</v>
@@ -8677,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8691,7 +8697,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E143">
         <v>3.521227138526164</v>
@@ -8727,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8741,7 +8747,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E144">
         <v>3.704772068908834</v>
@@ -8777,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8791,7 +8797,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E145">
         <v>4.126616365519087</v>
@@ -8827,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8841,7 +8847,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E146">
         <v>4.245160231267613</v>
@@ -8877,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8891,7 +8897,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E147">
         <v>4.229152349958373</v>
@@ -8927,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8941,7 +8947,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E148">
         <v>4.113073707261234</v>
@@ -8977,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8991,7 +8997,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E149">
         <v>3.642839509755204</v>
@@ -9027,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9041,7 +9047,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E150">
         <v>3.168034739342359</v>
@@ -9077,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9091,7 +9097,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D151" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E151">
         <v>2.998232417988513</v>
@@ -9127,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9141,7 +9147,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E152">
         <v>3.034053936494125</v>
@@ -9177,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9191,7 +9197,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D153" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E153">
         <v>2.914701276953577</v>
@@ -9227,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9241,7 +9247,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D154" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E154">
         <v>2.942385732505037</v>
@@ -9277,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9291,7 +9297,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E155">
         <v>2.891667239770102</v>
@@ -9327,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9341,7 +9347,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E156">
         <v>0.6731330742884634</v>
@@ -9377,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9391,7 +9397,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E157">
         <v>0.5049958305736757</v>
@@ -9427,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9441,7 +9447,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D158" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E158">
         <v>4.999995484409007</v>
@@ -9477,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9491,7 +9497,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E159">
         <v>4.49533934056099</v>
@@ -9527,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9541,7 +9547,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E160">
         <v>4.49533934056099</v>
@@ -9577,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9591,7 +9597,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E161">
         <v>5.75883309709841</v>
@@ -9627,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9641,7 +9647,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E162">
         <v>5.616961120807806</v>
@@ -9677,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9691,7 +9697,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D163" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E163">
         <v>-3.423739939881703</v>
@@ -9727,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9741,7 +9747,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D164" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E164">
         <v>-3.743311354600991</v>
@@ -9777,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9791,7 +9797,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D165" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E165">
         <v>-4.132985698695919</v>
@@ -9827,7 +9833,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9841,7 +9847,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D166" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E166">
         <v>-4.233476466219281</v>
@@ -9877,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9891,7 +9897,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D167" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E167">
         <v>-4.275085629955039</v>
@@ -9927,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9941,7 +9947,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D168" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E168">
         <v>-4.152544959638887</v>
@@ -9977,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9991,7 +9997,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D169" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E169">
         <v>-3.975060706658394</v>
@@ -10027,7 +10033,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10041,7 +10047,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D170" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E170">
         <v>-4.047254516344427</v>
@@ -10077,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10091,7 +10097,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D171" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E171">
         <v>-3.79843891093761</v>
@@ -10127,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10141,7 +10147,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E172">
         <v>-3.666707344934939</v>
@@ -10191,7 +10197,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D173" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E173">
         <v>-3.713489605052797</v>
@@ -10227,7 +10233,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10241,7 +10247,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E174">
         <v>-3.548252121908546</v>
@@ -10277,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10291,7 +10297,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E175">
         <v>-3.286247287427305</v>
@@ -10327,7 +10333,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10341,7 +10347,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D176" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E176">
         <v>1.158519820616992</v>
@@ -10377,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10391,7 +10397,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E177">
         <v>1.172691348768068</v>
@@ -10427,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10441,7 +10447,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D178" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E178">
         <v>1.000464874270701</v>
@@ -10477,7 +10483,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10491,7 +10497,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D179" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E179">
         <v>0.3824058924251874</v>
@@ -10527,7 +10533,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10541,7 +10547,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D180" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E180">
         <v>0.3824058924251874</v>
@@ -10577,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10591,7 +10597,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D181" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E181">
         <v>0.3824058924251874</v>
@@ -10627,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10641,7 +10647,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D182" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E182">
         <v>0.0213012212570054</v>
@@ -10677,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10691,7 +10697,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D183" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E183">
         <v>0.0213012212570054</v>
@@ -10727,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10777,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10827,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10877,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10927,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10941,7 +10947,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D188" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>1.582625511992627</v>
@@ -10977,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10991,7 +10997,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>1.559453546602203</v>
@@ -11027,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11041,7 +11047,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>1.547361538049228</v>
@@ -11077,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11091,7 +11097,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E191">
         <v>1.401993513086136</v>
@@ -11127,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11141,7 +11147,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D192" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E192">
         <v>1.434633300285655</v>
@@ -11177,7 +11183,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11191,7 +11197,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D193" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E193">
         <v>1.425858209046284</v>
@@ -11227,7 +11233,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11241,7 +11247,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D194" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E194">
         <v>1.475198819417429</v>
@@ -11277,7 +11283,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11291,7 +11297,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D195" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E195">
         <v>1.441005693114453</v>
@@ -11327,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11341,7 +11347,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E196">
         <v>1.488718514152899</v>
@@ -11377,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11391,7 +11397,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D197" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E197">
         <v>1.446244175787084</v>
@@ -11427,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11441,7 +11447,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E198">
         <v>1.493394055403994</v>
@@ -11477,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11491,7 +11497,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D199" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E199">
         <v>1.446322000480185</v>
@@ -11527,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11541,7 +11547,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D200" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E200">
         <v>1.493463516846493</v>
@@ -11577,7 +11583,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11591,7 +11597,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D201" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E201">
         <v>1.435847306141142</v>
@@ -11627,7 +11633,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11641,7 +11647,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D202" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E202">
         <v>1.484114461302094</v>
@@ -11677,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11691,7 +11697,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D203" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E203">
         <v>1.466561985673455</v>
@@ -11727,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11741,7 +11747,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D204" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E204">
         <v>1.511528458854815</v>
@@ -11777,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11791,7 +11797,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D205" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E205">
         <v>1.479399782082176</v>
@@ -11827,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11841,7 +11847,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D206" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E206">
         <v>1.522986671171852</v>
@@ -11877,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11891,7 +11897,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D207" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E207">
         <v>1.459395439652966</v>
@@ -11927,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11941,7 +11947,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D208" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E208">
         <v>1.505132049123094</v>
@@ -11977,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11991,7 +11997,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D209" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E209">
         <v>1.397112808581932</v>
@@ -12027,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12041,7 +12047,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D210" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E210">
         <v>1.449542476913426</v>
@@ -12077,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12091,7 +12097,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E211">
         <v>1.294143898865006</v>
@@ -12127,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12141,7 +12147,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D212" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E212">
         <v>1.357638882867572</v>
@@ -12177,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12191,7 +12197,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D213" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E213">
         <v>1.18030319903414</v>
@@ -12227,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12241,7 +12247,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D214" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E214">
         <v>1.18030319903414</v>
@@ -12277,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12291,7 +12297,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D215" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E215">
         <v>1.188653245722397</v>
@@ -12327,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12341,7 +12347,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D216" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E216">
         <v>0.9564817011303721</v>
@@ -12377,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12391,7 +12397,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D217" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E217">
         <v>0.9564817011303721</v>
@@ -12427,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12441,7 +12447,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D218" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E218">
         <v>0.9595778612972841</v>
@@ -12477,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12491,7 +12497,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D219" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E219">
         <v>0.7699303832078415</v>
@@ -12527,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12541,7 +12547,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D220" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E220">
         <v>0.7699303832078415</v>
@@ -12577,7 +12583,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12591,7 +12597,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E221">
         <v>0.7699303832078415</v>
@@ -12627,7 +12633,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12641,7 +12647,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E222">
         <v>0.7947444579985703</v>
@@ -12677,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12691,7 +12697,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E223">
         <v>0.681784458813524</v>
@@ -12727,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12741,7 +12747,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D224" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E224">
         <v>0.681784458813524</v>
@@ -12777,7 +12783,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12791,7 +12797,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D225" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E225">
         <v>0.6868602979367258</v>
@@ -12827,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12841,7 +12847,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E226">
         <v>0.6904864136981455</v>
@@ -12877,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12891,7 +12897,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D227" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E227">
         <v>0.6904864136981455</v>
@@ -12927,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12941,7 +12947,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D228" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E228">
         <v>0.6988520528231206</v>
@@ -12977,7 +12983,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12991,7 +12997,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D229" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E229">
         <v>0.5364590093992025</v>
@@ -13027,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13041,7 +13047,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D230" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E230">
         <v>0.5584533336781012</v>
@@ -13077,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13091,7 +13097,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D231" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E231">
         <v>0.4349435599285871</v>
@@ -13127,7 +13133,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13141,7 +13147,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D232" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E232">
         <v>0.4687561007130205</v>
@@ -13177,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13191,7 +13197,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D233" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E233">
         <v>0.4011997840155024</v>
@@ -13227,7 +13233,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13241,7 +13247,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E234">
         <v>0.4389407046823544</v>
@@ -13277,7 +13283,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13291,7 +13297,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D235" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E235">
         <v>0.3332852216938216</v>
@@ -13327,7 +13333,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13341,7 +13347,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D236" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E236">
         <v>0.3789326137951377</v>
@@ -13377,7 +13383,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13391,7 +13397,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E237">
         <v>0.3201663194080338</v>
@@ -13427,7 +13433,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13441,7 +13447,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D238" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E238">
         <v>0.3201663194080338</v>
@@ -13477,7 +13483,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13491,7 +13497,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D239" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E239">
         <v>0.3673409867008299</v>
@@ -13527,7 +13533,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13541,7 +13547,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D240" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E240">
         <v>0.385066244864444</v>
@@ -13577,7 +13583,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13591,7 +13597,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D241" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E241">
         <v>0.385066244864444</v>
@@ -13627,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13641,7 +13647,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D242" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E242">
         <v>0.385066244864444</v>
@@ -13677,7 +13683,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13691,7 +13697,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D243" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E243">
         <v>0.4246853984473891</v>
@@ -13727,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13741,7 +13747,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D244" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E244">
         <v>0.3952650685155521</v>
@@ -13777,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13791,7 +13797,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D245" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E245">
         <v>0.3952650685155521</v>
@@ -13827,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13841,7 +13847,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D246" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E246">
         <v>0.3952650685155521</v>
@@ -13877,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13891,7 +13897,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D247" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E247">
         <v>0.4336968963600101</v>
@@ -13927,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13941,7 +13947,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D248" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E248">
         <v>0.441533745152785</v>
@@ -13977,7 +13983,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13991,7 +13997,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D249" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E249">
         <v>0.441533745152785</v>
@@ -14027,7 +14033,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14041,7 +14047,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D250" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E250">
         <v>0.441533745152785</v>
@@ -14077,7 +14083,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14091,7 +14097,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D251" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E251">
         <v>0.4745790703439532</v>
@@ -14127,7 +14133,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14141,7 +14147,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E252">
         <v>0.5262223068621856</v>
@@ -14177,7 +14183,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14191,7 +14197,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E253">
         <v>0.5262223068621856</v>
@@ -14227,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14241,7 +14247,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D254" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E254">
         <v>0.5494083666603191</v>
@@ -14277,7 +14283,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14291,7 +14297,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D255" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E255">
         <v>1.134910071595908</v>
@@ -14327,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14341,7 +14347,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D256" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E256">
         <v>1.119751573421224</v>
@@ -14377,7 +14383,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14391,7 +14397,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D257" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E257">
         <v>1.055413005631895</v>
@@ -14427,7 +14433,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14441,7 +14447,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D258" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E258">
         <v>1.03217696150402</v>
@@ -14477,7 +14483,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14491,7 +14497,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D259" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E259">
         <v>0.897246951281871</v>
@@ -14527,7 +14533,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14541,7 +14547,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D260" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E260">
         <v>0.8706167327436121</v>
@@ -14577,7 +14583,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14591,7 +14597,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D261" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E261">
         <v>1.412833444305319</v>
@@ -14627,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14641,7 +14647,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D262" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E262">
         <v>1.399053391868887</v>
@@ -14677,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14691,7 +14697,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E263">
         <v>1.480439984508878</v>
@@ -14727,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14741,7 +14747,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D264" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E264">
         <v>1.457637705051676</v>
@@ -14827,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14841,7 +14847,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D266" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E266">
         <v>1.2222369081479</v>
@@ -14877,7 +14883,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14891,7 +14897,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E267">
         <v>1.311393675757068</v>
@@ -14927,7 +14933,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14941,7 +14947,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D268" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E268">
         <v>1.084160634764066</v>
@@ -14977,7 +14983,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14991,7 +14997,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D269" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E269">
         <v>1.193914185004133</v>
@@ -15027,7 +15033,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15041,7 +15047,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D270" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E270">
         <v>0.8573351083141707</v>
@@ -15077,7 +15083,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15091,7 +15097,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D271" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E271">
         <v>0.988341401428052</v>
@@ -15127,7 +15133,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15141,7 +15147,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E272">
         <v>0.7856322541233942</v>
@@ -15177,7 +15183,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15191,7 +15197,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D273" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E273">
         <v>0.9271686010995708</v>
@@ -15227,7 +15233,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15241,7 +15247,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E274">
         <v>0.666724382278634</v>
@@ -15277,7 +15283,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15291,7 +15297,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D275" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E275">
         <v>0.8120247704726087</v>
@@ -15327,7 +15333,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15341,7 +15347,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D276" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E276">
         <v>0.5554941770903916</v>
@@ -15377,7 +15383,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15391,7 +15397,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D277" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E277">
         <v>0.5343135639758354</v>
@@ -15427,7 +15433,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15441,7 +15447,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D278" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E278">
         <v>0.5543280182232331</v>
@@ -15477,7 +15483,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15491,7 +15497,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D279" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E279">
         <v>0.6169560865757506</v>
@@ -15527,7 +15533,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15541,7 +15547,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D280" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E280">
         <v>0.6169560865757506</v>
@@ -15577,7 +15583,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15591,7 +15597,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D281" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E281">
         <v>0.8673239084198645</v>
@@ -15627,7 +15633,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15641,7 +15647,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D282" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E282">
         <v>0.7616569728121176</v>
@@ -15677,7 +15683,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15691,7 +15697,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D283" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E283">
         <v>0.9495779791694832</v>
@@ -15727,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15741,7 +15747,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D284" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E284">
         <v>0.9388491310062772</v>
@@ -15777,7 +15783,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15827,7 +15833,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15877,7 +15883,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15891,7 +15897,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D287" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E287">
         <v>0.9972247567745822</v>
@@ -15927,7 +15933,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15941,7 +15947,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D288" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E288">
         <v>1.155095366349694</v>
@@ -15977,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +15997,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D289" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E289">
         <v>1.155095366349694</v>
@@ -16027,7 +16033,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16041,7 +16047,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D290" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E290">
         <v>1.155095366349694</v>
@@ -16077,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16091,7 +16097,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D291" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E291">
         <v>1.266654823722328</v>
@@ -16127,7 +16133,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16177,7 +16183,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16227,7 +16233,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16241,7 +16247,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D294" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E294">
         <v>1.216516290726816</v>
@@ -16277,7 +16283,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16291,7 +16297,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D295" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E295">
         <v>1.377468671679197</v>
@@ -16327,7 +16333,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16341,7 +16347,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D296" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E296">
         <v>1.377468671679197</v>
@@ -16377,7 +16383,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16397,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D297" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E297">
         <v>1.098022759601705</v>
@@ -16427,7 +16433,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16447,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D298" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E298">
         <v>1.26116642958748</v>
@@ -16477,7 +16483,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16491,7 +16497,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E299">
         <v>1.26116642958748</v>
@@ -16527,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16541,7 +16547,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D300" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E300">
         <v>0.8607264291791745</v>
@@ -16577,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16627,7 +16633,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16677,7 +16683,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16691,7 +16697,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D303" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E303">
         <v>0.824097311139564</v>
@@ -16727,7 +16733,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16741,7 +16747,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D304" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E304">
         <v>1.040422535211267</v>
@@ -16777,7 +16783,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16791,7 +16797,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D305" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E305">
         <v>1.040422535211267</v>
@@ -16827,7 +16833,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16841,7 +16847,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D306" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E306">
         <v>1.040422535211267</v>
@@ -16877,7 +16883,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16891,7 +16897,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D307" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E307">
         <v>0.6892070138707138</v>
@@ -16927,7 +16933,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16941,7 +16947,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D308" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E308">
         <v>0.904611358283171</v>
@@ -16977,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16991,7 +16997,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D309" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E309">
         <v>0.6020667096198637</v>
@@ -17027,7 +17033,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17041,7 +17047,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D310" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E310">
         <v>0.7705397234474891</v>
@@ -17077,7 +17083,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17091,7 +17097,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D311" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E311">
         <v>0.5104188656556885</v>
@@ -17127,7 +17133,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17141,7 +17147,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D312" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E312">
         <v>0.4186576811044649</v>
@@ -17177,7 +17183,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17197,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D313" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E313">
         <v>0.1677359829666414</v>
@@ -17227,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17277,7 +17283,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17327,7 +17333,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17347,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D316" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E316">
         <v>1.515642348344327</v>
@@ -17377,7 +17383,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17427,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17477,7 +17483,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17497,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D319" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E319">
         <v>1.493247566063977</v>
@@ -17527,7 +17533,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17577,7 +17583,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17627,7 +17633,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17647,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D322" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E322">
         <v>1.414710468897303</v>
@@ -17677,7 +17683,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17727,7 +17733,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17777,7 +17783,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17791,7 +17797,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D325" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E325">
         <v>1.396497005988024</v>
@@ -17827,7 +17833,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17877,7 +17883,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17927,7 +17933,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17947,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D328" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E328">
         <v>1.376951717138971</v>
@@ -17977,7 +17983,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18027,7 +18033,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18077,7 +18083,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18097,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D331" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E331">
         <v>1.359032433928708</v>
@@ -18127,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18177,7 +18183,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18227,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18241,7 +18247,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D334" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E334">
         <v>1.335880304635819</v>
@@ -18277,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18327,7 +18333,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18377,7 +18383,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18391,7 +18397,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D337" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E337">
         <v>1.309957507300225</v>
@@ -18427,7 +18433,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18541,7 +18547,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D340" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E340">
         <v>1.320449616201756</v>
@@ -18627,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18647,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D342" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E342">
         <v>1.284476712309384</v>
@@ -18677,7 +18683,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18727,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18777,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18797,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D345" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E345">
         <v>1.24169474125916</v>
@@ -18827,7 +18833,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18991,7 +18997,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D349" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E349">
         <v>1.182114445177575</v>
@@ -19077,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19127,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19147,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D352" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E352">
         <v>1.151200461638077</v>
@@ -19177,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19191,7 +19197,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D353" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E353">
         <v>1.119879175702464</v>
@@ -19277,7 +19283,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19291,7 +19297,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D355" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E355">
         <v>1.094826807940879</v>
@@ -19327,7 +19333,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19377,7 +19383,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19391,7 +19397,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D357" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E357">
         <v>1.064947268845516</v>
@@ -19427,7 +19433,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19491,7 +19497,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E359">
         <v>1.014148422477695</v>
@@ -19541,7 +19547,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D360" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E360">
         <v>0.7662610529884266</v>
@@ -19577,7 +19583,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19591,7 +19597,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D361" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E361">
         <v>0.7460729511326034</v>
@@ -19627,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19647,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D362" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E362">
         <v>0.7067614879649891</v>
@@ -19677,7 +19683,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19697,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D363" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E363">
         <v>0.6717864324675069</v>
@@ -19777,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,7 +19797,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D365" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E365">
         <v>0.5671969948491258</v>
@@ -19827,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19877,7 +19883,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19927,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,7 +19947,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D368" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E368">
         <v>0.605257854179015</v>
@@ -19977,7 +19983,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,7 +19997,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D369" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E369">
         <v>0.4201630112625956</v>
@@ -20027,7 +20033,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20041,7 +20047,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D370" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E370">
         <v>0.4201630112625956</v>
@@ -20077,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20091,7 +20097,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D371" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E371">
         <v>0.4879084704937777</v>
@@ -20127,7 +20133,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20141,7 +20147,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D372" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E372">
         <v>0.4879084704937777</v>
@@ -20177,7 +20183,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20197,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D373" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E373">
         <v>0.549200546946218</v>
@@ -20227,7 +20233,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20241,7 +20247,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D374" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E374">
         <v>0.549200546946218</v>
@@ -20277,7 +20283,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20291,7 +20297,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D375" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E375">
         <v>0.5264173880682987</v>
@@ -20327,7 +20333,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20341,7 +20347,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D376" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E376">
         <v>0.444542315946628</v>
@@ -20377,7 +20383,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20427,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20441,10 +20447,10 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D378" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E378">
-        <v>1.832497904442582</v>
+        <v>1.849151718357083</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20453,10 +20459,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002267502095557418</v>
+        <v>0.002290848281642917</v>
       </c>
       <c r="I378">
-        <v>0.1166923721709974</v>
+        <v>0.1333461860854988</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20468,16 +20474,16 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N378">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20491,10 +20497,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E379">
-        <v>1.862235072478937</v>
+        <v>1.879346381286305</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20503,10 +20509,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002237764927521063</v>
+        <v>0.002260653618713694</v>
       </c>
       <c r="I379">
-        <v>0.1157773823852632</v>
+        <v>0.1328886911926317</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20518,16 +20524,16 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N379">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20541,10 +20547,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E380">
-        <v>1.941522449473557</v>
+        <v>1.959853564080842</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20553,10 +20559,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002158477550526443</v>
+        <v>0.002180146435919158</v>
       </c>
       <c r="I380">
-        <v>0.1133377707854288</v>
+        <v>0.1316688853927144</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20568,16 +20574,16 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N380">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20591,10 +20597,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E381">
-        <v>1.921031393201559</v>
+        <v>1.939047260789276</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20603,10 +20609,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.00217896860679844</v>
+        <v>0.002200952739210724</v>
       </c>
       <c r="I381">
-        <v>0.1139682648245672</v>
+        <v>0.1319841324122837</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20618,16 +20624,16 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N381">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,10 +20647,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E382">
-        <v>1.823809713059375</v>
+        <v>1.840329862491058</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20653,10 +20659,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002276190286940625</v>
+        <v>0.002299670137508942</v>
       </c>
       <c r="I382">
-        <v>0.1169597011366346</v>
+        <v>0.1334798505683172</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20668,16 +20674,16 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N382">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20688,46 +20694,46 @@
         <v>83</v>
       </c>
       <c r="C383">
-        <v>0.9159503213647138</v>
+        <v>0.924345430822018</v>
       </c>
       <c r="D383" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E383">
-        <v>0.7959503213647137</v>
+        <v>0.9168738220654336</v>
       </c>
       <c r="F383">
         <v>-1</v>
       </c>
       <c r="G383">
-        <v>0.003624049678635286</v>
+        <v>0.003195654569177983</v>
       </c>
       <c r="H383">
-        <v>0.003504049678635286</v>
+        <v>0.003223126177934567</v>
       </c>
       <c r="I383">
-        <v>0.1200000000000001</v>
+        <v>0.00747160875658448</v>
       </c>
       <c r="J383">
         <v>0.8735804378292169</v>
       </c>
       <c r="K383">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="L383">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="M383">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="N383">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O383">
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20738,46 +20744,46 @@
         <v>84</v>
       </c>
       <c r="C384">
-        <v>0.5115789925525314</v>
+        <v>0.8250000000000011</v>
       </c>
       <c r="D384" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E384">
-        <v>0.6310907217822437</v>
+        <v>0.8261538461538473</v>
       </c>
       <c r="F384">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.003808421007447469</v>
+        <v>0.003274999999999999</v>
       </c>
       <c r="H384">
-        <v>0.003788909278217756</v>
+        <v>0.003313846153846152</v>
       </c>
       <c r="I384">
-        <v>0.1195117292297123</v>
+        <v>-0.001153846153846283</v>
       </c>
       <c r="J384">
-        <v>0.9930247032816077</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K384">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="L384">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="M384">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="N384">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="O384">
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>83</v>
+        <v>390</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20788,96 +20794,96 @@
         <v>84</v>
       </c>
       <c r="C385">
-        <v>0.3546209695665004</v>
+        <v>0.7590678857339097</v>
       </c>
       <c r="D385" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E385">
-        <v>0.4807514106088764</v>
+        <v>0.7592073916682776</v>
       </c>
       <c r="F385">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.0039653790304335</v>
+        <v>0.00334093211426609</v>
       </c>
       <c r="H385">
-        <v>0.003939248589391124</v>
+        <v>0.003380792608331722</v>
       </c>
       <c r="I385">
-        <v>0.126130441042376</v>
+        <v>-0.0001395059343678451</v>
       </c>
       <c r="J385">
-        <v>1.087577729176807</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K385">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="L385">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="M385">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="N385">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="386" spans="1:16">
       <c r="A386" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C386">
-        <v>0.6052731747783824</v>
+        <v>0.6361489520701504</v>
       </c>
       <c r="D386" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E386">
-        <v>0.6361489520701504</v>
+        <v>0.6343973974866144</v>
       </c>
       <c r="F386">
         <v>-1</v>
       </c>
       <c r="G386">
-        <v>0.003454726825221617</v>
+        <v>0.003463851047929849</v>
       </c>
       <c r="H386">
-        <v>0.003463851047929849</v>
+        <v>0.003505602602513386</v>
       </c>
       <c r="I386">
-        <v>-0.03087577729176805</v>
+        <v>0.001751554583536041</v>
       </c>
       <c r="J386">
         <v>1.087577729176807</v>
       </c>
       <c r="K386">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L386">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M386">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N386">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O386">
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20885,49 +20891,49 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C387">
-        <v>0.5715692369397383</v>
+        <v>0.6027022961997404</v>
       </c>
       <c r="D387" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E387">
-        <v>0.6027022961997404</v>
+        <v>0.6004361776797362</v>
       </c>
       <c r="F387">
         <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.003488430763060262</v>
+        <v>0.00349729770380026</v>
       </c>
       <c r="H387">
-        <v>0.00349729770380026</v>
+        <v>0.003539563822320264</v>
       </c>
       <c r="I387">
-        <v>-0.03113305926000209</v>
+        <v>0.002266118520004134</v>
       </c>
       <c r="J387">
         <v>1.1133059260002</v>
       </c>
       <c r="K387">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L387">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M387">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N387">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O387">
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20935,49 +20941,49 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C388">
-        <v>0.5504624129824054</v>
+        <v>0.5817565930359749</v>
       </c>
       <c r="D388" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E388">
-        <v>0.5817565930359749</v>
+        <v>0.5791682329288359</v>
       </c>
       <c r="F388">
         <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.003509537587017594</v>
+        <v>0.003518243406964025</v>
       </c>
       <c r="H388">
-        <v>0.003518243406964025</v>
+        <v>0.003560831767071164</v>
       </c>
       <c r="I388">
-        <v>-0.03129418005356954</v>
+        <v>0.002588360107139032</v>
       </c>
       <c r="J388">
         <v>1.129418005356942</v>
       </c>
       <c r="K388">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L388">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M388">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N388">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O388">
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20985,49 +20991,49 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C389">
-        <v>0.5356342747726197</v>
+        <v>0.5670416467209203</v>
       </c>
       <c r="D389" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E389">
-        <v>0.5670416467209203</v>
+        <v>0.5642269028243192</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.00352436572522738</v>
+        <v>0.00353295835327908</v>
       </c>
       <c r="H389">
-        <v>0.00353295835327908</v>
+        <v>0.003575773097175681</v>
       </c>
       <c r="I389">
-        <v>-0.03140737194830057</v>
+        <v>0.00281474389660108</v>
       </c>
       <c r="J389">
         <v>1.140737194830061</v>
       </c>
       <c r="K389">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L389">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M389">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N389">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21035,49 +21041,49 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C390">
-        <v>0.5146924062397964</v>
+        <v>0.5462596397799506</v>
       </c>
       <c r="D390" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E390">
-        <v>0.5462596397799506</v>
+        <v>0.543125172699642</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003545307593760203</v>
+        <v>0.003553740360220049</v>
       </c>
       <c r="H390">
-        <v>0.003553740360220049</v>
+        <v>0.003596874827300358</v>
       </c>
       <c r="I390">
-        <v>-0.03156723354015423</v>
+        <v>0.003134467080308623</v>
       </c>
       <c r="J390">
         <v>1.156723354015422</v>
       </c>
       <c r="K390">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L390">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M390">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N390">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21085,49 +21091,49 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C391">
-        <v>0.4645575619183708</v>
+        <v>0.4965075041938032</v>
       </c>
       <c r="D391" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E391">
-        <v>0.4965075041938032</v>
+        <v>0.4926076196429385</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003595442438081629</v>
+        <v>0.003603492495806196</v>
       </c>
       <c r="H391">
-        <v>0.003603492495806196</v>
+        <v>0.003647392380357062</v>
       </c>
       <c r="I391">
-        <v>-0.03194994227543235</v>
+        <v>0.003899884550864652</v>
       </c>
       <c r="J391">
         <v>1.194994227543228</v>
       </c>
       <c r="K391">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L391">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M391">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N391">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21135,49 +21141,49 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C392">
-        <v>0.4669894486475559</v>
+        <v>0.4989208269021548</v>
       </c>
       <c r="D392" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E392">
-        <v>0.4989208269021548</v>
+        <v>0.4950580703929572</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.003593010551352444</v>
+        <v>0.003601079173097845</v>
       </c>
       <c r="H392">
-        <v>0.003601079173097845</v>
+        <v>0.003644941929607042</v>
       </c>
       <c r="I392">
-        <v>-0.03193137825459891</v>
+        <v>0.00386275650919754</v>
       </c>
       <c r="J392">
         <v>1.193137825459881</v>
       </c>
       <c r="K392">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L392">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M392">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N392">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21185,49 +21191,49 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C393">
-        <v>0.4716631664178546</v>
+        <v>0.5035588674375657</v>
       </c>
       <c r="D393" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E393">
-        <v>0.5035588674375657</v>
+        <v>0.4997674653981437</v>
       </c>
       <c r="F393">
         <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.003588336833582145</v>
+        <v>0.003596441132562434</v>
       </c>
       <c r="H393">
-        <v>0.003596441132562434</v>
+        <v>0.003640232534601856</v>
       </c>
       <c r="I393">
-        <v>-0.03189570101971118</v>
+        <v>0.003791402039422076</v>
       </c>
       <c r="J393">
         <v>1.189570101971103</v>
       </c>
       <c r="K393">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L393">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M393">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N393">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21235,49 +21241,49 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C394">
-        <v>2.038444260870803</v>
+        <v>0.4998273424944029</v>
       </c>
       <c r="D394" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E394">
-        <v>2.174610103829883</v>
+        <v>0.4959785323789321</v>
       </c>
       <c r="F394">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G394">
-        <v>0.001781555739129197</v>
+        <v>0.003600172657505597</v>
       </c>
       <c r="H394">
-        <v>0.001925389896170116</v>
+        <v>0.003644021467621068</v>
       </c>
       <c r="I394">
-        <v>0.1361658429590804</v>
+        <v>0.00384881011547078</v>
       </c>
       <c r="J394">
-        <v>-0.0958539260229872</v>
+        <v>1.192440505773536</v>
       </c>
       <c r="K394">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="L394">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="M394">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N394">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O394">
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21285,31 +21291,31 @@
         <v>0</v>
       </c>
       <c r="B395" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C395">
-        <v>2.176625292888353</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D395" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E395">
-        <v>2.308666328921537</v>
+        <v>2.196527182350343</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001643374707111647</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H395">
-        <v>0.001791333671078463</v>
+        <v>0.001943472817649657</v>
       </c>
       <c r="I395">
-        <v>0.1320410360331836</v>
+        <v>0.1580829214795401</v>
       </c>
       <c r="J395">
-        <v>-0.1989740991704129</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K395">
         <v>1.34</v>
@@ -21318,16 +21324,166 @@
         <v>1.91</v>
       </c>
       <c r="M395">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="N395">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O395">
         <v>1</v>
       </c>
       <c r="P395" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16">
+      <c r="A396" s="1">
+        <v>0</v>
+      </c>
+      <c r="B396" t="s">
+        <v>85</v>
+      </c>
+      <c r="C396">
+        <v>2.176625292888353</v>
+      </c>
+      <c r="D396" t="s">
+        <v>214</v>
+      </c>
+      <c r="E396">
+        <v>2.332645810904945</v>
+      </c>
+      <c r="F396">
+        <v>1</v>
+      </c>
+      <c r="G396">
+        <v>0.001643374707111647</v>
+      </c>
+      <c r="H396">
+        <v>0.001807354189095055</v>
+      </c>
+      <c r="I396">
+        <v>0.1560205180165917</v>
+      </c>
+      <c r="J396">
+        <v>-0.1989740991704129</v>
+      </c>
+      <c r="K396">
+        <v>1.34</v>
+      </c>
+      <c r="L396">
+        <v>1.91</v>
+      </c>
+      <c r="M396">
+        <v>1.32</v>
+      </c>
+      <c r="N396">
+        <v>2.07</v>
+      </c>
+      <c r="O396">
+        <v>1</v>
+      </c>
+      <c r="P396" t="s">
         <v>402</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16">
+      <c r="A397" s="1">
+        <v>0</v>
+      </c>
+      <c r="B397" t="s">
+        <v>85</v>
+      </c>
+      <c r="C397">
+        <v>2.240948171745636</v>
+      </c>
+      <c r="D397" t="s">
+        <v>214</v>
+      </c>
+      <c r="E397">
+        <v>2.396008646794209</v>
+      </c>
+      <c r="F397">
+        <v>1</v>
+      </c>
+      <c r="G397">
+        <v>0.001579051828254363</v>
+      </c>
+      <c r="H397">
+        <v>0.001743991353205791</v>
+      </c>
+      <c r="I397">
+        <v>0.1550604750485727</v>
+      </c>
+      <c r="J397">
+        <v>-0.2469762475713705</v>
+      </c>
+      <c r="K397">
+        <v>1.34</v>
+      </c>
+      <c r="L397">
+        <v>1.91</v>
+      </c>
+      <c r="M397">
+        <v>1.32</v>
+      </c>
+      <c r="N397">
+        <v>2.07</v>
+      </c>
+      <c r="O397">
+        <v>1</v>
+      </c>
+      <c r="P397" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16">
+      <c r="A398" s="1">
+        <v>0</v>
+      </c>
+      <c r="B398" t="s">
+        <v>85</v>
+      </c>
+      <c r="C398">
+        <v>2.276110233960097</v>
+      </c>
+      <c r="D398" t="s">
+        <v>214</v>
+      </c>
+      <c r="E398">
+        <v>2.430645902109946</v>
+      </c>
+      <c r="F398">
+        <v>1</v>
+      </c>
+      <c r="G398">
+        <v>0.001543889766039903</v>
+      </c>
+      <c r="H398">
+        <v>0.001709354097890053</v>
+      </c>
+      <c r="I398">
+        <v>0.1545356681498489</v>
+      </c>
+      <c r="J398">
+        <v>-0.2732165925075352</v>
+      </c>
+      <c r="K398">
+        <v>1.34</v>
+      </c>
+      <c r="L398">
+        <v>1.91</v>
+      </c>
+      <c r="M398">
+        <v>1.32</v>
+      </c>
+      <c r="N398">
+        <v>2.07</v>
+      </c>
+      <c r="O398">
+        <v>1</v>
+      </c>
+      <c r="P398" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -658,7 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2016-02-15</t>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -658,7 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-24</t>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2016-02-15</t>
@@ -20450,7 +20450,7 @@
         <v>214</v>
       </c>
       <c r="E378">
-        <v>1.849151718357083</v>
+        <v>1.832459346186086</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20459,10 +20459,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002290848281642917</v>
+        <v>0.002287540653813915</v>
       </c>
       <c r="I378">
-        <v>0.1333461860854988</v>
+        <v>0.1166538139145015</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20474,10 +20474,10 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N378">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O378">
         <v>1</v>
@@ -20500,7 +20500,7 @@
         <v>214</v>
       </c>
       <c r="E379">
-        <v>1.879346381286305</v>
+        <v>1.863568998901042</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20509,10 +20509,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002260653618713694</v>
+        <v>0.002256431001098958</v>
       </c>
       <c r="I379">
-        <v>0.1328886911926317</v>
+        <v>0.1171113088073683</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20524,10 +20524,10 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N379">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20550,7 +20550,7 @@
         <v>214</v>
       </c>
       <c r="E380">
-        <v>1.959853564080842</v>
+        <v>1.946515793295413</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20559,10 +20559,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002180146435919158</v>
+        <v>0.002173484206704586</v>
       </c>
       <c r="I380">
-        <v>0.1316688853927144</v>
+        <v>0.1183311146072856</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20574,10 +20574,10 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N380">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20600,7 +20600,7 @@
         <v>214</v>
       </c>
       <c r="E381">
-        <v>1.939047260789276</v>
+        <v>1.925078995964709</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20609,10 +20609,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002200952739210724</v>
+        <v>0.002194921004035291</v>
       </c>
       <c r="I381">
-        <v>0.1319841324122837</v>
+        <v>0.1180158675877165</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20624,10 +20624,10 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N381">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20650,7 +20650,7 @@
         <v>214</v>
       </c>
       <c r="E382">
-        <v>1.840329862491058</v>
+        <v>1.823370161354423</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20659,10 +20659,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002299670137508942</v>
+        <v>0.002296629838645577</v>
       </c>
       <c r="I382">
-        <v>0.1334798505683172</v>
+        <v>0.1165201494316828</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20674,10 +20674,10 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N382">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20700,7 +20700,7 @@
         <v>214</v>
       </c>
       <c r="E383">
-        <v>0.9168738220654336</v>
+        <v>0.871930604552265</v>
       </c>
       <c r="F383">
         <v>-1</v>
@@ -20709,10 +20709,10 @@
         <v>0.003195654569177983</v>
       </c>
       <c r="H383">
-        <v>0.003223126177934567</v>
+        <v>0.003248069395447735</v>
       </c>
       <c r="I383">
-        <v>0.00747160875658448</v>
+        <v>0.05241482626975302</v>
       </c>
       <c r="J383">
         <v>0.8735804378292169</v>
@@ -20724,10 +20724,10 @@
         <v>2.06</v>
       </c>
       <c r="M383">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N383">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O383">
         <v>1</v>
@@ -20750,7 +20750,7 @@
         <v>214</v>
       </c>
       <c r="E384">
-        <v>0.8261538461538473</v>
+        <v>0.7784615384615399</v>
       </c>
       <c r="F384">
         <v>-1</v>
@@ -20759,10 +20759,10 @@
         <v>0.003274999999999999</v>
       </c>
       <c r="H384">
-        <v>0.003313846153846152</v>
+        <v>0.00334153846153846</v>
       </c>
       <c r="I384">
-        <v>-0.001153846153846283</v>
+        <v>0.0465384615384612</v>
       </c>
       <c r="J384">
         <v>0.9423076923076913</v>
@@ -20774,10 +20774,10 @@
         <v>2.05</v>
       </c>
       <c r="M384">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N384">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O384">
         <v>1</v>
@@ -20800,7 +20800,7 @@
         <v>214</v>
       </c>
       <c r="E385">
-        <v>0.7592073916682776</v>
+        <v>0.7094864035370134</v>
       </c>
       <c r="F385">
         <v>-1</v>
@@ -20809,10 +20809,10 @@
         <v>0.00334093211426609</v>
       </c>
       <c r="H385">
-        <v>0.003380792608331722</v>
+        <v>0.003410513596462987</v>
       </c>
       <c r="I385">
-        <v>-0.0001395059343678451</v>
+        <v>0.04958148219689629</v>
       </c>
       <c r="J385">
         <v>0.9930247032816077</v>
@@ -20824,10 +20824,10 @@
         <v>2.05</v>
       </c>
       <c r="M385">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N385">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O385">
         <v>1</v>
@@ -20850,7 +20850,7 @@
         <v>214</v>
       </c>
       <c r="E386">
-        <v>0.6343973974866144</v>
+        <v>0.5808942883195423</v>
       </c>
       <c r="F386">
         <v>-1</v>
@@ -20859,10 +20859,10 @@
         <v>0.003463851047929849</v>
       </c>
       <c r="H386">
-        <v>0.003505602602513386</v>
+        <v>0.003539105711680458</v>
       </c>
       <c r="I386">
-        <v>0.001751554583536041</v>
+        <v>0.05525466375060817</v>
       </c>
       <c r="J386">
         <v>1.087577729176807</v>
@@ -20874,10 +20874,10 @@
         <v>2.05</v>
       </c>
       <c r="M386">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N386">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O386">
         <v>1</v>
@@ -20900,7 +20900,7 @@
         <v>214</v>
       </c>
       <c r="E387">
-        <v>0.6004361776797362</v>
+        <v>0.5459039406397284</v>
       </c>
       <c r="F387">
         <v>-1</v>
@@ -20909,10 +20909,10 @@
         <v>0.00349729770380026</v>
       </c>
       <c r="H387">
-        <v>0.003539563822320264</v>
+        <v>0.003574096059360272</v>
       </c>
       <c r="I387">
-        <v>0.002266118520004134</v>
+        <v>0.056798355560012</v>
       </c>
       <c r="J387">
         <v>1.1133059260002</v>
@@ -20924,10 +20924,10 @@
         <v>2.05</v>
       </c>
       <c r="M387">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N387">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O387">
         <v>1</v>
@@ -20950,7 +20950,7 @@
         <v>214</v>
       </c>
       <c r="E388">
-        <v>0.5791682329288359</v>
+        <v>0.5239915127145585</v>
       </c>
       <c r="F388">
         <v>-1</v>
@@ -20959,10 +20959,10 @@
         <v>0.003518243406964025</v>
       </c>
       <c r="H388">
-        <v>0.003560831767071164</v>
+        <v>0.003596008487285442</v>
       </c>
       <c r="I388">
-        <v>0.002588360107139032</v>
+        <v>0.05776508032141647</v>
       </c>
       <c r="J388">
         <v>1.129418005356942</v>
@@ -20974,10 +20974,10 @@
         <v>2.05</v>
       </c>
       <c r="M388">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N388">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -21000,7 +21000,7 @@
         <v>214</v>
       </c>
       <c r="E389">
-        <v>0.5642269028243192</v>
+        <v>0.5085974150311168</v>
       </c>
       <c r="F389">
         <v>-1</v>
@@ -21009,10 +21009,10 @@
         <v>0.00353295835327908</v>
       </c>
       <c r="H389">
-        <v>0.003575773097175681</v>
+        <v>0.003611402584968883</v>
       </c>
       <c r="I389">
-        <v>0.00281474389660108</v>
+        <v>0.05844423168980351</v>
       </c>
       <c r="J389">
         <v>1.140737194830061</v>
@@ -21024,10 +21024,10 @@
         <v>2.05</v>
       </c>
       <c r="M389">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N389">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O389">
         <v>1</v>
@@ -21050,7 +21050,7 @@
         <v>214</v>
       </c>
       <c r="E390">
-        <v>0.543125172699642</v>
+        <v>0.4868562385390254</v>
       </c>
       <c r="F390">
         <v>-1</v>
@@ -21059,10 +21059,10 @@
         <v>0.003553740360220049</v>
       </c>
       <c r="H390">
-        <v>0.003596874827300358</v>
+        <v>0.003633143761460975</v>
       </c>
       <c r="I390">
-        <v>0.003134467080308623</v>
+        <v>0.05940340124092525</v>
       </c>
       <c r="J390">
         <v>1.156723354015422</v>
@@ -21074,10 +21074,10 @@
         <v>2.05</v>
       </c>
       <c r="M390">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N390">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21100,7 +21100,7 @@
         <v>214</v>
       </c>
       <c r="E391">
-        <v>0.4926076196429385</v>
+        <v>0.4348078505412096</v>
       </c>
       <c r="F391">
         <v>-1</v>
@@ -21109,10 +21109,10 @@
         <v>0.003603492495806196</v>
       </c>
       <c r="H391">
-        <v>0.003647392380357062</v>
+        <v>0.003685192149458791</v>
       </c>
       <c r="I391">
-        <v>0.003899884550864652</v>
+        <v>0.06169965365259356</v>
       </c>
       <c r="J391">
         <v>1.194994227543228</v>
@@ -21124,10 +21124,10 @@
         <v>2.05</v>
       </c>
       <c r="M391">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N391">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O391">
         <v>1</v>
@@ -21150,7 +21150,7 @@
         <v>214</v>
       </c>
       <c r="E392">
-        <v>0.4950580703929572</v>
+        <v>0.4373325573745621</v>
       </c>
       <c r="F392">
         <v>-1</v>
@@ -21159,10 +21159,10 @@
         <v>0.003601079173097845</v>
       </c>
       <c r="H392">
-        <v>0.003644941929607042</v>
+        <v>0.003682667442625438</v>
       </c>
       <c r="I392">
-        <v>0.00386275650919754</v>
+        <v>0.06158826952759267</v>
       </c>
       <c r="J392">
         <v>1.193137825459881</v>
@@ -21174,10 +21174,10 @@
         <v>2.05</v>
       </c>
       <c r="M392">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N392">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21200,7 +21200,7 @@
         <v>214</v>
       </c>
       <c r="E393">
-        <v>0.4997674653981437</v>
+        <v>0.4421846613192997</v>
       </c>
       <c r="F393">
         <v>-1</v>
@@ -21209,10 +21209,10 @@
         <v>0.003596441132562434</v>
       </c>
       <c r="H393">
-        <v>0.003640232534601856</v>
+        <v>0.0036778153386807</v>
       </c>
       <c r="I393">
-        <v>0.003791402039422076</v>
+        <v>0.06137420611826605</v>
       </c>
       <c r="J393">
         <v>1.189570101971103</v>
@@ -21224,10 +21224,10 @@
         <v>2.05</v>
       </c>
       <c r="M393">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N393">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O393">
         <v>1</v>
@@ -21250,7 +21250,7 @@
         <v>214</v>
       </c>
       <c r="E394">
-        <v>0.4959785323789321</v>
+        <v>0.4382809121479909</v>
       </c>
       <c r="F394">
         <v>-1</v>
@@ -21259,10 +21259,10 @@
         <v>0.003600172657505597</v>
       </c>
       <c r="H394">
-        <v>0.003644021467621068</v>
+        <v>0.003681719087852009</v>
       </c>
       <c r="I394">
-        <v>0.00384881011547078</v>
+        <v>0.06154643034641194</v>
       </c>
       <c r="J394">
         <v>1.192440505773536</v>
@@ -21274,10 +21274,10 @@
         <v>2.05</v>
       </c>
       <c r="M394">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N394">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O394">
         <v>1</v>
@@ -21300,7 +21300,7 @@
         <v>214</v>
       </c>
       <c r="E395">
-        <v>2.196527182350343</v>
+        <v>2.190361339391263</v>
       </c>
       <c r="F395">
         <v>1</v>
@@ -21309,10 +21309,10 @@
         <v>0.001781555739129197</v>
       </c>
       <c r="H395">
-        <v>0.001943472817649657</v>
+        <v>0.001929638660608737</v>
       </c>
       <c r="I395">
-        <v>0.1580829214795401</v>
+        <v>0.15191707852046</v>
       </c>
       <c r="J395">
         <v>-0.0958539260229872</v>
@@ -21324,10 +21324,10 @@
         <v>1.91</v>
       </c>
       <c r="M395">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N395">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O395">
         <v>1</v>
@@ -21350,7 +21350,7 @@
         <v>214</v>
       </c>
       <c r="E396">
-        <v>2.332645810904945</v>
+        <v>2.330604774871762</v>
       </c>
       <c r="F396">
         <v>1</v>
@@ -21359,10 +21359,10 @@
         <v>0.001643374707111647</v>
       </c>
       <c r="H396">
-        <v>0.001807354189095055</v>
+        <v>0.001789395225128238</v>
       </c>
       <c r="I396">
-        <v>0.1560205180165917</v>
+        <v>0.1539794819834084</v>
       </c>
       <c r="J396">
         <v>-0.1989740991704129</v>
@@ -21374,10 +21374,10 @@
         <v>1.91</v>
       </c>
       <c r="M396">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N396">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O396">
         <v>1</v>
@@ -21400,7 +21400,7 @@
         <v>214</v>
       </c>
       <c r="E397">
-        <v>2.396008646794209</v>
+        <v>2.395887696697064</v>
       </c>
       <c r="F397">
         <v>1</v>
@@ -21409,10 +21409,10 @@
         <v>0.001579051828254363</v>
       </c>
       <c r="H397">
-        <v>0.001743991353205791</v>
+        <v>0.001724112303302936</v>
       </c>
       <c r="I397">
-        <v>0.1550604750485727</v>
+        <v>0.1549395249514278</v>
       </c>
       <c r="J397">
         <v>-0.2469762475713705</v>
@@ -21424,10 +21424,10 @@
         <v>1.91</v>
       </c>
       <c r="M397">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N397">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O397">
         <v>1</v>
@@ -21450,7 +21450,7 @@
         <v>214</v>
       </c>
       <c r="E398">
-        <v>2.430645902109946</v>
+        <v>2.431574565810248</v>
       </c>
       <c r="F398">
         <v>1</v>
@@ -21459,10 +21459,10 @@
         <v>0.001543889766039903</v>
       </c>
       <c r="H398">
-        <v>0.001709354097890053</v>
+        <v>0.001688425434189752</v>
       </c>
       <c r="I398">
-        <v>0.1545356681498489</v>
+        <v>0.1554643318501507</v>
       </c>
       <c r="J398">
         <v>-0.2732165925075352</v>
@@ -21474,10 +21474,10 @@
         <v>1.91</v>
       </c>
       <c r="M398">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="N398">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O398">
         <v>1</v>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="404">
   <si>
     <t>trade_time</t>
   </si>
@@ -658,7 +658,7 @@
     <t>2021-03-09</t>
   </si>
   <si>
-    <t>2021-08-25</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2016-02-15</t>
@@ -1181,9 +1181,6 @@
   </si>
   <si>
     <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
   </si>
   <si>
     <t>2021-04-08</t>
@@ -1586,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P398"/>
+  <dimension ref="A1:P397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -20450,7 +20447,7 @@
         <v>214</v>
       </c>
       <c r="E378">
-        <v>1.832459346186086</v>
+        <v>1.882459346186085</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20459,10 +20456,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002287540653813915</v>
+        <v>0.002337540653813914</v>
       </c>
       <c r="I378">
-        <v>0.1166538139145015</v>
+        <v>0.1666538139145013</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20477,7 +20474,7 @@
         <v>1.36</v>
       </c>
       <c r="N378">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O378">
         <v>1</v>
@@ -20500,7 +20497,7 @@
         <v>214</v>
       </c>
       <c r="E379">
-        <v>1.863568998901042</v>
+        <v>1.913568998901042</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20509,10 +20506,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002256431001098958</v>
+        <v>0.002306431001098958</v>
       </c>
       <c r="I379">
-        <v>0.1171113088073683</v>
+        <v>0.1671113088073681</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20527,7 +20524,7 @@
         <v>1.36</v>
       </c>
       <c r="N379">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20550,7 +20547,7 @@
         <v>214</v>
       </c>
       <c r="E380">
-        <v>1.946515793295413</v>
+        <v>1.996515793295413</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20559,10 +20556,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002173484206704586</v>
+        <v>0.002223484206704587</v>
       </c>
       <c r="I380">
-        <v>0.1183311146072856</v>
+        <v>0.1683311146072854</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20577,7 +20574,7 @@
         <v>1.36</v>
       </c>
       <c r="N380">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20600,7 +20597,7 @@
         <v>214</v>
       </c>
       <c r="E381">
-        <v>1.925078995964709</v>
+        <v>1.975078995964709</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20609,10 +20606,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002194921004035291</v>
+        <v>0.002244921004035292</v>
       </c>
       <c r="I381">
-        <v>0.1180158675877165</v>
+        <v>0.1680158675877164</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20627,7 +20624,7 @@
         <v>1.36</v>
       </c>
       <c r="N381">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20650,7 +20647,7 @@
         <v>214</v>
       </c>
       <c r="E382">
-        <v>1.823370161354423</v>
+        <v>1.873370161354423</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20659,10 +20656,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002296629838645577</v>
+        <v>0.002346629838645577</v>
       </c>
       <c r="I382">
-        <v>0.1165201494316828</v>
+        <v>0.1665201494316826</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20677,7 +20674,7 @@
         <v>1.36</v>
       </c>
       <c r="N382">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20694,28 +20691,28 @@
         <v>83</v>
       </c>
       <c r="C383">
-        <v>0.924345430822018</v>
+        <v>0.8350000000000013</v>
       </c>
       <c r="D383" t="s">
         <v>214</v>
       </c>
       <c r="E383">
-        <v>0.871930604552265</v>
+        <v>0.8284615384615397</v>
       </c>
       <c r="F383">
         <v>-1</v>
       </c>
       <c r="G383">
-        <v>0.003195654569177983</v>
+        <v>0.003284999999999999</v>
       </c>
       <c r="H383">
-        <v>0.003248069395447735</v>
+        <v>0.00339153846153846</v>
       </c>
       <c r="I383">
-        <v>0.05241482626975302</v>
+        <v>0.006538461538461604</v>
       </c>
       <c r="J383">
-        <v>0.8735804378292169</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K383">
         <v>1.3</v>
@@ -20727,7 +20724,7 @@
         <v>1.36</v>
       </c>
       <c r="N383">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O383">
         <v>1</v>
@@ -20744,28 +20741,28 @@
         <v>84</v>
       </c>
       <c r="C384">
-        <v>0.8250000000000011</v>
+        <v>0.7590678857339097</v>
       </c>
       <c r="D384" t="s">
         <v>214</v>
       </c>
       <c r="E384">
-        <v>0.7784615384615399</v>
+        <v>0.7594864035370132</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.003274999999999999</v>
+        <v>0.00334093211426609</v>
       </c>
       <c r="H384">
-        <v>0.00334153846153846</v>
+        <v>0.003460513596462986</v>
       </c>
       <c r="I384">
-        <v>0.0465384615384612</v>
+        <v>-0.0004185178031035353</v>
       </c>
       <c r="J384">
-        <v>0.9423076923076913</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K384">
         <v>1.3</v>
@@ -20777,7 +20774,7 @@
         <v>1.36</v>
       </c>
       <c r="N384">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O384">
         <v>1</v>
@@ -20794,28 +20791,28 @@
         <v>84</v>
       </c>
       <c r="C385">
-        <v>0.7590678857339097</v>
+        <v>0.6361489520701504</v>
       </c>
       <c r="D385" t="s">
         <v>214</v>
       </c>
       <c r="E385">
-        <v>0.7094864035370134</v>
+        <v>0.6308942883195421</v>
       </c>
       <c r="F385">
         <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.00334093211426609</v>
+        <v>0.003463851047929849</v>
       </c>
       <c r="H385">
-        <v>0.003410513596462987</v>
+        <v>0.003589105711680458</v>
       </c>
       <c r="I385">
-        <v>0.04958148219689629</v>
+        <v>0.005254663750608346</v>
       </c>
       <c r="J385">
-        <v>0.9930247032816077</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K385">
         <v>1.3</v>
@@ -20827,7 +20824,7 @@
         <v>1.36</v>
       </c>
       <c r="N385">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O385">
         <v>1</v>
@@ -20844,28 +20841,28 @@
         <v>84</v>
       </c>
       <c r="C386">
-        <v>0.6361489520701504</v>
+        <v>0.6027022961997404</v>
       </c>
       <c r="D386" t="s">
         <v>214</v>
       </c>
       <c r="E386">
-        <v>0.5808942883195423</v>
+        <v>0.5959039406397282</v>
       </c>
       <c r="F386">
         <v>-1</v>
       </c>
       <c r="G386">
-        <v>0.003463851047929849</v>
+        <v>0.00349729770380026</v>
       </c>
       <c r="H386">
-        <v>0.003539105711680458</v>
+        <v>0.003624096059360272</v>
       </c>
       <c r="I386">
-        <v>0.05525466375060817</v>
+        <v>0.006798355560012181</v>
       </c>
       <c r="J386">
-        <v>1.087577729176807</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K386">
         <v>1.3</v>
@@ -20877,7 +20874,7 @@
         <v>1.36</v>
       </c>
       <c r="N386">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O386">
         <v>1</v>
@@ -20894,28 +20891,28 @@
         <v>84</v>
       </c>
       <c r="C387">
-        <v>0.6027022961997404</v>
+        <v>0.5817565930359749</v>
       </c>
       <c r="D387" t="s">
         <v>214</v>
       </c>
       <c r="E387">
-        <v>0.5459039406397284</v>
+        <v>0.5739915127145583</v>
       </c>
       <c r="F387">
         <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.00349729770380026</v>
+        <v>0.003518243406964025</v>
       </c>
       <c r="H387">
-        <v>0.003574096059360272</v>
+        <v>0.003646008487285442</v>
       </c>
       <c r="I387">
-        <v>0.056798355560012</v>
+        <v>0.007765080321416651</v>
       </c>
       <c r="J387">
-        <v>1.1133059260002</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K387">
         <v>1.3</v>
@@ -20927,7 +20924,7 @@
         <v>1.36</v>
       </c>
       <c r="N387">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O387">
         <v>1</v>
@@ -20944,28 +20941,28 @@
         <v>84</v>
       </c>
       <c r="C388">
-        <v>0.5817565930359749</v>
+        <v>0.5670416467209203</v>
       </c>
       <c r="D388" t="s">
         <v>214</v>
       </c>
       <c r="E388">
-        <v>0.5239915127145585</v>
+        <v>0.5585974150311166</v>
       </c>
       <c r="F388">
         <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.003518243406964025</v>
+        <v>0.00353295835327908</v>
       </c>
       <c r="H388">
-        <v>0.003596008487285442</v>
+        <v>0.003661402584968883</v>
       </c>
       <c r="I388">
-        <v>0.05776508032141647</v>
+        <v>0.008444231689803683</v>
       </c>
       <c r="J388">
-        <v>1.129418005356942</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K388">
         <v>1.3</v>
@@ -20977,7 +20974,7 @@
         <v>1.36</v>
       </c>
       <c r="N388">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20994,28 +20991,28 @@
         <v>84</v>
       </c>
       <c r="C389">
-        <v>0.5670416467209203</v>
+        <v>0.5462596397799506</v>
       </c>
       <c r="D389" t="s">
         <v>214</v>
       </c>
       <c r="E389">
-        <v>0.5085974150311168</v>
+        <v>0.5368562385390252</v>
       </c>
       <c r="F389">
         <v>-1</v>
       </c>
       <c r="G389">
-        <v>0.00353295835327908</v>
+        <v>0.003553740360220049</v>
       </c>
       <c r="H389">
-        <v>0.003611402584968883</v>
+        <v>0.003683143761460975</v>
       </c>
       <c r="I389">
-        <v>0.05844423168980351</v>
+        <v>0.009403401240925424</v>
       </c>
       <c r="J389">
-        <v>1.140737194830061</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K389">
         <v>1.3</v>
@@ -21027,7 +21024,7 @@
         <v>1.36</v>
       </c>
       <c r="N389">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O389">
         <v>1</v>
@@ -21044,28 +21041,28 @@
         <v>84</v>
       </c>
       <c r="C390">
-        <v>0.5462596397799506</v>
+        <v>0.4965075041938032</v>
       </c>
       <c r="D390" t="s">
         <v>214</v>
       </c>
       <c r="E390">
-        <v>0.4868562385390254</v>
+        <v>0.4848078505412095</v>
       </c>
       <c r="F390">
         <v>-1</v>
       </c>
       <c r="G390">
-        <v>0.003553740360220049</v>
+        <v>0.003603492495806196</v>
       </c>
       <c r="H390">
-        <v>0.003633143761460975</v>
+        <v>0.00373519214945879</v>
       </c>
       <c r="I390">
-        <v>0.05940340124092525</v>
+        <v>0.01169965365259373</v>
       </c>
       <c r="J390">
-        <v>1.156723354015422</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K390">
         <v>1.3</v>
@@ -21077,7 +21074,7 @@
         <v>1.36</v>
       </c>
       <c r="N390">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O390">
         <v>1</v>
@@ -21094,28 +21091,28 @@
         <v>84</v>
       </c>
       <c r="C391">
-        <v>0.4965075041938032</v>
+        <v>0.4989208269021548</v>
       </c>
       <c r="D391" t="s">
         <v>214</v>
       </c>
       <c r="E391">
-        <v>0.4348078505412096</v>
+        <v>0.4873325573745619</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003603492495806196</v>
+        <v>0.003601079173097845</v>
       </c>
       <c r="H391">
-        <v>0.003685192149458791</v>
+        <v>0.003732667442625438</v>
       </c>
       <c r="I391">
-        <v>0.06169965365259356</v>
+        <v>0.01158826952759284</v>
       </c>
       <c r="J391">
-        <v>1.194994227543228</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K391">
         <v>1.3</v>
@@ -21127,7 +21124,7 @@
         <v>1.36</v>
       </c>
       <c r="N391">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O391">
         <v>1</v>
@@ -21144,28 +21141,28 @@
         <v>84</v>
       </c>
       <c r="C392">
-        <v>0.4989208269021548</v>
+        <v>0.5035588674375657</v>
       </c>
       <c r="D392" t="s">
         <v>214</v>
       </c>
       <c r="E392">
-        <v>0.4373325573745621</v>
+        <v>0.4921846613192995</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.003601079173097845</v>
+        <v>0.003596441132562434</v>
       </c>
       <c r="H392">
-        <v>0.003682667442625438</v>
+        <v>0.0037278153386807</v>
       </c>
       <c r="I392">
-        <v>0.06158826952759267</v>
+        <v>0.01137420611826623</v>
       </c>
       <c r="J392">
-        <v>1.193137825459881</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K392">
         <v>1.3</v>
@@ -21177,7 +21174,7 @@
         <v>1.36</v>
       </c>
       <c r="N392">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O392">
         <v>1</v>
@@ -21194,28 +21191,28 @@
         <v>84</v>
       </c>
       <c r="C393">
-        <v>0.5035588674375657</v>
+        <v>0.4998273424944029</v>
       </c>
       <c r="D393" t="s">
         <v>214</v>
       </c>
       <c r="E393">
-        <v>0.4421846613192997</v>
+        <v>0.4882809121479907</v>
       </c>
       <c r="F393">
         <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.003596441132562434</v>
+        <v>0.003600172657505597</v>
       </c>
       <c r="H393">
-        <v>0.0036778153386807</v>
+        <v>0.003731719087852009</v>
       </c>
       <c r="I393">
-        <v>0.06137420611826605</v>
+        <v>0.01154643034641212</v>
       </c>
       <c r="J393">
-        <v>1.189570101971103</v>
+        <v>1.192440505773536</v>
       </c>
       <c r="K393">
         <v>1.3</v>
@@ -21227,7 +21224,7 @@
         <v>1.36</v>
       </c>
       <c r="N393">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O393">
         <v>1</v>
@@ -21241,43 +21238,43 @@
         <v>0</v>
       </c>
       <c r="B394" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C394">
-        <v>0.4998273424944029</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D394" t="s">
         <v>214</v>
       </c>
       <c r="E394">
-        <v>0.4382809121479909</v>
+        <v>2.240361339391263</v>
       </c>
       <c r="F394">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G394">
-        <v>0.003600172657505597</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H394">
-        <v>0.003681719087852009</v>
+        <v>0.001979638660608737</v>
       </c>
       <c r="I394">
-        <v>0.06154643034641194</v>
+        <v>0.2019170785204598</v>
       </c>
       <c r="J394">
-        <v>1.192440505773536</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K394">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L394">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="M394">
         <v>1.36</v>
       </c>
       <c r="N394">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O394">
         <v>1</v>
@@ -21294,28 +21291,28 @@
         <v>85</v>
       </c>
       <c r="C395">
-        <v>2.038444260870803</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D395" t="s">
         <v>214</v>
       </c>
       <c r="E395">
-        <v>2.190361339391263</v>
+        <v>2.380604774871761</v>
       </c>
       <c r="F395">
         <v>1</v>
       </c>
       <c r="G395">
-        <v>0.001781555739129197</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H395">
-        <v>0.001929638660608737</v>
+        <v>0.001839395225128238</v>
       </c>
       <c r="I395">
-        <v>0.15191707852046</v>
+        <v>0.2039794819834082</v>
       </c>
       <c r="J395">
-        <v>-0.0958539260229872</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K395">
         <v>1.34</v>
@@ -21327,7 +21324,7 @@
         <v>1.36</v>
       </c>
       <c r="N395">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O395">
         <v>1</v>
@@ -21344,28 +21341,28 @@
         <v>85</v>
       </c>
       <c r="C396">
-        <v>2.176625292888353</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D396" t="s">
         <v>214</v>
       </c>
       <c r="E396">
-        <v>2.330604774871762</v>
+        <v>2.445887696697064</v>
       </c>
       <c r="F396">
         <v>1</v>
       </c>
       <c r="G396">
-        <v>0.001643374707111647</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H396">
-        <v>0.001789395225128238</v>
+        <v>0.001774112303302936</v>
       </c>
       <c r="I396">
-        <v>0.1539794819834084</v>
+        <v>0.2049395249514276</v>
       </c>
       <c r="J396">
-        <v>-0.1989740991704129</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K396">
         <v>1.34</v>
@@ -21377,7 +21374,7 @@
         <v>1.36</v>
       </c>
       <c r="N396">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O396">
         <v>1</v>
@@ -21394,28 +21391,28 @@
         <v>85</v>
       </c>
       <c r="C397">
-        <v>2.240948171745636</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D397" t="s">
         <v>214</v>
       </c>
       <c r="E397">
-        <v>2.395887696697064</v>
+        <v>2.481574565810248</v>
       </c>
       <c r="F397">
         <v>1</v>
       </c>
       <c r="G397">
-        <v>0.001579051828254363</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H397">
-        <v>0.001724112303302936</v>
+        <v>0.001738425434189752</v>
       </c>
       <c r="I397">
-        <v>0.1549395249514278</v>
+        <v>0.2054643318501506</v>
       </c>
       <c r="J397">
-        <v>-0.2469762475713705</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K397">
         <v>1.34</v>
@@ -21427,63 +21424,13 @@
         <v>1.36</v>
       </c>
       <c r="N397">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O397">
         <v>1</v>
       </c>
       <c r="P397" t="s">
         <v>403</v>
-      </c>
-    </row>
-    <row r="398" spans="1:16">
-      <c r="A398" s="1">
-        <v>0</v>
-      </c>
-      <c r="B398" t="s">
-        <v>85</v>
-      </c>
-      <c r="C398">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D398" t="s">
-        <v>214</v>
-      </c>
-      <c r="E398">
-        <v>2.431574565810248</v>
-      </c>
-      <c r="F398">
-        <v>1</v>
-      </c>
-      <c r="G398">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H398">
-        <v>0.001688425434189752</v>
-      </c>
-      <c r="I398">
-        <v>0.1554643318501507</v>
-      </c>
-      <c r="J398">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K398">
-        <v>1.34</v>
-      </c>
-      <c r="L398">
-        <v>1.91</v>
-      </c>
-      <c r="M398">
-        <v>1.36</v>
-      </c>
-      <c r="N398">
-        <v>2.06</v>
-      </c>
-      <c r="O398">
-        <v>1</v>
-      </c>
-      <c r="P398" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="406">
   <si>
     <t>trade_time</t>
   </si>
@@ -656,6 +656,12 @@
   </si>
   <si>
     <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2021-08-26</t>
@@ -1680,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1730,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1780,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1830,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1880,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1930,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1980,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2030,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2080,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2130,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2180,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2230,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2280,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2330,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2380,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2430,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2480,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2530,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2580,7 +2586,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2630,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2680,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2730,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2780,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2830,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2880,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2930,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2980,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3030,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3080,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3130,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3180,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3230,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3280,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3330,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3380,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3430,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3480,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3530,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3580,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3630,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3680,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3730,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3780,7 +3786,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3830,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3880,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3930,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3980,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4030,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4080,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4130,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4180,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4230,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4280,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4330,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4380,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4430,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4480,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4530,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4580,7 +4586,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4630,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4680,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4730,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4780,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4830,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4880,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4930,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4980,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5030,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5080,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5130,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5180,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5230,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5280,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5330,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5380,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5430,7 +5436,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5480,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5530,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5580,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5630,7 +5636,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5680,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5730,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5780,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5830,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5880,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5930,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5980,7 +5986,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6030,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6080,7 +6086,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6130,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6180,7 +6186,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6280,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6330,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6380,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6430,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6480,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6530,7 +6536,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6580,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6630,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6680,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6730,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6780,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6830,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6880,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6930,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6980,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7030,7 +7036,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7080,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7130,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7180,7 +7186,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7230,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7280,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7330,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7380,7 +7386,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7430,7 +7436,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7480,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7530,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7580,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7630,7 +7636,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7680,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7730,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7780,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7830,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7880,7 +7886,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7930,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7980,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8030,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8080,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8130,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8180,7 +8186,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8680,7 +8686,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8830,7 +8836,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8930,7 +8936,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8980,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9030,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9080,7 +9086,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9130,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9180,7 +9186,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9230,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9280,7 +9286,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9330,7 +9336,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9380,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9430,7 +9436,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9480,7 +9486,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9530,7 +9536,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9580,7 +9586,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9630,7 +9636,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9680,7 +9686,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9730,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9780,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9830,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9880,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9930,7 +9936,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9980,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10030,7 +10036,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10080,7 +10086,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10130,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10230,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10280,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10380,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10430,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10480,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10530,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10580,7 +10586,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10630,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10680,7 +10686,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10730,7 +10736,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10780,7 +10786,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10830,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10880,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10980,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11030,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11080,7 +11086,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11130,7 +11136,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11180,7 +11186,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11230,7 +11236,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11280,7 +11286,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11330,7 +11336,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11380,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11430,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11480,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11530,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11580,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11630,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11680,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11730,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11780,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11830,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11880,7 +11886,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11930,7 +11936,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11980,7 +11986,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12030,7 +12036,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12080,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12130,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12180,7 +12186,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12230,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12280,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12330,7 +12336,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12380,7 +12386,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12430,7 +12436,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12480,7 +12486,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12530,7 +12536,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12580,7 +12586,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12630,7 +12636,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12680,7 +12686,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12730,7 +12736,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12780,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12830,7 +12836,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12880,7 +12886,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12930,7 +12936,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12980,7 +12986,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13030,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13080,7 +13086,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13130,7 +13136,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13180,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13230,7 +13236,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13280,7 +13286,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13330,7 +13336,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13380,7 +13386,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13430,7 +13436,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13480,7 +13486,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13530,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13580,7 +13586,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13630,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13680,7 +13686,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13730,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13780,7 +13786,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13830,7 +13836,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13880,7 +13886,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13930,7 +13936,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13980,7 +13986,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14030,7 +14036,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14080,7 +14086,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14130,7 +14136,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14180,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14230,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14280,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14330,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14380,7 +14386,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14430,7 +14436,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14480,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14530,7 +14536,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14580,7 +14586,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14630,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14680,7 +14686,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14730,7 +14736,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14830,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14880,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14930,7 +14936,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14980,7 +14986,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15030,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15080,7 +15086,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15130,7 +15136,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15180,7 +15186,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15230,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15280,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15330,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15380,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15430,7 +15436,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15480,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15530,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15580,7 +15586,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15630,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15680,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15730,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15780,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15830,7 +15836,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15880,7 +15886,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15930,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15980,7 +15986,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16030,7 +16036,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16080,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16130,7 +16136,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16180,7 +16186,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16230,7 +16236,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16280,7 +16286,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16330,7 +16336,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16380,7 +16386,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16430,7 +16436,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16480,7 +16486,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16530,7 +16536,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16580,7 +16586,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16630,7 +16636,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16680,7 +16686,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16730,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16780,7 +16786,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16830,7 +16836,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16880,7 +16886,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16930,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16980,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17030,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17080,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17130,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17180,7 +17186,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17230,7 +17236,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17280,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17330,7 +17336,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17380,7 +17386,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17430,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17480,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17530,7 +17536,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17580,7 +17586,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17630,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17680,7 +17686,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17730,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17780,7 +17786,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17830,7 +17836,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17880,7 +17886,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17930,7 +17936,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17980,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18030,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18080,7 +18086,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18130,7 +18136,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18180,7 +18186,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18230,7 +18236,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18280,7 +18286,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18330,7 +18336,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18380,7 +18386,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18430,7 +18436,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18630,7 +18636,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18680,7 +18686,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18730,7 +18736,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18780,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18830,7 +18836,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19080,7 +19086,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19130,7 +19136,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19180,7 +19186,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19280,7 +19286,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19330,7 +19336,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19380,7 +19386,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19430,7 +19436,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19580,7 +19586,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19630,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19680,7 +19686,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19780,7 +19786,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19830,7 +19836,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19880,7 +19886,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19930,7 +19936,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19980,7 +19986,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20030,7 +20036,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20080,7 +20086,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20130,7 +20136,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20180,7 +20186,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20230,7 +20236,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20280,7 +20286,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20330,7 +20336,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20430,7 +20436,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20447,7 +20453,7 @@
         <v>214</v>
       </c>
       <c r="E378">
-        <v>1.882459346186085</v>
+        <v>1.874132439228835</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -20456,10 +20462,10 @@
         <v>0.002164194467728416</v>
       </c>
       <c r="H378">
-        <v>0.002337540653813914</v>
+        <v>0.002325867560771165</v>
       </c>
       <c r="I378">
-        <v>0.1666538139145013</v>
+        <v>0.1583269069572508</v>
       </c>
       <c r="J378">
         <v>0.1673093042749371</v>
@@ -20471,16 +20477,16 @@
         <v>1.94</v>
       </c>
       <c r="M378">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N378">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O378">
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20494,10 +20500,10 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D379" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E379">
-        <v>1.913568998901042</v>
+        <v>1.895013344497358</v>
       </c>
       <c r="F379">
         <v>1</v>
@@ -20506,10 +20512,10 @@
         <v>0.002133542309906327</v>
       </c>
       <c r="H379">
-        <v>0.002306431001098958</v>
+        <v>0.002284986655502642</v>
       </c>
       <c r="I379">
-        <v>0.1671113088073681</v>
+        <v>0.1485556544036841</v>
       </c>
       <c r="J379">
         <v>0.1444345596315869</v>
@@ -20521,16 +20527,16 @@
         <v>1.94</v>
       </c>
       <c r="M379">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N379">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20544,10 +20550,10 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D380" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E380">
-        <v>1.996515793295413</v>
+        <v>1.977350235991771</v>
       </c>
       <c r="F380">
         <v>1</v>
@@ -20556,10 +20562,10 @@
         <v>0.002051815321311872</v>
       </c>
       <c r="H380">
-        <v>0.002223484206704587</v>
+        <v>0.002202649764008229</v>
       </c>
       <c r="I380">
-        <v>0.1683311146072854</v>
+        <v>0.1491655573036428</v>
       </c>
       <c r="J380">
         <v>0.0834442696357255</v>
@@ -20571,16 +20577,16 @@
         <v>1.94</v>
       </c>
       <c r="M380">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N380">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20594,10 +20600,10 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D381" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E381">
-        <v>1.975078995964709</v>
+        <v>1.95607106217085</v>
       </c>
       <c r="F381">
         <v>1</v>
@@ -20606,10 +20612,10 @@
         <v>0.002072936871623007</v>
       </c>
       <c r="H381">
-        <v>0.002244921004035292</v>
+        <v>0.002223928937829149</v>
       </c>
       <c r="I381">
-        <v>0.1680158675877164</v>
+        <v>0.1490079337938581</v>
       </c>
       <c r="J381">
         <v>0.09920662061418481</v>
@@ -20621,16 +20627,16 @@
         <v>1.94</v>
       </c>
       <c r="M381">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N381">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20644,10 +20650,10 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D382" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E382">
-        <v>1.873370161354423</v>
+        <v>1.855110086638581</v>
       </c>
       <c r="F382">
         <v>1</v>
@@ -20656,10 +20662,10 @@
         <v>0.002173149988077259</v>
       </c>
       <c r="H382">
-        <v>0.002346629838645577</v>
+        <v>0.002324889913361418</v>
       </c>
       <c r="I382">
-        <v>0.1665201494316826</v>
+        <v>0.1482600747158411</v>
       </c>
       <c r="J382">
         <v>0.1739925284158654</v>
@@ -20671,10 +20677,10 @@
         <v>1.94</v>
       </c>
       <c r="M382">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N382">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20694,10 +20700,10 @@
         <v>0.8350000000000013</v>
       </c>
       <c r="D383" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E383">
-        <v>0.8284615384615397</v>
+        <v>0.8178846153846164</v>
       </c>
       <c r="F383">
         <v>-1</v>
@@ -20706,10 +20712,10 @@
         <v>0.003284999999999999</v>
       </c>
       <c r="H383">
-        <v>0.00339153846153846</v>
+        <v>0.003362115384615384</v>
       </c>
       <c r="I383">
-        <v>0.006538461538461604</v>
+        <v>0.01711538461538487</v>
       </c>
       <c r="J383">
         <v>0.9423076923076913</v>
@@ -20721,16 +20727,16 @@
         <v>2.06</v>
       </c>
       <c r="M383">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N383">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O383">
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20738,28 +20744,28 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C384">
-        <v>0.7590678857339097</v>
+        <v>0.7690678857339099</v>
       </c>
       <c r="D384" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E384">
-        <v>0.7594864035370132</v>
+        <v>0.7494166505698294</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.00334093211426609</v>
+        <v>0.00335093211426609</v>
       </c>
       <c r="H384">
-        <v>0.003460513596462986</v>
+        <v>0.003430583349430171</v>
       </c>
       <c r="I384">
-        <v>-0.0004185178031035353</v>
+        <v>0.01965123516408052</v>
       </c>
       <c r="J384">
         <v>0.9930247032816077</v>
@@ -20768,19 +20774,19 @@
         <v>1.3</v>
       </c>
       <c r="L384">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M384">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N384">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O384">
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20794,10 +20800,10 @@
         <v>0.6361489520701504</v>
       </c>
       <c r="D385" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E385">
-        <v>0.6308942883195421</v>
+        <v>0.6217700656113101</v>
       </c>
       <c r="F385">
         <v>-1</v>
@@ -20806,10 +20812,10 @@
         <v>0.003463851047929849</v>
       </c>
       <c r="H385">
-        <v>0.003589105711680458</v>
+        <v>0.00355822993438869</v>
       </c>
       <c r="I385">
-        <v>0.005254663750608346</v>
+        <v>0.01437888645884033</v>
       </c>
       <c r="J385">
         <v>1.087577729176807</v>
@@ -20821,16 +20827,16 @@
         <v>2.05</v>
       </c>
       <c r="M385">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N385">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O385">
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20844,10 +20850,10 @@
         <v>0.6027022961997404</v>
       </c>
       <c r="D386" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E386">
-        <v>0.5959039406397282</v>
+        <v>0.5870369998997302</v>
       </c>
       <c r="F386">
         <v>-1</v>
@@ -20856,10 +20862,10 @@
         <v>0.00349729770380026</v>
       </c>
       <c r="H386">
-        <v>0.003624096059360272</v>
+        <v>0.003592963000100269</v>
       </c>
       <c r="I386">
-        <v>0.006798355560012181</v>
+        <v>0.01566529630001012</v>
       </c>
       <c r="J386">
         <v>1.1133059260002</v>
@@ -20871,16 +20877,16 @@
         <v>2.05</v>
       </c>
       <c r="M386">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N386">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O386">
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20894,10 +20900,10 @@
         <v>0.5817565930359749</v>
       </c>
       <c r="D387" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E387">
-        <v>0.5739915127145583</v>
+        <v>0.5652856927681278</v>
       </c>
       <c r="F387">
         <v>-1</v>
@@ -20906,10 +20912,10 @@
         <v>0.003518243406964025</v>
       </c>
       <c r="H387">
-        <v>0.003646008487285442</v>
+        <v>0.003614714307231872</v>
       </c>
       <c r="I387">
-        <v>0.007765080321416651</v>
+        <v>0.01647090026784714</v>
       </c>
       <c r="J387">
         <v>1.129418005356942</v>
@@ -20921,16 +20927,16 @@
         <v>2.05</v>
       </c>
       <c r="M387">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N387">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O387">
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20944,10 +20950,10 @@
         <v>0.5670416467209203</v>
       </c>
       <c r="D388" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E388">
-        <v>0.5585974150311166</v>
+        <v>0.5500047869794173</v>
       </c>
       <c r="F388">
         <v>-1</v>
@@ -20956,10 +20962,10 @@
         <v>0.00353295835327908</v>
       </c>
       <c r="H388">
-        <v>0.003661402584968883</v>
+        <v>0.003629995213020583</v>
       </c>
       <c r="I388">
-        <v>0.008444231689803683</v>
+        <v>0.01703685974150293</v>
       </c>
       <c r="J388">
         <v>1.140737194830061</v>
@@ -20971,16 +20977,16 @@
         <v>2.05</v>
       </c>
       <c r="M388">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N388">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O388">
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20994,10 +21000,10 @@
         <v>0.5462596397799506</v>
       </c>
       <c r="D389" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E389">
-        <v>0.5368562385390252</v>
+        <v>0.5284234720791794</v>
       </c>
       <c r="F389">
         <v>-1</v>
@@ -21006,10 +21012,10 @@
         <v>0.003553740360220049</v>
       </c>
       <c r="H389">
-        <v>0.003683143761460975</v>
+        <v>0.00365157652792082</v>
       </c>
       <c r="I389">
-        <v>0.009403401240925424</v>
+        <v>0.01783616770077123</v>
       </c>
       <c r="J389">
         <v>1.156723354015422</v>
@@ -21021,16 +21027,16 @@
         <v>2.05</v>
       </c>
       <c r="M389">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N389">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O389">
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21044,10 +21050,10 @@
         <v>0.4965075041938032</v>
       </c>
       <c r="D390" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E390">
-        <v>0.4848078505412095</v>
+        <v>0.4767577928166418</v>
       </c>
       <c r="F390">
         <v>-1</v>
@@ -21056,10 +21062,10 @@
         <v>0.003603492495806196</v>
       </c>
       <c r="H390">
-        <v>0.00373519214945879</v>
+        <v>0.003703242207183358</v>
       </c>
       <c r="I390">
-        <v>0.01169965365259373</v>
+        <v>0.01974971137716142</v>
       </c>
       <c r="J390">
         <v>1.194994227543228</v>
@@ -21071,16 +21077,16 @@
         <v>2.05</v>
       </c>
       <c r="M390">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N390">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O390">
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21088,28 +21094,28 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C391">
-        <v>0.4989208269021548</v>
+        <v>0.508920826902155</v>
       </c>
       <c r="D391" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E391">
-        <v>0.4873325573745619</v>
+        <v>0.4792639356291606</v>
       </c>
       <c r="F391">
         <v>-1</v>
       </c>
       <c r="G391">
-        <v>0.003601079173097845</v>
+        <v>0.003611079173097845</v>
       </c>
       <c r="H391">
-        <v>0.003732667442625438</v>
+        <v>0.003700736064370839</v>
       </c>
       <c r="I391">
-        <v>0.01158826952759284</v>
+        <v>0.02965689127299442</v>
       </c>
       <c r="J391">
         <v>1.193137825459881</v>
@@ -21118,19 +21124,19 @@
         <v>1.3</v>
       </c>
       <c r="L391">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M391">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N391">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O391">
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21138,28 +21144,28 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C392">
-        <v>0.5035588674375657</v>
+        <v>0.513558867437566</v>
       </c>
       <c r="D392" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E392">
-        <v>0.4921846613192995</v>
+        <v>0.4840803623390104</v>
       </c>
       <c r="F392">
         <v>-1</v>
       </c>
       <c r="G392">
-        <v>0.003596441132562434</v>
+        <v>0.003606441132562434</v>
       </c>
       <c r="H392">
-        <v>0.0037278153386807</v>
+        <v>0.003695919637660989</v>
       </c>
       <c r="I392">
-        <v>0.01137420611826623</v>
+        <v>0.02947850509855554</v>
       </c>
       <c r="J392">
         <v>1.189570101971103</v>
@@ -21168,19 +21174,19 @@
         <v>1.3</v>
       </c>
       <c r="L392">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M392">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N392">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O392">
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21188,28 +21194,28 @@
         <v>0</v>
       </c>
       <c r="B393" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C393">
-        <v>0.4998273424944029</v>
+        <v>0.5098273424944031</v>
       </c>
       <c r="D393" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E393">
-        <v>0.4882809121479907</v>
+        <v>0.4802053172057259</v>
       </c>
       <c r="F393">
         <v>-1</v>
       </c>
       <c r="G393">
-        <v>0.003600172657505597</v>
+        <v>0.003610172657505597</v>
       </c>
       <c r="H393">
-        <v>0.003731719087852009</v>
+        <v>0.003699794682794274</v>
       </c>
       <c r="I393">
-        <v>0.01154643034641212</v>
+        <v>0.02962202528867719</v>
       </c>
       <c r="J393">
         <v>1.192440505773536</v>
@@ -21218,19 +21224,19 @@
         <v>1.3</v>
       </c>
       <c r="L393">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M393">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="N393">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O393">
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21244,7 +21250,7 @@
         <v>2.038444260870803</v>
       </c>
       <c r="D394" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E394">
         <v>2.240361339391263</v>
@@ -21280,7 +21286,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21294,7 +21300,7 @@
         <v>2.176625292888353</v>
       </c>
       <c r="D395" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E395">
         <v>2.380604774871761</v>
@@ -21330,7 +21336,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21344,7 +21350,7 @@
         <v>2.240948171745636</v>
       </c>
       <c r="D396" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E396">
         <v>2.445887696697064</v>
@@ -21380,7 +21386,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21394,7 +21400,7 @@
         <v>2.276110233960097</v>
       </c>
       <c r="D397" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E397">
         <v>2.481574565810248</v>
@@ -21430,7 +21436,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="403">
   <si>
     <t>trade_time</t>
   </si>
@@ -262,9 +262,6 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -658,6 +655,9 @@
     <t>2021-08-31</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-08-26</t>
   </si>
   <si>
@@ -1181,9 +1181,6 @@
   </si>
   <si>
     <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
   </si>
   <si>
     <t>2021-04-09</t>
@@ -1583,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P393"/>
+  <dimension ref="A1:P392"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1644,7 +1641,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>-3.697130498869741</v>
@@ -1694,7 +1691,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>-3.697130498869741</v>
@@ -1744,7 +1741,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>-4.489266389421874</v>
@@ -1794,7 +1791,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>-4.489266389421874</v>
@@ -1844,7 +1841,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>-4.489266389421874</v>
@@ -1894,7 +1891,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>-4.489266389421874</v>
@@ -1944,7 +1941,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>-4.701411851904431</v>
@@ -1994,7 +1991,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>-4.701411851904431</v>
@@ -2044,7 +2041,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>-4.720848429424226</v>
@@ -2094,7 +2091,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>-4.720848429424226</v>
@@ -2144,7 +2141,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>-4.720848429424226</v>
@@ -2194,7 +2191,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>-4.896104022270815</v>
@@ -2244,7 +2241,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>-4.896104022270815</v>
@@ -2294,7 +2291,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>-5.17427456360058</v>
@@ -2344,7 +2341,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E16">
         <v>-5.17427456360058</v>
@@ -2394,7 +2391,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>-5.009626875608229</v>
@@ -2444,7 +2441,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18">
         <v>-5.009626875608229</v>
@@ -2494,7 +2491,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19">
         <v>-5.093871903520842</v>
@@ -2544,7 +2541,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E20">
         <v>-5.093871903520842</v>
@@ -2594,7 +2591,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>-5.117029968483751</v>
@@ -2644,7 +2641,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>-5.42733388782802</v>
@@ -2694,7 +2691,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23">
         <v>-5.42733388782802</v>
@@ -2744,7 +2741,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24">
         <v>-5.200191269318666</v>
@@ -2794,7 +2791,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.56384792965875</v>
@@ -2844,7 +2841,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E26">
         <v>-5.56384792965875</v>
@@ -2894,7 +2891,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>-5.140154081961497</v>
@@ -2944,7 +2941,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28">
         <v>-5.140154081961497</v>
@@ -2994,7 +2991,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29">
         <v>-5.278966456000339</v>
@@ -3044,7 +3041,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E30">
         <v>-5.066899264800722</v>
@@ -3094,7 +3091,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>-5.066899264800722</v>
@@ -3144,7 +3141,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>-5.339173680947644</v>
@@ -3194,7 +3191,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>-4.976752821893942</v>
@@ -3244,7 +3241,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>-4.976752821893942</v>
@@ -3294,7 +3291,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E35">
         <v>-5.332242465048126</v>
@@ -3344,7 +3341,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36">
         <v>-4.857873642384104</v>
@@ -3394,7 +3391,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>-4.857873642384104</v>
@@ -3444,7 +3441,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E38">
         <v>-5.212897748344369</v>
@@ -3494,7 +3491,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E39">
         <v>3.637557788757765</v>
@@ -3544,7 +3541,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E40">
         <v>3.637557788757765</v>
@@ -3594,7 +3591,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E41">
         <v>3.696125600943092</v>
@@ -3644,7 +3641,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E42">
         <v>3.696125600943092</v>
@@ -3694,7 +3691,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E43">
         <v>3.562106983197164</v>
@@ -3744,7 +3741,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44">
         <v>3.562106983197164</v>
@@ -3794,7 +3791,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45">
         <v>3.447106959801425</v>
@@ -3844,7 +3841,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>3.447106959801425</v>
@@ -3894,7 +3891,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>2.97063976553844</v>
@@ -3944,7 +3941,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48">
         <v>2.97063976553844</v>
@@ -3994,7 +3991,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49">
         <v>2.574206073921443</v>
@@ -4044,7 +4041,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E50">
         <v>2.574206073921443</v>
@@ -4094,7 +4091,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E51">
         <v>2.392623178946991</v>
@@ -4144,7 +4141,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>2.392623178946991</v>
@@ -4194,7 +4191,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E53">
         <v>2.257085968244024</v>
@@ -4244,7 +4241,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>2.257085968244024</v>
@@ -4294,7 +4291,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55">
         <v>2.268115776754144</v>
@@ -4344,7 +4341,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>2.268115776754144</v>
@@ -4394,7 +4391,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57">
         <v>2.130900537967008</v>
@@ -4444,7 +4441,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E58">
         <v>2.130900537967008</v>
@@ -4494,7 +4491,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>2.23740447163792</v>
@@ -4544,7 +4541,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>2.23740447163792</v>
@@ -4594,7 +4591,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>2.216035043209388</v>
@@ -4644,7 +4641,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E62">
         <v>2.216035043209388</v>
@@ -4694,7 +4691,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E63">
         <v>2.308272197921324</v>
@@ -4744,7 +4741,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E64">
         <v>2.308272197921324</v>
@@ -4794,7 +4791,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E65">
         <v>2.383994213343331</v>
@@ -4844,7 +4841,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E66">
         <v>2.383994213343331</v>
@@ -4894,7 +4891,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67">
         <v>2.341003053956531</v>
@@ -4944,7 +4941,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E68">
         <v>2.348235898796299</v>
@@ -4994,7 +4991,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E69">
         <v>2.327107470902277</v>
@@ -5044,7 +5041,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E70">
         <v>2.280646125088861</v>
@@ -5094,7 +5091,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.302015094188537</v>
@@ -5144,7 +5141,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E72">
         <v>2.347919152567092</v>
@@ -5194,7 +5191,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73">
         <v>2.148773116010439</v>
@@ -5244,7 +5241,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E74">
         <v>2.012974927806115</v>
@@ -5294,7 +5291,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>2.060469575425552</v>
@@ -5344,7 +5341,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E76">
         <v>1.907509472337494</v>
@@ -5394,7 +5391,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77">
         <v>1.98668904020824</v>
@@ -5444,7 +5441,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E78">
         <v>2.261468539033603</v>
@@ -5494,7 +5491,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79">
         <v>2.508912235031609</v>
@@ -5544,7 +5541,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D80" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E80">
         <v>2.586570834612932</v>
@@ -5594,7 +5591,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D81" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E81">
         <v>2.299653216265908</v>
@@ -5644,7 +5641,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82">
         <v>2.61595715496026</v>
@@ -5694,7 +5691,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E83">
         <v>2.61595715496026</v>
@@ -5744,7 +5741,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E84">
         <v>2.543317383832596</v>
@@ -5794,7 +5791,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E85">
         <v>2.543317383832596</v>
@@ -5844,7 +5841,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E86">
         <v>2.265161259044684</v>
@@ -5894,7 +5891,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E87">
         <v>2.290570133597897</v>
@@ -5944,7 +5941,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E88">
         <v>2.195461007763983</v>
@@ -5994,7 +5991,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>2.350628131035313</v>
@@ -6044,7 +6041,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E90">
         <v>1.879284692646113</v>
@@ -6094,7 +6091,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E91">
         <v>1.878152907522461</v>
@@ -6144,7 +6141,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E92">
         <v>1.878152907522461</v>
@@ -6194,7 +6191,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E93">
         <v>1.878152907522461</v>
@@ -6244,7 +6241,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E94">
         <v>2.076228086890248</v>
@@ -6294,7 +6291,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E95">
         <v>2.078321265243905</v>
@@ -6344,7 +6341,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E96">
         <v>2.078321265243905</v>
@@ -6394,7 +6391,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E97">
         <v>2.078321265243905</v>
@@ -6444,7 +6441,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E98">
         <v>2.102213303799785</v>
@@ -6494,7 +6491,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E99">
         <v>2.092366071428574</v>
@@ -6544,7 +6541,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E100">
         <v>2.092366071428574</v>
@@ -6594,7 +6591,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E101">
         <v>2.092366071428574</v>
@@ -6644,7 +6641,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D102" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E102">
         <v>2.352465933358952</v>
@@ -6694,7 +6691,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E103">
         <v>2.352465933358952</v>
@@ -6744,7 +6741,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E104">
         <v>2.316305612395345</v>
@@ -6794,7 +6791,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D105" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E105">
         <v>2.316305612395345</v>
@@ -6844,7 +6841,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D106" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E106">
         <v>2.316305612395345</v>
@@ -6894,7 +6891,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D107" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E107">
         <v>1.660853987552378</v>
@@ -6944,7 +6941,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D108" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E108">
         <v>1.706062187746931</v>
@@ -6994,7 +6991,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E109">
         <v>1.706062187746931</v>
@@ -7044,7 +7041,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D110" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E110">
         <v>1.706062187746931</v>
@@ -7094,7 +7091,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E111">
         <v>0.8890067354016997</v>
@@ -7144,7 +7141,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E112">
         <v>0.9778684643520892</v>
@@ -7194,7 +7191,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E113">
         <v>0.9778684643520892</v>
@@ -7244,7 +7241,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D114" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E114">
         <v>0.9778684643520892</v>
@@ -7294,7 +7291,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E115">
         <v>0.9778684643520892</v>
@@ -7344,7 +7341,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E116">
         <v>0.3875605450183359</v>
@@ -7394,7 +7391,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D117" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E117">
         <v>0.5227816757955743</v>
@@ -7444,7 +7441,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D118" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E118">
         <v>0.5227816757955743</v>
@@ -7494,7 +7491,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E119">
         <v>0.5227816757955743</v>
@@ -7544,7 +7541,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D120" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E120">
         <v>0.0491242407754946</v>
@@ -7594,7 +7591,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E121">
         <v>0.159781143472614</v>
@@ -7644,7 +7641,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E122">
         <v>0.159781143472614</v>
@@ -7694,7 +7691,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E123">
         <v>-0.4676849642004726</v>
@@ -7744,7 +7741,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D124" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E124">
         <v>-0.3747925900670488</v>
@@ -7794,7 +7791,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E125">
         <v>-0.8235135484933682</v>
@@ -7844,7 +7841,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E126">
         <v>-0.2477467025920381</v>
@@ -7894,7 +7891,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E127">
         <v>-0.8406732630037332</v>
@@ -7944,7 +7941,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E128">
         <v>-0.2128000927823077</v>
@@ -7994,7 +7991,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>0.387889534694934</v>
@@ -8030,7 +8027,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8044,7 +8041,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D130" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>0.3268838700002261</v>
@@ -8080,7 +8077,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8094,7 +8091,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D131" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>0.3619408673861413</v>
@@ -8130,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8144,7 +8141,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D132" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E132">
         <v>0.2887690811642036</v>
@@ -8180,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8194,7 +8191,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D133" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E133">
         <v>0.2054001299670292</v>
@@ -8230,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8244,7 +8241,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D134" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E134">
         <v>0.09424712584458561</v>
@@ -8280,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8294,7 +8291,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D135" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E135">
         <v>0.04964505068482161</v>
@@ -8330,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8344,7 +8341,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D136" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E136">
         <v>-0.06178174348131638</v>
@@ -8380,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8394,7 +8391,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D137" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>-0.07084042392839685</v>
@@ -8430,7 +8427,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8444,7 +8441,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D138" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E138">
         <v>3.461981920657827</v>
@@ -8494,7 +8491,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D139" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E139">
         <v>3.521227138526164</v>
@@ -8530,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8544,7 +8541,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D140" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E140">
         <v>3.704772068908834</v>
@@ -8580,7 +8577,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8594,7 +8591,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D141" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E141">
         <v>4.126616365519087</v>
@@ -8644,7 +8641,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D142" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E142">
         <v>4.245160231267613</v>
@@ -8680,7 +8677,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8694,7 +8691,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D143" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E143">
         <v>4.229152349958373</v>
@@ -8744,7 +8741,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D144" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E144">
         <v>4.113073707261234</v>
@@ -8794,7 +8791,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D145" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E145">
         <v>3.642839509755204</v>
@@ -8844,7 +8841,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D146" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E146">
         <v>3.168034739342359</v>
@@ -8894,7 +8891,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D147" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E147">
         <v>2.998232417988513</v>
@@ -8944,7 +8941,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E148">
         <v>3.034053936494125</v>
@@ -8994,7 +8991,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D149" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E149">
         <v>2.914701276953577</v>
@@ -9044,7 +9041,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D150" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E150">
         <v>2.942385732505037</v>
@@ -9094,7 +9091,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E151">
         <v>2.891667239770102</v>
@@ -9144,7 +9141,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E152">
         <v>0.6731330742884634</v>
@@ -9194,7 +9191,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E153">
         <v>0.5049958305736757</v>
@@ -9244,7 +9241,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E154">
         <v>4.999995484409007</v>
@@ -9294,7 +9291,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D155" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E155">
         <v>4.49533934056099</v>
@@ -9344,7 +9341,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>4.49533934056099</v>
@@ -9394,7 +9391,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D157" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>5.75883309709841</v>
@@ -9444,7 +9441,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D158" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E158">
         <v>5.616961120807806</v>
@@ -9494,7 +9491,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E159">
         <v>-3.423739939881703</v>
@@ -9544,7 +9541,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D160" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E160">
         <v>-3.743311354600991</v>
@@ -9594,7 +9591,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D161" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E161">
         <v>-4.132985698695919</v>
@@ -9644,7 +9641,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D162" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E162">
         <v>-4.233476466219281</v>
@@ -9694,7 +9691,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D163" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E163">
         <v>-4.275085629955039</v>
@@ -9744,7 +9741,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D164" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E164">
         <v>-4.152544959638887</v>
@@ -9794,7 +9791,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D165" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E165">
         <v>-3.975060706658394</v>
@@ -9844,7 +9841,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D166" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E166">
         <v>-4.047254516344427</v>
@@ -9894,7 +9891,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D167" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E167">
         <v>-3.79843891093761</v>
@@ -9944,7 +9941,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D168" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E168">
         <v>-3.666707344934939</v>
@@ -9994,7 +9991,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D169" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E169">
         <v>-3.713489605052797</v>
@@ -10044,7 +10041,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D170" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E170">
         <v>-3.548252121908546</v>
@@ -10094,7 +10091,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D171" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E171">
         <v>-3.286247287427305</v>
@@ -10130,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10144,7 +10141,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D172" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E172">
         <v>1.158519820616992</v>
@@ -10194,7 +10191,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D173" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E173">
         <v>1.172691348768068</v>
@@ -10244,7 +10241,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D174" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E174">
         <v>1.000464874270701</v>
@@ -10294,7 +10291,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D175" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>0.3824058924251874</v>
@@ -10344,7 +10341,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D176" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E176">
         <v>0.3824058924251874</v>
@@ -10394,7 +10391,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D177" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E177">
         <v>0.3824058924251874</v>
@@ -10444,7 +10441,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D178" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E178">
         <v>0.0213012212570054</v>
@@ -10494,7 +10491,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D179" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E179">
         <v>0.0213012212570054</v>
@@ -10730,7 +10727,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10744,7 +10741,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D184" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E184">
         <v>1.582625511992627</v>
@@ -10794,7 +10791,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D185" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E185">
         <v>1.559453546602203</v>
@@ -10844,7 +10841,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D186" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E186">
         <v>1.547361538049228</v>
@@ -10894,7 +10891,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D187" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E187">
         <v>1.401993513086136</v>
@@ -10944,7 +10941,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D188" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>1.434633300285655</v>
@@ -10994,7 +10991,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D189" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>1.425858209046284</v>
@@ -11044,7 +11041,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D190" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>1.475198819417429</v>
@@ -11094,7 +11091,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D191" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E191">
         <v>1.441005693114453</v>
@@ -11144,7 +11141,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D192" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E192">
         <v>1.488718514152899</v>
@@ -11194,7 +11191,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D193" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E193">
         <v>1.446244175787084</v>
@@ -11244,7 +11241,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D194" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E194">
         <v>1.493394055403994</v>
@@ -11294,7 +11291,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D195" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E195">
         <v>1.446322000480185</v>
@@ -11344,7 +11341,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D196" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E196">
         <v>1.493463516846493</v>
@@ -11394,7 +11391,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D197" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E197">
         <v>1.435847306141142</v>
@@ -11444,7 +11441,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D198" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E198">
         <v>1.484114461302094</v>
@@ -11494,7 +11491,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D199" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E199">
         <v>1.466561985673455</v>
@@ -11544,7 +11541,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D200" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E200">
         <v>1.511528458854815</v>
@@ -11594,7 +11591,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D201" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E201">
         <v>1.479399782082176</v>
@@ -11644,7 +11641,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D202" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E202">
         <v>1.522986671171852</v>
@@ -11694,7 +11691,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D203" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E203">
         <v>1.459395439652966</v>
@@ -11744,7 +11741,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D204" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E204">
         <v>1.505132049123094</v>
@@ -11794,7 +11791,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D205" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E205">
         <v>1.397112808581932</v>
@@ -11844,7 +11841,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D206" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E206">
         <v>1.449542476913426</v>
@@ -11894,7 +11891,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D207" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E207">
         <v>1.294143898865006</v>
@@ -11944,7 +11941,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D208" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E208">
         <v>1.357638882867572</v>
@@ -11994,7 +11991,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D209" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E209">
         <v>1.18030319903414</v>
@@ -12044,7 +12041,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D210" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E210">
         <v>1.18030319903414</v>
@@ -12094,7 +12091,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D211" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E211">
         <v>1.188653245722397</v>
@@ -12144,7 +12141,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D212" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E212">
         <v>0.9564817011303721</v>
@@ -12194,7 +12191,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D213" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E213">
         <v>0.9564817011303721</v>
@@ -12244,7 +12241,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D214" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E214">
         <v>0.9595778612972841</v>
@@ -12294,7 +12291,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D215" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E215">
         <v>0.7699303832078415</v>
@@ -12344,7 +12341,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D216" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E216">
         <v>0.7699303832078415</v>
@@ -12394,7 +12391,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D217" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E217">
         <v>0.7699303832078415</v>
@@ -12444,7 +12441,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D218" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E218">
         <v>0.7947444579985703</v>
@@ -12494,7 +12491,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D219" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E219">
         <v>0.681784458813524</v>
@@ -12544,7 +12541,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D220" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E220">
         <v>0.681784458813524</v>
@@ -12594,7 +12591,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E221">
         <v>0.6868602979367258</v>
@@ -12644,7 +12641,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D222" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.6904864136981455</v>
@@ -12694,7 +12691,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D223" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E223">
         <v>0.6904864136981455</v>
@@ -12744,7 +12741,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D224" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E224">
         <v>0.6988520528231206</v>
@@ -12794,7 +12791,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D225" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E225">
         <v>0.5364590093992025</v>
@@ -12844,7 +12841,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D226" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E226">
         <v>0.5584533336781012</v>
@@ -12894,7 +12891,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D227" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E227">
         <v>0.4349435599285871</v>
@@ -12944,7 +12941,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D228" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E228">
         <v>0.4687561007130205</v>
@@ -12994,7 +12991,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D229" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E229">
         <v>0.4011997840155024</v>
@@ -13044,7 +13041,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D230" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E230">
         <v>0.4389407046823544</v>
@@ -13094,7 +13091,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D231" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E231">
         <v>0.3332852216938216</v>
@@ -13144,7 +13141,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D232" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E232">
         <v>0.3789326137951377</v>
@@ -13194,7 +13191,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D233" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E233">
         <v>0.3201663194080338</v>
@@ -13244,7 +13241,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D234" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E234">
         <v>0.3201663194080338</v>
@@ -13294,7 +13291,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D235" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E235">
         <v>0.3673409867008299</v>
@@ -13344,7 +13341,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D236" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E236">
         <v>0.385066244864444</v>
@@ -13394,7 +13391,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D237" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E237">
         <v>0.385066244864444</v>
@@ -13444,7 +13441,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D238" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E238">
         <v>0.385066244864444</v>
@@ -13494,7 +13491,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D239" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E239">
         <v>0.4246853984473891</v>
@@ -13544,7 +13541,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D240" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E240">
         <v>0.3952650685155521</v>
@@ -13594,7 +13591,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D241" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E241">
         <v>0.3952650685155521</v>
@@ -13644,7 +13641,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D242" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E242">
         <v>0.3952650685155521</v>
@@ -13694,7 +13691,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D243" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E243">
         <v>0.4336968963600101</v>
@@ -13744,7 +13741,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D244" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E244">
         <v>0.441533745152785</v>
@@ -13794,7 +13791,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D245" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E245">
         <v>0.441533745152785</v>
@@ -13844,7 +13841,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D246" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E246">
         <v>0.441533745152785</v>
@@ -13894,7 +13891,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D247" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E247">
         <v>0.4745790703439532</v>
@@ -13944,7 +13941,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D248" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E248">
         <v>0.5262223068621856</v>
@@ -13994,7 +13991,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D249" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E249">
         <v>0.5262223068621856</v>
@@ -14044,7 +14041,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D250" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E250">
         <v>0.5494083666603191</v>
@@ -14094,7 +14091,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D251" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E251">
         <v>1.134910071595908</v>
@@ -14144,7 +14141,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D252" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>1.119751573421224</v>
@@ -14194,7 +14191,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D253" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E253">
         <v>1.055413005631895</v>
@@ -14244,7 +14241,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D254" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E254">
         <v>1.03217696150402</v>
@@ -14294,7 +14291,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D255" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E255">
         <v>0.897246951281871</v>
@@ -14344,7 +14341,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D256" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E256">
         <v>0.8706167327436121</v>
@@ -14394,7 +14391,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D257" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E257">
         <v>1.412833444305319</v>
@@ -14444,7 +14441,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D258" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E258">
         <v>1.399053391868887</v>
@@ -14494,7 +14491,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D259" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E259">
         <v>1.480439984508878</v>
@@ -14544,7 +14541,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D260" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>1.457637705051676</v>
@@ -14644,7 +14641,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D262" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E262">
         <v>1.2222369081479</v>
@@ -14694,7 +14691,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D263" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E263">
         <v>1.311393675757068</v>
@@ -14744,7 +14741,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D264" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E264">
         <v>1.084160634764066</v>
@@ -14794,7 +14791,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D265" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E265">
         <v>1.193914185004133</v>
@@ -14844,7 +14841,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D266" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E266">
         <v>0.8573351083141707</v>
@@ -14894,7 +14891,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D267" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E267">
         <v>0.988341401428052</v>
@@ -14944,7 +14941,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D268" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E268">
         <v>0.7856322541233942</v>
@@ -14994,7 +14991,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D269" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E269">
         <v>0.9271686010995708</v>
@@ -15044,7 +15041,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D270" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E270">
         <v>0.666724382278634</v>
@@ -15094,7 +15091,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D271" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E271">
         <v>0.8120247704726087</v>
@@ -15144,7 +15141,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D272" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.5554941770903916</v>
@@ -15194,7 +15191,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D273" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E273">
         <v>0.5343135639758354</v>
@@ -15244,7 +15241,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D274" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.5543280182232331</v>
@@ -15294,7 +15291,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D275" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E275">
         <v>0.6169560865757506</v>
@@ -15344,7 +15341,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D276" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E276">
         <v>0.6169560865757506</v>
@@ -15394,7 +15391,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D277" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E277">
         <v>0.8673239084198645</v>
@@ -15444,7 +15441,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E278">
         <v>0.7616569728121176</v>
@@ -15494,7 +15491,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D279" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E279">
         <v>0.9495779791694832</v>
@@ -15544,7 +15541,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D280" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E280">
         <v>0.9388491310062772</v>
@@ -15694,7 +15691,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D283" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E283">
         <v>0.9972247567745822</v>
@@ -15744,7 +15741,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D284" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E284">
         <v>1.155095366349694</v>
@@ -15794,7 +15791,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D285" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E285">
         <v>1.155095366349694</v>
@@ -15844,7 +15841,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D286" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E286">
         <v>1.155095366349694</v>
@@ -15894,7 +15891,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D287" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E287">
         <v>1.266654823722328</v>
@@ -16044,7 +16041,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D290" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E290">
         <v>1.216516290726816</v>
@@ -16094,7 +16091,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D291" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E291">
         <v>1.377468671679197</v>
@@ -16144,7 +16141,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D292" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E292">
         <v>1.377468671679197</v>
@@ -16194,7 +16191,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D293" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E293">
         <v>1.098022759601705</v>
@@ -16244,7 +16241,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D294" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E294">
         <v>1.26116642958748</v>
@@ -16294,7 +16291,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D295" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E295">
         <v>1.26116642958748</v>
@@ -16344,7 +16341,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D296" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E296">
         <v>0.8607264291791745</v>
@@ -16494,7 +16491,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D299" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E299">
         <v>0.824097311139564</v>
@@ -16544,7 +16541,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D300" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E300">
         <v>1.040422535211267</v>
@@ -16594,7 +16591,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D301" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E301">
         <v>1.040422535211267</v>
@@ -16644,7 +16641,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D302" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E302">
         <v>1.040422535211267</v>
@@ -16694,7 +16691,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D303" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E303">
         <v>0.6892070138707138</v>
@@ -16744,7 +16741,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D304" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E304">
         <v>0.904611358283171</v>
@@ -16794,7 +16791,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D305" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E305">
         <v>0.6020667096198637</v>
@@ -16844,7 +16841,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D306" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E306">
         <v>0.7705397234474891</v>
@@ -16894,7 +16891,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D307" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E307">
         <v>0.5104188656556885</v>
@@ -16944,7 +16941,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D308" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E308">
         <v>0.4186576811044649</v>
@@ -16994,7 +16991,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D309" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E309">
         <v>0.1677359829666414</v>
@@ -17144,7 +17141,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D312" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E312">
         <v>1.515642348344327</v>
@@ -17294,7 +17291,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D315" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E315">
         <v>1.493247566063977</v>
@@ -17444,7 +17441,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D318" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E318">
         <v>1.414710468897303</v>
@@ -17594,7 +17591,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D321" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E321">
         <v>1.396497005988024</v>
@@ -17744,7 +17741,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D324" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E324">
         <v>1.376951717138971</v>
@@ -17894,7 +17891,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D327" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E327">
         <v>1.359032433928708</v>
@@ -18044,7 +18041,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D330" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E330">
         <v>1.335880304635819</v>
@@ -18194,7 +18191,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D333" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E333">
         <v>1.309957507300225</v>
@@ -18344,7 +18341,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D336" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E336">
         <v>1.320449616201756</v>
@@ -18444,7 +18441,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D338" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E338">
         <v>1.284476712309384</v>
@@ -18594,7 +18591,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D341" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E341">
         <v>1.24169474125916</v>
@@ -18794,7 +18791,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D345" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E345">
         <v>1.182114445177575</v>
@@ -18944,7 +18941,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D348" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E348">
         <v>1.151200461638077</v>
@@ -18994,7 +18991,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D349" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E349">
         <v>1.119879175702464</v>
@@ -19094,7 +19091,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D351" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E351">
         <v>1.094826807940879</v>
@@ -19194,7 +19191,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D353" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E353">
         <v>1.064947268845516</v>
@@ -19294,7 +19291,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D355" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E355">
         <v>1.014148422477695</v>
@@ -19344,7 +19341,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D356" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E356">
         <v>0.7662610529884266</v>
@@ -19394,7 +19391,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D357" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E357">
         <v>0.7460729511326034</v>
@@ -19444,7 +19441,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D358" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E358">
         <v>0.7067614879649891</v>
@@ -19494,7 +19491,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D359" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E359">
         <v>0.6717864324675069</v>
@@ -19594,7 +19591,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D361" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E361">
         <v>0.5671969948491258</v>
@@ -19744,7 +19741,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D364" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E364">
         <v>0.605257854179015</v>
@@ -19794,7 +19791,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D365" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E365">
         <v>0.4201630112625956</v>
@@ -19844,7 +19841,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D366" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E366">
         <v>0.4201630112625956</v>
@@ -19894,7 +19891,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D367" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E367">
         <v>0.4879084704937777</v>
@@ -19944,7 +19941,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D368" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E368">
         <v>0.4879084704937777</v>
@@ -19994,7 +19991,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D369" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E369">
         <v>0.549200546946218</v>
@@ -20044,7 +20041,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D370" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E370">
         <v>0.549200546946218</v>
@@ -20094,7 +20091,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D371" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>0.5264173880682987</v>
@@ -20144,7 +20141,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D372" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E372">
         <v>0.444542315946628</v>
@@ -20180,7 +20177,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20244,7 +20241,7 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D374" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E374">
         <v>1.874132439228835</v>
@@ -20294,7 +20291,7 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D375" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E375">
         <v>1.895013344497358</v>
@@ -20344,7 +20341,7 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D376" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E376">
         <v>2.012343579813627</v>
@@ -20394,7 +20391,7 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D377" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>1.990118664933999</v>
@@ -20444,7 +20441,7 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D378" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E378">
         <v>1.88467053493363</v>
@@ -20480,7 +20477,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20491,28 +20488,28 @@
         <v>81</v>
       </c>
       <c r="C379">
-        <v>0.8350000000000013</v>
+        <v>0.7690678857339099</v>
       </c>
       <c r="D379" t="s">
         <v>213</v>
       </c>
       <c r="E379">
-        <v>0.8013461538461553</v>
+        <v>0.7499746743073008</v>
       </c>
       <c r="F379">
         <v>-1</v>
       </c>
       <c r="G379">
-        <v>0.003284999999999999</v>
+        <v>0.00335093211426609</v>
       </c>
       <c r="H379">
-        <v>0.003458653846153845</v>
+        <v>0.0035900253256927</v>
       </c>
       <c r="I379">
-        <v>0.03365384615384603</v>
+        <v>0.01909321142660914</v>
       </c>
       <c r="J379">
-        <v>0.9423076923076913</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K379">
         <v>1.3</v>
@@ -20521,10 +20518,10 @@
         <v>2.06</v>
       </c>
       <c r="M379">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N379">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20541,28 +20538,28 @@
         <v>81</v>
       </c>
       <c r="C380">
-        <v>0.7690678857339099</v>
+        <v>0.6461489520701507</v>
       </c>
       <c r="D380" t="s">
         <v>213</v>
       </c>
       <c r="E380">
-        <v>0.7298351683729329</v>
+        <v>0.6147638472771657</v>
       </c>
       <c r="F380">
         <v>-1</v>
       </c>
       <c r="G380">
-        <v>0.00335093211426609</v>
+        <v>0.003473851047929849</v>
       </c>
       <c r="H380">
-        <v>0.003530164831627067</v>
+        <v>0.003725236152722834</v>
       </c>
       <c r="I380">
-        <v>0.039232717360977</v>
+        <v>0.03138510479298495</v>
       </c>
       <c r="J380">
-        <v>0.9930247032816077</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K380">
         <v>1.3</v>
@@ -20571,10 +20568,10 @@
         <v>2.06</v>
       </c>
       <c r="M380">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N380">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20591,28 +20588,28 @@
         <v>81</v>
       </c>
       <c r="C381">
-        <v>0.6461489520701507</v>
+        <v>0.6127022961997406</v>
       </c>
       <c r="D381" t="s">
         <v>213</v>
       </c>
       <c r="E381">
-        <v>0.596515401860702</v>
+        <v>0.5779725258197146</v>
       </c>
       <c r="F381">
         <v>-1</v>
       </c>
       <c r="G381">
-        <v>0.003473851047929849</v>
+        <v>0.003507297703800259</v>
       </c>
       <c r="H381">
-        <v>0.003663484598139297</v>
+        <v>0.003762027474180285</v>
       </c>
       <c r="I381">
-        <v>0.04963355020944871</v>
+        <v>0.034729770380026</v>
       </c>
       <c r="J381">
-        <v>1.087577729176807</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K381">
         <v>1.3</v>
@@ -20621,10 +20618,10 @@
         <v>2.06</v>
       </c>
       <c r="M381">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N381">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20638,43 +20635,43 @@
         <v>0</v>
       </c>
       <c r="B382" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C382">
-        <v>0.6027022961997404</v>
+        <v>0.5917565930359752</v>
       </c>
       <c r="D382" t="s">
         <v>213</v>
       </c>
       <c r="E382">
-        <v>0.5602386443397185</v>
+        <v>0.5549322523395726</v>
       </c>
       <c r="F382">
         <v>-1</v>
       </c>
       <c r="G382">
-        <v>0.00349729770380026</v>
+        <v>0.003528243406964025</v>
       </c>
       <c r="H382">
-        <v>0.003699761355660281</v>
+        <v>0.003785067747660428</v>
       </c>
       <c r="I382">
-        <v>0.04246365186002188</v>
+        <v>0.03682434069640261</v>
       </c>
       <c r="J382">
-        <v>1.1133059260002</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K382">
         <v>1.3</v>
       </c>
       <c r="L382">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M382">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N382">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20688,43 +20685,43 @@
         <v>0</v>
       </c>
       <c r="B383" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C383">
-        <v>0.5817565930359749</v>
+        <v>0.5770416467209205</v>
       </c>
       <c r="D383" t="s">
         <v>213</v>
       </c>
       <c r="E383">
-        <v>0.5375206124467113</v>
+        <v>0.5387458113930126</v>
       </c>
       <c r="F383">
         <v>-1</v>
       </c>
       <c r="G383">
-        <v>0.003518243406964025</v>
+        <v>0.003542958353279079</v>
       </c>
       <c r="H383">
-        <v>0.003722479387553288</v>
+        <v>0.003801254188606987</v>
       </c>
       <c r="I383">
-        <v>0.04423598058926359</v>
+        <v>0.03829583532790792</v>
       </c>
       <c r="J383">
-        <v>1.129418005356942</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K383">
         <v>1.3</v>
       </c>
       <c r="L383">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M383">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N383">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O383">
         <v>1</v>
@@ -20738,43 +20735,43 @@
         <v>0</v>
       </c>
       <c r="B384" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C384">
-        <v>0.5670416467209203</v>
+        <v>0.5562596397799509</v>
       </c>
       <c r="D384" t="s">
         <v>213</v>
       </c>
       <c r="E384">
-        <v>0.5215605552896139</v>
+        <v>0.5158856037579458</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.00353295835327908</v>
+        <v>0.00356374036022005</v>
       </c>
       <c r="H384">
-        <v>0.003738439444710386</v>
+        <v>0.003824114396242054</v>
       </c>
       <c r="I384">
-        <v>0.04548109143130641</v>
+        <v>0.04037403602200507</v>
       </c>
       <c r="J384">
-        <v>1.140737194830061</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K384">
         <v>1.3</v>
       </c>
       <c r="L384">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M384">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N384">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O384">
         <v>1</v>
@@ -20788,43 +20785,43 @@
         <v>0</v>
       </c>
       <c r="B385" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C385">
-        <v>0.5462596397799506</v>
+        <v>0.5065075041938034</v>
       </c>
       <c r="D385" t="s">
         <v>213</v>
       </c>
       <c r="E385">
-        <v>0.4990200708382544</v>
+        <v>0.4611582546131838</v>
       </c>
       <c r="F385">
         <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.003553740360220049</v>
+        <v>0.003613492495806197</v>
       </c>
       <c r="H385">
-        <v>0.003760979929161746</v>
+        <v>0.003878841745386816</v>
       </c>
       <c r="I385">
-        <v>0.04723956894169623</v>
+        <v>0.04534924958061959</v>
       </c>
       <c r="J385">
-        <v>1.156723354015422</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K385">
         <v>1.3</v>
       </c>
       <c r="L385">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M385">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N385">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O385">
         <v>1</v>
@@ -20841,28 +20838,28 @@
         <v>81</v>
       </c>
       <c r="C386">
-        <v>0.5065075041938034</v>
+        <v>0.508920826902155</v>
       </c>
       <c r="D386" t="s">
         <v>213</v>
       </c>
       <c r="E386">
-        <v>0.4450581391640482</v>
+        <v>0.4638129095923704</v>
       </c>
       <c r="F386">
         <v>-1</v>
       </c>
       <c r="G386">
-        <v>0.003613492495806197</v>
+        <v>0.003611079173097845</v>
       </c>
       <c r="H386">
-        <v>0.003814941860835952</v>
+        <v>0.00387618709040763</v>
       </c>
       <c r="I386">
-        <v>0.06144936502975518</v>
+        <v>0.04510791730978458</v>
       </c>
       <c r="J386">
-        <v>1.194994227543228</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K386">
         <v>1.3</v>
@@ -20871,10 +20868,10 @@
         <v>2.06</v>
       </c>
       <c r="M386">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N386">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O386">
         <v>1</v>
@@ -20891,28 +20888,28 @@
         <v>81</v>
       </c>
       <c r="C387">
-        <v>0.508920826902155</v>
+        <v>0.513558867437566</v>
       </c>
       <c r="D387" t="s">
         <v>213</v>
       </c>
       <c r="E387">
-        <v>0.4476756661015682</v>
+        <v>0.4689147541813226</v>
       </c>
       <c r="F387">
         <v>-1</v>
       </c>
       <c r="G387">
-        <v>0.003611079173097845</v>
+        <v>0.003606441132562434</v>
       </c>
       <c r="H387">
-        <v>0.003812324333898432</v>
+        <v>0.003871085245818677</v>
       </c>
       <c r="I387">
-        <v>0.06124516080058684</v>
+        <v>0.0446441132562434</v>
       </c>
       <c r="J387">
-        <v>1.193137825459881</v>
+        <v>1.189570101971103</v>
       </c>
       <c r="K387">
         <v>1.3</v>
@@ -20921,10 +20918,10 @@
         <v>2.06</v>
       </c>
       <c r="M387">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N387">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O387">
         <v>1</v>
@@ -20941,28 +20938,28 @@
         <v>81</v>
       </c>
       <c r="C388">
-        <v>0.513558867437566</v>
+        <v>0.5098273424944031</v>
       </c>
       <c r="D388" t="s">
         <v>213</v>
       </c>
       <c r="E388">
-        <v>0.4527061562207446</v>
+        <v>0.4648100767438434</v>
       </c>
       <c r="F388">
         <v>-1</v>
       </c>
       <c r="G388">
-        <v>0.003606441132562434</v>
+        <v>0.003610172657505597</v>
       </c>
       <c r="H388">
-        <v>0.003807293843779255</v>
+        <v>0.003875189923256157</v>
       </c>
       <c r="I388">
-        <v>0.06085271121682134</v>
+        <v>0.04501726575055964</v>
       </c>
       <c r="J388">
-        <v>1.189570101971103</v>
+        <v>1.192440505773536</v>
       </c>
       <c r="K388">
         <v>1.3</v>
@@ -20971,10 +20968,10 @@
         <v>2.06</v>
       </c>
       <c r="M388">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="N388">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20988,43 +20985,43 @@
         <v>0</v>
       </c>
       <c r="B389" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C389">
-        <v>0.5098273424944031</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D389" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E389">
-        <v>0.448658886859314</v>
+        <v>2.240361339391263</v>
       </c>
       <c r="F389">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G389">
-        <v>0.003610172657505597</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H389">
-        <v>0.003811341113140686</v>
+        <v>0.001979638660608737</v>
       </c>
       <c r="I389">
-        <v>0.0611684556350891</v>
+        <v>0.2019170785204598</v>
       </c>
       <c r="J389">
-        <v>1.192440505773536</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K389">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L389">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M389">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="N389">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O389">
         <v>1</v>
@@ -21038,31 +21035,31 @@
         <v>0</v>
       </c>
       <c r="B390" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C390">
-        <v>2.038444260870803</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D390" t="s">
         <v>214</v>
       </c>
       <c r="E390">
-        <v>2.240361339391263</v>
+        <v>2.380604774871761</v>
       </c>
       <c r="F390">
         <v>1</v>
       </c>
       <c r="G390">
-        <v>0.001781555739129197</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H390">
-        <v>0.001979638660608737</v>
+        <v>0.001839395225128238</v>
       </c>
       <c r="I390">
-        <v>0.2019170785204598</v>
+        <v>0.2039794819834082</v>
       </c>
       <c r="J390">
-        <v>-0.0958539260229872</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K390">
         <v>1.34</v>
@@ -21088,31 +21085,31 @@
         <v>0</v>
       </c>
       <c r="B391" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C391">
-        <v>2.176625292888353</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D391" t="s">
         <v>214</v>
       </c>
       <c r="E391">
-        <v>2.380604774871761</v>
+        <v>2.445887696697064</v>
       </c>
       <c r="F391">
         <v>1</v>
       </c>
       <c r="G391">
-        <v>0.001643374707111647</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H391">
-        <v>0.001839395225128238</v>
+        <v>0.001774112303302936</v>
       </c>
       <c r="I391">
-        <v>0.2039794819834082</v>
+        <v>0.2049395249514276</v>
       </c>
       <c r="J391">
-        <v>-0.1989740991704129</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K391">
         <v>1.34</v>
@@ -21138,31 +21135,31 @@
         <v>0</v>
       </c>
       <c r="B392" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C392">
-        <v>2.240948171745636</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D392" t="s">
         <v>214</v>
       </c>
       <c r="E392">
-        <v>2.445887696697064</v>
+        <v>2.481574565810248</v>
       </c>
       <c r="F392">
         <v>1</v>
       </c>
       <c r="G392">
-        <v>0.001579051828254363</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H392">
-        <v>0.001774112303302936</v>
+        <v>0.001738425434189752</v>
       </c>
       <c r="I392">
-        <v>0.2049395249514276</v>
+        <v>0.2054643318501506</v>
       </c>
       <c r="J392">
-        <v>-0.2469762475713705</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K392">
         <v>1.34</v>
@@ -21181,56 +21178,6 @@
       </c>
       <c r="P392" t="s">
         <v>402</v>
-      </c>
-    </row>
-    <row r="393" spans="1:16">
-      <c r="A393" s="1">
-        <v>0</v>
-      </c>
-      <c r="B393" t="s">
-        <v>83</v>
-      </c>
-      <c r="C393">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D393" t="s">
-        <v>214</v>
-      </c>
-      <c r="E393">
-        <v>2.481574565810248</v>
-      </c>
-      <c r="F393">
-        <v>1</v>
-      </c>
-      <c r="G393">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H393">
-        <v>0.001738425434189752</v>
-      </c>
-      <c r="I393">
-        <v>0.2054643318501506</v>
-      </c>
-      <c r="J393">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K393">
-        <v>1.34</v>
-      </c>
-      <c r="L393">
-        <v>1.91</v>
-      </c>
-      <c r="M393">
-        <v>1.36</v>
-      </c>
-      <c r="N393">
-        <v>2.11</v>
-      </c>
-      <c r="O393">
-        <v>1</v>
-      </c>
-      <c r="P393" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="400">
   <si>
     <t>trade_time</t>
   </si>
@@ -655,7 +655,7 @@
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
+    <t>2021-09-02</t>
   </si>
   <si>
     <t>2021-08-26</t>
@@ -1183,9 +1183,6 @@
     <t>2021-01-29</t>
   </si>
   <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
     <t>2021-04-14</t>
   </si>
   <si>
@@ -1205,12 +1202,6 @@
   </si>
   <si>
     <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1580,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P392"/>
+  <dimension ref="A1:P389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -20488,28 +20479,28 @@
         <v>81</v>
       </c>
       <c r="C379">
-        <v>0.7690678857339099</v>
+        <v>0.6461489520701507</v>
       </c>
       <c r="D379" t="s">
         <v>213</v>
       </c>
       <c r="E379">
-        <v>0.7499746743073008</v>
+        <v>0.6347638472771657</v>
       </c>
       <c r="F379">
         <v>-1</v>
       </c>
       <c r="G379">
-        <v>0.00335093211426609</v>
+        <v>0.003473851047929849</v>
       </c>
       <c r="H379">
-        <v>0.0035900253256927</v>
+        <v>0.003745236152722834</v>
       </c>
       <c r="I379">
-        <v>0.01909321142660914</v>
+        <v>0.01138510479298493</v>
       </c>
       <c r="J379">
-        <v>0.9930247032816077</v>
+        <v>1.087577729176807</v>
       </c>
       <c r="K379">
         <v>1.3</v>
@@ -20521,7 +20512,7 @@
         <v>1.43</v>
       </c>
       <c r="N379">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O379">
         <v>1</v>
@@ -20538,28 +20529,28 @@
         <v>81</v>
       </c>
       <c r="C380">
-        <v>0.6461489520701507</v>
+        <v>0.6127022961997406</v>
       </c>
       <c r="D380" t="s">
         <v>213</v>
       </c>
       <c r="E380">
-        <v>0.6147638472771657</v>
+        <v>0.5979725258197146</v>
       </c>
       <c r="F380">
         <v>-1</v>
       </c>
       <c r="G380">
-        <v>0.003473851047929849</v>
+        <v>0.003507297703800259</v>
       </c>
       <c r="H380">
-        <v>0.003725236152722834</v>
+        <v>0.003782027474180286</v>
       </c>
       <c r="I380">
-        <v>0.03138510479298495</v>
+        <v>0.01472977038002599</v>
       </c>
       <c r="J380">
-        <v>1.087577729176807</v>
+        <v>1.1133059260002</v>
       </c>
       <c r="K380">
         <v>1.3</v>
@@ -20571,7 +20562,7 @@
         <v>1.43</v>
       </c>
       <c r="N380">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O380">
         <v>1</v>
@@ -20588,28 +20579,28 @@
         <v>81</v>
       </c>
       <c r="C381">
-        <v>0.6127022961997406</v>
+        <v>0.5917565930359752</v>
       </c>
       <c r="D381" t="s">
         <v>213</v>
       </c>
       <c r="E381">
-        <v>0.5779725258197146</v>
+        <v>0.5749322523395726</v>
       </c>
       <c r="F381">
         <v>-1</v>
       </c>
       <c r="G381">
-        <v>0.003507297703800259</v>
+        <v>0.003528243406964025</v>
       </c>
       <c r="H381">
-        <v>0.003762027474180285</v>
+        <v>0.003805067747660427</v>
       </c>
       <c r="I381">
-        <v>0.034729770380026</v>
+        <v>0.0168243406964026</v>
       </c>
       <c r="J381">
-        <v>1.1133059260002</v>
+        <v>1.129418005356942</v>
       </c>
       <c r="K381">
         <v>1.3</v>
@@ -20621,7 +20612,7 @@
         <v>1.43</v>
       </c>
       <c r="N381">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O381">
         <v>1</v>
@@ -20638,28 +20629,28 @@
         <v>81</v>
       </c>
       <c r="C382">
-        <v>0.5917565930359752</v>
+        <v>0.5770416467209205</v>
       </c>
       <c r="D382" t="s">
         <v>213</v>
       </c>
       <c r="E382">
-        <v>0.5549322523395726</v>
+        <v>0.5587458113930126</v>
       </c>
       <c r="F382">
         <v>-1</v>
       </c>
       <c r="G382">
-        <v>0.003528243406964025</v>
+        <v>0.003542958353279079</v>
       </c>
       <c r="H382">
-        <v>0.003785067747660428</v>
+        <v>0.003821254188606988</v>
       </c>
       <c r="I382">
-        <v>0.03682434069640261</v>
+        <v>0.01829583532790791</v>
       </c>
       <c r="J382">
-        <v>1.129418005356942</v>
+        <v>1.140737194830061</v>
       </c>
       <c r="K382">
         <v>1.3</v>
@@ -20671,7 +20662,7 @@
         <v>1.43</v>
       </c>
       <c r="N382">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O382">
         <v>1</v>
@@ -20688,28 +20679,28 @@
         <v>81</v>
       </c>
       <c r="C383">
-        <v>0.5770416467209205</v>
+        <v>0.5562596397799509</v>
       </c>
       <c r="D383" t="s">
         <v>213</v>
       </c>
       <c r="E383">
-        <v>0.5387458113930126</v>
+        <v>0.5358856037579458</v>
       </c>
       <c r="F383">
         <v>-1</v>
       </c>
       <c r="G383">
-        <v>0.003542958353279079</v>
+        <v>0.00356374036022005</v>
       </c>
       <c r="H383">
-        <v>0.003801254188606987</v>
+        <v>0.003844114396242054</v>
       </c>
       <c r="I383">
-        <v>0.03829583532790792</v>
+        <v>0.02037403602200505</v>
       </c>
       <c r="J383">
-        <v>1.140737194830061</v>
+        <v>1.156723354015422</v>
       </c>
       <c r="K383">
         <v>1.3</v>
@@ -20721,7 +20712,7 @@
         <v>1.43</v>
       </c>
       <c r="N383">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O383">
         <v>1</v>
@@ -20738,28 +20729,28 @@
         <v>81</v>
       </c>
       <c r="C384">
-        <v>0.5562596397799509</v>
+        <v>0.5065075041938034</v>
       </c>
       <c r="D384" t="s">
         <v>213</v>
       </c>
       <c r="E384">
-        <v>0.5158856037579458</v>
+        <v>0.4811582546131838</v>
       </c>
       <c r="F384">
         <v>-1</v>
       </c>
       <c r="G384">
-        <v>0.00356374036022005</v>
+        <v>0.003613492495806197</v>
       </c>
       <c r="H384">
-        <v>0.003824114396242054</v>
+        <v>0.003898841745386816</v>
       </c>
       <c r="I384">
-        <v>0.04037403602200507</v>
+        <v>0.02534924958061957</v>
       </c>
       <c r="J384">
-        <v>1.156723354015422</v>
+        <v>1.194994227543228</v>
       </c>
       <c r="K384">
         <v>1.3</v>
@@ -20771,7 +20762,7 @@
         <v>1.43</v>
       </c>
       <c r="N384">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O384">
         <v>1</v>
@@ -20788,28 +20779,28 @@
         <v>81</v>
       </c>
       <c r="C385">
-        <v>0.5065075041938034</v>
+        <v>0.508920826902155</v>
       </c>
       <c r="D385" t="s">
         <v>213</v>
       </c>
       <c r="E385">
-        <v>0.4611582546131838</v>
+        <v>0.4838129095923704</v>
       </c>
       <c r="F385">
         <v>-1</v>
       </c>
       <c r="G385">
-        <v>0.003613492495806197</v>
+        <v>0.003611079173097845</v>
       </c>
       <c r="H385">
-        <v>0.003878841745386816</v>
+        <v>0.003896187090407629</v>
       </c>
       <c r="I385">
-        <v>0.04534924958061959</v>
+        <v>0.02510791730978457</v>
       </c>
       <c r="J385">
-        <v>1.194994227543228</v>
+        <v>1.193137825459881</v>
       </c>
       <c r="K385">
         <v>1.3</v>
@@ -20821,7 +20812,7 @@
         <v>1.43</v>
       </c>
       <c r="N385">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O385">
         <v>1</v>
@@ -20835,43 +20826,43 @@
         <v>0</v>
       </c>
       <c r="B386" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C386">
-        <v>0.508920826902155</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D386" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E386">
-        <v>0.4638129095923704</v>
+        <v>2.240361339391263</v>
       </c>
       <c r="F386">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G386">
-        <v>0.003611079173097845</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H386">
-        <v>0.00387618709040763</v>
+        <v>0.001979638660608737</v>
       </c>
       <c r="I386">
-        <v>0.04510791730978458</v>
+        <v>0.2019170785204598</v>
       </c>
       <c r="J386">
-        <v>1.193137825459881</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K386">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L386">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M386">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N386">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="O386">
         <v>1</v>
@@ -20885,43 +20876,43 @@
         <v>0</v>
       </c>
       <c r="B387" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C387">
-        <v>0.513558867437566</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D387" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E387">
-        <v>0.4689147541813226</v>
+        <v>2.380604774871761</v>
       </c>
       <c r="F387">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G387">
-        <v>0.003606441132562434</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H387">
-        <v>0.003871085245818677</v>
+        <v>0.001839395225128238</v>
       </c>
       <c r="I387">
-        <v>0.0446441132562434</v>
+        <v>0.2039794819834082</v>
       </c>
       <c r="J387">
-        <v>1.189570101971103</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K387">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L387">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M387">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N387">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="O387">
         <v>1</v>
@@ -20935,43 +20926,43 @@
         <v>0</v>
       </c>
       <c r="B388" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C388">
-        <v>0.5098273424944031</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D388" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E388">
-        <v>0.4648100767438434</v>
+        <v>2.445887696697064</v>
       </c>
       <c r="F388">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G388">
-        <v>0.003610172657505597</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H388">
-        <v>0.003875189923256157</v>
+        <v>0.001774112303302936</v>
       </c>
       <c r="I388">
-        <v>0.04501726575055964</v>
+        <v>0.2049395249514276</v>
       </c>
       <c r="J388">
-        <v>1.192440505773536</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K388">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L388">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M388">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N388">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="O388">
         <v>1</v>
@@ -20988,28 +20979,28 @@
         <v>82</v>
       </c>
       <c r="C389">
-        <v>2.038444260870803</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D389" t="s">
         <v>214</v>
       </c>
       <c r="E389">
-        <v>2.240361339391263</v>
+        <v>2.481574565810248</v>
       </c>
       <c r="F389">
         <v>1</v>
       </c>
       <c r="G389">
-        <v>0.001781555739129197</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H389">
-        <v>0.001979638660608737</v>
+        <v>0.001738425434189752</v>
       </c>
       <c r="I389">
-        <v>0.2019170785204598</v>
+        <v>0.2054643318501506</v>
       </c>
       <c r="J389">
-        <v>-0.0958539260229872</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K389">
         <v>1.34</v>
@@ -21028,156 +21019,6 @@
       </c>
       <c r="P389" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="390" spans="1:16">
-      <c r="A390" s="1">
-        <v>0</v>
-      </c>
-      <c r="B390" t="s">
-        <v>82</v>
-      </c>
-      <c r="C390">
-        <v>2.176625292888353</v>
-      </c>
-      <c r="D390" t="s">
-        <v>214</v>
-      </c>
-      <c r="E390">
-        <v>2.380604774871761</v>
-      </c>
-      <c r="F390">
-        <v>1</v>
-      </c>
-      <c r="G390">
-        <v>0.001643374707111647</v>
-      </c>
-      <c r="H390">
-        <v>0.001839395225128238</v>
-      </c>
-      <c r="I390">
-        <v>0.2039794819834082</v>
-      </c>
-      <c r="J390">
-        <v>-0.1989740991704129</v>
-      </c>
-      <c r="K390">
-        <v>1.34</v>
-      </c>
-      <c r="L390">
-        <v>1.91</v>
-      </c>
-      <c r="M390">
-        <v>1.36</v>
-      </c>
-      <c r="N390">
-        <v>2.11</v>
-      </c>
-      <c r="O390">
-        <v>1</v>
-      </c>
-      <c r="P390" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="391" spans="1:16">
-      <c r="A391" s="1">
-        <v>0</v>
-      </c>
-      <c r="B391" t="s">
-        <v>82</v>
-      </c>
-      <c r="C391">
-        <v>2.240948171745636</v>
-      </c>
-      <c r="D391" t="s">
-        <v>214</v>
-      </c>
-      <c r="E391">
-        <v>2.445887696697064</v>
-      </c>
-      <c r="F391">
-        <v>1</v>
-      </c>
-      <c r="G391">
-        <v>0.001579051828254363</v>
-      </c>
-      <c r="H391">
-        <v>0.001774112303302936</v>
-      </c>
-      <c r="I391">
-        <v>0.2049395249514276</v>
-      </c>
-      <c r="J391">
-        <v>-0.2469762475713705</v>
-      </c>
-      <c r="K391">
-        <v>1.34</v>
-      </c>
-      <c r="L391">
-        <v>1.91</v>
-      </c>
-      <c r="M391">
-        <v>1.36</v>
-      </c>
-      <c r="N391">
-        <v>2.11</v>
-      </c>
-      <c r="O391">
-        <v>1</v>
-      </c>
-      <c r="P391" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="392" spans="1:16">
-      <c r="A392" s="1">
-        <v>0</v>
-      </c>
-      <c r="B392" t="s">
-        <v>82</v>
-      </c>
-      <c r="C392">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D392" t="s">
-        <v>214</v>
-      </c>
-      <c r="E392">
-        <v>2.481574565810248</v>
-      </c>
-      <c r="F392">
-        <v>1</v>
-      </c>
-      <c r="G392">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H392">
-        <v>0.001738425434189752</v>
-      </c>
-      <c r="I392">
-        <v>0.2054643318501506</v>
-      </c>
-      <c r="J392">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K392">
-        <v>1.34</v>
-      </c>
-      <c r="L392">
-        <v>1.91</v>
-      </c>
-      <c r="M392">
-        <v>1.36</v>
-      </c>
-      <c r="N392">
-        <v>2.11</v>
-      </c>
-      <c r="O392">
-        <v>1</v>
-      </c>
-      <c r="P392" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="391">
   <si>
     <t>trade_time</t>
   </si>
@@ -259,9 +259,6 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -655,9 +652,6 @@
     <t>2021-08-31</t>
   </si>
   <si>
-    <t>2021-09-02</t>
-  </si>
-  <si>
     <t>2021-08-26</t>
   </si>
   <si>
@@ -1181,27 +1175,6 @@
   </si>
   <si>
     <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1571,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P389"/>
+  <dimension ref="A1:P382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1632,7 +1605,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2">
         <v>-3.697130498869741</v>
@@ -1668,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1682,7 +1655,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3">
         <v>-3.697130498869741</v>
@@ -1718,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1732,7 +1705,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>-4.489266389421874</v>
@@ -1768,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1782,7 +1755,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>-4.489266389421874</v>
@@ -1818,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1832,7 +1805,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6">
         <v>-4.489266389421874</v>
@@ -1868,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1882,7 +1855,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>-4.489266389421874</v>
@@ -1918,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1932,7 +1905,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>-4.701411851904431</v>
@@ -1968,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1982,7 +1955,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>-4.701411851904431</v>
@@ -2018,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2032,7 +2005,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>-4.720848429424226</v>
@@ -2068,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2082,7 +2055,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>-4.720848429424226</v>
@@ -2118,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2132,7 +2105,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12">
         <v>-4.720848429424226</v>
@@ -2168,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2182,7 +2155,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13">
         <v>-4.896104022270815</v>
@@ -2218,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2232,7 +2205,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14">
         <v>-4.896104022270815</v>
@@ -2268,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2282,7 +2255,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15">
         <v>-5.17427456360058</v>
@@ -2318,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2332,7 +2305,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>-5.17427456360058</v>
@@ -2368,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2382,7 +2355,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>-5.009626875608229</v>
@@ -2418,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2432,7 +2405,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>-5.009626875608229</v>
@@ -2468,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2482,7 +2455,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E19">
         <v>-5.093871903520842</v>
@@ -2518,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2532,7 +2505,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20">
         <v>-5.093871903520842</v>
@@ -2568,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2582,7 +2555,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21">
         <v>-5.117029968483751</v>
@@ -2618,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2632,7 +2605,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22">
         <v>-5.42733388782802</v>
@@ -2668,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2682,7 +2655,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23">
         <v>-5.42733388782802</v>
@@ -2718,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2732,7 +2705,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24">
         <v>-5.200191269318666</v>
@@ -2768,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2782,7 +2755,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>-5.56384792965875</v>
@@ -2818,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2832,7 +2805,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26">
         <v>-5.56384792965875</v>
@@ -2868,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2882,7 +2855,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>-5.140154081961497</v>
@@ -2918,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2932,7 +2905,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28">
         <v>-5.140154081961497</v>
@@ -2968,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2982,7 +2955,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29">
         <v>-5.278966456000339</v>
@@ -3018,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3032,7 +3005,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>-5.066899264800722</v>
@@ -3068,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3082,7 +3055,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>-5.066899264800722</v>
@@ -3118,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3132,7 +3105,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E32">
         <v>-5.339173680947644</v>
@@ -3168,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3182,7 +3155,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>-4.976752821893942</v>
@@ -3218,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3232,7 +3205,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34">
         <v>-4.976752821893942</v>
@@ -3268,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3282,7 +3255,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E35">
         <v>-5.332242465048126</v>
@@ -3318,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3332,7 +3305,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36">
         <v>-4.857873642384104</v>
@@ -3368,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3382,7 +3355,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37">
         <v>-4.857873642384104</v>
@@ -3418,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3432,7 +3405,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38">
         <v>-5.212897748344369</v>
@@ -3468,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3482,7 +3455,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E39">
         <v>3.637557788757765</v>
@@ -3518,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3532,7 +3505,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E40">
         <v>3.637557788757765</v>
@@ -3568,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3582,7 +3555,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E41">
         <v>3.696125600943092</v>
@@ -3618,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3632,7 +3605,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42">
         <v>3.696125600943092</v>
@@ -3668,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3682,7 +3655,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43">
         <v>3.562106983197164</v>
@@ -3718,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3732,7 +3705,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44">
         <v>3.562106983197164</v>
@@ -3768,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3782,7 +3755,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45">
         <v>3.447106959801425</v>
@@ -3818,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3832,7 +3805,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E46">
         <v>3.447106959801425</v>
@@ -3868,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3882,7 +3855,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47">
         <v>2.97063976553844</v>
@@ -3918,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3932,7 +3905,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E48">
         <v>2.97063976553844</v>
@@ -3968,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3982,7 +3955,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49">
         <v>2.574206073921443</v>
@@ -4018,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4032,7 +4005,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>2.574206073921443</v>
@@ -4068,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4082,7 +4055,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>2.392623178946991</v>
@@ -4118,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4132,7 +4105,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>2.392623178946991</v>
@@ -4168,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4182,7 +4155,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>2.257085968244024</v>
@@ -4218,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4232,7 +4205,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54">
         <v>2.257085968244024</v>
@@ -4268,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4282,7 +4255,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55">
         <v>2.268115776754144</v>
@@ -4318,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4332,7 +4305,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56">
         <v>2.268115776754144</v>
@@ -4368,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4382,7 +4355,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E57">
         <v>2.130900537967008</v>
@@ -4418,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4432,7 +4405,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58">
         <v>2.130900537967008</v>
@@ -4468,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4482,7 +4455,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E59">
         <v>2.23740447163792</v>
@@ -4518,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4532,7 +4505,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E60">
         <v>2.23740447163792</v>
@@ -4568,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4582,7 +4555,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E61">
         <v>2.216035043209388</v>
@@ -4618,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4632,7 +4605,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>2.216035043209388</v>
@@ -4668,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4682,7 +4655,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>2.308272197921324</v>
@@ -4718,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4732,7 +4705,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>2.308272197921324</v>
@@ -4768,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4782,7 +4755,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E65">
         <v>2.383994213343331</v>
@@ -4818,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4832,7 +4805,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E66">
         <v>2.383994213343331</v>
@@ -4868,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4882,7 +4855,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E67">
         <v>2.341003053956531</v>
@@ -4918,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4932,7 +4905,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E68">
         <v>2.348235898796299</v>
@@ -4968,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4982,7 +4955,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E69">
         <v>2.327107470902277</v>
@@ -5018,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5032,7 +5005,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E70">
         <v>2.280646125088861</v>
@@ -5068,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5082,7 +5055,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E71">
         <v>2.302015094188537</v>
@@ -5118,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5132,7 +5105,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D72" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E72">
         <v>2.347919152567092</v>
@@ -5168,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5182,7 +5155,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E73">
         <v>2.148773116010439</v>
@@ -5218,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5232,7 +5205,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E74">
         <v>2.012974927806115</v>
@@ -5268,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5282,7 +5255,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E75">
         <v>2.060469575425552</v>
@@ -5318,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5332,7 +5305,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E76">
         <v>1.907509472337494</v>
@@ -5368,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5382,7 +5355,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E77">
         <v>1.98668904020824</v>
@@ -5418,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5432,7 +5405,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E78">
         <v>2.261468539033603</v>
@@ -5468,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5482,7 +5455,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E79">
         <v>2.508912235031609</v>
@@ -5518,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5532,7 +5505,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D80" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E80">
         <v>2.586570834612932</v>
@@ -5568,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5582,7 +5555,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E81">
         <v>2.299653216265908</v>
@@ -5618,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5632,7 +5605,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D82" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E82">
         <v>2.61595715496026</v>
@@ -5668,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5682,7 +5655,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D83" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E83">
         <v>2.61595715496026</v>
@@ -5718,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5732,7 +5705,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D84" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E84">
         <v>2.543317383832596</v>
@@ -5768,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5782,7 +5755,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E85">
         <v>2.543317383832596</v>
@@ -5818,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5832,7 +5805,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E86">
         <v>2.265161259044684</v>
@@ -5868,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5882,7 +5855,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E87">
         <v>2.290570133597897</v>
@@ -5918,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5932,7 +5905,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E88">
         <v>2.195461007763983</v>
@@ -5968,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5982,7 +5955,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E89">
         <v>2.350628131035313</v>
@@ -6018,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6032,7 +6005,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D90" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E90">
         <v>1.879284692646113</v>
@@ -6068,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6082,7 +6055,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D91" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E91">
         <v>1.878152907522461</v>
@@ -6118,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6132,7 +6105,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E92">
         <v>1.878152907522461</v>
@@ -6168,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6182,7 +6155,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E93">
         <v>1.878152907522461</v>
@@ -6218,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6232,7 +6205,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D94" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E94">
         <v>2.076228086890248</v>
@@ -6268,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6282,7 +6255,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E95">
         <v>2.078321265243905</v>
@@ -6318,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6332,7 +6305,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E96">
         <v>2.078321265243905</v>
@@ -6368,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6382,7 +6355,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D97" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E97">
         <v>2.078321265243905</v>
@@ -6418,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6432,7 +6405,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E98">
         <v>2.102213303799785</v>
@@ -6468,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6482,7 +6455,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E99">
         <v>2.092366071428574</v>
@@ -6518,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6532,7 +6505,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E100">
         <v>2.092366071428574</v>
@@ -6568,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6582,7 +6555,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E101">
         <v>2.092366071428574</v>
@@ -6618,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6632,7 +6605,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D102" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E102">
         <v>2.352465933358952</v>
@@ -6668,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6682,7 +6655,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E103">
         <v>2.352465933358952</v>
@@ -6718,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6732,7 +6705,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E104">
         <v>2.316305612395345</v>
@@ -6768,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6782,7 +6755,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D105" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E105">
         <v>2.316305612395345</v>
@@ -6818,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6832,7 +6805,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D106" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E106">
         <v>2.316305612395345</v>
@@ -6868,7 +6841,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6882,7 +6855,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D107" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E107">
         <v>1.660853987552378</v>
@@ -6918,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6932,7 +6905,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D108" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E108">
         <v>1.706062187746931</v>
@@ -6968,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6982,7 +6955,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E109">
         <v>1.706062187746931</v>
@@ -7018,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7032,7 +7005,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D110" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E110">
         <v>1.706062187746931</v>
@@ -7068,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7082,7 +7055,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D111" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E111">
         <v>0.8890067354016997</v>
@@ -7118,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7132,7 +7105,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E112">
         <v>0.9778684643520892</v>
@@ -7168,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7182,7 +7155,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D113" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E113">
         <v>0.9778684643520892</v>
@@ -7218,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7232,7 +7205,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E114">
         <v>0.9778684643520892</v>
@@ -7268,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7282,7 +7255,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E115">
         <v>0.9778684643520892</v>
@@ -7318,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7332,7 +7305,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E116">
         <v>0.3875605450183359</v>
@@ -7368,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7382,7 +7355,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D117" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E117">
         <v>0.5227816757955743</v>
@@ -7418,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7432,7 +7405,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D118" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E118">
         <v>0.5227816757955743</v>
@@ -7468,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7482,7 +7455,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E119">
         <v>0.5227816757955743</v>
@@ -7518,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7532,7 +7505,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E120">
         <v>0.0491242407754946</v>
@@ -7568,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7582,7 +7555,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E121">
         <v>0.159781143472614</v>
@@ -7618,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7632,7 +7605,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E122">
         <v>0.159781143472614</v>
@@ -7668,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7682,7 +7655,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D123" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E123">
         <v>-0.4676849642004726</v>
@@ -7718,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7732,7 +7705,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E124">
         <v>-0.3747925900670488</v>
@@ -7768,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7782,7 +7755,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E125">
         <v>-0.8235135484933682</v>
@@ -7818,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7832,7 +7805,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D126" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E126">
         <v>-0.2477467025920381</v>
@@ -7868,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7882,7 +7855,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D127" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E127">
         <v>-0.8406732630037332</v>
@@ -7918,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7932,7 +7905,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D128" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E128">
         <v>-0.2128000927823077</v>
@@ -7968,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7982,7 +7955,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D129" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E129">
         <v>0.387889534694934</v>
@@ -8018,7 +7991,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8032,7 +8005,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E130">
         <v>0.3268838700002261</v>
@@ -8068,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8082,7 +8055,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D131" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E131">
         <v>0.3619408673861413</v>
@@ -8118,7 +8091,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8132,7 +8105,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E132">
         <v>0.2887690811642036</v>
@@ -8168,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8182,7 +8155,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D133" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E133">
         <v>0.2054001299670292</v>
@@ -8218,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8232,7 +8205,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D134" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E134">
         <v>0.09424712584458561</v>
@@ -8268,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8282,7 +8255,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D135" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E135">
         <v>0.04964505068482161</v>
@@ -8318,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8332,7 +8305,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D136" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E136">
         <v>-0.06178174348131638</v>
@@ -8368,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8382,7 +8355,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D137" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E137">
         <v>-0.07084042392839685</v>
@@ -8418,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8432,7 +8405,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D138" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E138">
         <v>3.461981920657827</v>
@@ -8468,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8482,7 +8455,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D139" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E139">
         <v>3.521227138526164</v>
@@ -8518,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8532,7 +8505,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D140" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E140">
         <v>3.704772068908834</v>
@@ -8568,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8582,7 +8555,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D141" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E141">
         <v>4.126616365519087</v>
@@ -8618,7 +8591,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8632,7 +8605,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D142" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E142">
         <v>4.245160231267613</v>
@@ -8668,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8682,7 +8655,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D143" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E143">
         <v>4.229152349958373</v>
@@ -8718,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8732,7 +8705,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D144" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E144">
         <v>4.113073707261234</v>
@@ -8768,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8782,7 +8755,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D145" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E145">
         <v>3.642839509755204</v>
@@ -8818,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8832,7 +8805,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D146" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E146">
         <v>3.168034739342359</v>
@@ -8868,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8882,7 +8855,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D147" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E147">
         <v>2.998232417988513</v>
@@ -8918,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8932,7 +8905,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D148" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E148">
         <v>3.034053936494125</v>
@@ -8968,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8982,7 +8955,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D149" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E149">
         <v>2.914701276953577</v>
@@ -9018,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9032,7 +9005,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E150">
         <v>2.942385732505037</v>
@@ -9068,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9082,7 +9055,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D151" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E151">
         <v>2.891667239770102</v>
@@ -9118,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9132,7 +9105,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E152">
         <v>0.6731330742884634</v>
@@ -9168,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9182,7 +9155,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D153" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E153">
         <v>0.5049958305736757</v>
@@ -9218,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9232,7 +9205,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E154">
         <v>4.999995484409007</v>
@@ -9268,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9282,7 +9255,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E155">
         <v>4.49533934056099</v>
@@ -9318,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9332,7 +9305,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E156">
         <v>4.49533934056099</v>
@@ -9368,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9382,7 +9355,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E157">
         <v>5.75883309709841</v>
@@ -9418,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9432,7 +9405,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E158">
         <v>5.616961120807806</v>
@@ -9468,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9482,7 +9455,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D159" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E159">
         <v>-3.423739939881703</v>
@@ -9518,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9532,7 +9505,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D160" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E160">
         <v>-3.743311354600991</v>
@@ -9568,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9582,7 +9555,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D161" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E161">
         <v>-4.132985698695919</v>
@@ -9618,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9632,7 +9605,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D162" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E162">
         <v>-4.233476466219281</v>
@@ -9668,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9682,7 +9655,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D163" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E163">
         <v>-4.275085629955039</v>
@@ -9718,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9732,7 +9705,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E164">
         <v>-4.152544959638887</v>
@@ -9768,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9782,7 +9755,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D165" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E165">
         <v>-3.975060706658394</v>
@@ -9818,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9832,7 +9805,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D166" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E166">
         <v>-4.047254516344427</v>
@@ -9868,7 +9841,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9882,7 +9855,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D167" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E167">
         <v>-3.79843891093761</v>
@@ -9918,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9932,7 +9905,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D168" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E168">
         <v>-3.666707344934939</v>
@@ -9982,7 +9955,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D169" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E169">
         <v>-3.713489605052797</v>
@@ -10018,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10032,7 +10005,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D170" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E170">
         <v>-3.548252121908546</v>
@@ -10068,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10082,7 +10055,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D171" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E171">
         <v>-3.286247287427305</v>
@@ -10118,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10132,7 +10105,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D172" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E172">
         <v>1.158519820616992</v>
@@ -10168,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10182,7 +10155,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D173" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E173">
         <v>1.172691348768068</v>
@@ -10218,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10232,7 +10205,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D174" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E174">
         <v>1.000464874270701</v>
@@ -10268,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10282,7 +10255,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D175" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E175">
         <v>0.3824058924251874</v>
@@ -10318,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10332,7 +10305,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D176" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E176">
         <v>0.3824058924251874</v>
@@ -10368,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10382,7 +10355,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D177" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E177">
         <v>0.3824058924251874</v>
@@ -10418,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10432,7 +10405,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D178" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E178">
         <v>0.0213012212570054</v>
@@ -10468,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10482,7 +10455,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D179" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E179">
         <v>0.0213012212570054</v>
@@ -10518,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10568,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10618,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10668,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10718,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10732,7 +10705,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D184" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E184">
         <v>1.582625511992627</v>
@@ -10768,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10782,7 +10755,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D185" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E185">
         <v>1.559453546602203</v>
@@ -10818,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10832,7 +10805,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D186" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E186">
         <v>1.547361538049228</v>
@@ -10868,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10882,7 +10855,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D187" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E187">
         <v>1.401993513086136</v>
@@ -10918,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10932,7 +10905,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D188" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E188">
         <v>1.434633300285655</v>
@@ -10968,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10982,7 +10955,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D189" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E189">
         <v>1.425858209046284</v>
@@ -11018,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11032,7 +11005,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D190" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E190">
         <v>1.475198819417429</v>
@@ -11068,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11082,7 +11055,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D191" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E191">
         <v>1.441005693114453</v>
@@ -11118,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11132,7 +11105,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E192">
         <v>1.488718514152899</v>
@@ -11168,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11182,7 +11155,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E193">
         <v>1.446244175787084</v>
@@ -11218,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11232,7 +11205,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D194" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E194">
         <v>1.493394055403994</v>
@@ -11268,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11282,7 +11255,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D195" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E195">
         <v>1.446322000480185</v>
@@ -11318,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11332,7 +11305,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D196" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E196">
         <v>1.493463516846493</v>
@@ -11368,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11382,7 +11355,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D197" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E197">
         <v>1.435847306141142</v>
@@ -11418,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11432,7 +11405,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D198" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E198">
         <v>1.484114461302094</v>
@@ -11468,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11482,7 +11455,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D199" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E199">
         <v>1.466561985673455</v>
@@ -11518,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11532,7 +11505,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D200" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E200">
         <v>1.511528458854815</v>
@@ -11568,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11582,7 +11555,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D201" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E201">
         <v>1.479399782082176</v>
@@ -11618,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11632,7 +11605,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D202" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E202">
         <v>1.522986671171852</v>
@@ -11668,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11682,7 +11655,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D203" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E203">
         <v>1.459395439652966</v>
@@ -11718,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11732,7 +11705,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D204" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E204">
         <v>1.505132049123094</v>
@@ -11768,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11782,7 +11755,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D205" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E205">
         <v>1.397112808581932</v>
@@ -11818,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11832,7 +11805,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D206" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E206">
         <v>1.449542476913426</v>
@@ -11868,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11882,7 +11855,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D207" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E207">
         <v>1.294143898865006</v>
@@ -11918,7 +11891,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11932,7 +11905,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D208" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E208">
         <v>1.357638882867572</v>
@@ -11968,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11982,7 +11955,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D209" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E209">
         <v>1.18030319903414</v>
@@ -12018,7 +11991,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12032,7 +12005,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D210" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E210">
         <v>1.18030319903414</v>
@@ -12068,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12082,7 +12055,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D211" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E211">
         <v>1.188653245722397</v>
@@ -12118,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12132,7 +12105,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D212" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E212">
         <v>0.9564817011303721</v>
@@ -12168,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12182,7 +12155,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D213" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E213">
         <v>0.9564817011303721</v>
@@ -12218,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12232,7 +12205,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D214" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E214">
         <v>0.9595778612972841</v>
@@ -12268,7 +12241,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12282,7 +12255,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D215" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E215">
         <v>0.7699303832078415</v>
@@ -12318,7 +12291,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12332,7 +12305,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D216" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E216">
         <v>0.7699303832078415</v>
@@ -12368,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12382,7 +12355,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D217" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E217">
         <v>0.7699303832078415</v>
@@ -12418,7 +12391,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12432,7 +12405,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D218" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E218">
         <v>0.7947444579985703</v>
@@ -12468,7 +12441,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12482,7 +12455,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D219" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E219">
         <v>0.681784458813524</v>
@@ -12518,7 +12491,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12532,7 +12505,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D220" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E220">
         <v>0.681784458813524</v>
@@ -12568,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12582,7 +12555,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D221" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E221">
         <v>0.6868602979367258</v>
@@ -12618,7 +12591,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12632,7 +12605,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E222">
         <v>0.6904864136981455</v>
@@ -12668,7 +12641,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12682,7 +12655,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D223" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E223">
         <v>0.6904864136981455</v>
@@ -12718,7 +12691,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12732,7 +12705,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D224" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E224">
         <v>0.6988520528231206</v>
@@ -12768,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12782,7 +12755,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D225" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E225">
         <v>0.5364590093992025</v>
@@ -12818,7 +12791,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12832,7 +12805,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D226" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E226">
         <v>0.5584533336781012</v>
@@ -12868,7 +12841,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12882,7 +12855,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D227" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E227">
         <v>0.4349435599285871</v>
@@ -12918,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12932,7 +12905,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D228" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E228">
         <v>0.4687561007130205</v>
@@ -12968,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12982,7 +12955,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D229" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E229">
         <v>0.4011997840155024</v>
@@ -13018,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13032,7 +13005,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D230" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E230">
         <v>0.4389407046823544</v>
@@ -13068,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13082,7 +13055,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D231" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E231">
         <v>0.3332852216938216</v>
@@ -13118,7 +13091,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13132,7 +13105,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D232" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E232">
         <v>0.3789326137951377</v>
@@ -13168,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13182,7 +13155,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D233" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E233">
         <v>0.3201663194080338</v>
@@ -13218,7 +13191,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13232,7 +13205,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D234" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E234">
         <v>0.3201663194080338</v>
@@ -13268,7 +13241,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13282,7 +13255,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D235" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E235">
         <v>0.3673409867008299</v>
@@ -13318,7 +13291,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13332,7 +13305,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D236" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E236">
         <v>0.385066244864444</v>
@@ -13368,7 +13341,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13382,7 +13355,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D237" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E237">
         <v>0.385066244864444</v>
@@ -13418,7 +13391,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13432,7 +13405,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D238" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E238">
         <v>0.385066244864444</v>
@@ -13468,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13482,7 +13455,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D239" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E239">
         <v>0.4246853984473891</v>
@@ -13518,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13532,7 +13505,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D240" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E240">
         <v>0.3952650685155521</v>
@@ -13568,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13582,7 +13555,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D241" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E241">
         <v>0.3952650685155521</v>
@@ -13618,7 +13591,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13632,7 +13605,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D242" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E242">
         <v>0.3952650685155521</v>
@@ -13668,7 +13641,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13682,7 +13655,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D243" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E243">
         <v>0.4336968963600101</v>
@@ -13718,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13732,7 +13705,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D244" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E244">
         <v>0.441533745152785</v>
@@ -13768,7 +13741,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13782,7 +13755,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D245" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E245">
         <v>0.441533745152785</v>
@@ -13818,7 +13791,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13832,7 +13805,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D246" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E246">
         <v>0.441533745152785</v>
@@ -13868,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13882,7 +13855,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D247" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E247">
         <v>0.4745790703439532</v>
@@ -13918,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13932,7 +13905,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D248" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E248">
         <v>0.5262223068621856</v>
@@ -13968,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13982,7 +13955,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D249" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E249">
         <v>0.5262223068621856</v>
@@ -14018,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14032,7 +14005,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D250" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E250">
         <v>0.5494083666603191</v>
@@ -14068,7 +14041,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14082,7 +14055,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D251" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E251">
         <v>1.134910071595908</v>
@@ -14118,7 +14091,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14132,7 +14105,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D252" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E252">
         <v>1.119751573421224</v>
@@ -14168,7 +14141,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14182,7 +14155,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D253" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E253">
         <v>1.055413005631895</v>
@@ -14218,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14232,7 +14205,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D254" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E254">
         <v>1.03217696150402</v>
@@ -14268,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14282,7 +14255,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D255" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E255">
         <v>0.897246951281871</v>
@@ -14318,7 +14291,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14332,7 +14305,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D256" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E256">
         <v>0.8706167327436121</v>
@@ -14368,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14382,7 +14355,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D257" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E257">
         <v>1.412833444305319</v>
@@ -14418,7 +14391,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14432,7 +14405,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D258" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E258">
         <v>1.399053391868887</v>
@@ -14468,7 +14441,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14482,7 +14455,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D259" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E259">
         <v>1.480439984508878</v>
@@ -14518,7 +14491,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14532,7 +14505,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D260" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E260">
         <v>1.457637705051676</v>
@@ -14618,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14632,7 +14605,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D262" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E262">
         <v>1.2222369081479</v>
@@ -14668,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14682,7 +14655,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D263" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E263">
         <v>1.311393675757068</v>
@@ -14718,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14732,7 +14705,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D264" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E264">
         <v>1.084160634764066</v>
@@ -14768,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14782,7 +14755,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D265" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E265">
         <v>1.193914185004133</v>
@@ -14818,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14832,7 +14805,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D266" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E266">
         <v>0.8573351083141707</v>
@@ -14868,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14882,7 +14855,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D267" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E267">
         <v>0.988341401428052</v>
@@ -14918,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14932,7 +14905,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D268" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E268">
         <v>0.7856322541233942</v>
@@ -14968,7 +14941,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14982,7 +14955,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D269" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E269">
         <v>0.9271686010995708</v>
@@ -15018,7 +14991,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15032,7 +15005,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D270" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E270">
         <v>0.666724382278634</v>
@@ -15068,7 +15041,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15082,7 +15055,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D271" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E271">
         <v>0.8120247704726087</v>
@@ -15118,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15132,7 +15105,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E272">
         <v>0.5554941770903916</v>
@@ -15168,7 +15141,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15182,7 +15155,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D273" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E273">
         <v>0.5343135639758354</v>
@@ -15218,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15232,7 +15205,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D274" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E274">
         <v>0.5543280182232331</v>
@@ -15268,7 +15241,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15282,7 +15255,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D275" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E275">
         <v>0.6169560865757506</v>
@@ -15318,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15332,7 +15305,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D276" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E276">
         <v>0.6169560865757506</v>
@@ -15368,7 +15341,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15382,7 +15355,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D277" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E277">
         <v>0.8673239084198645</v>
@@ -15418,7 +15391,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15432,7 +15405,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D278" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E278">
         <v>0.7616569728121176</v>
@@ -15468,7 +15441,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15482,7 +15455,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D279" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E279">
         <v>0.9495779791694832</v>
@@ -15518,7 +15491,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15532,7 +15505,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D280" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E280">
         <v>0.9388491310062772</v>
@@ -15568,7 +15541,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15618,7 +15591,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15668,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15682,7 +15655,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D283" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E283">
         <v>0.9972247567745822</v>
@@ -15718,7 +15691,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15732,7 +15705,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D284" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E284">
         <v>1.155095366349694</v>
@@ -15768,7 +15741,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15782,7 +15755,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D285" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E285">
         <v>1.155095366349694</v>
@@ -15818,7 +15791,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15832,7 +15805,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D286" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E286">
         <v>1.155095366349694</v>
@@ -15868,7 +15841,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15882,7 +15855,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D287" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E287">
         <v>1.266654823722328</v>
@@ -15918,7 +15891,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15968,7 +15941,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16018,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16032,7 +16005,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D290" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E290">
         <v>1.216516290726816</v>
@@ -16068,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16082,7 +16055,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D291" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E291">
         <v>1.377468671679197</v>
@@ -16118,7 +16091,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16132,7 +16105,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D292" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E292">
         <v>1.377468671679197</v>
@@ -16168,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16182,7 +16155,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D293" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E293">
         <v>1.098022759601705</v>
@@ -16218,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16232,7 +16205,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D294" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E294">
         <v>1.26116642958748</v>
@@ -16268,7 +16241,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16282,7 +16255,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D295" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E295">
         <v>1.26116642958748</v>
@@ -16318,7 +16291,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16332,7 +16305,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D296" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E296">
         <v>0.8607264291791745</v>
@@ -16368,7 +16341,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16418,7 +16391,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16468,7 +16441,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16482,7 +16455,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D299" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E299">
         <v>0.824097311139564</v>
@@ -16518,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16532,7 +16505,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D300" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E300">
         <v>1.040422535211267</v>
@@ -16568,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16582,7 +16555,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D301" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E301">
         <v>1.040422535211267</v>
@@ -16618,7 +16591,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16632,7 +16605,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D302" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E302">
         <v>1.040422535211267</v>
@@ -16668,7 +16641,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16682,7 +16655,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D303" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E303">
         <v>0.6892070138707138</v>
@@ -16718,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16732,7 +16705,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D304" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E304">
         <v>0.904611358283171</v>
@@ -16768,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16782,7 +16755,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D305" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E305">
         <v>0.6020667096198637</v>
@@ -16818,7 +16791,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16832,7 +16805,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D306" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E306">
         <v>0.7705397234474891</v>
@@ -16868,7 +16841,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16882,7 +16855,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D307" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E307">
         <v>0.5104188656556885</v>
@@ -16918,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16932,7 +16905,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D308" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E308">
         <v>0.4186576811044649</v>
@@ -16968,7 +16941,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16982,7 +16955,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D309" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E309">
         <v>0.1677359829666414</v>
@@ -17018,7 +16991,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17068,7 +17041,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17118,7 +17091,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17132,7 +17105,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D312" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E312">
         <v>1.515642348344327</v>
@@ -17168,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17218,7 +17191,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17268,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17282,7 +17255,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D315" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E315">
         <v>1.493247566063977</v>
@@ -17318,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17368,7 +17341,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17418,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17432,7 +17405,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D318" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E318">
         <v>1.414710468897303</v>
@@ -17468,7 +17441,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17518,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17541,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17582,7 +17555,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D321" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E321">
         <v>1.396497005988024</v>
@@ -17618,7 +17591,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17668,7 +17641,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17691,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17732,7 +17705,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D324" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E324">
         <v>1.376951717138971</v>
@@ -17768,7 +17741,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17818,7 +17791,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17841,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17882,7 +17855,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D327" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E327">
         <v>1.359032433928708</v>
@@ -17918,7 +17891,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17968,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18032,7 +18005,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D330" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E330">
         <v>1.335880304635819</v>
@@ -18068,7 +18041,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18118,7 +18091,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18168,7 +18141,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18182,7 +18155,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D333" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E333">
         <v>1.309957507300225</v>
@@ -18218,7 +18191,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18332,7 +18305,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D336" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E336">
         <v>1.320449616201756</v>
@@ -18418,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18432,7 +18405,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D338" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E338">
         <v>1.284476712309384</v>
@@ -18468,7 +18441,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18518,7 +18491,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18568,7 +18541,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18582,7 +18555,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D341" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E341">
         <v>1.24169474125916</v>
@@ -18618,7 +18591,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18782,7 +18755,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D345" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E345">
         <v>1.182114445177575</v>
@@ -18868,7 +18841,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18918,7 +18891,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18932,7 +18905,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D348" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E348">
         <v>1.151200461638077</v>
@@ -18968,7 +18941,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18982,7 +18955,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D349" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E349">
         <v>1.119879175702464</v>
@@ -19068,7 +19041,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19082,7 +19055,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D351" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E351">
         <v>1.094826807940879</v>
@@ -19118,7 +19091,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19168,7 +19141,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19182,7 +19155,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D353" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E353">
         <v>1.064947268845516</v>
@@ -19218,7 +19191,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19282,7 +19255,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D355" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E355">
         <v>1.014148422477695</v>
@@ -19332,7 +19305,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D356" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E356">
         <v>0.7662610529884266</v>
@@ -19368,7 +19341,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19382,7 +19355,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D357" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E357">
         <v>0.7460729511326034</v>
@@ -19418,7 +19391,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19432,7 +19405,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D358" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E358">
         <v>0.7067614879649891</v>
@@ -19468,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19482,7 +19455,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D359" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E359">
         <v>0.6717864324675069</v>
@@ -19568,7 +19541,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19582,7 +19555,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D361" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E361">
         <v>0.5671969948491258</v>
@@ -19618,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19668,7 +19641,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19718,7 +19691,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19732,7 +19705,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D364" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E364">
         <v>0.605257854179015</v>
@@ -19768,7 +19741,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19782,7 +19755,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D365" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E365">
         <v>0.4201630112625956</v>
@@ -19818,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19832,7 +19805,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D366" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E366">
         <v>0.4201630112625956</v>
@@ -19868,7 +19841,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19882,7 +19855,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D367" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E367">
         <v>0.4879084704937777</v>
@@ -19918,7 +19891,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19932,7 +19905,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D368" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E368">
         <v>0.4879084704937777</v>
@@ -19968,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19982,7 +19955,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D369" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E369">
         <v>0.549200546946218</v>
@@ -20018,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20032,7 +20005,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D370" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E370">
         <v>0.549200546946218</v>
@@ -20068,7 +20041,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20082,7 +20055,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D371" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E371">
         <v>0.5264173880682987</v>
@@ -20118,7 +20091,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20132,7 +20105,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D372" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E372">
         <v>0.444542315946628</v>
@@ -20168,7 +20141,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20218,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20232,7 +20205,7 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D374" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E374">
         <v>1.874132439228835</v>
@@ -20268,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20282,7 +20255,7 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D375" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E375">
         <v>1.895013344497358</v>
@@ -20318,7 +20291,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20332,7 +20305,7 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D376" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E376">
         <v>2.012343579813627</v>
@@ -20368,7 +20341,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20382,7 +20355,7 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D377" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E377">
         <v>1.990118664933999</v>
@@ -20418,7 +20391,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20432,7 +20405,7 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D378" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E378">
         <v>1.88467053493363</v>
@@ -20468,7 +20441,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20479,46 +20452,46 @@
         <v>81</v>
       </c>
       <c r="C379">
-        <v>0.6461489520701507</v>
+        <v>2.038444260870803</v>
       </c>
       <c r="D379" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E379">
-        <v>0.6347638472771657</v>
+        <v>2.240361339391263</v>
       </c>
       <c r="F379">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G379">
-        <v>0.003473851047929849</v>
+        <v>0.001781555739129197</v>
       </c>
       <c r="H379">
-        <v>0.003745236152722834</v>
+        <v>0.001979638660608737</v>
       </c>
       <c r="I379">
-        <v>0.01138510479298493</v>
+        <v>0.2019170785204598</v>
       </c>
       <c r="J379">
-        <v>1.087577729176807</v>
+        <v>-0.0958539260229872</v>
       </c>
       <c r="K379">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L379">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M379">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N379">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20529,46 +20502,46 @@
         <v>81</v>
       </c>
       <c r="C380">
-        <v>0.6127022961997406</v>
+        <v>2.176625292888353</v>
       </c>
       <c r="D380" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E380">
-        <v>0.5979725258197146</v>
+        <v>2.380604774871761</v>
       </c>
       <c r="F380">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G380">
-        <v>0.003507297703800259</v>
+        <v>0.001643374707111647</v>
       </c>
       <c r="H380">
-        <v>0.003782027474180286</v>
+        <v>0.001839395225128238</v>
       </c>
       <c r="I380">
-        <v>0.01472977038002599</v>
+        <v>0.2039794819834082</v>
       </c>
       <c r="J380">
-        <v>1.1133059260002</v>
+        <v>-0.1989740991704129</v>
       </c>
       <c r="K380">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L380">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M380">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N380">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20579,46 +20552,46 @@
         <v>81</v>
       </c>
       <c r="C381">
-        <v>0.5917565930359752</v>
+        <v>2.240948171745636</v>
       </c>
       <c r="D381" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E381">
-        <v>0.5749322523395726</v>
+        <v>2.445887696697064</v>
       </c>
       <c r="F381">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G381">
-        <v>0.003528243406964025</v>
+        <v>0.001579051828254363</v>
       </c>
       <c r="H381">
-        <v>0.003805067747660427</v>
+        <v>0.001774112303302936</v>
       </c>
       <c r="I381">
-        <v>0.0168243406964026</v>
+        <v>0.2049395249514276</v>
       </c>
       <c r="J381">
-        <v>1.129418005356942</v>
+        <v>-0.2469762475713705</v>
       </c>
       <c r="K381">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L381">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M381">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N381">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20629,396 +20602,46 @@
         <v>81</v>
       </c>
       <c r="C382">
-        <v>0.5770416467209205</v>
+        <v>2.276110233960097</v>
       </c>
       <c r="D382" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E382">
-        <v>0.5587458113930126</v>
+        <v>2.481574565810248</v>
       </c>
       <c r="F382">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G382">
-        <v>0.003542958353279079</v>
+        <v>0.001543889766039903</v>
       </c>
       <c r="H382">
-        <v>0.003821254188606988</v>
+        <v>0.001738425434189752</v>
       </c>
       <c r="I382">
-        <v>0.01829583532790791</v>
+        <v>0.2054643318501506</v>
       </c>
       <c r="J382">
-        <v>1.140737194830061</v>
+        <v>-0.2732165925075352</v>
       </c>
       <c r="K382">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="L382">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="M382">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="N382">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O382">
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="383" spans="1:16">
-      <c r="A383" s="1">
-        <v>0</v>
-      </c>
-      <c r="B383" t="s">
-        <v>81</v>
-      </c>
-      <c r="C383">
-        <v>0.5562596397799509</v>
-      </c>
-      <c r="D383" t="s">
-        <v>213</v>
-      </c>
-      <c r="E383">
-        <v>0.5358856037579458</v>
-      </c>
-      <c r="F383">
-        <v>-1</v>
-      </c>
-      <c r="G383">
-        <v>0.00356374036022005</v>
-      </c>
-      <c r="H383">
-        <v>0.003844114396242054</v>
-      </c>
-      <c r="I383">
-        <v>0.02037403602200505</v>
-      </c>
-      <c r="J383">
-        <v>1.156723354015422</v>
-      </c>
-      <c r="K383">
-        <v>1.3</v>
-      </c>
-      <c r="L383">
-        <v>2.06</v>
-      </c>
-      <c r="M383">
-        <v>1.43</v>
-      </c>
-      <c r="N383">
-        <v>2.19</v>
-      </c>
-      <c r="O383">
-        <v>1</v>
-      </c>
-      <c r="P383" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="384" spans="1:16">
-      <c r="A384" s="1">
-        <v>0</v>
-      </c>
-      <c r="B384" t="s">
-        <v>81</v>
-      </c>
-      <c r="C384">
-        <v>0.5065075041938034</v>
-      </c>
-      <c r="D384" t="s">
-        <v>213</v>
-      </c>
-      <c r="E384">
-        <v>0.4811582546131838</v>
-      </c>
-      <c r="F384">
-        <v>-1</v>
-      </c>
-      <c r="G384">
-        <v>0.003613492495806197</v>
-      </c>
-      <c r="H384">
-        <v>0.003898841745386816</v>
-      </c>
-      <c r="I384">
-        <v>0.02534924958061957</v>
-      </c>
-      <c r="J384">
-        <v>1.194994227543228</v>
-      </c>
-      <c r="K384">
-        <v>1.3</v>
-      </c>
-      <c r="L384">
-        <v>2.06</v>
-      </c>
-      <c r="M384">
-        <v>1.43</v>
-      </c>
-      <c r="N384">
-        <v>2.19</v>
-      </c>
-      <c r="O384">
-        <v>1</v>
-      </c>
-      <c r="P384" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="385" spans="1:16">
-      <c r="A385" s="1">
-        <v>0</v>
-      </c>
-      <c r="B385" t="s">
-        <v>81</v>
-      </c>
-      <c r="C385">
-        <v>0.508920826902155</v>
-      </c>
-      <c r="D385" t="s">
-        <v>213</v>
-      </c>
-      <c r="E385">
-        <v>0.4838129095923704</v>
-      </c>
-      <c r="F385">
-        <v>-1</v>
-      </c>
-      <c r="G385">
-        <v>0.003611079173097845</v>
-      </c>
-      <c r="H385">
-        <v>0.003896187090407629</v>
-      </c>
-      <c r="I385">
-        <v>0.02510791730978457</v>
-      </c>
-      <c r="J385">
-        <v>1.193137825459881</v>
-      </c>
-      <c r="K385">
-        <v>1.3</v>
-      </c>
-      <c r="L385">
-        <v>2.06</v>
-      </c>
-      <c r="M385">
-        <v>1.43</v>
-      </c>
-      <c r="N385">
-        <v>2.19</v>
-      </c>
-      <c r="O385">
-        <v>1</v>
-      </c>
-      <c r="P385" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="386" spans="1:16">
-      <c r="A386" s="1">
-        <v>0</v>
-      </c>
-      <c r="B386" t="s">
-        <v>82</v>
-      </c>
-      <c r="C386">
-        <v>2.038444260870803</v>
-      </c>
-      <c r="D386" t="s">
-        <v>214</v>
-      </c>
-      <c r="E386">
-        <v>2.240361339391263</v>
-      </c>
-      <c r="F386">
-        <v>1</v>
-      </c>
-      <c r="G386">
-        <v>0.001781555739129197</v>
-      </c>
-      <c r="H386">
-        <v>0.001979638660608737</v>
-      </c>
-      <c r="I386">
-        <v>0.2019170785204598</v>
-      </c>
-      <c r="J386">
-        <v>-0.0958539260229872</v>
-      </c>
-      <c r="K386">
-        <v>1.34</v>
-      </c>
-      <c r="L386">
-        <v>1.91</v>
-      </c>
-      <c r="M386">
-        <v>1.36</v>
-      </c>
-      <c r="N386">
-        <v>2.11</v>
-      </c>
-      <c r="O386">
-        <v>1</v>
-      </c>
-      <c r="P386" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="387" spans="1:16">
-      <c r="A387" s="1">
-        <v>0</v>
-      </c>
-      <c r="B387" t="s">
-        <v>82</v>
-      </c>
-      <c r="C387">
-        <v>2.176625292888353</v>
-      </c>
-      <c r="D387" t="s">
-        <v>214</v>
-      </c>
-      <c r="E387">
-        <v>2.380604774871761</v>
-      </c>
-      <c r="F387">
-        <v>1</v>
-      </c>
-      <c r="G387">
-        <v>0.001643374707111647</v>
-      </c>
-      <c r="H387">
-        <v>0.001839395225128238</v>
-      </c>
-      <c r="I387">
-        <v>0.2039794819834082</v>
-      </c>
-      <c r="J387">
-        <v>-0.1989740991704129</v>
-      </c>
-      <c r="K387">
-        <v>1.34</v>
-      </c>
-      <c r="L387">
-        <v>1.91</v>
-      </c>
-      <c r="M387">
-        <v>1.36</v>
-      </c>
-      <c r="N387">
-        <v>2.11</v>
-      </c>
-      <c r="O387">
-        <v>1</v>
-      </c>
-      <c r="P387" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="388" spans="1:16">
-      <c r="A388" s="1">
-        <v>0</v>
-      </c>
-      <c r="B388" t="s">
-        <v>82</v>
-      </c>
-      <c r="C388">
-        <v>2.240948171745636</v>
-      </c>
-      <c r="D388" t="s">
-        <v>214</v>
-      </c>
-      <c r="E388">
-        <v>2.445887696697064</v>
-      </c>
-      <c r="F388">
-        <v>1</v>
-      </c>
-      <c r="G388">
-        <v>0.001579051828254363</v>
-      </c>
-      <c r="H388">
-        <v>0.001774112303302936</v>
-      </c>
-      <c r="I388">
-        <v>0.2049395249514276</v>
-      </c>
-      <c r="J388">
-        <v>-0.2469762475713705</v>
-      </c>
-      <c r="K388">
-        <v>1.34</v>
-      </c>
-      <c r="L388">
-        <v>1.91</v>
-      </c>
-      <c r="M388">
-        <v>1.36</v>
-      </c>
-      <c r="N388">
-        <v>2.11</v>
-      </c>
-      <c r="O388">
-        <v>1</v>
-      </c>
-      <c r="P388" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="389" spans="1:16">
-      <c r="A389" s="1">
-        <v>0</v>
-      </c>
-      <c r="B389" t="s">
-        <v>82</v>
-      </c>
-      <c r="C389">
-        <v>2.276110233960097</v>
-      </c>
-      <c r="D389" t="s">
-        <v>214</v>
-      </c>
-      <c r="E389">
-        <v>2.481574565810248</v>
-      </c>
-      <c r="F389">
-        <v>1</v>
-      </c>
-      <c r="G389">
-        <v>0.001543889766039903</v>
-      </c>
-      <c r="H389">
-        <v>0.001738425434189752</v>
-      </c>
-      <c r="I389">
-        <v>0.2054643318501506</v>
-      </c>
-      <c r="J389">
-        <v>-0.2732165925075352</v>
-      </c>
-      <c r="K389">
-        <v>1.34</v>
-      </c>
-      <c r="L389">
-        <v>1.91</v>
-      </c>
-      <c r="M389">
-        <v>1.36</v>
-      </c>
-      <c r="N389">
-        <v>2.11</v>
-      </c>
-      <c r="O389">
-        <v>1</v>
-      </c>
-      <c r="P389" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00525-601333.xlsx
+++ b/s60_signal/position-00525-601333.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="399">
   <si>
     <t>trade_time</t>
   </si>
@@ -259,6 +259,9 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -652,6 +655,9 @@
     <t>2021-08-31</t>
   </si>
   <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
     <t>2021-08-26</t>
   </si>
   <si>
@@ -1175,6 +1181,24 @@
   </si>
   <si>
     <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
   </si>
   <si>
     <t>2021-06-03</t>
@@ -1544,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P382"/>
+  <dimension ref="A1:P390"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1605,7 +1629,7 @@
         <v>-2.854846432353775</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>-3.697130498869741</v>
@@ -1641,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1655,7 +1679,7 @@
         <v>-2.62076620166601</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>-3.697130498869741</v>
@@ -1691,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1705,7 +1729,7 @@
         <v>-4.485186158734111</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>-4.489266389421874</v>
@@ -1741,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1755,7 +1779,7 @@
         <v>-4.51518615873411</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>-4.489266389421874</v>
@@ -1791,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1805,7 +1829,7 @@
         <v>-4.713642972037302</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>-4.489266389421874</v>
@@ -1841,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1855,7 +1879,7 @@
         <v>-4.634340477403791</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>-4.489266389421874</v>
@@ -1891,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1905,7 +1929,7 @@
         <v>-3.266622461213251</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>-4.701411851904431</v>
@@ -1941,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1955,7 +1979,7 @@
         <v>-3.041411252685536</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>-4.701411851904431</v>
@@ -1991,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2005,7 +2029,7 @@
         <v>-5.103665541825247</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>-4.720848429424226</v>
@@ -2041,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2055,7 +2079,7 @@
         <v>-5.25845433329753</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>-4.720848429424226</v>
@@ -2091,7 +2115,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2105,7 +2129,7 @@
         <v>-5.165214803841085</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>-4.720848429424226</v>
@@ -2141,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2155,7 +2179,7 @@
         <v>-3.423632276024851</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13">
         <v>-4.896104022270815</v>
@@ -2191,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2205,7 +2229,7 @@
         <v>-3.201802817354617</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>-4.896104022270815</v>
@@ -2241,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2255,7 +2279,7 @@
         <v>-5.46619039597134</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>-5.17427456360058</v>
@@ -2291,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2305,7 +2329,7 @@
         <v>-5.367636688167424</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16">
         <v>-5.17427456360058</v>
@@ -2341,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2355,7 +2379,7 @@
         <v>-3.515182964200185</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17">
         <v>-5.009626875608229</v>
@@ -2391,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2405,7 +2429,7 @@
         <v>-3.295325366506034</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18">
         <v>-5.009626875608229</v>
@@ -2441,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2455,7 +2479,7 @@
         <v>-5.587318998787936</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19">
         <v>-5.093871903520842</v>
@@ -2491,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2505,7 +2529,7 @@
         <v>-5.485666652307316</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20">
         <v>-5.093871903520842</v>
@@ -2541,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2555,7 +2579,7 @@
         <v>-3.383806326393561</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>-5.117029968483751</v>
@@ -2591,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2605,7 +2629,7 @@
         <v>-5.701917832377204</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>-5.42733388782802</v>
@@ -2641,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2655,7 +2679,7 @@
         <v>-5.59733388782802</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23">
         <v>-5.42733388782802</v>
@@ -2691,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2705,7 +2729,7 @@
         <v>-3.452316380679396</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E24">
         <v>-5.200191269318666</v>
@@ -2741,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2755,7 +2779,7 @@
         <v>-5.790650734012472</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25">
         <v>-5.56384792965875</v>
@@ -2791,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2805,7 +2829,7 @@
         <v>-5.683796878026108</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E26">
         <v>-5.56384792965875</v>
@@ -2841,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2855,7 +2879,7 @@
         <v>-3.62044684029153</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>-5.140154081961497</v>
@@ -2891,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2905,7 +2929,7 @@
         <v>-3.402856464543962</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28">
         <v>-5.140154081961497</v>
@@ -2941,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2955,7 +2979,7 @@
         <v>-5.726591204078023</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29">
         <v>-5.278966456000339</v>
@@ -2991,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3005,7 +3029,7 @@
         <v>-3.561370374839291</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30">
         <v>-5.066899264800722</v>
@@ -3041,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3055,7 +3079,7 @@
         <v>-3.342507582912753</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>-5.066899264800722</v>
@@ -3091,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3105,7 +3129,7 @@
         <v>-5.648428495941216</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>-5.339173680947644</v>
@@ -3141,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3155,7 +3179,7 @@
         <v>-3.48867163055963</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>-4.976752821893942</v>
@@ -3191,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3205,7 +3229,7 @@
         <v>-3.26824301952553</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>-4.976752821893942</v>
@@ -3241,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3255,7 +3279,7 @@
         <v>-5.552242465048126</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E35">
         <v>-5.332242465048126</v>
@@ -3291,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3305,7 +3329,7 @@
         <v>-3.39280132450331</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36">
         <v>-4.857873642384104</v>
@@ -3341,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3355,7 +3379,7 @@
         <v>-3.170307814569535</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>-4.857873642384104</v>
@@ -3391,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3405,7 +3429,7 @@
         <v>-5.425398675496686</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E38">
         <v>-5.212897748344369</v>
@@ -3441,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3455,7 +3479,7 @@
         <v>3.896409547559524</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E39">
         <v>3.637557788757765</v>
@@ -3491,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3505,7 +3529,7 @@
         <v>3.686370782301712</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E40">
         <v>3.637557788757765</v>
@@ -3541,7 +3565,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3555,7 +3579,7 @@
         <v>3.999857615280466</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E41">
         <v>3.696125600943092</v>
@@ -3591,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3605,7 +3629,7 @@
         <v>3.791532275574967</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E42">
         <v>3.696125600943092</v>
@@ -3641,7 +3665,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3655,7 +3679,7 @@
         <v>4.016648312008632</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E43">
         <v>3.562106983197164</v>
@@ -3691,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3705,7 +3729,7 @@
         <v>3.808601079081239</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E44">
         <v>3.562106983197164</v>
@@ -3741,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3755,7 +3779,7 @@
         <v>3.921540730472905</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E45">
         <v>3.447106959801425</v>
@@ -3791,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3805,7 +3829,7 @@
         <v>3.777106959801425</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>3.447106959801425</v>
@@ -3841,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3855,7 +3879,7 @@
         <v>3.355765574180636</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>2.97063976553844</v>
@@ -3891,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3905,7 +3929,7 @@
         <v>3.197275277886988</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E48">
         <v>2.97063976553844</v>
@@ -3941,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3955,7 +3979,7 @@
         <v>2.908811773838419</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49">
         <v>2.574206073921443</v>
@@ -3991,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4005,7 +4029,7 @@
         <v>2.739217035300243</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E50">
         <v>2.574206073921443</v>
@@ -4041,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4055,7 +4079,7 @@
         <v>2.722206373258291</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E51">
         <v>2.392623178946991</v>
@@ -4091,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4105,7 +4129,7 @@
         <v>2.547975475699491</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>2.392623178946991</v>
@@ -4141,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4155,7 +4179,7 @@
         <v>2.662325508545921</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53">
         <v>2.257085968244024</v>
@@ -4191,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4205,7 +4229,7 @@
         <v>2.48660688764023</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>2.257085968244024</v>
@@ -4241,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4255,7 +4279,7 @@
         <v>2.572063968281066</v>
       </c>
       <c r="D55" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E55">
         <v>2.268115776754144</v>
@@ -4291,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4305,7 +4329,7 @@
         <v>2.444102824635875</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>2.268115776754144</v>
@@ -4341,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4355,7 +4379,7 @@
         <v>2.542389919676129</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E57">
         <v>2.130900537967008</v>
@@ -4391,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4405,7 +4429,7 @@
         <v>2.413691532587338</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58">
         <v>2.130900537967008</v>
@@ -4441,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4455,7 +4479,7 @@
         <v>2.556171463010396</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>2.23740447163792</v>
@@ -4491,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4505,7 +4529,7 @@
         <v>2.42781547451376</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>2.23740447163792</v>
@@ -4541,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4555,7 +4579,7 @@
         <v>2.603222072464918</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>2.216035043209388</v>
@@ -4591,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4605,7 +4629,7 @@
         <v>2.476035043209388</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E62">
         <v>2.216035043209388</v>
@@ -4641,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4655,7 +4679,7 @@
         <v>2.630154654909835</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E63">
         <v>2.308272197921324</v>
@@ -4691,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4705,7 +4729,7 @@
         <v>2.503636758137409</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E64">
         <v>2.308272197921324</v>
@@ -4741,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4755,7 +4779,7 @@
         <v>2.66030827488601</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E65">
         <v>2.383994213343331</v>
@@ -4791,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4805,7 +4829,7 @@
         <v>2.534539536373861</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E66">
         <v>2.383994213343331</v>
@@ -4841,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4855,7 +4879,7 @@
         <v>2.666210421069824</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E67">
         <v>2.341003053956531</v>
@@ -4891,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4905,7 +4929,7 @@
         <v>2.695754551182147</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E68">
         <v>2.348235898796299</v>
@@ -4941,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4955,7 +4979,7 @@
         <v>2.688387107470901</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E69">
         <v>2.327107470902277</v>
@@ -4991,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5005,7 +5029,7 @@
         <v>2.705527881761642</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E70">
         <v>2.280646125088861</v>
@@ -5041,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5055,7 +5079,7 @@
         <v>2.704460392769203</v>
       </c>
       <c r="D71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.302015094188537</v>
@@ -5091,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5105,7 +5129,7 @@
         <v>2.691670022178227</v>
       </c>
       <c r="D72" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E72">
         <v>2.347919152567092</v>
@@ -5141,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5155,7 +5179,7 @@
         <v>2.574738018548341</v>
       </c>
       <c r="D73" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E73">
         <v>2.148773116010439</v>
@@ -5191,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5205,7 +5229,7 @@
         <v>2.466405959031657</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E74">
         <v>2.012974927806115</v>
@@ -5241,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5255,7 +5279,7 @@
         <v>2.470469575425553</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>2.060469575425552</v>
@@ -5291,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5305,7 +5329,7 @@
         <v>2.334498089130185</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E76">
         <v>1.907509472337494</v>
@@ -5341,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5355,7 +5379,7 @@
         <v>2.408213021180041</v>
       </c>
       <c r="D77" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E77">
         <v>1.98668904020824</v>
@@ -5391,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5405,7 +5429,7 @@
         <v>2.636918489431684</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E78">
         <v>2.261468539033603</v>
@@ -5441,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5455,7 +5479,7 @@
         <v>2.846696727407958</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E79">
         <v>2.508912235031609</v>
@@ -5491,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5505,7 +5529,7 @@
         <v>2.895704330159931</v>
       </c>
       <c r="D80" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E80">
         <v>2.586570834612932</v>
@@ -5541,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5555,7 +5579,7 @@
         <v>2.722943884604967</v>
       </c>
       <c r="D81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E81">
         <v>2.299653216265908</v>
@@ -5591,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5605,7 +5629,7 @@
         <v>3.129386015914413</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E82">
         <v>2.61595715496026</v>
@@ -5641,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5655,7 +5679,7 @@
         <v>3.221443332486905</v>
       </c>
       <c r="D83" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E83">
         <v>2.61595715496026</v>
@@ -5691,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5705,7 +5729,7 @@
         <v>3.148767058664957</v>
       </c>
       <c r="D84" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E84">
         <v>2.543317383832596</v>
@@ -5741,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5755,7 +5779,7 @@
         <v>3.240583616942411</v>
       </c>
       <c r="D85" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E85">
         <v>2.543317383832596</v>
@@ -5791,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5805,7 +5829,7 @@
         <v>2.818890215375663</v>
       </c>
       <c r="D86" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E86">
         <v>2.265161259044684</v>
@@ -5841,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5855,7 +5879,7 @@
         <v>2.720096541548477</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E87">
         <v>2.290570133597897</v>
@@ -5891,7 +5915,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5905,7 +5929,7 @@
         <v>2.660713894763869</v>
       </c>
       <c r="D88" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E88">
         <v>2.195461007763983</v>
@@ -5941,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5955,7 +5979,7 @@
         <v>2.662179072315689</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E89">
         <v>2.350628131035313</v>
@@ -5991,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6005,7 +6029,7 @@
         <v>2.50859182943727</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E90">
         <v>1.879284692646113</v>
@@ -6041,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6055,7 +6079,7 @@
         <v>1.429538633940146</v>
       </c>
       <c r="D91" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E91">
         <v>1.878152907522461</v>
@@ -6091,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6105,7 +6129,7 @@
         <v>1.456166808206322</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E92">
         <v>1.878152907522461</v>
@@ -6141,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6155,7 +6179,7 @@
         <v>1.449885065544568</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E93">
         <v>1.878152907522461</v>
@@ -6191,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6205,7 +6229,7 @@
         <v>2.698459413109759</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E94">
         <v>2.076228086890248</v>
@@ -6241,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6255,7 +6279,7 @@
         <v>1.59503398119919</v>
       </c>
       <c r="D95" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E95">
         <v>2.078321265243905</v>
@@ -6291,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6305,7 +6329,7 @@
         <v>1.621269054878052</v>
       </c>
       <c r="D96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E96">
         <v>2.078321265243905</v>
@@ -6341,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6355,7 +6379,7 @@
         <v>1.618918318089434</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E97">
         <v>2.078321265243905</v>
@@ -6391,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6405,7 +6429,7 @@
         <v>2.723511029411768</v>
       </c>
       <c r="D98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E98">
         <v>2.102213303799785</v>
@@ -6441,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6455,7 +6479,7 @@
         <v>1.616869862075268</v>
       </c>
       <c r="D99" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E99">
         <v>2.092366071428574</v>
@@ -6491,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6505,7 +6529,7 @@
         <v>1.643053069053712</v>
       </c>
       <c r="D100" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E100">
         <v>2.092366071428574</v>
@@ -6541,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6555,7 +6579,7 @@
         <v>1.641220999269276</v>
       </c>
       <c r="D101" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E101">
         <v>2.092366071428574</v>
@@ -6591,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6605,7 +6629,7 @@
         <v>2.964772546531684</v>
       </c>
       <c r="D102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E102">
         <v>2.352465933358952</v>
@@ -6641,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6655,7 +6679,7 @@
         <v>3.058874750922595</v>
       </c>
       <c r="D103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E103">
         <v>2.352465933358952</v>
@@ -6691,7 +6715,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6705,7 +6729,7 @@
         <v>1.827161991904428</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E104">
         <v>2.316305612395345</v>
@@ -6741,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6755,7 +6779,7 @@
         <v>1.852845692636247</v>
       </c>
       <c r="D105" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E105">
         <v>2.316305612395345</v>
@@ -6791,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6805,7 +6829,7 @@
         <v>1.856008685318062</v>
       </c>
       <c r="D106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E106">
         <v>2.316305612395345</v>
@@ -6841,7 +6865,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6855,7 +6879,7 @@
         <v>2.202638839481067</v>
       </c>
       <c r="D107" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E107">
         <v>1.660853987552378</v>
@@ -6891,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6905,7 +6929,7 @@
         <v>1.162859112673973</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E108">
         <v>1.706062187746931</v>
@@ -6941,7 +6965,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6955,7 +6979,7 @@
         <v>1.190120729983537</v>
       </c>
       <c r="D109" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E109">
         <v>1.706062187746931</v>
@@ -6991,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7005,7 +7029,7 @@
         <v>1.177504556887906</v>
       </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E110">
         <v>1.706062187746931</v>
@@ -7041,7 +7065,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7055,7 +7079,7 @@
         <v>1.416777838279337</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E111">
         <v>0.8890067354016997</v>
@@ -7091,7 +7115,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7105,7 +7129,7 @@
         <v>0.4778746789142878</v>
       </c>
       <c r="D112" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E112">
         <v>0.9778684643520892</v>
@@ -7141,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7155,7 +7179,7 @@
         <v>0.5356519963541242</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E113">
         <v>0.9778684643520892</v>
@@ -7191,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7205,7 +7229,7 @@
         <v>0.5067633376342062</v>
       </c>
       <c r="D114" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E114">
         <v>0.9778684643520892</v>
@@ -7241,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7255,7 +7279,7 @@
         <v>0.477876750435021</v>
       </c>
       <c r="D115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E115">
         <v>0.9778684643520892</v>
@@ -7291,7 +7315,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7305,7 +7329,7 @@
         <v>0.943733873523156</v>
       </c>
       <c r="D116" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E116">
         <v>0.3875605450183359</v>
@@ -7341,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7355,7 +7379,7 @@
         <v>0.06555271377484218</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E117">
         <v>0.5227816757955743</v>
@@ -7391,7 +7415,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7405,7 +7429,7 @@
         <v>0.09542075958535357</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E118">
         <v>0.5227816757955743</v>
@@ -7441,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7455,7 +7479,7 @@
         <v>0.05674030148024301</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E119">
         <v>0.5227816757955743</v>
@@ -7491,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7505,7 +7529,7 @@
         <v>0.5054107307431819</v>
       </c>
       <c r="D120" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E120">
         <v>0.0491242407754946</v>
@@ -7541,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7555,7 +7579,7 @@
         <v>-0.3165053464950738</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E121">
         <v>0.159781143472614</v>
@@ -7591,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7605,7 +7629,7 @@
         <v>-0.33348527076694</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E122">
         <v>0.159781143472614</v>
@@ -7641,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7655,7 +7679,7 @@
         <v>0.01013524264121379</v>
       </c>
       <c r="D123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E123">
         <v>-0.4676849642004726</v>
@@ -7691,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7705,7 +7729,7 @@
         <v>-0.7744137591392919</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E124">
         <v>-0.3747925900670488</v>
@@ -7741,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7755,7 +7779,7 @@
         <v>-0.2557695520702179</v>
       </c>
       <c r="D125" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E125">
         <v>-0.8235135484933682</v>
@@ -7791,7 +7815,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7805,7 +7829,7 @@
         <v>-0.2776909319810326</v>
       </c>
       <c r="D126" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E126">
         <v>-0.2477467025920381</v>
@@ -7841,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7855,7 +7879,7 @@
         <v>-0.3908011343092124</v>
       </c>
       <c r="D127" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E127">
         <v>-0.8406732630037332</v>
@@ -7891,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7905,7 +7929,7 @@
         <v>-0.3888256670434034</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E128">
         <v>-0.2128000927823077</v>
@@ -7941,7 +7965,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7955,7 +7979,7 @@
         <v>1.099323115887907</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>0.387889534694934</v>
@@ -7991,7 +8015,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8005,7 +8029,7 @@
         <v>1.083343993906462</v>
       </c>
       <c r="D130" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E130">
         <v>0.3268838700002261</v>
@@ -8041,7 +8065,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8055,7 +8079,7 @@
         <v>1.145349122599034</v>
       </c>
       <c r="D131" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E131">
         <v>0.3619408673861413</v>
@@ -8091,7 +8115,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8105,7 +8129,7 @@
         <v>1.076892851489177</v>
       </c>
       <c r="D132" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E132">
         <v>0.2887690811642036</v>
@@ -8141,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8155,7 +8179,7 @@
         <v>0.9728953765433594</v>
       </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E133">
         <v>0.2054001299670292</v>
@@ -8191,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8205,7 +8229,7 @@
         <v>0.8720431896132981</v>
       </c>
       <c r="D134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E134">
         <v>0.09424712584458561</v>
@@ -8241,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8255,7 +8279,7 @@
         <v>0.8315744964187708</v>
       </c>
       <c r="D135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E135">
         <v>0.04964505068482161</v>
@@ -8291,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8305,7 +8329,7 @@
         <v>0.7304738922292362</v>
       </c>
       <c r="D136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E136">
         <v>-0.06178174348131638</v>
@@ -8341,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8355,7 +8379,7 @@
         <v>0.7222547015649674</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>-0.07084042392839685</v>
@@ -8391,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8405,7 +8429,7 @@
         <v>4.23617325128652</v>
       </c>
       <c r="D138" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E138">
         <v>3.461981920657827</v>
@@ -8441,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8455,7 +8479,7 @@
         <v>4.2899280718093</v>
       </c>
       <c r="D139" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E139">
         <v>3.521227138526164</v>
@@ -8491,7 +8515,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8505,7 +8529,7 @@
         <v>4.456463450453921</v>
       </c>
       <c r="D140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E140">
         <v>3.704772068908834</v>
@@ -8541,7 +8565,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8555,7 +8579,7 @@
         <v>4.839214417852447</v>
       </c>
       <c r="D141" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E141">
         <v>4.126616365519087</v>
@@ -8591,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8605,7 +8629,7 @@
         <v>5.014744472529706</v>
       </c>
       <c r="D142" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E142">
         <v>4.245160231267613</v>
@@ -8641,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8655,7 +8679,7 @@
         <v>5.000093781157554</v>
       </c>
       <c r="D143" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E143">
         <v>4.229152349958373</v>
@@ -8691,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8705,7 +8729,7 @@
         <v>4.826926790424525</v>
       </c>
       <c r="D144" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E144">
         <v>4.113073707261234</v>
@@ -8741,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8755,7 +8779,7 @@
         <v>4.400270331049441</v>
       </c>
       <c r="D145" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E145">
         <v>3.642839509755204</v>
@@ -8791,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8805,7 +8829,7 @@
         <v>3.969466864791235</v>
       </c>
       <c r="D146" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E146">
         <v>3.168034739342359</v>
@@ -8841,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8855,7 +8879,7 @@
         <v>3.815400534424922</v>
       </c>
       <c r="D147" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E147">
         <v>2.998232417988513</v>
@@ -8891,7 +8915,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8905,7 +8929,7 @@
         <v>3.847902386344885</v>
       </c>
       <c r="D148" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E148">
         <v>3.034053936494125</v>
@@ -8941,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8955,7 +8979,7 @@
         <v>3.739610425856585</v>
       </c>
       <c r="D149" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E149">
         <v>2.914701276953577</v>
@@ -8991,7 +9015,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9005,7 +9029,7 @@
         <v>3.764729296087544</v>
       </c>
       <c r="D150" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E150">
         <v>2.942385732505037</v>
@@ -9041,7 +9065,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9055,7 +9079,7 @@
         <v>3.718711008498303</v>
       </c>
       <c r="D151" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E151">
         <v>2.891667239770102</v>
@@ -9091,7 +9115,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9105,7 +9129,7 @@
         <v>1.436486720612095</v>
       </c>
       <c r="D152" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E152">
         <v>0.6731330742884634</v>
@@ -9141,7 +9165,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9155,7 +9179,7 @@
         <v>1.244726820412753</v>
       </c>
       <c r="D153" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E153">
         <v>0.5049958305736757</v>
@@ -9191,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9205,7 +9229,7 @@
         <v>5.702914875007628</v>
       </c>
       <c r="D154" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E154">
         <v>4.999995484409007</v>
@@ -9241,7 +9265,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9255,7 +9279,7 @@
         <v>4.505339340560991</v>
       </c>
       <c r="D155" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E155">
         <v>4.49533934056099</v>
@@ -9291,7 +9315,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9305,7 +9329,7 @@
         <v>4.306808901002787</v>
       </c>
       <c r="D156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E156">
         <v>4.49533934056099</v>
@@ -9341,7 +9365,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9355,7 +9379,7 @@
         <v>6.509809176848197</v>
       </c>
       <c r="D157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E157">
         <v>5.75883309709841</v>
@@ -9391,7 +9415,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9405,7 +9429,7 @@
         <v>5.149505019504025</v>
       </c>
       <c r="D158" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E158">
         <v>5.616961120807806</v>
@@ -9441,7 +9465,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9455,7 +9479,7 @@
         <v>-4.927818287598177</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E159">
         <v>-3.423739939881703</v>
@@ -9491,7 +9515,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9505,7 +9529,7 @@
         <v>-5.351739552021721</v>
       </c>
       <c r="D160" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E160">
         <v>-3.743311354600991</v>
@@ -9541,7 +9565,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9555,7 +9579,7 @@
         <v>-5.566679746992302</v>
       </c>
       <c r="D161" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E161">
         <v>-4.132985698695919</v>
@@ -9591,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9605,7 +9629,7 @@
         <v>-5.696609439803341</v>
       </c>
       <c r="D162" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E162">
         <v>-4.233476466219281</v>
@@ -9641,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9655,7 +9679,7 @@
         <v>-5.75040807221059</v>
       </c>
       <c r="D163" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E163">
         <v>-4.275085629955039</v>
@@ -9691,7 +9715,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9705,7 +9729,7 @@
         <v>-5.591968923585961</v>
       </c>
       <c r="D164" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E164">
         <v>-4.152544959638887</v>
@@ -9741,7 +9765,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9755,7 +9779,7 @@
         <v>-5.362490385040697</v>
       </c>
       <c r="D165" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E165">
         <v>-3.975060706658394</v>
@@ -9791,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9805,7 +9829,7 @@
         <v>-2.507111743839585</v>
       </c>
       <c r="D166" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E166">
         <v>-4.047254516344427</v>
@@ -9841,7 +9865,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9855,7 +9879,7 @@
         <v>-5.134126961939156</v>
       </c>
       <c r="D167" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E167">
         <v>-3.79843891093761</v>
@@ -9891,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9905,7 +9929,7 @@
         <v>-4.963804430565657</v>
       </c>
       <c r="D168" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E168">
         <v>-3.666707344934939</v>
@@ -9955,7 +9979,7 @@
         <v>-5.024291625916282</v>
       </c>
       <c r="D169" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E169">
         <v>-3.713489605052797</v>
@@ -9991,7 +10015,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10005,7 +10029,7 @@
         <v>-4.810647567313472</v>
       </c>
       <c r="D170" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E170">
         <v>-3.548252121908546</v>
@@ -10041,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10055,7 +10079,7 @@
         <v>-4.527367099438266</v>
       </c>
       <c r="D171" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E171">
         <v>-3.286247287427305</v>
@@ -10091,7 +10115,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10105,7 +10129,7 @@
         <v>1.259915097541094</v>
       </c>
       <c r="D172" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E172">
         <v>1.158519820616992</v>
@@ -10141,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10155,7 +10179,7 @@
         <v>1.184916726583275</v>
       </c>
       <c r="D173" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E173">
         <v>1.172691348768068</v>
@@ -10191,7 +10215,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10205,7 +10229,7 @@
         <v>1.049813709099592</v>
       </c>
       <c r="D174" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E174">
         <v>1.000464874270701</v>
@@ -10241,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10255,7 +10279,7 @@
         <v>0.7166882287391596</v>
       </c>
       <c r="D175" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E175">
         <v>0.3824058924251874</v>
@@ -10291,7 +10315,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10305,7 +10329,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D176" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E176">
         <v>0.3824058924251874</v>
@@ -10341,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10355,7 +10379,7 @@
         <v>0.7157220123393015</v>
       </c>
       <c r="D177" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E177">
         <v>0.3824058924251874</v>
@@ -10391,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10405,7 +10429,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D178" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E178">
         <v>0.0213012212570054</v>
@@ -10441,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10455,7 +10479,7 @@
         <v>0.4186991258332231</v>
       </c>
       <c r="D179" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E179">
         <v>0.0213012212570054</v>
@@ -10491,7 +10515,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10541,7 +10565,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10591,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10641,7 +10665,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10691,7 +10715,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10705,7 +10729,7 @@
         <v>1.268624677776261</v>
       </c>
       <c r="D184" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E184">
         <v>1.582625511992627</v>
@@ -10741,7 +10765,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10755,7 +10779,7 @@
         <v>1.285793821195491</v>
       </c>
       <c r="D185" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E185">
         <v>1.559453546602203</v>
@@ -10791,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10805,7 +10829,7 @@
         <v>1.316780702717756</v>
       </c>
       <c r="D186" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E186">
         <v>1.547361538049228</v>
@@ -10841,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10855,7 +10879,7 @@
         <v>1.133068166503446</v>
       </c>
       <c r="D187" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E187">
         <v>1.401993513086136</v>
@@ -10891,7 +10915,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10905,7 +10929,7 @@
         <v>1.088256848758593</v>
       </c>
       <c r="D188" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>1.434633300285655</v>
@@ -10941,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10955,7 +10979,7 @@
         <v>1.813623858427708</v>
       </c>
       <c r="D189" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>1.425858209046284</v>
@@ -10991,7 +11015,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11005,7 +11029,7 @@
         <v>1.056087101886501</v>
       </c>
       <c r="D190" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>1.475198819417429</v>
@@ -11041,7 +11065,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11055,7 +11079,7 @@
         <v>1.831484324717041</v>
       </c>
       <c r="D191" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E191">
         <v>1.441005693114453</v>
@@ -11091,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11105,7 +11129,7 @@
         <v>1.069742445733029</v>
       </c>
       <c r="D192" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E192">
         <v>1.488718514152899</v>
@@ -11141,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11155,7 +11179,7 @@
         <v>1.837661043092234</v>
       </c>
       <c r="D193" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E193">
         <v>1.446244175787084</v>
@@ -11191,7 +11215,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11205,7 +11229,7 @@
         <v>1.074464898769252</v>
       </c>
       <c r="D194" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E194">
         <v>1.493394055403994</v>
@@ -11241,7 +11265,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11255,7 +11279,7 @@
         <v>1.837752806536338</v>
       </c>
       <c r="D195" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E195">
         <v>1.446322000480185</v>
@@ -11291,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11305,7 +11329,7 @@
         <v>1.074535057149301</v>
       </c>
       <c r="D196" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E196">
         <v>1.493463516846493</v>
@@ -11341,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11355,7 +11379,7 @@
         <v>1.825402047539555</v>
       </c>
       <c r="D197" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E197">
         <v>1.435847306141142</v>
@@ -11391,7 +11415,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11405,7 +11429,7 @@
         <v>1.065092198372015</v>
       </c>
       <c r="D198" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E198">
         <v>1.484114461302094</v>
@@ -11441,7 +11465,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11455,7 +11479,7 @@
         <v>1.861617863704522</v>
       </c>
       <c r="D199" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E199">
         <v>1.466561985673455</v>
@@ -11491,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11505,7 +11529,7 @@
         <v>1.092781252756369</v>
       </c>
       <c r="D200" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E200">
         <v>1.511528458854815</v>
@@ -11541,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11555,7 +11579,7 @@
         <v>1.876754966932714</v>
       </c>
       <c r="D201" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E201">
         <v>1.479399782082176</v>
@@ -11591,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11605,7 +11629,7 @@
         <v>1.104354430414379</v>
       </c>
       <c r="D202" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E202">
         <v>1.522986671171852</v>
@@ -11641,7 +11665,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11655,7 +11679,7 @@
         <v>1.85316775720275</v>
       </c>
       <c r="D203" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E203">
         <v>1.459395439652966</v>
@@ -11691,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11705,7 +11729,7 @@
         <v>1.086320665000584</v>
       </c>
       <c r="D204" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E204">
         <v>1.505132049123094</v>
@@ -11741,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11755,7 +11779,7 @@
         <v>1.779730028029443</v>
       </c>
       <c r="D205" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E205">
         <v>1.397112808581932</v>
@@ -11791,7 +11815,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11805,7 +11829,7 @@
         <v>1.030173337885802</v>
       </c>
       <c r="D206" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E206">
         <v>1.449542476913426</v>
@@ -11841,7 +11865,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11855,7 +11879,7 @@
         <v>1.658318925527395</v>
       </c>
       <c r="D207" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E207">
         <v>1.294143898865006</v>
@@ -11891,7 +11915,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11905,7 +11929,7 @@
         <v>0.9373476342006919</v>
       </c>
       <c r="D208" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E208">
         <v>1.357638882867572</v>
@@ -11941,7 +11965,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11955,7 +11979,7 @@
         <v>1.524088846622344</v>
       </c>
       <c r="D209" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E209">
         <v>1.18030319903414</v>
@@ -11991,7 +12015,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12005,7 +12029,7 @@
         <v>1.516096053953746</v>
       </c>
       <c r="D210" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E210">
         <v>1.18030319903414</v>
@@ -12041,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12055,7 +12079,7 @@
         <v>0.8347210928606277</v>
       </c>
       <c r="D211" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E211">
         <v>1.188653245722397</v>
@@ -12091,7 +12115,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12105,7 +12129,7 @@
         <v>1.2601799162582</v>
       </c>
       <c r="D212" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E212">
         <v>0.9564817011303721</v>
@@ -12141,7 +12165,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12155,7 +12179,7 @@
         <v>1.266536433399546</v>
       </c>
       <c r="D213" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E213">
         <v>0.9564817011303721</v>
@@ -12191,7 +12215,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12205,7 +12229,7 @@
         <v>0.6329476828100669</v>
       </c>
       <c r="D214" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E214">
         <v>0.9595778612972841</v>
@@ -12241,7 +12265,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12255,7 +12279,7 @@
         <v>1.040216421991335</v>
       </c>
       <c r="D215" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E215">
         <v>0.7699303832078415</v>
@@ -12291,7 +12315,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12305,7 +12329,7 @@
         <v>1.041744836579313</v>
       </c>
       <c r="D216" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E216">
         <v>0.7699303832078415</v>
@@ -12341,7 +12365,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12355,7 +12379,7 @@
         <v>1.074973289025366</v>
       </c>
       <c r="D217" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E217">
         <v>0.7699303832078415</v>
@@ -12391,7 +12415,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12405,7 +12429,7 @@
         <v>0.4647730618769197</v>
       </c>
       <c r="D218" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E218">
         <v>0.7947444579985703</v>
@@ -12441,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12455,7 +12479,7 @@
         <v>0.9454421251514917</v>
       </c>
       <c r="D219" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E219">
         <v>0.681784458813524</v>
@@ -12491,7 +12515,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12505,7 +12529,7 @@
         <v>0.9844592651697082</v>
       </c>
       <c r="D220" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E220">
         <v>0.681784458813524</v>
@@ -12541,7 +12565,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12555,7 +12579,7 @@
         <v>0.3853101688408485</v>
       </c>
       <c r="D221" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E221">
         <v>0.6868602979367258</v>
@@ -12591,7 +12615,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12605,7 +12629,7 @@
         <v>0.9549493355627496</v>
       </c>
       <c r="D222" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E222">
         <v>0.6904864136981455</v>
@@ -12641,7 +12665,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12655,7 +12679,7 @@
         <v>0.9933950039169015</v>
       </c>
       <c r="D223" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E223">
         <v>0.6904864136981455</v>
@@ -12691,7 +12715,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12705,7 +12729,7 @@
         <v>0.3931549162293728</v>
       </c>
       <c r="D224" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E224">
         <v>0.6988520528231206</v>
@@ -12741,7 +12765,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12755,7 +12779,7 @@
         <v>0.8352295499502258</v>
       </c>
       <c r="D225" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E225">
         <v>0.5364590093992025</v>
@@ -12791,7 +12815,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12805,7 +12829,7 @@
         <v>0.2543003607121168</v>
       </c>
       <c r="D226" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E226">
         <v>0.5584533336781012</v>
@@ -12841,7 +12865,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12855,7 +12879,7 @@
         <v>0.7309868197475642</v>
       </c>
       <c r="D227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E227">
         <v>0.4349435599285871</v>
@@ -12891,7 +12915,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12905,7 +12929,7 @@
         <v>0.1627849405923385</v>
       </c>
       <c r="D228" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E228">
         <v>0.4687561007130205</v>
@@ -12941,7 +12965,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12955,7 +12979,7 @@
         <v>0.6963364946308443</v>
       </c>
       <c r="D229" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E229">
         <v>0.4011997840155024</v>
@@ -12991,7 +13015,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13005,7 +13029,7 @@
         <v>0.1323651784259154</v>
       </c>
       <c r="D230" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E230">
         <v>0.4389407046823544</v>
@@ -13041,7 +13065,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13055,7 +13079,7 @@
         <v>0.6265973619781331</v>
       </c>
       <c r="D231" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E231">
         <v>0.3332852216938216</v>
@@ -13091,7 +13115,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13105,7 +13129,7 @@
         <v>0.07114070731801236</v>
       </c>
       <c r="D232" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E232">
         <v>0.3789326137951377</v>
@@ -13141,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13155,7 +13179,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D233" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E233">
         <v>0.3201663194080338</v>
@@ -13191,7 +13215,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13205,7 +13229,7 @@
         <v>0.5557568490496352</v>
       </c>
       <c r="D234" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E234">
         <v>0.3201663194080338</v>
@@ -13241,7 +13265,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13255,7 +13279,7 @@
         <v>0.05931411480963034</v>
       </c>
       <c r="D235" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E235">
         <v>0.3673409867008299</v>
@@ -13291,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13305,7 +13329,7 @@
         <v>0.621266404836974</v>
       </c>
       <c r="D236" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E236">
         <v>0.385066244864444</v>
@@ -13341,7 +13365,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13355,7 +13379,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D237" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E237">
         <v>0.385066244864444</v>
@@ -13391,7 +13415,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13405,7 +13429,7 @@
         <v>0.6239502035590574</v>
       </c>
       <c r="D238" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E238">
         <v>0.385066244864444</v>
@@ -13441,7 +13465,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13455,7 +13479,7 @@
         <v>0.1788660848919132</v>
       </c>
       <c r="D239" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E239">
         <v>0.4246853984473891</v>
@@ -13491,7 +13515,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13505,7 +13529,7 @@
         <v>0.6324090002289315</v>
       </c>
       <c r="D240" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E240">
         <v>0.3952650685155521</v>
@@ -13541,7 +13565,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13555,7 +13579,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D241" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E241">
         <v>0.3952650685155521</v>
@@ -13591,7 +13615,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13605,7 +13629,7 @@
         <v>0.6346665794551472</v>
       </c>
       <c r="D242" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E242">
         <v>0.3952650685155521</v>
@@ -13641,7 +13665,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13655,7 +13679,7 @@
         <v>0.1881211368021729</v>
       </c>
       <c r="D243" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E243">
         <v>0.4336968963600101</v>
@@ -13691,7 +13715,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13705,7 +13729,7 @@
         <v>0.6829592558982664</v>
       </c>
       <c r="D244" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E244">
         <v>0.441533745152785</v>
@@ -13741,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13755,7 +13779,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D245" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E245">
         <v>0.441533745152785</v>
@@ -13791,7 +13815,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13805,7 +13829,7 @@
         <v>0.6832832187874041</v>
       </c>
       <c r="D246" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E246">
         <v>0.441533745152785</v>
@@ -13841,7 +13865,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13855,7 +13879,7 @@
         <v>0.2301082344073033</v>
       </c>
       <c r="D247" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E247">
         <v>0.4745790703439532</v>
@@ -13891,7 +13915,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13905,7 +13929,7 @@
         <v>0.7754846695867457</v>
       </c>
       <c r="D248" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E248">
         <v>0.5262223068621856</v>
@@ -13941,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13955,7 +13979,7 @@
         <v>0.824717831524155</v>
       </c>
       <c r="D249" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E249">
         <v>0.5262223068621856</v>
@@ -13991,7 +14015,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14005,7 +14029,7 @@
         <v>0.3069599441376254</v>
       </c>
       <c r="D250" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E250">
         <v>0.5494083666603191</v>
@@ -14041,7 +14065,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14055,7 +14079,7 @@
         <v>0.9599629043208022</v>
       </c>
       <c r="D251" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E251">
         <v>1.134910071595908</v>
@@ -14091,7 +14115,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14105,7 +14129,7 @@
         <v>1.286097121996389</v>
       </c>
       <c r="D252" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E252">
         <v>1.119751573421224</v>
@@ -14141,7 +14165,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14155,7 +14179,7 @@
         <v>0.8954130056318945</v>
       </c>
       <c r="D253" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E253">
         <v>1.055413005631895</v>
@@ -14191,7 +14215,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14205,7 +14229,7 @@
         <v>1.202360441278745</v>
       </c>
       <c r="D254" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E254">
         <v>1.03217696150402</v>
@@ -14241,7 +14265,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14255,7 +14279,7 @@
         <v>0.7184047868704915</v>
       </c>
       <c r="D255" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E255">
         <v>0.897246951281871</v>
@@ -14291,7 +14315,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14305,7 +14329,7 @@
         <v>1.037880541268793</v>
       </c>
       <c r="D256" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E256">
         <v>0.8706167327436121</v>
@@ -14341,7 +14365,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14355,7 +14379,7 @@
         <v>1.344384991739593</v>
       </c>
       <c r="D257" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E257">
         <v>1.412833444305319</v>
@@ -14391,7 +14415,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14405,7 +14429,7 @@
         <v>1.295455729615361</v>
       </c>
       <c r="D258" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E258">
         <v>1.399053391868887</v>
@@ -14441,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14455,7 +14479,7 @@
         <v>1.247900082267936</v>
       </c>
       <c r="D259" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E259">
         <v>1.480439984508878</v>
@@ -14491,7 +14515,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14505,7 +14529,7 @@
         <v>1.223974537812843</v>
       </c>
       <c r="D260" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E260">
         <v>1.457637705051676</v>
@@ -14591,7 +14615,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14605,7 +14629,7 @@
         <v>1.0622369081479</v>
       </c>
       <c r="D262" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E262">
         <v>1.2222369081479</v>
@@ -14641,7 +14665,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14655,7 +14679,7 @@
         <v>1.39714237911996</v>
       </c>
       <c r="D263" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E263">
         <v>1.311393675757068</v>
@@ -14691,7 +14715,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14705,7 +14729,7 @@
         <v>0.8656248277462677</v>
       </c>
       <c r="D264" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E264">
         <v>1.084160634764066</v>
@@ -14741,7 +14765,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14755,7 +14779,7 @@
         <v>1.243914185004134</v>
       </c>
       <c r="D265" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E265">
         <v>1.193914185004133</v>
@@ -14791,7 +14815,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14805,7 +14829,7 @@
         <v>0.6264474161926654</v>
       </c>
       <c r="D266" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E266">
         <v>0.8573351083141707</v>
@@ -14841,7 +14865,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14855,7 +14879,7 @@
         <v>1.057513009802735</v>
       </c>
       <c r="D267" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E267">
         <v>0.988341401428052</v>
@@ -14891,7 +14915,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14905,7 +14929,7 @@
         <v>0.5508399511301141</v>
       </c>
       <c r="D268" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E268">
         <v>0.7856322541233942</v>
@@ -14941,7 +14965,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -14955,7 +14979,7 @@
         <v>0.9985888821014035</v>
       </c>
       <c r="D269" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E269">
         <v>0.9271686010995708</v>
@@ -14991,7 +15015,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15005,7 +15029,7 @@
         <v>0.4053416723149885</v>
       </c>
       <c r="D270" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E270">
         <v>0.666724382278634</v>
@@ -15041,7 +15065,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15055,7 +15079,7 @@
         <v>0.9008725121695709</v>
       </c>
       <c r="D271" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E271">
         <v>0.8120247704726087</v>
@@ -15091,7 +15115,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15105,7 +15129,7 @@
         <v>0.2524265204263942</v>
       </c>
       <c r="D272" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E272">
         <v>0.5554941770903916</v>
@@ -15141,7 +15165,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15155,7 +15179,7 @@
         <v>0.2294545121727958</v>
       </c>
       <c r="D273" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E273">
         <v>0.5343135639758354</v>
@@ -15191,7 +15215,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15205,7 +15229,7 @@
         <v>0.2511617312072869</v>
       </c>
       <c r="D274" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E274">
         <v>0.5543280182232331</v>
@@ -15241,7 +15265,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15255,7 +15279,7 @@
         <v>0.330938321030898</v>
       </c>
       <c r="D275" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E275">
         <v>0.6169560865757506</v>
@@ -15291,7 +15315,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15305,7 +15329,7 @@
         <v>0.3190867008632514</v>
       </c>
       <c r="D276" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E276">
         <v>0.6169560865757506</v>
@@ -15341,7 +15365,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15355,7 +15379,7 @@
         <v>0.8973239084198648</v>
       </c>
       <c r="D277" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E277">
         <v>0.8673239084198645</v>
@@ -15391,7 +15415,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15405,7 +15429,7 @@
         <v>0.5047409711889603</v>
       </c>
       <c r="D278" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E278">
         <v>0.7616569728121176</v>
@@ -15441,7 +15465,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15455,7 +15479,7 @@
         <v>1.010348978763694</v>
       </c>
       <c r="D279" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E279">
         <v>0.9495779791694832</v>
@@ -15491,7 +15515,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15505,7 +15529,7 @@
         <v>0.7124003213085996</v>
       </c>
       <c r="D280" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E280">
         <v>0.9388491310062772</v>
@@ -15541,7 +15565,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15591,7 +15615,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15641,7 +15665,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15655,7 +15679,7 @@
         <v>0.7739548177870597</v>
       </c>
       <c r="D283" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E283">
         <v>0.9972247567745822</v>
@@ -15691,7 +15715,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15705,7 +15729,7 @@
         <v>1.172471829824657</v>
       </c>
       <c r="D284" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E284">
         <v>1.155095366349694</v>
@@ -15741,7 +15765,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15755,7 +15779,7 @@
         <v>1.208783598087175</v>
       </c>
       <c r="D285" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E285">
         <v>1.155095366349694</v>
@@ -15791,7 +15815,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15805,7 +15829,7 @@
         <v>1.163574451712196</v>
       </c>
       <c r="D286" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E286">
         <v>1.155095366349694</v>
@@ -15841,7 +15865,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15855,7 +15879,7 @@
         <v>1.083287783547417</v>
       </c>
       <c r="D287" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E287">
         <v>1.266654823722328</v>
@@ -15891,7 +15915,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15941,7 +15965,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +16015,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16005,7 +16029,7 @@
         <v>1.005187969924811</v>
       </c>
       <c r="D290" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E290">
         <v>1.216516290726816</v>
@@ -16041,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16055,7 +16079,7 @@
         <v>1.37922305764411</v>
       </c>
       <c r="D291" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E291">
         <v>1.377468671679197</v>
@@ -16091,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16105,7 +16129,7 @@
         <v>1.373157894736842</v>
       </c>
       <c r="D292" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E292">
         <v>1.377468671679197</v>
@@ -16141,7 +16165,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16155,7 +16179,7 @@
         <v>0.8802418207681344</v>
       </c>
       <c r="D293" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E293">
         <v>1.098022759601705</v>
@@ -16191,7 +16215,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16205,7 +16229,7 @@
         <v>1.287126600284493</v>
       </c>
       <c r="D294" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E294">
         <v>1.26116642958748</v>
@@ -16241,7 +16265,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16255,7 +16279,7 @@
         <v>1.286927453769557</v>
       </c>
       <c r="D295" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E295">
         <v>1.26116642958748</v>
@@ -16291,7 +16315,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16305,7 +16329,7 @@
         <v>0.5899232633927847</v>
       </c>
       <c r="D296" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E296">
         <v>0.8607264291791745</v>
@@ -16341,7 +16365,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16465,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16455,7 +16479,7 @@
         <v>0.50590909090909</v>
       </c>
       <c r="D299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E299">
         <v>0.824097311139564</v>
@@ -16491,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16505,7 +16529,7 @@
         <v>1.058847631241997</v>
       </c>
       <c r="D300" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E300">
         <v>1.040422535211267</v>
@@ -16541,7 +16565,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16555,7 +16579,7 @@
         <v>1.101209987195902</v>
       </c>
       <c r="D301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E301">
         <v>1.040422535211267</v>
@@ -16591,7 +16615,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16605,7 +16629,7 @@
         <v>1.061209987195902</v>
       </c>
       <c r="D302" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E302">
         <v>1.040422535211267</v>
@@ -16641,7 +16665,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16655,7 +16679,7 @@
         <v>0.3348874640146549</v>
       </c>
       <c r="D303" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E303">
         <v>0.6892070138707138</v>
@@ -16691,7 +16715,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16705,7 +16729,7 @@
         <v>0.9751517927244169</v>
       </c>
       <c r="D304" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E304">
         <v>0.904611358283171</v>
@@ -16741,7 +16765,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16755,7 +16779,7 @@
         <v>0.22440600683947</v>
       </c>
       <c r="D305" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E305">
         <v>0.6020667096198637</v>
@@ -16791,7 +16815,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16805,7 +16829,7 @@
         <v>0.8937171036328486</v>
       </c>
       <c r="D306" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E306">
         <v>0.7705397234474891</v>
@@ -16841,7 +16865,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16855,7 +16879,7 @@
         <v>0.1082096332420339</v>
       </c>
       <c r="D307" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E307">
         <v>0.5104188656556885</v>
@@ -16891,7 +16915,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16905,7 +16929,7 @@
         <v>-0.008130440028267572</v>
       </c>
       <c r="D308" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E308">
         <v>0.4186576811044649</v>
@@ -16941,7 +16965,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16955,7 +16979,7 @@
         <v>-0.2955074520936858</v>
       </c>
       <c r="D309" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E309">
         <v>0.1677359829666414</v>
@@ -16991,7 +17015,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17041,7 +17065,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17091,7 +17115,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17105,7 +17129,7 @@
         <v>1.724076346434568</v>
       </c>
       <c r="D312" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E312">
         <v>1.515642348344327</v>
@@ -17141,7 +17165,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17215,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17241,7 +17265,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17255,7 +17279,7 @@
         <v>1.696820681178639</v>
       </c>
       <c r="D315" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E315">
         <v>1.493247566063977</v>
@@ -17291,7 +17315,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17391,7 +17415,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17405,7 +17429,7 @@
         <v>1.664882012342569</v>
       </c>
       <c r="D318" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E318">
         <v>1.414710468897303</v>
@@ -17441,7 +17465,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17515,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17541,7 +17565,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17555,7 +17579,7 @@
         <v>1.643053663665036</v>
       </c>
       <c r="D321" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E321">
         <v>1.396497005988024</v>
@@ -17591,7 +17615,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17665,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17691,7 +17715,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17705,7 +17729,7 @@
         <v>1.61962915718182</v>
       </c>
       <c r="D324" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E324">
         <v>1.376951717138971</v>
@@ -17741,7 +17765,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17791,7 +17815,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17841,7 +17865,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17855,7 +17879,7 @@
         <v>1.598153375013795</v>
       </c>
       <c r="D327" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E327">
         <v>1.359032433928708</v>
@@ -17891,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17991,7 +18015,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18005,7 +18029,7 @@
         <v>1.570406166624607</v>
       </c>
       <c r="D330" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E330">
         <v>1.335880304635819</v>
@@ -18041,7 +18065,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18091,7 +18115,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18141,7 +18165,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18155,7 +18179,7 @@
         <v>1.53933838661172</v>
       </c>
       <c r="D333" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E333">
         <v>1.309957507300225</v>
@@ -18191,7 +18215,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18305,7 +18329,7 @@
         <v>1.510449616201756</v>
       </c>
       <c r="D336" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E336">
         <v>1.320449616201756</v>
@@ -18391,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18405,7 +18429,7 @@
         <v>1.474476712309384</v>
       </c>
       <c r="D338" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E338">
         <v>1.284476712309384</v>
@@ -18441,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18491,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18541,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18555,7 +18579,7 @@
         <v>1.43169474125916</v>
       </c>
       <c r="D341" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E341">
         <v>1.24169474125916</v>
@@ -18591,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18755,7 +18779,7 @@
         <v>1.372114445177575</v>
       </c>
       <c r="D345" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E345">
         <v>1.182114445177575</v>
@@ -18841,7 +18865,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18891,7 +18915,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18905,7 +18929,7 @@
         <v>1.341200461638077</v>
       </c>
       <c r="D348" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E348">
         <v>1.151200461638077</v>
@@ -18941,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18955,7 +18979,7 @@
         <v>1.309879175702464</v>
       </c>
       <c r="D349" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E349">
         <v>1.119879175702464</v>
@@ -19041,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19055,7 +19079,7 @@
         <v>1.284826807940879</v>
       </c>
       <c r="D351" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E351">
         <v>1.094826807940879</v>
@@ -19091,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19155,7 +19179,7 @@
         <v>1.254947268845516</v>
       </c>
       <c r="D353" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E353">
         <v>1.064947268845516</v>
@@ -19191,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19255,7 +19279,7 @@
         <v>1.204148422477695</v>
       </c>
       <c r="D355" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E355">
         <v>1.014148422477695</v>
@@ -19305,7 +19329,7 @@
         <v>0.7565800947331744</v>
       </c>
       <c r="D356" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E356">
         <v>0.7662610529884266</v>
@@ -19341,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19355,7 +19379,7 @@
         <v>0.7358955841180959</v>
       </c>
       <c r="D357" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E357">
         <v>0.7460729511326034</v>
@@ -19391,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19405,7 +19429,7 @@
         <v>0.6769876002917579</v>
       </c>
       <c r="D358" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E358">
         <v>0.7067614879649891</v>
@@ -19441,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19455,7 +19479,7 @@
         <v>0.6104223551406667</v>
       </c>
       <c r="D359" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E359">
         <v>0.6717864324675069</v>
@@ -19541,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19555,7 +19579,7 @@
         <v>0.798189415570248</v>
       </c>
       <c r="D361" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E361">
         <v>0.5671969948491258</v>
@@ -19591,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19665,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19715,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19705,7 +19729,7 @@
         <v>0.8309217545939529</v>
       </c>
       <c r="D364" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E364">
         <v>0.605257854179015</v>
@@ -19741,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19755,7 +19779,7 @@
         <v>0.4620509780675748</v>
       </c>
       <c r="D365" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E365">
         <v>0.4201630112625956</v>
@@ -19791,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19805,7 +19829,7 @@
         <v>0.480352697095435</v>
       </c>
       <c r="D366" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E366">
         <v>0.4201630112625956</v>
@@ -19841,7 +19865,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19855,7 +19879,7 @@
         <v>0.5468482902083864</v>
       </c>
       <c r="D367" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E367">
         <v>0.4879084704937777</v>
@@ -19891,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19905,7 +19929,7 @@
         <v>0.5179084704937775</v>
       </c>
       <c r="D368" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E368">
         <v>0.4879084704937777</v>
@@ -19941,7 +19965,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19955,7 +19979,7 @@
         <v>0.5818340929808579</v>
       </c>
       <c r="D369" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E369">
         <v>0.549200546946218</v>
@@ -19991,7 +20015,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20005,7 +20029,7 @@
         <v>0.5548113035551514</v>
       </c>
       <c r="D370" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E370">
         <v>0.549200546946218</v>
@@ -20041,7 +20065,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20055,7 +20079,7 @@
         <v>0.5632483895834637</v>
       </c>
       <c r="D371" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E371">
         <v>0.5264173880682987</v>
@@ -20091,7 +20115,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20105,7 +20129,7 @@
         <v>0.3499850704488205</v>
       </c>
       <c r="D372" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E372">
         <v>0.444542315946628</v>
@@ -20141,7 +20165,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20215,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20205,7 +20229,7 @@
         <v>1.715805532271584</v>
       </c>
       <c r="D374" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E374">
         <v>1.874132439228835</v>
@@ -20241,7 +20265,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20255,7 +20279,7 @@
         <v>1.746457690093673</v>
       </c>
       <c r="D375" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E375">
         <v>1.895013344497358</v>
@@ -20291,7 +20315,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20305,7 +20329,7 @@
         <v>1.828184678688128</v>
       </c>
       <c r="D376" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E376">
         <v>2.012343579813627</v>
@@ -20341,7 +20365,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20355,7 +20379,7 @@
         <v>1.807063128376992</v>
       </c>
       <c r="D377" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E377">
         <v>1.990118664933999</v>
@@ -20391,7 +20415,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20405,7 +20429,7 @@
         <v>1.70685001192274</v>
       </c>
       <c r="D378" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E378">
         <v>1.88467053493363</v>
@@ -20441,7 +20465,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20452,46 +20476,46 @@
         <v>81</v>
       </c>
       <c r="C379">
-        <v>2.038444260870803</v>
+        <v>0.9896293432561745</v>
       </c>
       <c r="D379" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E379">
-        <v>2.240361339391263</v>
+        <v>1.043421930121298</v>
       </c>
       <c r="F379">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G379">
-        <v>0.001781555739129197</v>
+        <v>0.003610370656743825</v>
       </c>
       <c r="H379">
-        <v>0.001979638660608737</v>
+        <v>0.003716578069878702</v>
       </c>
       <c r="I379">
-        <v>0.2019170785204598</v>
+        <v>-0.05379258686512345</v>
       </c>
       <c r="J379">
-        <v>-0.0958539260229872</v>
+        <v>0.8735804378292169</v>
       </c>
       <c r="K379">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="L379">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M379">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="N379">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="O379">
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20502,46 +20526,46 @@
         <v>81</v>
       </c>
       <c r="C380">
-        <v>2.176625292888353</v>
+        <v>0.8865384615384628</v>
       </c>
       <c r="D380" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E380">
-        <v>2.380604774871761</v>
+        <v>0.9382692307692322</v>
       </c>
       <c r="F380">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G380">
-        <v>0.001643374707111647</v>
+        <v>0.003713461538461537</v>
       </c>
       <c r="H380">
-        <v>0.001839395225128238</v>
+        <v>0.003821730769230768</v>
       </c>
       <c r="I380">
-        <v>0.2039794819834082</v>
+        <v>-0.05173076923076936</v>
       </c>
       <c r="J380">
-        <v>-0.1989740991704129</v>
+        <v>0.9423076923076913</v>
       </c>
       <c r="K380">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="L380">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M380">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="N380">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="O380">
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20552,46 +20576,46 @@
         <v>81</v>
       </c>
       <c r="C381">
-        <v>2.240948171745636</v>
+        <v>0.8104629450775882</v>
       </c>
       <c r="D381" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E381">
-        <v>2.445887696697064</v>
+        <v>0.8606722039791401</v>
       </c>
       <c r="F381">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G381">
-        <v>0.001579051828254363</v>
+        <v>0.003789537054922412</v>
       </c>
       <c r="H381">
-        <v>0.001774112303302936</v>
+        <v>0.00389932779602086</v>
       </c>
       <c r="I381">
-        <v>0.2049395249514276</v>
+        <v>-0.05020925890155192</v>
       </c>
       <c r="J381">
-        <v>-0.2469762475713705</v>
+        <v>0.9930247032816077</v>
       </c>
       <c r="K381">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="L381">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="M381">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="N381">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="O381">
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20602,46 +20626,446 @@
         <v>81</v>
       </c>
       <c r="C382">
-        <v>2.276110233960097</v>
+        <v>0.6686334062347892</v>
       </c>
       <c r="D382" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E382">
-        <v>2.481574565810248</v>
+        <v>0.7160060743594849</v>
       </c>
       <c r="F382">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G382">
-        <v>0.001543889766039903</v>
+        <v>0.003931366593765211</v>
       </c>
       <c r="H382">
-        <v>0.001738425434189752</v>
+        <v>0.004043993925640515</v>
       </c>
       <c r="I382">
-        <v>0.2054643318501506</v>
+        <v>-0.04737266812469576</v>
       </c>
       <c r="J382">
+        <v>1.087577729176807</v>
+      </c>
+      <c r="K382">
+        <v>1.5</v>
+      </c>
+      <c r="L382">
+        <v>2.3</v>
+      </c>
+      <c r="M382">
+        <v>1.53</v>
+      </c>
+      <c r="N382">
+        <v>2.38</v>
+      </c>
+      <c r="O382">
+        <v>1</v>
+      </c>
+      <c r="P382" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="383" spans="1:16">
+      <c r="A383" s="1">
+        <v>0</v>
+      </c>
+      <c r="B383" t="s">
+        <v>81</v>
+      </c>
+      <c r="C383">
+        <v>0.6300411109997004</v>
+      </c>
+      <c r="D383" t="s">
+        <v>213</v>
+      </c>
+      <c r="E383">
+        <v>0.6766419332196945</v>
+      </c>
+      <c r="F383">
+        <v>-1</v>
+      </c>
+      <c r="G383">
+        <v>0.0039699588890003</v>
+      </c>
+      <c r="H383">
+        <v>0.004083358066780306</v>
+      </c>
+     